--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6449DD0-F1F8-4EBD-B42B-616AD888EBE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56401978-88B9-47A4-B572-C9EEF46C63CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,19 +47,10 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>tc={5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}</author>
-    <author>tc={E017DF4E-5656-4CEF-B774-80BA936A6D56}</author>
-    <author>tc={8A92D669-9E50-4C59-82E5-97B139270D19}</author>
     <author>tc={121DA4BD-014E-470E-AB44-B9514592A80F}</author>
-    <author>tc={41A1A9E9-8671-443A-BC53-E9E6789FC6B2}</author>
-    <author>tc={7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}</author>
-    <author>tc={917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}</author>
     <author>tc={FDDDF671-A2B6-4958-A032-5551C66219BE}</author>
-    <author>tc={9ABBA003-3752-4178-8927-349ABCC5DB99}</author>
-    <author>tc={45640671-D7E4-4EA6-9099-D4E52C010FD7}</author>
-    <author>tc={C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}</author>
     <author>tc={FCC3DA67-C366-4123-AE95-236C8FC56568}</author>
     <author>tc={24A13EBD-8030-4299-B820-E3DBAA902DCC}</author>
-    <author>tc={65177E12-2939-4BCC-8B47-DB95E81C94F5}</author>
   </authors>
   <commentList>
     <comment ref="C15" authorId="0" shapeId="0" xr:uid="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
@@ -70,25 +61,7 @@
     Nach Andres Input zusammengefasst zu einem Eintrag.</t>
       </text>
     </comment>
-    <comment ref="C29" authorId="1" shapeId="0" xr:uid="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    „NextJS Page Compilation Duration“ ergänzt nach Andres Input.
-Reply:
-    „Application/Package Build Duration“ von Lattice nach Andres Input ergänzt.</t>
-      </text>
-    </comment>
-    <comment ref="D29" authorId="2" shapeId="0" xr:uid="{8A92D669-9E50-4C59-82E5-97B139270D19}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Lattice von NextJS Page Compilation Duration</t>
-      </text>
-    </comment>
-    <comment ref="H34" authorId="3" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
+    <comment ref="H34" authorId="1" shapeId="0" xr:uid="{121DA4BD-014E-470E-AB44-B9514592A80F}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -96,31 +69,7 @@
     Nach Andres Input von Business zu Process verschoben.</t>
       </text>
     </comment>
-    <comment ref="C52" authorId="4" shapeId="0" xr:uid="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    „Time to Restore Services“ ergänzt nach Andres Input.</t>
-      </text>
-    </comment>
-    <comment ref="H58" authorId="5" shapeId="0" xr:uid="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von DevEx zu Business/HR gewechselt.</t>
-      </text>
-    </comment>
-    <comment ref="H61" authorId="6" shapeId="0" xr:uid="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input von Business zu Quality verschoben.</t>
-      </text>
-    </comment>
-    <comment ref="J69" authorId="7" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
+    <comment ref="J69" authorId="2" shapeId="0" xr:uid="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -128,31 +77,7 @@
     Von Knowledge Expansion zu Upskilling gewechselt.</t>
       </text>
     </comment>
-    <comment ref="C76" authorId="8" shapeId="0" xr:uid="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Kommentar zu einer Metrik zusammengefasst.</t>
-      </text>
-    </comment>
-    <comment ref="C80" authorId="9" shapeId="0" xr:uid="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input Availability hinzugefügt.</t>
-      </text>
-    </comment>
-    <comment ref="C90" authorId="10" shapeId="0" xr:uid="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</t>
-      </text>
-    </comment>
-    <comment ref="F90" authorId="11" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
+    <comment ref="F90" authorId="3" shapeId="0" xr:uid="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -160,20 +85,12 @@
     Nach Andres Input angepasst.</t>
       </text>
     </comment>
-    <comment ref="H91" authorId="12" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
+    <comment ref="H91" authorId="4" shapeId="0" xr:uid="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Nach Andres Anregung von Business zu DevEx/Upskilling gewechselt.</t>
-      </text>
-    </comment>
-    <comment ref="C92" authorId="13" shapeId="0" xr:uid="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Zusammengefasst nach Andres Input</t>
       </text>
     </comment>
   </commentList>
@@ -501,9 +418,6 @@
     <t>Diff Authoring Time</t>
   </si>
   <si>
-    <t>Aims to capture all active human developertime spent on a particular diff, split by the different roles involved. This information is made available in a privacy-aware manner. Active human work on a computer tends to be highly sequential, even if such individual sequences can be extremely short.</t>
-  </si>
-  <si>
     <t>Discoverability of Documentation and Expertise</t>
   </si>
   <si>
@@ -2400,6 +2314,9 @@
   </si>
   <si>
     <t>Data Collection Type</t>
+  </si>
+  <si>
+    <t>Aims to capture all active human developer time spent on a particular diff, split by the different roles involved. This information is made available in a privacy-aware manner. Active human work on a computer tends to be highly sequential, even if such individual sequences can be extremely short.</t>
   </si>
 </sst>
 </file>
@@ -3215,48 +3132,17 @@
   <threadedComment ref="C15" dT="2025-05-23T08:51:40.12" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{5DABF24C-F7F6-4498-BB7E-BFB15DB8540E}">
     <text>Nach Andres Input zusammengefasst zu einem Eintrag.</text>
   </threadedComment>
-  <threadedComment ref="C29" dT="2025-05-23T09:38:31.42" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
-    <text xml:space="preserve">„NextJS Page Compilation Duration“ ergänzt nach Andres Input.
-</text>
-  </threadedComment>
-  <threadedComment ref="C29" dT="2025-05-23T09:41:48.20" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{B9D6B62F-97AD-4141-950D-E7ECA7254F2F}" parentId="{E017DF4E-5656-4CEF-B774-80BA936A6D56}">
-    <text>„Application/Package Build Duration“ von Lattice nach Andres Input ergänzt.</text>
-  </threadedComment>
-  <threadedComment ref="D29" dT="2025-05-23T09:41:06.69" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{8A92D669-9E50-4C59-82E5-97B139270D19}">
-    <text>Lattice von NextJS Page Compilation Duration</text>
-  </threadedComment>
   <threadedComment ref="H34" dT="2025-06-02T18:38:57.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{121DA4BD-014E-470E-AB44-B9514592A80F}">
     <text>Nach Andres Input von Business zu Process verschoben.</text>
   </threadedComment>
-  <threadedComment ref="C52" dT="2025-05-23T09:31:57.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{41A1A9E9-8671-443A-BC53-E9E6789FC6B2}">
-    <text>„Time to Restore Services“ ergänzt nach Andres Input.</text>
-  </threadedComment>
-  <threadedComment ref="H58" dT="2025-06-03T11:52:12.80" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{7C21EAC9-D7DB-489B-AFEF-DEF502EE6ECC}">
-    <text>Nach Andres Input von DevEx zu Business/HR gewechselt.</text>
-  </threadedComment>
-  <threadedComment ref="H61" dT="2025-06-02T18:36:03.58" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{917C3D96-4AA9-4D8E-8F4B-AEDAD8831587}">
-    <text>Nach Andres Input von Business zu Quality verschoben.</text>
-  </threadedComment>
   <threadedComment ref="J69" dT="2025-06-03T11:54:41.83" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{FDDDF671-A2B6-4958-A032-5551C66219BE}">
     <text>Von Knowledge Expansion zu Upskilling gewechselt.</text>
-  </threadedComment>
-  <threadedComment ref="C76" dT="2025-06-02T18:24:12.03" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{9ABBA003-3752-4178-8927-349ABCC5DB99}">
-    <text>Nach Andres Kommentar zu einer Metrik zusammengefasst.</text>
-  </threadedComment>
-  <threadedComment ref="C80" dT="2025-06-03T12:09:36.50" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{45640671-D7E4-4EA6-9099-D4E52C010FD7}">
-    <text>Nach Andres Input Availability hinzugefügt.</text>
-  </threadedComment>
-  <threadedComment ref="C90" dT="2025-06-03T12:08:14.41" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{C9FB5614-C3E5-4863-BFB7-AAB3A42EAACD}">
-    <text>Nach Andres Input. Production Incidents und System Uptime / Availability hinzugefügt.</text>
   </threadedComment>
   <threadedComment ref="F90" dT="2025-06-03T12:03:43.98" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{FCC3DA67-C366-4123-AE95-236C8FC56568}">
     <text>Nach Andres Input angepasst.</text>
   </threadedComment>
   <threadedComment ref="H91" dT="2025-06-03T12:00:31.64" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{24A13EBD-8030-4299-B820-E3DBAA902DCC}">
     <text>Nach Andres Anregung von Business zu DevEx/Upskilling gewechselt.</text>
-  </threadedComment>
-  <threadedComment ref="C92" dT="2025-05-23T08:56:36.61" personId="{2315245B-EC09-46AB-A06E-DE769C358132}" id="{65177E12-2939-4BCC-8B47-DB95E81C94F5}">
-    <text>Zusammengefasst nach Andres Input</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3295,16 +3181,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="E1" s="14" t="s">
         <v>269</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1" s="20" t="s">
         <v>4</v>
@@ -3322,25 +3208,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="20" t="s">
+        <v>522</v>
+      </c>
+      <c r="N1" s="20" t="s">
         <v>523</v>
       </c>
-      <c r="N1" s="20" t="s">
-        <v>524</v>
-      </c>
       <c r="O1" s="20" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="P1" s="18" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="Q1" s="18" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="S1" s="18" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3354,16 +3240,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3396,16 +3282,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S2" s="15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3428,7 +3314,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3461,13 +3347,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S3" s="15" t="s">
         <v>9</v>
@@ -3481,22 +3367,22 @@
         <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I4" s="3">
         <f>VLOOKUP(H4,cardsort_group_IDs!A:B,2,0)</f>
@@ -3526,13 +3412,13 @@
         <v>8</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S4" s="15" t="s">
         <v>9</v>
@@ -3549,16 +3435,16 @@
         <v>9</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>15</v>
@@ -3591,13 +3477,13 @@
         <v>3</v>
       </c>
       <c r="P5" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q5" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S5" s="15" t="s">
         <v>9</v>
@@ -3611,22 +3497,22 @@
         <v>29</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I6" s="3">
         <f>VLOOKUP(H6,cardsort_group_IDs!A:B,2,0)</f>
@@ -3656,13 +3542,13 @@
         <v>4</v>
       </c>
       <c r="P6" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q6" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R6" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S6" s="15" t="s">
         <v>9</v>
@@ -3688,7 +3574,7 @@
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>10</v>
@@ -3721,13 +3607,13 @@
         <v>1</v>
       </c>
       <c r="P7" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q7" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R7" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S7" s="15" t="s">
         <v>9</v>
@@ -3744,16 +3630,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>36</v>
@@ -3786,13 +3672,13 @@
         <v>26</v>
       </c>
       <c r="P8" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q8" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S8" s="15" t="s">
         <v>9</v>
@@ -3818,7 +3704,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>36</v>
@@ -3851,13 +3737,13 @@
         <v>1</v>
       </c>
       <c r="P9" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R9" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S9" s="15" t="s">
         <v>9</v>
@@ -3874,7 +3760,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E10" s="16">
         <v>501</v>
@@ -3883,7 +3769,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>36</v>
@@ -3916,13 +3802,13 @@
         <v>2</v>
       </c>
       <c r="P10" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R10" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S10" s="15" t="s">
         <v>9</v>
@@ -3939,7 +3825,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E11" s="16">
         <v>501</v>
@@ -3948,7 +3834,7 @@
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>15</v>
@@ -3981,13 +3867,13 @@
         <v>3</v>
       </c>
       <c r="P11" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R11" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S11" s="15" t="s">
         <v>9</v>
@@ -4004,16 +3890,16 @@
         <v>9</v>
       </c>
       <c r="D12" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="E12" s="16" t="s">
         <v>449</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>450</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>36</v>
@@ -4046,13 +3932,13 @@
         <v>6</v>
       </c>
       <c r="P12" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S12" s="15" t="s">
         <v>9</v>
@@ -4069,16 +3955,16 @@
         <v>50</v>
       </c>
       <c r="D13" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>540</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>541</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>51</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>52</v>
@@ -4111,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="P13" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S13" s="15" t="s">
         <v>9</v>
@@ -4131,10 +4017,10 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>674</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>675</v>
       </c>
       <c r="E14" s="16">
         <v>131</v>
@@ -4143,7 +4029,7 @@
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>36</v>
@@ -4176,13 +4062,13 @@
         <v>4</v>
       </c>
       <c r="P14" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q14" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R14" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S14" s="15" t="s">
         <v>9</v>
@@ -4196,19 +4082,19 @@
         <v>55</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>57</v>
@@ -4241,13 +4127,13 @@
         <v>26</v>
       </c>
       <c r="P15" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q15" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R15" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S15" s="15" t="s">
         <v>9</v>
@@ -4261,22 +4147,22 @@
         <v>59</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>9</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I16" s="3">
         <f>VLOOKUP(H16,cardsort_group_IDs!A:B,2,0)</f>
@@ -4306,13 +4192,13 @@
         <v>5</v>
       </c>
       <c r="P16" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R16" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="S16" s="15" t="s">
         <v>9</v>
@@ -4329,16 +4215,16 @@
         <v>9</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>64</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>15</v>
@@ -4371,13 +4257,13 @@
         <v>3</v>
       </c>
       <c r="P17" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R17" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S17" s="15" t="s">
         <v>9</v>
@@ -4391,19 +4277,19 @@
         <v>65</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>9</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>67</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>52</v>
@@ -4436,13 +4322,13 @@
         <v>2</v>
       </c>
       <c r="P18" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R18" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S18" s="15" t="s">
         <v>9</v>
@@ -4468,7 +4354,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>10</v>
@@ -4501,13 +4387,13 @@
         <v>1</v>
       </c>
       <c r="P19" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R19" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S19" s="15" t="s">
         <v>9</v>
@@ -4527,13 +4413,13 @@
         <v>9</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>74</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>75</v>
@@ -4566,13 +4452,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R20" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S20" s="15" t="s">
         <v>9</v>
@@ -4589,7 +4475,7 @@
         <v>9</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E21" s="16">
         <v>131</v>
@@ -4598,7 +4484,7 @@
         <v>77</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>75</v>
@@ -4631,13 +4517,13 @@
         <v>3</v>
       </c>
       <c r="P21" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q21" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R21" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S21" s="15" t="s">
         <v>9</v>
@@ -4651,19 +4537,19 @@
         <v>28</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>652</v>
       </c>
-      <c r="D22" s="16" t="s">
-        <v>653</v>
-      </c>
       <c r="E22" s="16" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>78</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -4696,13 +4582,13 @@
         <v>16</v>
       </c>
       <c r="P22" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q22" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R22" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S22" s="15" t="s">
         <v>9</v>
@@ -4719,7 +4605,7 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E23" s="16">
         <v>501</v>
@@ -4728,10 +4614,10 @@
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I23" s="3">
         <f>VLOOKUP(H23,cardsort_group_IDs!A:B,2,0)</f>
@@ -4761,13 +4647,13 @@
         <v>2</v>
       </c>
       <c r="P23" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q23" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R23" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S23" s="15" t="s">
         <v>9</v>
@@ -4781,7 +4667,7 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>9</v>
@@ -4793,7 +4679,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>36</v>
@@ -4826,13 +4712,13 @@
         <v>1</v>
       </c>
       <c r="P24" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q24" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R24" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S24" s="15" t="s">
         <v>9</v>
@@ -4849,16 +4735,16 @@
         <v>9</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>85</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>75</v>
@@ -4891,13 +4777,13 @@
         <v>21</v>
       </c>
       <c r="P25" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q25" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R25" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S25" s="15" t="s">
         <v>9</v>
@@ -4911,19 +4797,19 @@
         <v>86</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D26" s="15">
         <v>170</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>36</v>
@@ -4956,13 +4842,13 @@
         <v>4</v>
       </c>
       <c r="P26" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q26" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R26" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S26" s="15" t="s">
         <v>9</v>
@@ -4979,7 +4865,7 @@
         <v>9</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E27" s="16">
         <v>501</v>
@@ -4988,7 +4874,7 @@
         <v>91</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>75</v>
@@ -5021,13 +4907,13 @@
         <v>2</v>
       </c>
       <c r="P27" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q27" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R27" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S27" s="15" t="s">
         <v>9</v>
@@ -5044,16 +4930,16 @@
         <v>9</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>93</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -5086,13 +4972,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q28" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R28" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S28" s="15" t="s">
         <v>9</v>
@@ -5106,19 +4992,19 @@
         <v>95</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D29" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="E29" s="16" t="s">
         <v>542</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>543</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>96</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>21</v>
@@ -5151,13 +5037,13 @@
         <v>8</v>
       </c>
       <c r="P29" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q29" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R29" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S29" s="15" t="s">
         <v>9</v>
@@ -5174,19 +5060,19 @@
         <v>9</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I30" s="3">
         <f>VLOOKUP(H30,cardsort_group_IDs!A:B,2,0)</f>
@@ -5216,13 +5102,13 @@
         <v>3</v>
       </c>
       <c r="P30" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q30" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R30" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S30" s="15" t="s">
         <v>9</v>
@@ -5236,22 +5122,22 @@
         <v>100</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>101</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I31" s="3">
         <f>VLOOKUP(H31,cardsort_group_IDs!A:B,2,0)</f>
@@ -5281,10 +5167,10 @@
         <v>43</v>
       </c>
       <c r="P31" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q31" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R31" t="s">
         <v>732</v>
@@ -5313,7 +5199,7 @@
         <v>104</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>10</v>
@@ -5346,13 +5232,13 @@
         <v>1</v>
       </c>
       <c r="P32" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q32" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R32" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S32" s="15" t="s">
         <v>9</v>
@@ -5366,19 +5252,19 @@
         <v>105</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>106</v>
+        <v>738</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>15</v>
@@ -5411,13 +5297,13 @@
         <v>17</v>
       </c>
       <c r="P33" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q33" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R33" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="S33" s="15" t="s">
         <v>9</v>
@@ -5428,22 +5314,22 @@
         <v>39</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E34" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>108</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>15</v>
@@ -5476,13 +5362,13 @@
         <v>3</v>
       </c>
       <c r="P34" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q34" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R34" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S34" s="15" t="s">
         <v>9</v>
@@ -5496,22 +5382,22 @@
         <v>61</v>
       </c>
       <c r="C35" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D35" s="16" t="s">
-        <v>532</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>533</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>110</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I35" s="3">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5541,13 +5427,13 @@
         <v>14</v>
       </c>
       <c r="P35" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R35" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S35" s="15" t="s">
         <v>9</v>
@@ -5558,25 +5444,25 @@
         <v>41</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>445</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>112</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5606,13 +5492,13 @@
         <v>6</v>
       </c>
       <c r="P36" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q36" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R36" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S36" s="15" t="s">
         <v>9</v>
@@ -5623,22 +5509,22 @@
         <v>42</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>575</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>
@@ -5671,13 +5557,13 @@
         <v>2</v>
       </c>
       <c r="P37" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q37" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R37" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S37" s="15" t="s">
         <v>9</v>
@@ -5688,32 +5574,32 @@
         <v>43</v>
       </c>
       <c r="B38" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>116</v>
-      </c>
       <c r="G38" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I38" s="3">
         <f>VLOOKUP(H38,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K38" s="3">
         <f>VLOOKUP(J38,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5736,13 +5622,13 @@
         <v>3</v>
       </c>
       <c r="P38" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q38" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R38" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S38" s="15" t="s">
         <v>9</v>
@@ -5753,22 +5639,22 @@
         <v>44</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D39" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>21</v>
@@ -5778,7 +5664,7 @@
         <v>202</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K39" s="3">
         <f>VLOOKUP(J39,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5801,13 +5687,13 @@
         <v>3</v>
       </c>
       <c r="P39" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q39" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R39" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S39" s="15" t="s">
         <v>9</v>
@@ -5818,22 +5704,22 @@
         <v>45</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="G40" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>21</v>
@@ -5843,7 +5729,7 @@
         <v>202</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K40" s="3">
         <f>VLOOKUP(J40,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5866,13 +5752,13 @@
         <v>2</v>
       </c>
       <c r="P40" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q40" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R40" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S40" s="15" t="s">
         <v>9</v>
@@ -5883,22 +5769,22 @@
         <v>46</v>
       </c>
       <c r="B41" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>126</v>
-      </c>
       <c r="G41" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>52</v>
@@ -5908,7 +5794,7 @@
         <v>206</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K41" s="3">
         <f>VLOOKUP(J41,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5931,13 +5817,13 @@
         <v>2</v>
       </c>
       <c r="P41" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q41" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R41" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S41" s="15" t="s">
         <v>9</v>
@@ -5948,25 +5834,25 @@
         <v>50</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>467</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I42" s="3">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -5996,13 +5882,13 @@
         <v>2</v>
       </c>
       <c r="P42" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q42" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R42" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S42" s="15" t="s">
         <v>9</v>
@@ -6013,7 +5899,7 @@
         <v>51</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>9</v>
@@ -6025,10 +5911,10 @@
         <v>506</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>15</v>
@@ -6061,13 +5947,13 @@
         <v>1</v>
       </c>
       <c r="P43" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q43" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R43" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S43" s="15" t="s">
         <v>9</v>
@@ -6078,7 +5964,7 @@
         <v>54</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>9</v>
@@ -6090,10 +5976,10 @@
         <v>506</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6126,13 +6012,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q44" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R44" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S44" s="15" t="s">
         <v>9</v>
@@ -6143,25 +6029,25 @@
         <v>56</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>553</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6191,13 +6077,13 @@
         <v>4</v>
       </c>
       <c r="P45" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q45" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R45" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S45" s="15" t="s">
         <v>9</v>
@@ -6208,7 +6094,7 @@
         <v>57</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>9</v>
@@ -6220,10 +6106,10 @@
         <v>509</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>10</v>
@@ -6256,13 +6142,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q46" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R46" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S46" s="15" t="s">
         <v>9</v>
@@ -6273,25 +6159,25 @@
         <v>58</v>
       </c>
       <c r="B47" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>574</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="G47" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I47" s="3">
         <f>VLOOKUP(H47,cardsort_group_IDs!A:B,2,0)</f>
@@ -6321,13 +6207,13 @@
         <v>4</v>
       </c>
       <c r="P47" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q47" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R47" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="S47" s="15" t="s">
         <v>9</v>
@@ -6338,25 +6224,25 @@
         <v>59</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D48" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E48" s="16" t="s">
-        <v>446</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="G48" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I48" s="3">
         <f>VLOOKUP(H48,cardsort_group_IDs!A:B,2,0)</f>
@@ -6386,13 +6272,13 @@
         <v>4</v>
       </c>
       <c r="P48" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q48" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R48" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S48" s="15" t="s">
         <v>9</v>
@@ -6403,22 +6289,22 @@
         <v>62</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="6" t="s">
+      <c r="D49" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="16" t="s">
-        <v>659</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>146</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>15</v>
@@ -6451,13 +6337,13 @@
         <v>11</v>
       </c>
       <c r="P49" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q49" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R49" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S49" s="15" t="s">
         <v>9</v>
@@ -6468,22 +6354,22 @@
         <v>63</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>36</v>
@@ -6516,13 +6402,13 @@
         <v>4</v>
       </c>
       <c r="P50" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q50" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R50" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S50" s="15" t="s">
         <v>9</v>
@@ -6533,7 +6419,7 @@
         <v>64</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>9</v>
@@ -6545,10 +6431,10 @@
         <v>9</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>21</v>
@@ -6581,13 +6467,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q51" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R51" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S51" s="15" t="s">
         <v>9</v>
@@ -6598,22 +6484,22 @@
         <v>65</v>
       </c>
       <c r="B52" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D52" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="D52" s="16" t="s">
-        <v>660</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>153</v>
-      </c>
       <c r="G52" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>21</v>
@@ -6623,7 +6509,7 @@
         <v>202</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K52" s="3">
         <f>VLOOKUP(J52,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6646,13 +6532,13 @@
         <v>16</v>
       </c>
       <c r="P52" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q52" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R52" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S52" s="15" t="s">
         <v>9</v>
@@ -6663,10 +6549,10 @@
         <v>66</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>9</v>
@@ -6675,10 +6561,10 @@
         <v>235</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>52</v>
@@ -6711,13 +6597,13 @@
         <v>1</v>
       </c>
       <c r="P53" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q53" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R53" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S53" s="15" t="s">
         <v>9</v>
@@ -6728,22 +6614,22 @@
         <v>67</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="15" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E54" s="16" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>52</v>
@@ -6753,7 +6639,7 @@
         <v>206</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K54" s="3">
         <f>VLOOKUP(J54,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6776,13 +6662,13 @@
         <v>3</v>
       </c>
       <c r="P54" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q54" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R54" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="S54" s="15" t="s">
         <v>9</v>
@@ -6793,22 +6679,22 @@
         <v>69</v>
       </c>
       <c r="B55" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="E55" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>447</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>75</v>
@@ -6841,13 +6727,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q55" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R55" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S55" s="15" t="s">
         <v>9</v>
@@ -6858,22 +6744,22 @@
         <v>70</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="G56" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>36</v>
@@ -6906,13 +6792,13 @@
         <v>2</v>
       </c>
       <c r="P56" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q56" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R56" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S56" s="15" t="s">
         <v>9</v>
@@ -6923,22 +6809,22 @@
         <v>71</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E57" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E57" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>162</v>
-      </c>
       <c r="G57" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>15</v>
@@ -6971,13 +6857,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q57" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R57" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S57" s="15" t="s">
         <v>9</v>
@@ -6988,22 +6874,22 @@
         <v>72</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E58" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E58" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>164</v>
-      </c>
       <c r="G58" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -7013,7 +6899,7 @@
         <v>201</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K58" s="3">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7036,13 +6922,13 @@
         <v>3</v>
       </c>
       <c r="P58" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q58" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R58" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S58" s="15" t="s">
         <v>9</v>
@@ -7053,22 +6939,22 @@
         <v>73</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E59" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E59" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>167</v>
-      </c>
       <c r="G59" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>21</v>
@@ -7078,7 +6964,7 @@
         <v>202</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K59" s="3">
         <f>VLOOKUP(J59,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7101,13 +6987,13 @@
         <v>3</v>
       </c>
       <c r="P59" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q59" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R59" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S59" s="15" t="s">
         <v>9</v>
@@ -7118,7 +7004,7 @@
         <v>74</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>9</v>
@@ -7130,10 +7016,10 @@
         <v>183</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7166,13 +7052,13 @@
         <v>1</v>
       </c>
       <c r="P60" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q60" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R60" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S60" s="15" t="s">
         <v>9</v>
@@ -7183,22 +7069,22 @@
         <v>75</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E61" s="16">
         <v>183</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>36</v>
@@ -7231,13 +7117,13 @@
         <v>2</v>
       </c>
       <c r="P61" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q61" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R61" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S61" s="15" t="s">
         <v>9</v>
@@ -7248,22 +7134,22 @@
         <v>76</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="D62" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="G62" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>10</v>
@@ -7273,7 +7159,7 @@
         <v>201</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K62" s="3">
         <f>VLOOKUP(J62,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7296,13 +7182,13 @@
         <v>2</v>
       </c>
       <c r="P62" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q62" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R62" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S62" s="15" t="s">
         <v>9</v>
@@ -7313,25 +7199,25 @@
         <v>77</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I63" s="3">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
@@ -7361,13 +7247,13 @@
         <v>3</v>
       </c>
       <c r="P63" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q63" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R63" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S63" s="15" t="s">
         <v>9</v>
@@ -7378,25 +7264,25 @@
         <v>78</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C64" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="D64" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="F64" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D64" s="15" t="s">
-        <v>668</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="G64" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I64" s="3">
         <f>VLOOKUP(H64,cardsort_group_IDs!A:B,2,0)</f>
@@ -7426,13 +7312,13 @@
         <v>11</v>
       </c>
       <c r="P64" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q64" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R64" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S64" s="15" t="s">
         <v>9</v>
@@ -7443,22 +7329,22 @@
         <v>79</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>686</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="G65" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>75</v>
@@ -7491,13 +7377,13 @@
         <v>4</v>
       </c>
       <c r="P65" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q65" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R65" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S65" s="15" t="s">
         <v>9</v>
@@ -7508,7 +7394,7 @@
         <v>80</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>9</v>
@@ -7520,10 +7406,10 @@
         <v>509</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>75</v>
@@ -7556,13 +7442,13 @@
         <v>1</v>
       </c>
       <c r="P66" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q66" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R66" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S66" s="15" t="s">
         <v>9</v>
@@ -7573,22 +7459,22 @@
         <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E67" s="16">
         <v>202</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>36</v>
@@ -7621,13 +7507,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q67" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R67" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S67" s="15" t="s">
         <v>9</v>
@@ -7638,7 +7524,7 @@
         <v>82</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>9</v>
@@ -7650,10 +7536,10 @@
         <v>509</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>10</v>
@@ -7663,7 +7549,7 @@
         <v>201</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K68" s="3">
         <f>VLOOKUP(J68,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7686,13 +7572,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q68" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R68" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S68" s="15" t="s">
         <v>9</v>
@@ -7703,32 +7589,32 @@
         <v>83</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>661</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>662</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>466</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="G69" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I69" s="3">
         <f>VLOOKUP(H69,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K69" s="3">
         <f>VLOOKUP(J69,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7751,13 +7637,13 @@
         <v>5</v>
       </c>
       <c r="P69" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q69" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R69" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S69" s="15" t="s">
         <v>9</v>
@@ -7768,22 +7654,22 @@
         <v>84</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E70" s="16">
         <v>501</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -7793,7 +7679,7 @@
         <v>202</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K70" s="3">
         <f>VLOOKUP(J70,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7816,13 +7702,13 @@
         <v>2</v>
       </c>
       <c r="P70" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q70" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R70" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S70" s="15" t="s">
         <v>9</v>
@@ -7833,22 +7719,22 @@
         <v>85</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>462</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>463</v>
-      </c>
-      <c r="E71" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="G71" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>15</v>
@@ -7881,13 +7767,13 @@
         <v>1</v>
       </c>
       <c r="P71" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q71" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R71" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S71" s="15" t="s">
         <v>9</v>
@@ -7898,22 +7784,22 @@
         <v>87</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="E72" s="16" t="s">
-        <v>552</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="G72" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>15</v>
@@ -7946,13 +7832,13 @@
         <v>3</v>
       </c>
       <c r="P72" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q72" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R72" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S72" s="15" t="s">
         <v>9</v>
@@ -7963,22 +7849,22 @@
         <v>88</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>529</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>530</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>196</v>
-      </c>
       <c r="G73" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>36</v>
@@ -8011,13 +7897,13 @@
         <v>3</v>
       </c>
       <c r="P73" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q73" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R73" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S73" s="15" t="s">
         <v>9</v>
@@ -8028,22 +7914,22 @@
         <v>89</v>
       </c>
       <c r="B74" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="15" t="s">
+        <v>453</v>
+      </c>
+      <c r="E74" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="F74" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>454</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>453</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="G74" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>36</v>
@@ -8076,13 +7962,13 @@
         <v>4</v>
       </c>
       <c r="P74" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q74" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R74" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S74" s="15" t="s">
         <v>9</v>
@@ -8093,22 +7979,22 @@
         <v>90</v>
       </c>
       <c r="B75" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="D75" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="E75" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>655</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>687</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="G75" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>36</v>
@@ -8141,13 +8027,13 @@
         <v>14</v>
       </c>
       <c r="P75" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q75" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R75" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S75" s="15" t="s">
         <v>9</v>
@@ -8158,22 +8044,22 @@
         <v>91</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D76" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="E76" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>549</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="G76" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8206,13 +8092,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q76" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R76" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S76" s="15" t="s">
         <v>9</v>
@@ -8223,22 +8109,22 @@
         <v>92</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E77" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F77" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E77" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>204</v>
-      </c>
       <c r="G77" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>52</v>
@@ -8248,7 +8134,7 @@
         <v>206</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K77" s="3">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8271,13 +8157,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q77" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R77" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S77" s="15" t="s">
         <v>9</v>
@@ -8288,7 +8174,7 @@
         <v>93</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>9</v>
@@ -8300,10 +8186,10 @@
         <v>509</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>10</v>
@@ -8336,13 +8222,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q78" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R78" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S78" s="15" t="s">
         <v>9</v>
@@ -8353,22 +8239,22 @@
         <v>94</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="D79" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="E79" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="F79" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>456</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>208</v>
-      </c>
       <c r="G79" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>75</v>
@@ -8401,13 +8287,13 @@
         <v>4</v>
       </c>
       <c r="P79" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q79" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R79" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S79" s="15" t="s">
         <v>9</v>
@@ -8418,22 +8304,22 @@
         <v>95</v>
       </c>
       <c r="B80" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C80" s="4" t="s">
+      <c r="D80" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="E80" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="F80" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="D80" s="16" t="s">
-        <v>438</v>
-      </c>
-      <c r="E80" s="16" t="s">
-        <v>579</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="G80" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>21</v>
@@ -8443,7 +8329,7 @@
         <v>202</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K80" s="3">
         <f>VLOOKUP(J80,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8466,13 +8352,13 @@
         <v>3</v>
       </c>
       <c r="P80" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q80" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R80" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S80" s="15" t="s">
         <v>9</v>
@@ -8483,7 +8369,7 @@
         <v>97</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>9</v>
@@ -8495,10 +8381,10 @@
         <v>508</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>21</v>
@@ -8508,7 +8394,7 @@
         <v>202</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K81" s="3">
         <f>VLOOKUP(J81,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8531,13 +8417,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q81" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R81" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S81" s="15" t="s">
         <v>9</v>
@@ -8548,10 +8434,10 @@
         <v>98</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D82" s="13">
         <v>209</v>
@@ -8560,10 +8446,10 @@
         <v>506</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>10</v>
@@ -8573,7 +8459,7 @@
         <v>201</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K82" s="3">
         <f>VLOOKUP(J82,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8596,13 +8482,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q82" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R82" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S82" s="15" t="s">
         <v>9</v>
@@ -8613,7 +8499,7 @@
         <v>99</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>9</v>
@@ -8625,10 +8511,10 @@
         <v>508</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>10</v>
@@ -8638,7 +8524,7 @@
         <v>201</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K83" s="3">
         <f>VLOOKUP(J83,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8661,13 +8547,13 @@
         <v>1</v>
       </c>
       <c r="P83" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q83" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R83" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S83" s="15" t="s">
         <v>9</v>
@@ -8678,7 +8564,7 @@
         <v>100</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>9</v>
@@ -8690,10 +8576,10 @@
         <v>509</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>10</v>
@@ -8703,7 +8589,7 @@
         <v>201</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K84" s="3">
         <f>VLOOKUP(J84,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8726,13 +8612,13 @@
         <v>1</v>
       </c>
       <c r="P84" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q84" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R84" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S84" s="15" t="s">
         <v>9</v>
@@ -8743,22 +8629,22 @@
         <v>102</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E85" s="16">
         <v>501</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8791,13 +8677,13 @@
         <v>2</v>
       </c>
       <c r="P85" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q85" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R85" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S85" s="15" t="s">
         <v>9</v>
@@ -8808,25 +8694,25 @@
         <v>104</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="D86" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="E86" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="D86" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="E86" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="G86" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I86" s="3">
         <f>VLOOKUP(H86,cardsort_group_IDs!A:B,2,0)</f>
@@ -8856,13 +8742,13 @@
         <v>2</v>
       </c>
       <c r="P86" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q86" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R86" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S86" s="15" t="s">
         <v>9</v>
@@ -8873,22 +8759,22 @@
         <v>105</v>
       </c>
       <c r="B87" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="E87" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D87" s="16" t="s">
-        <v>550</v>
-      </c>
-      <c r="E87" s="16" t="s">
-        <v>551</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>227</v>
-      </c>
       <c r="G87" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8898,7 +8784,7 @@
         <v>202</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K87" s="3">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8921,13 +8807,13 @@
         <v>4</v>
       </c>
       <c r="P87" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q87" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R87" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S87" s="15" t="s">
         <v>9</v>
@@ -8938,22 +8824,22 @@
         <v>107</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E88" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>534</v>
-      </c>
-      <c r="E88" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>229</v>
-      </c>
       <c r="G88" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -8986,13 +8872,13 @@
         <v>7</v>
       </c>
       <c r="P88" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q88" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R88" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S88" s="15" t="s">
         <v>9</v>
@@ -9003,22 +8889,22 @@
         <v>108</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D89" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="E89" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>558</v>
-      </c>
-      <c r="E89" s="16" t="s">
-        <v>559</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="G89" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>15</v>
@@ -9051,13 +8937,13 @@
         <v>8</v>
       </c>
       <c r="P89" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q89" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R89" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S89" s="15" t="s">
         <v>9</v>
@@ -9068,22 +8954,22 @@
         <v>109</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="E90" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="F90" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C90" s="4" t="s">
-        <v>568</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>569</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>233</v>
-      </c>
       <c r="G90" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>21</v>
@@ -9093,7 +8979,7 @@
         <v>202</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K90" s="3">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9116,13 +9002,13 @@
         <v>8</v>
       </c>
       <c r="P90" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q90" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R90" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S90" s="15" t="s">
         <v>9</v>
@@ -9133,32 +9019,32 @@
         <v>112</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D91" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="F91" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>704</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E91" s="16" t="s">
-        <v>703</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>235</v>
-      </c>
       <c r="G91" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I91" s="3">
         <f>VLOOKUP(H91,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9181,13 +9067,13 @@
         <v>2</v>
       </c>
       <c r="P91" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q91" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R91" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S91" s="15" t="s">
         <v>9</v>
@@ -9198,22 +9084,22 @@
         <v>114</v>
       </c>
       <c r="B92" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>556</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D92" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="E92" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="G92" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>57</v>
@@ -9246,13 +9132,13 @@
         <v>14</v>
       </c>
       <c r="P92" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q92" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R92" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S92" s="15" t="s">
         <v>9</v>
@@ -9263,7 +9149,7 @@
         <v>115</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>9</v>
@@ -9275,10 +9161,10 @@
         <v>183</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>52</v>
@@ -9288,7 +9174,7 @@
         <v>206</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9311,13 +9197,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q93" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R93" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S93" s="15" t="s">
         <v>9</v>
@@ -9328,22 +9214,22 @@
         <v>116</v>
       </c>
       <c r="B94" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D94" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F94" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C94" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>459</v>
-      </c>
-      <c r="E94" s="16" t="s">
-        <v>458</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>242</v>
-      </c>
       <c r="G94" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>36</v>
@@ -9353,7 +9239,7 @@
         <v>205</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="K94" s="3">
         <f>VLOOKUP(J94,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9376,13 +9262,13 @@
         <v>4</v>
       </c>
       <c r="P94" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q94" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R94" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S94" s="15" t="s">
         <v>9</v>
@@ -9396,19 +9282,19 @@
         <v>41</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>36</v>
@@ -9441,13 +9327,13 @@
         <v>5</v>
       </c>
       <c r="P95" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q95" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R95" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S95" s="15" t="s">
         <v>9</v>
@@ -9458,7 +9344,7 @@
         <v>118</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
@@ -9470,10 +9356,10 @@
         <v>9</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>21</v>
@@ -9483,7 +9369,7 @@
         <v>202</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K96" s="3">
         <f>VLOOKUP(J96,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9506,13 +9392,13 @@
         <v>1</v>
       </c>
       <c r="P96" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q96" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R96" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S96" s="15" t="s">
         <v>9</v>
@@ -9523,22 +9409,22 @@
         <v>119</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E97" s="16">
         <v>501</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9571,13 +9457,13 @@
         <v>2</v>
       </c>
       <c r="P97" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q97" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R97" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S97" s="15" t="s">
         <v>9</v>
@@ -9588,22 +9474,22 @@
         <v>120</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="F98" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="E98" s="16" t="s">
-        <v>444</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>251</v>
-      </c>
       <c r="G98" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>15</v>
@@ -9636,13 +9522,13 @@
         <v>3</v>
       </c>
       <c r="P98" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q98" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R98" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S98" s="15" t="s">
         <v>9</v>
@@ -9653,22 +9539,22 @@
         <v>121</v>
       </c>
       <c r="B99" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="D99" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="E99" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C99" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>666</v>
-      </c>
-      <c r="E99" s="16" t="s">
-        <v>448</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>253</v>
-      </c>
       <c r="G99" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>15</v>
@@ -9701,13 +9587,13 @@
         <v>8</v>
       </c>
       <c r="P99" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q99" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R99" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S99" s="15" t="s">
         <v>9</v>
@@ -9718,22 +9604,22 @@
         <v>122</v>
       </c>
       <c r="B100" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>664</v>
+      </c>
+      <c r="E100" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="F100" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>664</v>
-      </c>
-      <c r="D100" s="13" t="s">
-        <v>665</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>560</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>255</v>
-      </c>
       <c r="G100" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>15</v>
@@ -9766,13 +9652,13 @@
         <v>5</v>
       </c>
       <c r="P100" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q100" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R100" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S100" s="15" t="s">
         <v>9</v>
@@ -9783,32 +9669,32 @@
         <v>124</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C101" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C101" s="4" t="s">
+      <c r="D101" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="E101" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="D101" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="E101" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>258</v>
-      </c>
       <c r="G101" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I101" s="3">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K101" s="3">
         <f>VLOOKUP(J101,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9831,13 +9717,13 @@
         <v>7</v>
       </c>
       <c r="P101" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q101" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R101" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S101" s="15" t="s">
         <v>9</v>
@@ -9848,22 +9734,22 @@
         <v>126</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C102" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E102" s="16">
         <v>501</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>57</v>
@@ -9896,13 +9782,13 @@
         <v>2</v>
       </c>
       <c r="P102" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q102" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R102" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S102" s="15" t="s">
         <v>9</v>
@@ -9913,22 +9799,22 @@
         <v>127</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C103" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D103" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="E103" s="16" t="s">
         <v>296</v>
       </c>
-      <c r="D103" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="E103" s="16" t="s">
-        <v>297</v>
-      </c>
       <c r="F103" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>57</v>
@@ -9961,13 +9847,13 @@
         <v>3</v>
       </c>
       <c r="P103" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q103" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R103" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S103" s="15" t="s">
         <v>9</v>
@@ -9978,22 +9864,22 @@
         <v>128</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E104" s="16">
         <v>501</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>57</v>
@@ -10026,13 +9912,13 @@
         <v>2</v>
       </c>
       <c r="P104" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q104" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R104" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S104" s="15" t="s">
         <v>9</v>
@@ -10043,22 +9929,22 @@
         <v>129</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="E105" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="F105" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="C105" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>649</v>
-      </c>
-      <c r="E105" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>648</v>
-      </c>
       <c r="G105" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>57</v>
@@ -10091,13 +9977,13 @@
         <v>27</v>
       </c>
       <c r="P105" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q105" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R105" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S105" s="15" t="s">
         <v>9</v>
@@ -10108,25 +9994,25 @@
         <v>130</v>
       </c>
       <c r="B106" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>537</v>
+      </c>
+      <c r="E106" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>538</v>
-      </c>
-      <c r="E106" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>268</v>
-      </c>
       <c r="G106" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I106" s="3">
         <f>VLOOKUP(H106,cardsort_group_IDs!A:B,2,0)</f>
@@ -10156,13 +10042,13 @@
         <v>5</v>
       </c>
       <c r="P106" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q106" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R106" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S106" s="15" t="s">
         <v>9</v>
@@ -10173,22 +10059,22 @@
         <v>134</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="C107" s="4" t="s">
-        <v>300</v>
-      </c>
       <c r="D107" s="13" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G107" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H107" t="s">
         <v>36</v>
@@ -10221,13 +10107,13 @@
         <v>11</v>
       </c>
       <c r="P107" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q107" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R107" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S107" s="15" t="s">
         <v>9</v>
@@ -10238,7 +10124,7 @@
         <v>135</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>9</v>
@@ -10250,20 +10136,20 @@
         <v>183</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G108" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H108" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I108" s="3">
         <f>VLOOKUP(H108,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J108" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K108" s="3">
         <f>VLOOKUP(J108,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10286,13 +10172,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q108" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R108" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S108" s="15" t="s">
         <v>9</v>
@@ -10303,7 +10189,7 @@
         <v>136</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10315,10 +10201,10 @@
         <v>240</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G109" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H109" t="s">
         <v>57</v>
@@ -10351,13 +10237,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q109" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R109" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="S109" s="15" t="s">
         <v>9</v>
@@ -10368,25 +10254,25 @@
         <v>137</v>
       </c>
       <c r="B110" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C110" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="C110" s="4" t="s">
+      <c r="D110" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E110" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="D110" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E110" s="17" t="s">
-        <v>304</v>
-      </c>
       <c r="F110" s="4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G110" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H110" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I110" s="3">
         <f>VLOOKUP(H110,cardsort_group_IDs!A:B,2,0)</f>
@@ -10416,13 +10302,13 @@
         <v>6</v>
       </c>
       <c r="P110" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q110" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R110" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S110" s="15" t="s">
         <v>9</v>
@@ -10433,10 +10319,10 @@
         <v>138</v>
       </c>
       <c r="B111" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>305</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="D111" s="15" t="s">
         <v>9</v>
@@ -10445,10 +10331,10 @@
         <v>236</v>
       </c>
       <c r="F111" s="11" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G111" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H111" t="s">
         <v>10</v>
@@ -10481,13 +10367,13 @@
         <v>1</v>
       </c>
       <c r="P111" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q111" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R111" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S111" s="15" t="s">
         <v>9</v>
@@ -10498,7 +10384,7 @@
         <v>139</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
@@ -10510,10 +10396,10 @@
         <v>9</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>21</v>
@@ -10523,7 +10409,7 @@
         <v>202</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K112" s="3">
         <f>VLOOKUP(J112,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10546,13 +10432,13 @@
         <v>1</v>
       </c>
       <c r="P112" s="15" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="Q112" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R112" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S112" s="15" t="s">
         <v>9</v>
@@ -10563,22 +10449,22 @@
         <v>140</v>
       </c>
       <c r="B113" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="E113" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="C113" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>643</v>
-      </c>
-      <c r="E113" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>612</v>
-      </c>
       <c r="G113" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>15</v>
@@ -10611,13 +10497,13 @@
         <v>18</v>
       </c>
       <c r="P113" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q113" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R113" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S113" s="15">
         <v>2</v>
@@ -10628,22 +10514,22 @@
         <v>141</v>
       </c>
       <c r="B114" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="E114" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>618</v>
-      </c>
-      <c r="E114" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>617</v>
-      </c>
       <c r="G114" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>57</v>
@@ -10676,13 +10562,13 @@
         <v>3</v>
       </c>
       <c r="P114" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q114" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R114" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S114" s="15">
         <v>129</v>
@@ -10693,22 +10579,22 @@
         <v>142</v>
       </c>
       <c r="B115" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E115" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="F115" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="C115" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>594</v>
-      </c>
-      <c r="E115" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>620</v>
-      </c>
       <c r="G115" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>57</v>
@@ -10741,13 +10627,13 @@
         <v>2</v>
       </c>
       <c r="P115" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q115" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R115" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S115" s="15">
         <v>19</v>
@@ -10758,22 +10644,22 @@
         <v>143</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="15" t="s">
         <v>625</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="15" t="s">
+      <c r="E116" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="E116" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>627</v>
-      </c>
       <c r="G116" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>57</v>
@@ -10806,13 +10692,13 @@
         <v>5</v>
       </c>
       <c r="P116" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q116" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R116" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S116" s="15" t="s">
         <v>9</v>
@@ -10823,22 +10709,22 @@
         <v>144</v>
       </c>
       <c r="B117" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E117" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10871,16 +10757,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Q117" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R117" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S117" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10888,22 +10774,22 @@
         <v>145</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D118" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E118" s="16" t="s">
         <v>9</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H118" t="s">
         <v>10</v>
@@ -10936,16 +10822,16 @@
         <v>1</v>
       </c>
       <c r="P118" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Q118" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R118" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S118" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10953,22 +10839,22 @@
         <v>146</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D119" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E119" s="16" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H119" t="s">
         <v>10</v>
@@ -11001,16 +10887,16 @@
         <v>6</v>
       </c>
       <c r="P119" s="15" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="Q119" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R119" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S119" s="15" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
@@ -11018,22 +10904,22 @@
         <v>147</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="E120" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D120" s="13" t="s">
-        <v>640</v>
-      </c>
-      <c r="E120" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F120" s="3" t="s">
-        <v>639</v>
-      </c>
       <c r="G120" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11066,16 +10952,16 @@
         <v>1</v>
       </c>
       <c r="P120" s="15" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q120" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R120" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S120" s="15" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.25">
@@ -11083,22 +10969,22 @@
         <v>148</v>
       </c>
       <c r="B121" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D121" t="s">
+        <v>677</v>
+      </c>
+      <c r="E121" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="D121" t="s">
-        <v>678</v>
-      </c>
-      <c r="E121" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="F121" s="3" t="s">
-        <v>645</v>
-      </c>
       <c r="G121" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>10</v>
@@ -11131,16 +11017,16 @@
         <v>11</v>
       </c>
       <c r="P121" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q121" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R121" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S121" s="15" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.25">
@@ -11148,22 +11034,22 @@
         <v>149</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D122" s="15" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E122" s="16" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>21</v>
@@ -11173,7 +11059,7 @@
         <v>202</v>
       </c>
       <c r="J122" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K122" s="3">
         <f>VLOOKUP(J122,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -11196,16 +11082,16 @@
         <v>3</v>
       </c>
       <c r="P122" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q122" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R122" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S122" s="15" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
@@ -11213,25 +11099,25 @@
         <v>150</v>
       </c>
       <c r="B123" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="15" t="s">
         <v>669</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D123" s="15" t="s">
+      <c r="E123" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="E123" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F123" s="3" t="s">
-        <v>671</v>
-      </c>
       <c r="G123" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11261,16 +11147,16 @@
         <v>2</v>
       </c>
       <c r="P123" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q123" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R123" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S123" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="124" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11278,22 +11164,22 @@
         <v>151</v>
       </c>
       <c r="B124" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="C124" s="4" t="s">
-        <v>692</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="F124" s="3" t="s">
-        <v>683</v>
-      </c>
       <c r="G124" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>15</v>
@@ -11326,13 +11212,13 @@
         <v>1</v>
       </c>
       <c r="P124" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q124" s="15" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="R124" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S124" s="15" t="s">
         <v>9</v>
@@ -11343,25 +11229,25 @@
         <v>152</v>
       </c>
       <c r="B125" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="C125" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="F125" s="3" t="s">
-        <v>699</v>
-      </c>
       <c r="G125" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I125" s="3">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11391,13 +11277,13 @@
         <v>1</v>
       </c>
       <c r="P125" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q125" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R125" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S125" s="15" t="s">
         <v>9</v>
@@ -11408,7 +11294,7 @@
         <v>153</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>9</v>
@@ -11417,16 +11303,16 @@
         <v>9</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F126" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I126" s="3">
         <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
@@ -11456,16 +11342,16 @@
         <v>1</v>
       </c>
       <c r="P126" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q126" s="15" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="R126" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="S126" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.25">
@@ -11473,25 +11359,25 @@
         <v>154</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="F127" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="C127" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D127" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>707</v>
-      </c>
       <c r="G127" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="I127" s="3">
         <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
@@ -11521,16 +11407,16 @@
         <v>1</v>
       </c>
       <c r="P127" s="15" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q127" s="15" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="R127" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="S127" s="15" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.25">
@@ -11694,16 +11580,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" t="s">
         <v>418</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>709</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>419</v>
-      </c>
-      <c r="C1" t="s">
-        <v>710</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11711,13 +11597,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" t="s">
+        <v>719</v>
+      </c>
+      <c r="D2" t="s">
         <v>312</v>
-      </c>
-      <c r="C2" t="s">
-        <v>720</v>
-      </c>
-      <c r="D2" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11725,13 +11611,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C3" t="s">
+        <v>719</v>
+      </c>
+      <c r="D3" t="s">
         <v>314</v>
-      </c>
-      <c r="C3" t="s">
-        <v>720</v>
-      </c>
-      <c r="D3" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -11739,13 +11625,13 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D4" t="s">
         <v>316</v>
-      </c>
-      <c r="C4" t="s">
-        <v>720</v>
-      </c>
-      <c r="D4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11753,13 +11639,13 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" t="s">
+        <v>719</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>318</v>
-      </c>
-      <c r="C5" t="s">
-        <v>720</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11767,13 +11653,13 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" t="s">
+        <v>719</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="C6" t="s">
-        <v>720</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11781,13 +11667,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C7" t="s">
+        <v>719</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>322</v>
-      </c>
-      <c r="C7" t="s">
-        <v>720</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11795,13 +11681,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" t="s">
+        <v>719</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>324</v>
-      </c>
-      <c r="C8" t="s">
-        <v>720</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11809,13 +11695,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>325</v>
+      </c>
+      <c r="C9" t="s">
+        <v>719</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>326</v>
-      </c>
-      <c r="C9" t="s">
-        <v>720</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11823,13 +11709,13 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" t="s">
+        <v>719</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="C10" t="s">
-        <v>720</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11837,13 +11723,13 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D11" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11851,13 +11737,13 @@
         <v>20</v>
       </c>
       <c r="B12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" t="s">
+        <v>719</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>330</v>
-      </c>
-      <c r="C12" t="s">
-        <v>720</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11865,13 +11751,13 @@
         <v>21</v>
       </c>
       <c r="B13" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" t="s">
+        <v>719</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>332</v>
-      </c>
-      <c r="C13" t="s">
-        <v>720</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11879,13 +11765,13 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C14" t="s">
+        <v>719</v>
+      </c>
+      <c r="D14" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="C14" t="s">
-        <v>720</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11893,13 +11779,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C15" t="s">
+        <v>719</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>336</v>
-      </c>
-      <c r="C15" t="s">
-        <v>720</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11907,13 +11793,13 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C16" t="s">
+        <v>719</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>338</v>
-      </c>
-      <c r="C16" t="s">
-        <v>720</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11921,13 +11807,13 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C17" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D17" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11935,13 +11821,13 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
+        <v>339</v>
+      </c>
+      <c r="C18" t="s">
+        <v>719</v>
+      </c>
+      <c r="D18" s="11" t="s">
         <v>340</v>
-      </c>
-      <c r="C18" t="s">
-        <v>720</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11949,13 +11835,13 @@
         <v>45</v>
       </c>
       <c r="B19" t="s">
+        <v>341</v>
+      </c>
+      <c r="C19" t="s">
+        <v>719</v>
+      </c>
+      <c r="D19" s="11" t="s">
         <v>342</v>
-      </c>
-      <c r="C19" t="s">
-        <v>720</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11963,13 +11849,13 @@
         <v>46</v>
       </c>
       <c r="B20" t="s">
+        <v>343</v>
+      </c>
+      <c r="C20" t="s">
+        <v>719</v>
+      </c>
+      <c r="D20" s="11" t="s">
         <v>344</v>
-      </c>
-      <c r="C20" t="s">
-        <v>720</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11977,13 +11863,13 @@
         <v>47</v>
       </c>
       <c r="B21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C21" t="s">
+        <v>719</v>
+      </c>
+      <c r="D21" s="11" t="s">
         <v>346</v>
-      </c>
-      <c r="C21" t="s">
-        <v>720</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11991,13 +11877,13 @@
         <v>49</v>
       </c>
       <c r="B22" t="s">
+        <v>347</v>
+      </c>
+      <c r="C22" t="s">
+        <v>719</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>348</v>
-      </c>
-      <c r="C22" t="s">
-        <v>720</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -12005,13 +11891,13 @@
         <v>50</v>
       </c>
       <c r="B23" t="s">
+        <v>349</v>
+      </c>
+      <c r="C23" t="s">
+        <v>719</v>
+      </c>
+      <c r="D23" s="11" t="s">
         <v>350</v>
-      </c>
-      <c r="C23" t="s">
-        <v>720</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -12019,13 +11905,13 @@
         <v>51</v>
       </c>
       <c r="B24" t="s">
+        <v>351</v>
+      </c>
+      <c r="C24" t="s">
+        <v>719</v>
+      </c>
+      <c r="D24" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="C24" t="s">
-        <v>720</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -12033,13 +11919,13 @@
         <v>52</v>
       </c>
       <c r="B25" t="s">
+        <v>353</v>
+      </c>
+      <c r="C25" t="s">
+        <v>719</v>
+      </c>
+      <c r="D25" s="11" t="s">
         <v>354</v>
-      </c>
-      <c r="C25" t="s">
-        <v>720</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12047,13 +11933,13 @@
         <v>57</v>
       </c>
       <c r="B26" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26" t="s">
+        <v>719</v>
+      </c>
+      <c r="D26" s="11" t="s">
         <v>356</v>
-      </c>
-      <c r="C26" t="s">
-        <v>720</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12061,13 +11947,13 @@
         <v>62</v>
       </c>
       <c r="B27" t="s">
+        <v>357</v>
+      </c>
+      <c r="C27" t="s">
+        <v>719</v>
+      </c>
+      <c r="D27" s="11" t="s">
         <v>358</v>
-      </c>
-      <c r="C27" t="s">
-        <v>720</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12075,13 +11961,13 @@
         <v>70</v>
       </c>
       <c r="B28" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" t="s">
+        <v>719</v>
+      </c>
+      <c r="D28" s="11" t="s">
         <v>360</v>
-      </c>
-      <c r="C28" t="s">
-        <v>720</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12089,13 +11975,13 @@
         <v>87</v>
       </c>
       <c r="B29" t="s">
+        <v>361</v>
+      </c>
+      <c r="C29" t="s">
+        <v>719</v>
+      </c>
+      <c r="D29" s="11" t="s">
         <v>362</v>
-      </c>
-      <c r="C29" t="s">
-        <v>720</v>
-      </c>
-      <c r="D29" s="11" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12103,13 +11989,13 @@
         <v>92</v>
       </c>
       <c r="B30" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C30" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12117,13 +12003,13 @@
         <v>96</v>
       </c>
       <c r="B31" t="s">
+        <v>364</v>
+      </c>
+      <c r="C31" t="s">
+        <v>719</v>
+      </c>
+      <c r="D31" s="11" t="s">
         <v>365</v>
-      </c>
-      <c r="C31" t="s">
-        <v>720</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -12131,13 +12017,13 @@
         <v>101</v>
       </c>
       <c r="B32" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" t="s">
+        <v>719</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>367</v>
-      </c>
-      <c r="C32" t="s">
-        <v>720</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12145,13 +12031,13 @@
         <v>105</v>
       </c>
       <c r="B33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" t="s">
+        <v>719</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>369</v>
-      </c>
-      <c r="C33" t="s">
-        <v>720</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -12159,13 +12045,13 @@
         <v>108</v>
       </c>
       <c r="B34" t="s">
+        <v>370</v>
+      </c>
+      <c r="C34" t="s">
+        <v>719</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>371</v>
-      </c>
-      <c r="C34" t="s">
-        <v>720</v>
-      </c>
-      <c r="D34" s="11" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12173,13 +12059,13 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
+        <v>372</v>
+      </c>
+      <c r="C35" t="s">
+        <v>719</v>
+      </c>
+      <c r="D35" s="11" t="s">
         <v>373</v>
-      </c>
-      <c r="C35" t="s">
-        <v>720</v>
-      </c>
-      <c r="D35" s="11" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12187,13 +12073,13 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C36" t="s">
+        <v>719</v>
+      </c>
+      <c r="D36" s="11" t="s">
         <v>375</v>
-      </c>
-      <c r="C36" t="s">
-        <v>720</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12201,13 +12087,13 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
+        <v>377</v>
+      </c>
+      <c r="C37" t="s">
+        <v>719</v>
+      </c>
+      <c r="D37" s="11" t="s">
         <v>378</v>
-      </c>
-      <c r="C37" t="s">
-        <v>720</v>
-      </c>
-      <c r="D37" s="11" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="12" customFormat="1" x14ac:dyDescent="0.25">
@@ -12215,13 +12101,13 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
+        <v>379</v>
+      </c>
+      <c r="C38" t="s">
+        <v>719</v>
+      </c>
+      <c r="D38" s="11" t="s">
         <v>380</v>
-      </c>
-      <c r="C38" t="s">
-        <v>720</v>
-      </c>
-      <c r="D38" s="11" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -12229,13 +12115,13 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
+        <v>381</v>
+      </c>
+      <c r="C39" t="s">
+        <v>719</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>382</v>
-      </c>
-      <c r="C39" t="s">
-        <v>720</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12246,10 +12132,10 @@
         <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12257,13 +12143,13 @@
         <v>182</v>
       </c>
       <c r="B41" t="s">
+        <v>384</v>
+      </c>
+      <c r="C41" t="s">
+        <v>719</v>
+      </c>
+      <c r="D41" s="11" t="s">
         <v>385</v>
-      </c>
-      <c r="C41" t="s">
-        <v>720</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12271,13 +12157,13 @@
         <v>183</v>
       </c>
       <c r="B42" t="s">
+        <v>386</v>
+      </c>
+      <c r="C42" t="s">
+        <v>719</v>
+      </c>
+      <c r="D42" s="11" t="s">
         <v>387</v>
-      </c>
-      <c r="C42" t="s">
-        <v>720</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12285,13 +12171,13 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C43" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12299,13 +12185,13 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C44" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12316,10 +12202,10 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -12327,13 +12213,13 @@
         <v>202</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C46" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12341,13 +12227,13 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C47" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D47" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12355,13 +12241,13 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C48" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12369,13 +12255,13 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C49" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12383,10 +12269,10 @@
         <v>232</v>
       </c>
       <c r="B50" t="s">
+        <v>395</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>396</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12394,13 +12280,13 @@
         <v>233</v>
       </c>
       <c r="B51" t="s">
+        <v>397</v>
+      </c>
+      <c r="C51" t="s">
+        <v>719</v>
+      </c>
+      <c r="D51" s="11" t="s">
         <v>398</v>
-      </c>
-      <c r="C51" t="s">
-        <v>720</v>
-      </c>
-      <c r="D51" s="11" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12408,13 +12294,13 @@
         <v>234</v>
       </c>
       <c r="B52" t="s">
+        <v>399</v>
+      </c>
+      <c r="C52" t="s">
+        <v>719</v>
+      </c>
+      <c r="D52" s="11" t="s">
         <v>400</v>
-      </c>
-      <c r="C52" t="s">
-        <v>720</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12422,13 +12308,13 @@
         <v>235</v>
       </c>
       <c r="B53" t="s">
+        <v>401</v>
+      </c>
+      <c r="C53" t="s">
+        <v>719</v>
+      </c>
+      <c r="D53" s="11" t="s">
         <v>402</v>
-      </c>
-      <c r="C53" t="s">
-        <v>720</v>
-      </c>
-      <c r="D53" s="11" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12436,13 +12322,13 @@
         <v>236</v>
       </c>
       <c r="B54" t="s">
+        <v>403</v>
+      </c>
+      <c r="C54" t="s">
+        <v>719</v>
+      </c>
+      <c r="D54" s="11" t="s">
         <v>404</v>
-      </c>
-      <c r="C54" t="s">
-        <v>720</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12450,13 +12336,13 @@
         <v>237</v>
       </c>
       <c r="B55" t="s">
+        <v>405</v>
+      </c>
+      <c r="C55" t="s">
+        <v>719</v>
+      </c>
+      <c r="D55" s="11" t="s">
         <v>406</v>
-      </c>
-      <c r="C55" t="s">
-        <v>720</v>
-      </c>
-      <c r="D55" s="11" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12464,13 +12350,13 @@
         <v>238</v>
       </c>
       <c r="B56" t="s">
+        <v>407</v>
+      </c>
+      <c r="C56" t="s">
+        <v>719</v>
+      </c>
+      <c r="D56" s="11" t="s">
         <v>408</v>
-      </c>
-      <c r="C56" t="s">
-        <v>720</v>
-      </c>
-      <c r="D56" s="11" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12478,13 +12364,13 @@
         <v>240</v>
       </c>
       <c r="B57" t="s">
+        <v>409</v>
+      </c>
+      <c r="C57" t="s">
+        <v>719</v>
+      </c>
+      <c r="D57" s="11" t="s">
         <v>410</v>
-      </c>
-      <c r="C57" t="s">
-        <v>720</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12492,13 +12378,13 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
+        <v>411</v>
+      </c>
+      <c r="C58" t="s">
+        <v>719</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>412</v>
-      </c>
-      <c r="C58" t="s">
-        <v>720</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12506,13 +12392,13 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
+        <v>413</v>
+      </c>
+      <c r="C59" t="s">
+        <v>719</v>
+      </c>
+      <c r="D59" s="11" t="s">
         <v>414</v>
-      </c>
-      <c r="C59" t="s">
-        <v>720</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12520,13 +12406,13 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
+        <v>415</v>
+      </c>
+      <c r="C60" t="s">
+        <v>719</v>
+      </c>
+      <c r="D60" s="11" t="s">
         <v>416</v>
-      </c>
-      <c r="C60" t="s">
-        <v>720</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12534,13 +12420,13 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C61" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12548,13 +12434,13 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C62" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12562,13 +12448,13 @@
         <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C63" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12576,13 +12462,13 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
+        <v>468</v>
+      </c>
+      <c r="C64" t="s">
+        <v>719</v>
+      </c>
+      <c r="D64" s="11" t="s">
         <v>469</v>
-      </c>
-      <c r="C64" t="s">
-        <v>720</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12590,13 +12476,13 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C65" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12607,10 +12493,10 @@
         <v>66</v>
       </c>
       <c r="C66" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12618,13 +12504,13 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C67" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12635,10 +12521,10 @@
         <v>70</v>
       </c>
       <c r="C68" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12646,13 +12532,13 @@
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C69" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12660,923 +12546,923 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C70" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D70" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
+        <v>481</v>
+      </c>
+      <c r="B71" t="s">
         <v>482</v>
       </c>
-      <c r="B71" t="s">
-        <v>483</v>
-      </c>
       <c r="C71" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="B72" t="s">
         <v>484</v>
       </c>
-      <c r="B72" t="s">
-        <v>485</v>
-      </c>
       <c r="C72" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B73" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C73" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="B74" t="s">
         <v>487</v>
       </c>
-      <c r="B74" t="s">
-        <v>488</v>
-      </c>
       <c r="C74" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C75" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="13" t="s">
+        <v>489</v>
+      </c>
+      <c r="B76" t="s">
         <v>490</v>
       </c>
-      <c r="B76" t="s">
-        <v>491</v>
-      </c>
       <c r="C76" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
+        <v>491</v>
+      </c>
+      <c r="B77" t="s">
         <v>492</v>
       </c>
-      <c r="B77" t="s">
-        <v>493</v>
-      </c>
       <c r="C77" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C78" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B79" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C79" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B80" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C80" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B81" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C81" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B82" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C82" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
+        <v>498</v>
+      </c>
+      <c r="B83" t="s">
         <v>499</v>
       </c>
-      <c r="B83" t="s">
-        <v>500</v>
-      </c>
       <c r="C83" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="B84" t="s">
         <v>501</v>
       </c>
-      <c r="B84" t="s">
-        <v>502</v>
-      </c>
       <c r="C84" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="B86" t="s">
         <v>504</v>
       </c>
-      <c r="B86" t="s">
-        <v>505</v>
-      </c>
       <c r="C86" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="B87" t="s">
         <v>506</v>
       </c>
-      <c r="B87" t="s">
-        <v>507</v>
-      </c>
       <c r="C87" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="13" t="s">
+        <v>507</v>
+      </c>
+      <c r="B88" t="s">
         <v>508</v>
       </c>
-      <c r="B88" t="s">
-        <v>509</v>
-      </c>
       <c r="C88" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
+        <v>509</v>
+      </c>
+      <c r="B89" t="s">
         <v>510</v>
       </c>
-      <c r="B89" t="s">
-        <v>511</v>
-      </c>
       <c r="C89" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="B90" t="s">
         <v>512</v>
       </c>
-      <c r="B90" t="s">
-        <v>513</v>
-      </c>
       <c r="C90" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B91" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="C91" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B92" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C92" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="13" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B93" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C93" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B94" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C94" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B95" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C95" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B96" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C96" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B97" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C97" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="B98" t="s">
         <v>473</v>
       </c>
-      <c r="B98" t="s">
-        <v>474</v>
-      </c>
       <c r="C98" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B99" t="s">
         <v>80</v>
       </c>
       <c r="C99" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B100" t="s">
         <v>90</v>
       </c>
       <c r="C100" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
+        <v>474</v>
+      </c>
+      <c r="B101" t="s">
         <v>475</v>
       </c>
-      <c r="B101" t="s">
-        <v>476</v>
-      </c>
       <c r="C101" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
+        <v>476</v>
+      </c>
+      <c r="B102" t="s">
         <v>477</v>
       </c>
-      <c r="B102" t="s">
-        <v>478</v>
-      </c>
       <c r="C102" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
+        <v>478</v>
+      </c>
+      <c r="B103" t="s">
         <v>479</v>
       </c>
-      <c r="B103" t="s">
-        <v>480</v>
-      </c>
       <c r="C103" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="13" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B104" t="s">
         <v>19</v>
       </c>
       <c r="C104" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B105" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C105" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="13" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C106" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B107" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C107" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B108" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C108" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D108" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B109" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C109" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D109" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="13" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B110" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C110" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="13" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B111" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D111" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B112" t="s">
         <v>39</v>
       </c>
       <c r="C112" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D112" s="11" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B113" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C113" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D113" s="11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B114" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C114" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D114" s="11" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="13" t="s">
+        <v>580</v>
+      </c>
+      <c r="B115" t="s">
         <v>581</v>
       </c>
-      <c r="B115" t="s">
-        <v>582</v>
-      </c>
       <c r="C115" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D115" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B116" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C116" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D116" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B117" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C117" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D117" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B118" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C118" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D118" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="13" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B119" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C119" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D119" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B120" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C120" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D120" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B121" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C121" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D121" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="13" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B122" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C122" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D122" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B123" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="C123" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D123" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B124" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C124" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D124" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B125" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C125" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D125" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B126" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C126" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D126" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B127" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="C127" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D127" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B128" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C128" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D128" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B129" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C129" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D129" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B130" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="C130" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D130" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="13" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B131" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C131" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D131" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="13" t="s">
+        <v>639</v>
+      </c>
+      <c r="B132" t="s">
         <v>640</v>
       </c>
-      <c r="B132" t="s">
-        <v>641</v>
-      </c>
       <c r="C132" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D132" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="13" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B133" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C133" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D133" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="13" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B134" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C134" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D134" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="13" t="s">
+        <v>692</v>
+      </c>
+      <c r="B135" t="s">
+        <v>694</v>
+      </c>
+      <c r="C135" t="s">
+        <v>719</v>
+      </c>
+      <c r="D135" t="s">
         <v>693</v>
-      </c>
-      <c r="B135" t="s">
-        <v>695</v>
-      </c>
-      <c r="C135" t="s">
-        <v>720</v>
-      </c>
-      <c r="D135" t="s">
-        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -13627,7 +13513,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13712,7 +13598,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13856,7 +13742,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B22">
         <v>323</v>
@@ -13864,7 +13750,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B23">
         <v>324</v>
@@ -13872,7 +13758,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B24">
         <v>325</v>
@@ -13880,7 +13766,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B25">
         <v>326</v>
@@ -13896,7 +13782,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -13904,7 +13790,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13912,7 +13798,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13920,7 +13806,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13928,7 +13814,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13954,50 +13840,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>711</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
+        <v>714</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>715</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>717</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>718</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>720</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>721</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56401978-88B9-47A4-B572-C9EEF46C63CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1977848B-A203-4DB4-B88D-D1732F9C5A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2307,16 +2307,16 @@
     <t>Avg. Weekly Focus Time per Engineer; Avg. Number of Days with Sufficient Focus Time; Focus Time and Interruption Metrics; Uninterrupted Focus Time</t>
   </si>
   <si>
-    <t>telemetry</t>
-  </si>
-  <si>
-    <t>survey</t>
-  </si>
-  <si>
     <t>Data Collection Type</t>
   </si>
   <si>
     <t>Aims to capture all active human developer time spent on a particular diff, split by the different roles involved. This information is made available in a privacy-aware manner. Active human work on a computer tends to be highly sequential, even if such individual sequences can be extremely short.</t>
+  </si>
+  <si>
+    <t>qualitative</t>
+  </si>
+  <si>
+    <t>quantitative</t>
   </si>
 </sst>
 </file>
@@ -2393,7 +2393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2446,12 +2446,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2464,6 +2458,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2509,16 +2513,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2539,21 +2533,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2639,21 +2633,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3189,31 +3183,31 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="20" t="s">
-        <v>737</v>
-      </c>
-      <c r="H1" s="20" t="s">
+      <c r="G1" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="1" t="s">
         <v>525</v>
       </c>
       <c r="P1" s="18" t="s">
@@ -3249,7 +3243,7 @@
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3314,7 +3308,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3379,7 +3373,7 @@
         <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>524</v>
@@ -3444,7 +3438,7 @@
         <v>27</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>15</v>
@@ -3509,7 +3503,7 @@
         <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>524</v>
@@ -3574,7 +3568,7 @@
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>10</v>
@@ -3639,7 +3633,7 @@
         <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>36</v>
@@ -3704,7 +3698,7 @@
         <v>40</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>36</v>
@@ -3769,7 +3763,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>36</v>
@@ -3834,7 +3828,7 @@
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>15</v>
@@ -3899,7 +3893,7 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>36</v>
@@ -3964,7 +3958,7 @@
         <v>51</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>52</v>
@@ -4029,7 +4023,7 @@
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>36</v>
@@ -4094,7 +4088,7 @@
         <v>56</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>57</v>
@@ -4159,7 +4153,7 @@
         <v>60</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>524</v>
@@ -4224,7 +4218,7 @@
         <v>64</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>15</v>
@@ -4289,7 +4283,7 @@
         <v>67</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>52</v>
@@ -4354,7 +4348,7 @@
         <v>71</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>10</v>
@@ -4419,7 +4413,7 @@
         <v>74</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>75</v>
@@ -4484,7 +4478,7 @@
         <v>77</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>75</v>
@@ -4549,7 +4543,7 @@
         <v>78</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -4614,7 +4608,7 @@
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>524</v>
@@ -4679,7 +4673,7 @@
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>36</v>
@@ -4744,7 +4738,7 @@
         <v>85</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>75</v>
@@ -4809,7 +4803,7 @@
         <v>87</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>36</v>
@@ -4874,7 +4868,7 @@
         <v>91</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>75</v>
@@ -4939,7 +4933,7 @@
         <v>93</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>15</v>
@@ -5004,7 +4998,7 @@
         <v>96</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>21</v>
@@ -5069,7 +5063,7 @@
         <v>98</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>524</v>
@@ -5134,7 +5128,7 @@
         <v>101</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>524</v>
@@ -5199,7 +5193,7 @@
         <v>104</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>10</v>
@@ -5261,10 +5255,10 @@
         <v>463</v>
       </c>
       <c r="F33" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="G33" s="3" t="s">
         <v>738</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>735</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>15</v>
@@ -5329,7 +5323,7 @@
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>15</v>
@@ -5394,7 +5388,7 @@
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>524</v>
@@ -5459,7 +5453,7 @@
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>524</v>
@@ -5524,7 +5518,7 @@
         <v>113</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>
@@ -5589,7 +5583,7 @@
         <v>115</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>524</v>
@@ -5654,7 +5648,7 @@
         <v>119</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>21</v>
@@ -5719,7 +5713,7 @@
         <v>122</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>21</v>
@@ -5784,7 +5778,7 @@
         <v>125</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>52</v>
@@ -5849,7 +5843,7 @@
         <v>128</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>524</v>
@@ -5914,7 +5908,7 @@
         <v>130</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>15</v>
@@ -5979,7 +5973,7 @@
         <v>132</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6044,7 +6038,7 @@
         <v>134</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>524</v>
@@ -6109,7 +6103,7 @@
         <v>137</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>10</v>
@@ -6174,7 +6168,7 @@
         <v>139</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>524</v>
@@ -6239,7 +6233,7 @@
         <v>141</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>524</v>
@@ -6304,7 +6298,7 @@
         <v>145</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>15</v>
@@ -6369,7 +6363,7 @@
         <v>148</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>36</v>
@@ -6434,7 +6428,7 @@
         <v>150</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>21</v>
@@ -6499,7 +6493,7 @@
         <v>152</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>21</v>
@@ -6564,7 +6558,7 @@
         <v>154</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>52</v>
@@ -6629,7 +6623,7 @@
         <v>155</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>52</v>
@@ -6694,7 +6688,7 @@
         <v>157</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>75</v>
@@ -6759,7 +6753,7 @@
         <v>159</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>36</v>
@@ -6824,7 +6818,7 @@
         <v>161</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>15</v>
@@ -6889,7 +6883,7 @@
         <v>163</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -6954,7 +6948,7 @@
         <v>166</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>21</v>
@@ -7019,7 +7013,7 @@
         <v>169</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7084,7 +7078,7 @@
         <v>171</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>36</v>
@@ -7149,7 +7143,7 @@
         <v>173</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>10</v>
@@ -7214,7 +7208,7 @@
         <v>175</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>524</v>
@@ -7279,7 +7273,7 @@
         <v>178</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>524</v>
@@ -7344,7 +7338,7 @@
         <v>180</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>75</v>
@@ -7409,7 +7403,7 @@
         <v>182</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>75</v>
@@ -7474,7 +7468,7 @@
         <v>184</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>36</v>
@@ -7539,7 +7533,7 @@
         <v>186</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>10</v>
@@ -7604,7 +7598,7 @@
         <v>188</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>524</v>
@@ -7669,7 +7663,7 @@
         <v>189</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -7734,7 +7728,7 @@
         <v>191</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>15</v>
@@ -7799,7 +7793,7 @@
         <v>193</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>15</v>
@@ -7864,7 +7858,7 @@
         <v>195</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>36</v>
@@ -7929,7 +7923,7 @@
         <v>197</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>36</v>
@@ -7994,7 +7988,7 @@
         <v>199</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>36</v>
@@ -8059,7 +8053,7 @@
         <v>201</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8124,7 +8118,7 @@
         <v>203</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>52</v>
@@ -8189,7 +8183,7 @@
         <v>205</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>10</v>
@@ -8254,7 +8248,7 @@
         <v>207</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>75</v>
@@ -8319,7 +8313,7 @@
         <v>210</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>21</v>
@@ -8384,7 +8378,7 @@
         <v>212</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>21</v>
@@ -8449,7 +8443,7 @@
         <v>214</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>10</v>
@@ -8514,7 +8508,7 @@
         <v>216</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>10</v>
@@ -8579,7 +8573,7 @@
         <v>218</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>10</v>
@@ -8644,7 +8638,7 @@
         <v>221</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8709,7 +8703,7 @@
         <v>224</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>524</v>
@@ -8774,7 +8768,7 @@
         <v>226</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8839,7 +8833,7 @@
         <v>228</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -8904,7 +8898,7 @@
         <v>230</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>15</v>
@@ -8969,7 +8963,7 @@
         <v>232</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>21</v>
@@ -9034,7 +9028,7 @@
         <v>234</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>524</v>
@@ -9099,7 +9093,7 @@
         <v>237</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>57</v>
@@ -9164,7 +9158,7 @@
         <v>239</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>52</v>
@@ -9229,7 +9223,7 @@
         <v>241</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>36</v>
@@ -9294,7 +9288,7 @@
         <v>243</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>36</v>
@@ -9359,7 +9353,7 @@
         <v>245</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>21</v>
@@ -9424,7 +9418,7 @@
         <v>248</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9489,7 +9483,7 @@
         <v>250</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>15</v>
@@ -9554,7 +9548,7 @@
         <v>252</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>15</v>
@@ -9619,7 +9613,7 @@
         <v>254</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>15</v>
@@ -9684,7 +9678,7 @@
         <v>257</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>524</v>
@@ -9749,7 +9743,7 @@
         <v>260</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>57</v>
@@ -9814,7 +9808,7 @@
         <v>263</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>57</v>
@@ -9879,7 +9873,7 @@
         <v>265</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>57</v>
@@ -9944,7 +9938,7 @@
         <v>647</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>57</v>
@@ -10009,7 +10003,7 @@
         <v>267</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>524</v>
@@ -10074,7 +10068,7 @@
         <v>517</v>
       </c>
       <c r="G107" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H107" t="s">
         <v>36</v>
@@ -10139,7 +10133,7 @@
         <v>519</v>
       </c>
       <c r="G108" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H108" t="s">
         <v>524</v>
@@ -10204,7 +10198,7 @@
         <v>520</v>
       </c>
       <c r="G109" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H109" t="s">
         <v>57</v>
@@ -10269,7 +10263,7 @@
         <v>521</v>
       </c>
       <c r="G110" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H110" t="s">
         <v>524</v>
@@ -10334,7 +10328,7 @@
         <v>516</v>
       </c>
       <c r="G111" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H111" t="s">
         <v>10</v>
@@ -10399,7 +10393,7 @@
         <v>570</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>21</v>
@@ -10464,7 +10458,7 @@
         <v>611</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>15</v>
@@ -10529,7 +10523,7 @@
         <v>616</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>57</v>
@@ -10594,7 +10588,7 @@
         <v>619</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>57</v>
@@ -10659,7 +10653,7 @@
         <v>626</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>57</v>
@@ -10724,7 +10718,7 @@
         <v>631</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10789,7 +10783,7 @@
         <v>632</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H118" t="s">
         <v>10</v>
@@ -10854,7 +10848,7 @@
         <v>636</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H119" t="s">
         <v>10</v>
@@ -10919,7 +10913,7 @@
         <v>638</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -10984,7 +10978,7 @@
         <v>644</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>10</v>
@@ -11049,7 +11043,7 @@
         <v>655</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>21</v>
@@ -11114,7 +11108,7 @@
         <v>670</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>524</v>
@@ -11179,7 +11173,7 @@
         <v>682</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>15</v>
@@ -11244,7 +11238,7 @@
         <v>698</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>524</v>
@@ -11309,7 +11303,7 @@
         <v>701</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>524</v>
@@ -11374,7 +11368,7 @@
         <v>706</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H127" s="3" t="s">
         <v>524</v>
@@ -11522,8 +11516,8 @@
     <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F48">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F73">
     <cfRule type="duplicateValues" dxfId="17" priority="7"/>
@@ -11546,20 +11540,20 @@
     <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="9" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
     <cfRule type="duplicateValues" dxfId="7" priority="12"/>
     <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J69">
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J106">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD9DB2D-DC22-420E-B101-F5877A0D68F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092770D1-0B9B-474B-9130-819E1EE4F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2378,7 +2378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2428,12 +2428,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2441,21 +2435,21 @@
   <dxfs count="39">
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2501,16 +2495,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2531,21 +2515,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2631,21 +2615,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2826,6 +2810,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3131,7 +3125,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S124"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3143,8 +3136,7 @@
     <col min="6" max="6" width="36.5703125" style="3" customWidth="1"/>
     <col min="7" max="7" width="31.7109375" style="3" customWidth="1"/>
     <col min="8" max="9" width="17.85546875" style="3" customWidth="1"/>
-    <col min="10" max="12" width="28.42578125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="28.42578125" style="20" customWidth="1"/>
+    <col min="10" max="13" width="28.42578125" style="3" customWidth="1"/>
     <col min="14" max="15" width="9.140625" style="3"/>
     <col min="16" max="16" width="18.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="30.7109375" style="14" customWidth="1"/>
@@ -3190,7 +3182,7 @@
       <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="1" t="s">
         <v>515</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -3212,7 +3204,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2</v>
       </c>
@@ -3277,7 +3269,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -3342,7 +3334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>9</v>
       </c>
@@ -3407,7 +3399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>10</v>
       </c>
@@ -3472,7 +3464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>11</v>
       </c>
@@ -3537,7 +3529,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>12</v>
       </c>
@@ -3602,7 +3594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>13</v>
       </c>
@@ -3667,7 +3659,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>14</v>
       </c>
@@ -3732,7 +3724,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>15</v>
       </c>
@@ -3797,7 +3789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>16</v>
       </c>
@@ -3862,7 +3854,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>17</v>
       </c>
@@ -3927,7 +3919,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>18</v>
       </c>
@@ -3992,7 +3984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>19</v>
       </c>
@@ -4057,7 +4049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>20</v>
       </c>
@@ -4122,7 +4114,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>22</v>
       </c>
@@ -4187,7 +4179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>23</v>
       </c>
@@ -4252,7 +4244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>24</v>
       </c>
@@ -4317,7 +4309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>25</v>
       </c>
@@ -4382,7 +4374,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>26</v>
       </c>
@@ -4447,7 +4439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>27</v>
       </c>
@@ -4512,7 +4504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>29</v>
       </c>
@@ -4577,7 +4569,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>30</v>
       </c>
@@ -4642,7 +4634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>31</v>
       </c>
@@ -4707,7 +4699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>32</v>
       </c>
@@ -4772,7 +4764,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>33</v>
       </c>
@@ -4837,7 +4829,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>34</v>
       </c>
@@ -4902,7 +4894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>35</v>
       </c>
@@ -4967,7 +4959,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" ht="180" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>36</v>
       </c>
@@ -5032,7 +5024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="255" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>37</v>
       </c>
@@ -5097,7 +5089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>38</v>
       </c>
@@ -5162,7 +5154,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>39</v>
       </c>
@@ -5227,7 +5219,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>40</v>
       </c>
@@ -5292,7 +5284,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>41</v>
       </c>
@@ -5357,7 +5349,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>42</v>
       </c>
@@ -5422,7 +5414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>43</v>
       </c>
@@ -5487,7 +5479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>44</v>
       </c>
@@ -5552,7 +5544,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>45</v>
       </c>
@@ -5617,7 +5609,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>46</v>
       </c>
@@ -5722,7 +5714,7 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="M40" s="20">
+      <c r="M40" s="3">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
@@ -5747,7 +5739,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="41" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>51</v>
       </c>
@@ -5812,7 +5804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>54</v>
       </c>
@@ -5877,7 +5869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>56</v>
       </c>
@@ -5942,7 +5934,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>57</v>
       </c>
@@ -6007,7 +5999,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="360" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="360" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>58</v>
       </c>
@@ -6112,7 +6104,7 @@
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="M46" s="20">
+      <c r="M46" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -6137,7 +6129,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>62</v>
       </c>
@@ -6202,7 +6194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>63</v>
       </c>
@@ -6267,7 +6259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>64</v>
       </c>
@@ -6332,7 +6324,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>65</v>
       </c>
@@ -6397,7 +6389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>66</v>
       </c>
@@ -6462,7 +6454,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>67</v>
       </c>
@@ -6527,7 +6519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>69</v>
       </c>
@@ -6592,7 +6584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>70</v>
       </c>
@@ -6657,7 +6649,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>71</v>
       </c>
@@ -6722,7 +6714,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>72</v>
       </c>
@@ -6787,7 +6779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>73</v>
       </c>
@@ -6852,7 +6844,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>74</v>
       </c>
@@ -6917,7 +6909,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>75</v>
       </c>
@@ -6982,7 +6974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>76</v>
       </c>
@@ -7047,7 +7039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>78</v>
       </c>
@@ -7112,7 +7104,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>79</v>
       </c>
@@ -7177,7 +7169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="165" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>80</v>
       </c>
@@ -7242,7 +7234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>81</v>
       </c>
@@ -7307,7 +7299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>82</v>
       </c>
@@ -7372,7 +7364,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>83</v>
       </c>
@@ -7437,7 +7429,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>84</v>
       </c>
@@ -7502,7 +7494,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>85</v>
       </c>
@@ -7567,7 +7559,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>87</v>
       </c>
@@ -7632,7 +7624,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>88</v>
       </c>
@@ -7697,7 +7689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>89</v>
       </c>
@@ -7762,7 +7754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>90</v>
       </c>
@@ -7827,7 +7819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>91</v>
       </c>
@@ -7892,7 +7884,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>92</v>
       </c>
@@ -7957,7 +7949,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>93</v>
       </c>
@@ -8022,7 +8014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>94</v>
       </c>
@@ -8087,7 +8079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>95</v>
       </c>
@@ -8152,7 +8144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>97</v>
       </c>
@@ -8217,7 +8209,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>98</v>
       </c>
@@ -8282,7 +8274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>99</v>
       </c>
@@ -8347,7 +8339,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>100</v>
       </c>
@@ -8412,7 +8404,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>102</v>
       </c>
@@ -8477,7 +8469,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>104</v>
       </c>
@@ -8542,7 +8534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>105</v>
       </c>
@@ -8607,7 +8599,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="180" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>107</v>
       </c>
@@ -8672,7 +8664,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>108</v>
       </c>
@@ -8737,7 +8729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>109</v>
       </c>
@@ -8802,7 +8794,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>112</v>
       </c>
@@ -8867,7 +8859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>114</v>
       </c>
@@ -8932,7 +8924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>115</v>
       </c>
@@ -8997,7 +8989,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>116</v>
       </c>
@@ -9062,7 +9054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>117</v>
       </c>
@@ -9127,7 +9119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>118</v>
       </c>
@@ -9192,7 +9184,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>119</v>
       </c>
@@ -9257,7 +9249,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>120</v>
       </c>
@@ -9322,7 +9314,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>121</v>
       </c>
@@ -9387,7 +9379,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>122</v>
       </c>
@@ -9452,7 +9444,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>124</v>
       </c>
@@ -9517,7 +9509,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>126</v>
       </c>
@@ -9582,7 +9574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>127</v>
       </c>
@@ -9647,7 +9639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>128</v>
       </c>
@@ -9712,7 +9704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>129</v>
       </c>
@@ -9777,7 +9769,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" ht="135" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>130</v>
       </c>
@@ -9842,7 +9834,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>134</v>
       </c>
@@ -9907,7 +9899,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>135</v>
       </c>
@@ -9972,7 +9964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>136</v>
       </c>
@@ -10037,7 +10029,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>137</v>
       </c>
@@ -10102,7 +10094,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>138</v>
       </c>
@@ -10167,7 +10159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="109" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>139</v>
       </c>
@@ -10232,7 +10224,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>140</v>
       </c>
@@ -10297,7 +10289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>141</v>
       </c>
@@ -10362,7 +10354,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>142</v>
       </c>
@@ -10427,7 +10419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="113" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>143</v>
       </c>
@@ -10492,7 +10484,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>144</v>
       </c>
@@ -10557,7 +10549,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>145</v>
       </c>
@@ -10622,7 +10614,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>146</v>
       </c>
@@ -10687,7 +10679,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="117" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>147</v>
       </c>
@@ -10752,7 +10744,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="118" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>148</v>
       </c>
@@ -10817,7 +10809,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="119" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>149</v>
       </c>
@@ -10882,7 +10874,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="120" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>150</v>
       </c>
@@ -10947,7 +10939,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>151</v>
       </c>
@@ -11012,7 +11004,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>152</v>
       </c>
@@ -11077,7 +11069,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>153</v>
       </c>
@@ -11142,7 +11134,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="124" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
         <v>154</v>
       </c>
@@ -11208,110 +11200,104 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M124" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="Focus Work"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="B1:B108">
+    <cfRule type="duplicateValues" dxfId="38" priority="45"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="38" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="37" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="36" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="35" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="33" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="duplicateValues" dxfId="32" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:B39">
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="30" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B44">
-    <cfRule type="duplicateValues" dxfId="29" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B45">
-    <cfRule type="duplicateValues" dxfId="28" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B46">
-    <cfRule type="duplicateValues" dxfId="27" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71">
-    <cfRule type="duplicateValues" dxfId="26" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B93">
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B94">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B109:B113 B116:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F46">
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
     <cfRule type="duplicateValues" dxfId="19" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="18" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F78">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F84">
-    <cfRule type="duplicateValues" dxfId="16" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F97">
-    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J33">
-    <cfRule type="duplicateValues" dxfId="12" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J45">
-    <cfRule type="duplicateValues" dxfId="10" priority="16"/>
     <cfRule type="duplicateValues" dxfId="9" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J61">
-    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66">
-    <cfRule type="duplicateValues" dxfId="6" priority="10"/>
     <cfRule type="duplicateValues" dxfId="5" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J103">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
     <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B108">
-    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -13588,8 +13574,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092770D1-0B9B-474B-9130-819E1EE4F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8CB8A3-5C8B-4EE7-BE73-5BB2CFCB5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="742">
   <si>
     <t>id</t>
   </si>
@@ -491,9 +491,6 @@
   </si>
   <si>
     <t>Initiative Progress and ROI</t>
-  </si>
-  <si>
-    <t>DXI Framework</t>
   </si>
   <si>
     <t>Measures the financial impact and advancement of specific developer experience (DevEx) improvement projects, linking technical efforts to business outcomes. It evaluates whether investments in tools, processes, or workflows deliver measurable returns.</t>
@@ -1470,15 +1467,6 @@
     <t>501o</t>
   </si>
   <si>
-    <t>509; 7; 14; 31; 49; 52; 57; 96;108; 192; 234; 32; 131</t>
-  </si>
-  <si>
-    <t>509; 505</t>
-  </si>
-  <si>
-    <t>509; 9</t>
-  </si>
-  <si>
     <t>504; 214</t>
   </si>
   <si>
@@ -1671,9 +1659,6 @@
     <t>501c; 501l; 501b; 501e; 501g; 501d; 5a</t>
   </si>
   <si>
-    <t>509; 5; 160; 501; 115; 146; 183</t>
-  </si>
-  <si>
     <t>501b; 5a</t>
   </si>
   <si>
@@ -1683,9 +1668,6 @@
     <t>202a; 131i; 131g</t>
   </si>
   <si>
-    <t>509; 131; 202; 146</t>
-  </si>
-  <si>
     <t>501b; 501d</t>
   </si>
   <si>
@@ -1710,9 +1692,6 @@
     <t>508; 506; 9; 50; 160; 131; 202; 182; 146</t>
   </si>
   <si>
-    <t>509; 505; 506; 508; 9; 160; 202; 146</t>
-  </si>
-  <si>
     <t>20a</t>
   </si>
   <si>
@@ -1740,9 +1719,6 @@
     <t>9; 57; 183</t>
   </si>
   <si>
-    <t>505; 506; 509; 508; 9; 96; 160; 501; 131; 202; 146; 182</t>
-  </si>
-  <si>
     <t>232a</t>
   </si>
   <si>
@@ -2124,24 +2100,15 @@
     <t>Number of tasks that developers assign to their AI agents.</t>
   </si>
   <si>
-    <t>509; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512</t>
-  </si>
-  <si>
     <t>9; 36; 52; 62; 240; 243; 244; 160; 501; 183; 512</t>
   </si>
   <si>
-    <t>509; 501; 512</t>
-  </si>
-  <si>
     <t>503; 9; 17; 5; 115; 501; 115; 183; 182; 512</t>
   </si>
   <si>
     <t>AI change/trust confidence</t>
   </si>
   <si>
-    <t>509; 505; 506; 508; 9; 160; 501; 131; 202; 183; 146; 512</t>
-  </si>
-  <si>
     <t>% capacity worked per AI tool; Agent hourly rate</t>
   </si>
   <si>
@@ -2308,6 +2275,57 @@
   </si>
   <si>
     <t>50</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>DX Core 4 Framework</t>
+  </si>
+  <si>
+    <t>https://getdx.com/research/measuring-developer-productivity-with-the-dx-core-4/</t>
+  </si>
+  <si>
+    <t>514; 505; 506; 508; 9; 160; 501; 131; 202; 183; 146; 512</t>
+  </si>
+  <si>
+    <t>505; 506; 514; 508; 9; 96; 160; 501; 131; 202; 146; 182</t>
+  </si>
+  <si>
+    <t>514; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512</t>
+  </si>
+  <si>
+    <t>514; 7; 14; 31; 49; 52; 57; 96;108; 192; 234; 32; 131</t>
+  </si>
+  <si>
+    <t>514; 5; 160; 501; 115; 146; 183</t>
+  </si>
+  <si>
+    <t>514; 505</t>
+  </si>
+  <si>
+    <t>514; 505; 506; 508; 9; 160; 202; 146</t>
+  </si>
+  <si>
+    <t>514; 9</t>
+  </si>
+  <si>
+    <t>514; 501; 512</t>
+  </si>
+  <si>
+    <t>514; 131; 202; 146</t>
+  </si>
+  <si>
+    <t>DXI Metric</t>
+  </si>
+  <si>
+    <t>Developer Experience Index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proprietary composite score that aims to predict engineering effectiveness and can be linked to financial impact. It is meant to capture whether developers have the right conditions to work effectively. Built by combining self-reports on 14 dimensions, including deep work, local iteration speed, release process, and confidence in making changes. </t>
+  </si>
+  <si>
+    <t>514; 509</t>
   </si>
 </sst>
 </file>
@@ -3125,7 +3143,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S124"/>
+  <dimension ref="A1:S125"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3156,16 +3174,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>261</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>262</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3183,25 +3201,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3215,16 +3233,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3257,16 +3275,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R2" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3289,7 +3307,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3322,13 +3340,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R3" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>9</v>
@@ -3345,16 +3363,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3387,13 +3405,13 @@
         <v>3</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R4" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>9</v>
@@ -3407,22 +3425,22 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3452,13 +3470,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R5" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>9</v>
@@ -3484,7 +3502,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3517,13 +3535,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R6" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>9</v>
@@ -3540,16 +3558,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>679</v>
+        <v>728</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -3585,10 +3603,10 @@
         <v>128</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R7" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>9</v>
@@ -3614,7 +3632,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -3647,13 +3665,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R8" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>9</v>
@@ -3670,7 +3688,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E9" s="15">
         <v>501</v>
@@ -3679,7 +3697,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -3712,13 +3730,13 @@
         <v>2</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R9" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>9</v>
@@ -3735,7 +3753,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E10" s="15">
         <v>501</v>
@@ -3744,7 +3762,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3777,13 +3795,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R10" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>9</v>
@@ -3800,16 +3818,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="14" t="s">
+        <v>440</v>
+      </c>
+      <c r="E11" s="15" t="s">
         <v>441</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>442</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -3842,13 +3860,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R11" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>9</v>
@@ -3865,16 +3883,16 @@
         <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>50</v>
@@ -3907,13 +3925,13 @@
         <v>8</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R12" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>9</v>
@@ -3927,10 +3945,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>664</v>
+        <v>656</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="E13" s="15">
         <v>131</v>
@@ -3939,7 +3957,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -3975,10 +3993,10 @@
         <v>128</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R13" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>9</v>
@@ -3992,19 +4010,19 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -4037,13 +4055,13 @@
         <v>26</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R14" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>9</v>
@@ -4057,22 +4075,22 @@
         <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>686</v>
+        <v>675</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4105,10 +4123,10 @@
         <v>128</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R15" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>9</v>
@@ -4125,16 +4143,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4167,13 +4185,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R16" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>9</v>
@@ -4187,19 +4205,19 @@
         <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>50</v>
@@ -4232,13 +4250,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R17" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>9</v>
@@ -4264,7 +4282,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4297,13 +4315,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R18" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>9</v>
@@ -4323,13 +4341,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>73</v>
@@ -4362,13 +4380,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R19" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>9</v>
@@ -4385,7 +4403,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E20" s="15">
         <v>131</v>
@@ -4394,7 +4412,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>73</v>
@@ -4427,13 +4445,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R20" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>9</v>
@@ -4447,19 +4465,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4495,10 +4513,10 @@
         <v>128</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R21" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>9</v>
@@ -4512,7 +4530,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>9</v>
@@ -4524,7 +4542,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>34</v>
@@ -4557,13 +4575,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R22" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>9</v>
@@ -4580,16 +4598,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>546</v>
+        <v>729</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>73</v>
@@ -4625,10 +4643,10 @@
         <v>128</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R23" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>9</v>
@@ -4642,19 +4660,19 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D24" s="14">
         <v>170</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>34</v>
@@ -4687,13 +4705,13 @@
         <v>4</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R24" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>9</v>
@@ -4710,7 +4728,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E25" s="15">
         <v>501</v>
@@ -4719,7 +4737,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>73</v>
@@ -4752,13 +4770,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R25" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>9</v>
@@ -4775,16 +4793,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4817,13 +4835,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R26" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>9</v>
@@ -4837,19 +4855,19 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -4882,13 +4900,13 @@
         <v>8</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R27" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>9</v>
@@ -4905,19 +4923,19 @@
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -4947,13 +4965,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R28" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>9</v>
@@ -4967,22 +4985,22 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>698</v>
+        <v>687</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>674</v>
+        <v>730</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
@@ -5015,10 +5033,10 @@
         <v>128</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R29" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>9</v>
@@ -5044,7 +5062,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5077,13 +5095,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R30" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>9</v>
@@ -5097,19 +5115,19 @@
         <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>663</v>
+        <v>655</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>456</v>
+        <v>731</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5145,10 +5163,10 @@
         <v>128</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R31" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>9</v>
@@ -5165,16 +5183,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5207,13 +5225,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R32" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>9</v>
@@ -5230,19 +5248,19 @@
         <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>523</v>
+        <v>732</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5275,10 +5293,10 @@
         <v>128</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R33" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>9</v>
@@ -5292,22 +5310,22 @@
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
@@ -5337,13 +5355,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R34" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>9</v>
@@ -5357,19 +5375,19 @@
         <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
@@ -5402,13 +5420,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R35" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>9</v>
@@ -5425,19 +5443,19 @@
         <v>9</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5467,13 +5485,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R36" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>9</v>
@@ -5487,19 +5505,19 @@
         <v>113</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5535,10 +5553,10 @@
         <v>128</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R37" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>9</v>
@@ -5558,13 +5576,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>457</v>
+        <v>733</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5597,13 +5615,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R38" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>9</v>
@@ -5623,13 +5641,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -5665,10 +5683,10 @@
         <v>128</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R39" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>9</v>
@@ -5682,22 +5700,22 @@
         <v>123</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5727,16 +5745,16 @@
         <v>13</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R40" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5759,7 +5777,7 @@
         <v>125</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5792,13 +5810,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R41" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>9</v>
@@ -5824,7 +5842,7 @@
         <v>127</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>15</v>
@@ -5857,13 +5875,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R42" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>9</v>
@@ -5877,22 +5895,22 @@
         <v>128</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>129</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -5922,13 +5940,13 @@
         <v>4</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R43" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>9</v>
@@ -5948,13 +5966,13 @@
         <v>9</v>
       </c>
       <c r="E44" s="15">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -5987,13 +6005,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R44" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>9</v>
@@ -6004,25 +6022,25 @@
         <v>58</v>
       </c>
       <c r="B45" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>556</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="E45" s="15" t="s">
-        <v>564</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6055,10 +6073,10 @@
         <v>128</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R45" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S45" s="14" t="s">
         <v>9</v>
@@ -6069,25 +6087,25 @@
         <v>59</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D46" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E46" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E46" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="G46" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I46" s="3">
         <f>VLOOKUP(H46,cardsort_group_IDs!A:B,2,0)</f>
@@ -6120,13 +6138,13 @@
         <v>128</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R46" t="s">
+        <v>713</v>
+      </c>
+      <c r="S46" s="14" t="s">
         <v>724</v>
-      </c>
-      <c r="S46" s="14" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6134,22 +6152,22 @@
         <v>62</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="D47" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>734</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>649</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>140</v>
-      </c>
       <c r="G47" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -6182,13 +6200,13 @@
         <v>11</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R47" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>9</v>
@@ -6199,22 +6217,22 @@
         <v>63</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>34</v>
@@ -6250,10 +6268,10 @@
         <v>128</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R48" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>9</v>
@@ -6264,7 +6282,7 @@
         <v>64</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>9</v>
@@ -6276,10 +6294,10 @@
         <v>9</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6312,13 +6330,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R49" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>9</v>
@@ -6329,22 +6347,22 @@
         <v>65</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>650</v>
-      </c>
-      <c r="E50" s="15" t="s">
-        <v>535</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="G50" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -6377,13 +6395,13 @@
         <v>16</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R50" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>9</v>
@@ -6394,10 +6412,10 @@
         <v>66</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>9</v>
@@ -6406,10 +6424,10 @@
         <v>235</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>50</v>
@@ -6442,13 +6460,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R51" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>9</v>
@@ -6459,22 +6477,22 @@
         <v>67</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>50</v>
@@ -6507,13 +6525,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R52" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>9</v>
@@ -6524,22 +6542,22 @@
         <v>69</v>
       </c>
       <c r="B53" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="E53" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C53" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>426</v>
-      </c>
-      <c r="E53" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>73</v>
@@ -6572,13 +6590,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R53" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>9</v>
@@ -6589,22 +6607,22 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>280</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="G54" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>34</v>
@@ -6637,13 +6655,13 @@
         <v>2</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R54" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>9</v>
@@ -6654,22 +6672,22 @@
         <v>71</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E55" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F55" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E55" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F55" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -6702,13 +6720,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R55" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>9</v>
@@ -6719,22 +6737,22 @@
         <v>72</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E56" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="G56" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>10</v>
@@ -6744,7 +6762,7 @@
         <v>201</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K56" s="3">
         <f>VLOOKUP(J56,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6767,13 +6785,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R56" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>9</v>
@@ -6784,22 +6802,22 @@
         <v>73</v>
       </c>
       <c r="B57" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E57" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="G57" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
@@ -6809,7 +6827,7 @@
         <v>202</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K57" s="3">
         <f>VLOOKUP(J57,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6832,13 +6850,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R57" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>9</v>
@@ -6849,7 +6867,7 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>9</v>
@@ -6861,10 +6879,10 @@
         <v>183</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -6897,13 +6915,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R58" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>9</v>
@@ -6914,22 +6932,22 @@
         <v>75</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E59" s="15">
         <v>183</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
@@ -6962,13 +6980,13 @@
         <v>2</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R59" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>9</v>
@@ -6979,22 +6997,22 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D60" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="G60" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7027,13 +7045,13 @@
         <v>2</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R60" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>9</v>
@@ -7044,25 +7062,25 @@
         <v>78</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="D61" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>546</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="D61" s="14" t="s">
-        <v>658</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>554</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>171</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I61" s="3">
         <f>VLOOKUP(H61,cardsort_group_IDs!A:B,2,0)</f>
@@ -7095,10 +7113,10 @@
         <v>128</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R61" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>9</v>
@@ -7109,22 +7127,22 @@
         <v>79</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="E62" s="15" t="s">
+        <v>736</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="E62" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="G62" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>73</v>
@@ -7160,10 +7178,10 @@
         <v>128</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R62" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>9</v>
@@ -7174,22 +7192,22 @@
         <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="15">
+        <v>514</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" s="15">
-        <v>509</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>73</v>
@@ -7222,13 +7240,13 @@
         <v>1</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R63" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S63" s="14" t="s">
         <v>9</v>
@@ -7239,22 +7257,22 @@
         <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E64" s="15">
         <v>202</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>34</v>
@@ -7287,13 +7305,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R64" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S64" s="14" t="s">
         <v>9</v>
@@ -7304,22 +7322,22 @@
         <v>82</v>
       </c>
       <c r="B65" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="15">
+        <v>514</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" s="15">
-        <v>509</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>179</v>
-      </c>
       <c r="G65" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>10</v>
@@ -7329,7 +7347,7 @@
         <v>201</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K65" s="3">
         <f>VLOOKUP(J65,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7352,13 +7370,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R65" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S65" s="14" t="s">
         <v>9</v>
@@ -7369,32 +7387,32 @@
         <v>83</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="E66" s="15" t="s">
+        <v>735</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>651</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>652</v>
-      </c>
-      <c r="E66" s="15" t="s">
-        <v>458</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>181</v>
-      </c>
       <c r="G66" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I66" s="3">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K66" s="3">
         <f>VLOOKUP(J66,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7420,10 +7438,10 @@
         <v>128</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R66" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S66" s="14" t="s">
         <v>9</v>
@@ -7440,16 +7458,16 @@
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E67" s="15">
         <v>501</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>21</v>
@@ -7482,13 +7500,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R67" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S67" s="14" t="s">
         <v>9</v>
@@ -7499,22 +7517,22 @@
         <v>85</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>454</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>455</v>
-      </c>
-      <c r="E68" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>184</v>
-      </c>
       <c r="G68" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>15</v>
@@ -7547,13 +7565,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R68" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S68" s="14" t="s">
         <v>9</v>
@@ -7564,22 +7582,22 @@
         <v>87</v>
       </c>
       <c r="B69" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E69" s="15" t="s">
-        <v>542</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="G69" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7612,13 +7630,13 @@
         <v>3</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R69" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S69" s="14" t="s">
         <v>9</v>
@@ -7629,22 +7647,22 @@
         <v>88</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="E70" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="F70" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>520</v>
-      </c>
-      <c r="E70" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>188</v>
-      </c>
       <c r="G70" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>34</v>
@@ -7677,13 +7695,13 @@
         <v>3</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q70" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R70" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S70" s="14" t="s">
         <v>9</v>
@@ -7694,22 +7712,22 @@
         <v>89</v>
       </c>
       <c r="B71" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="E71" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="F71" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D71" s="14" t="s">
-        <v>446</v>
-      </c>
-      <c r="E71" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>190</v>
-      </c>
       <c r="G71" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>34</v>
@@ -7742,13 +7760,13 @@
         <v>4</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R71" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S71" s="14" t="s">
         <v>9</v>
@@ -7759,22 +7777,22 @@
         <v>90</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="D72" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="E72" s="15" t="s">
-        <v>677</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="G72" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>34</v>
@@ -7810,10 +7828,10 @@
         <v>128</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R72" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S72" s="14" t="s">
         <v>9</v>
@@ -7824,22 +7842,22 @@
         <v>91</v>
       </c>
       <c r="B73" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D73" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="E73" s="15" t="s">
-        <v>539</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="G73" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -7872,13 +7890,13 @@
         <v>4</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R73" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S73" s="14" t="s">
         <v>9</v>
@@ -7889,22 +7907,22 @@
         <v>92</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E74" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E74" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>196</v>
-      </c>
       <c r="G74" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>50</v>
@@ -7937,13 +7955,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q74" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R74" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S74" s="14" t="s">
         <v>9</v>
@@ -7954,22 +7972,22 @@
         <v>93</v>
       </c>
       <c r="B75" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="15">
+        <v>514</v>
+      </c>
+      <c r="F75" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C75" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" s="15">
-        <v>509</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="G75" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8002,13 +8020,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R75" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>9</v>
@@ -8019,22 +8037,22 @@
         <v>94</v>
       </c>
       <c r="B76" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D76" s="14" t="s">
+        <v>447</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>448</v>
-      </c>
-      <c r="E76" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>200</v>
-      </c>
       <c r="G76" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>73</v>
@@ -8067,13 +8085,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R76" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S76" s="14" t="s">
         <v>9</v>
@@ -8084,22 +8102,22 @@
         <v>95</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="C77" s="4" t="s">
+      <c r="D77" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>561</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="D77" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>569</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>203</v>
-      </c>
       <c r="G77" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>21</v>
@@ -8109,7 +8127,7 @@
         <v>202</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K77" s="3">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8132,13 +8150,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R77" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S77" s="14" t="s">
         <v>9</v>
@@ -8149,7 +8167,7 @@
         <v>97</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>9</v>
@@ -8161,10 +8179,10 @@
         <v>508</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8197,13 +8215,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q78" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R78" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>9</v>
@@ -8214,10 +8232,10 @@
         <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D79" s="12">
         <v>209</v>
@@ -8226,10 +8244,10 @@
         <v>506</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>10</v>
@@ -8239,7 +8257,7 @@
         <v>201</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K79" s="3">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8262,13 +8280,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R79" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S79" s="14" t="s">
         <v>9</v>
@@ -8279,7 +8297,7 @@
         <v>99</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>9</v>
@@ -8291,10 +8309,10 @@
         <v>508</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>10</v>
@@ -8327,13 +8345,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R80" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S80" s="14" t="s">
         <v>9</v>
@@ -8344,22 +8362,22 @@
         <v>100</v>
       </c>
       <c r="B81" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="15">
+        <v>514</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E81" s="15">
-        <v>509</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>211</v>
-      </c>
       <c r="G81" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>10</v>
@@ -8392,13 +8410,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R81" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S81" s="14" t="s">
         <v>9</v>
@@ -8409,22 +8427,22 @@
         <v>102</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E82" s="15">
         <v>501</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8457,13 +8475,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R82" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S82" s="14" t="s">
         <v>9</v>
@@ -8474,25 +8492,25 @@
         <v>104</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C83" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C83" s="4" t="s">
+      <c r="D83" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="D83" s="14" t="s">
-        <v>432</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>217</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I83" s="3">
         <f>VLOOKUP(H83,cardsort_group_IDs!A:B,2,0)</f>
@@ -8522,13 +8540,13 @@
         <v>2</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R83" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S83" s="14" t="s">
         <v>9</v>
@@ -8539,22 +8557,22 @@
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>534</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>540</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>541</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>219</v>
-      </c>
       <c r="G84" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>21</v>
@@ -8587,13 +8605,13 @@
         <v>4</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q84" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R84" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S84" s="14" t="s">
         <v>9</v>
@@ -8604,22 +8622,22 @@
         <v>107</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>519</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>524</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>525</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="G85" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8652,13 +8670,13 @@
         <v>7</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q85" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R85" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S85" s="14" t="s">
         <v>9</v>
@@ -8669,22 +8687,22 @@
         <v>108</v>
       </c>
       <c r="B86" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D86" s="14" t="s">
+        <v>540</v>
+      </c>
+      <c r="E86" s="15" t="s">
+        <v>541</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>548</v>
-      </c>
-      <c r="E86" s="15" t="s">
-        <v>549</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="G86" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8717,13 +8735,13 @@
         <v>8</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q86" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R86" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S86" s="14" t="s">
         <v>9</v>
@@ -8734,22 +8752,22 @@
         <v>109</v>
       </c>
       <c r="B87" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="D87" s="15" t="s">
+        <v>551</v>
+      </c>
+      <c r="E87" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>559</v>
-      </c>
-      <c r="E87" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>225</v>
-      </c>
       <c r="G87" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8759,7 +8777,7 @@
         <v>202</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K87" s="3">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8782,13 +8800,13 @@
         <v>8</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q87" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R87" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S87" s="14" t="s">
         <v>9</v>
@@ -8799,32 +8817,32 @@
         <v>112</v>
       </c>
       <c r="B88" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C88" s="4" t="s">
-        <v>694</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" s="15" t="s">
-        <v>693</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="G88" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I88" s="3">
         <f>VLOOKUP(H88,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K88" s="3">
         <f>VLOOKUP(J88,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8850,10 +8868,10 @@
         <v>128</v>
       </c>
       <c r="Q88" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R88" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S88" s="14" t="s">
         <v>9</v>
@@ -8864,22 +8882,22 @@
         <v>114</v>
       </c>
       <c r="B89" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="E89" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="D89" s="12" t="s">
-        <v>547</v>
-      </c>
-      <c r="E89" s="15" t="s">
-        <v>687</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>230</v>
-      </c>
       <c r="G89" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>55</v>
@@ -8915,10 +8933,10 @@
         <v>128</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R89" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S89" s="14" t="s">
         <v>9</v>
@@ -8929,7 +8947,7 @@
         <v>115</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>9</v>
@@ -8941,10 +8959,10 @@
         <v>183</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>50</v>
@@ -8977,13 +8995,13 @@
         <v>1</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q90" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R90" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S90" s="14" t="s">
         <v>9</v>
@@ -8994,22 +9012,22 @@
         <v>116</v>
       </c>
       <c r="B91" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D91" s="14" t="s">
+        <v>450</v>
+      </c>
+      <c r="E91" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="F91" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>451</v>
-      </c>
-      <c r="E91" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>234</v>
-      </c>
       <c r="G91" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>34</v>
@@ -9019,7 +9037,7 @@
         <v>205</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9042,13 +9060,13 @@
         <v>4</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R91" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S91" s="14" t="s">
         <v>9</v>
@@ -9062,19 +9080,19 @@
         <v>39</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>34</v>
@@ -9110,10 +9128,10 @@
         <v>128</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R92" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S92" s="14" t="s">
         <v>9</v>
@@ -9124,7 +9142,7 @@
         <v>118</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>9</v>
@@ -9136,10 +9154,10 @@
         <v>9</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>21</v>
@@ -9149,7 +9167,7 @@
         <v>202</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9172,13 +9190,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R93" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S93" s="14" t="s">
         <v>9</v>
@@ -9189,22 +9207,22 @@
         <v>119</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E94" s="15">
         <v>501</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>15</v>
@@ -9237,13 +9255,13 @@
         <v>2</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q94" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R94" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S94" s="14" t="s">
         <v>9</v>
@@ -9254,22 +9272,22 @@
         <v>120</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="14" t="s">
+        <v>433</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>243</v>
-      </c>
       <c r="G95" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
@@ -9290,11 +9308,11 @@
         <v>3</v>
       </c>
       <c r="M95" s="3">
-        <f t="shared" ref="M95:M124" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
+        <f t="shared" ref="M95:M125" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="N95" s="3">
-        <f t="shared" ref="N95:N124" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
+        <f t="shared" ref="N95:N125" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O95" s="3">
@@ -9302,13 +9320,13 @@
         <v>3</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R95" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S95" s="14" t="s">
         <v>9</v>
@@ -9319,22 +9337,22 @@
         <v>121</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D96" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="E96" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>656</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>245</v>
-      </c>
       <c r="G96" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>15</v>
@@ -9370,10 +9388,10 @@
         <v>128</v>
       </c>
       <c r="Q96" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R96" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S96" s="14" t="s">
         <v>9</v>
@@ -9384,22 +9402,22 @@
         <v>122</v>
       </c>
       <c r="B97" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="E97" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C97" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="E97" s="15" t="s">
-        <v>550</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="G97" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9435,10 +9453,10 @@
         <v>128</v>
       </c>
       <c r="Q97" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R97" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S97" s="14" t="s">
         <v>9</v>
@@ -9449,25 +9467,25 @@
         <v>124</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="D98" s="14" t="s">
-        <v>526</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>527</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>250</v>
-      </c>
       <c r="G98" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9497,13 +9515,13 @@
         <v>7</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q98" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R98" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S98" s="14" t="s">
         <v>9</v>
@@ -9514,22 +9532,22 @@
         <v>126</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E99" s="15">
         <v>501</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>55</v>
@@ -9562,13 +9580,13 @@
         <v>2</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R99" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S99" s="14" t="s">
         <v>9</v>
@@ -9579,22 +9597,22 @@
         <v>127</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C100" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>434</v>
+      </c>
+      <c r="E100" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="D100" s="14" t="s">
-        <v>435</v>
-      </c>
-      <c r="E100" s="15" t="s">
-        <v>289</v>
-      </c>
       <c r="F100" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>55</v>
@@ -9627,13 +9645,13 @@
         <v>3</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R100" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S100" s="14" t="s">
         <v>9</v>
@@ -9644,22 +9662,22 @@
         <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E101" s="15">
         <v>501</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>55</v>
@@ -9692,13 +9710,13 @@
         <v>2</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q101" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R101" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S101" s="14" t="s">
         <v>9</v>
@@ -9709,22 +9727,22 @@
         <v>129</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>55</v>
@@ -9760,10 +9778,10 @@
         <v>128</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R102" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S102" s="14" t="s">
         <v>9</v>
@@ -9774,25 +9792,25 @@
         <v>130</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>522</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>528</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>529</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="G103" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I103" s="3">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
@@ -9822,13 +9840,13 @@
         <v>5</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R103" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S103" s="14" t="s">
         <v>9</v>
@@ -9839,22 +9857,22 @@
         <v>134</v>
       </c>
       <c r="B104" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C104" s="4" t="s">
-        <v>292</v>
-      </c>
       <c r="D104" s="12" t="s">
-        <v>667</v>
+        <v>659</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G104" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -9890,10 +9908,10 @@
         <v>128</v>
       </c>
       <c r="Q104" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R104" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S104" s="14" t="s">
         <v>9</v>
@@ -9904,7 +9922,7 @@
         <v>135</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -9916,20 +9934,20 @@
         <v>183</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="G105" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H105" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I105" s="3">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J105" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K105" s="3">
         <f>VLOOKUP(J105,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9952,13 +9970,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q105" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R105" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S105" s="14" t="s">
         <v>9</v>
@@ -9969,7 +9987,7 @@
         <v>136</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
@@ -9981,10 +9999,10 @@
         <v>240</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="G106" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H106" t="s">
         <v>55</v>
@@ -10017,13 +10035,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q106" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R106" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="S106" s="14" t="s">
         <v>9</v>
@@ -10034,25 +10052,25 @@
         <v>137</v>
       </c>
       <c r="B107" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C107" s="4" t="s">
+      <c r="D107" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="16" t="s">
         <v>295</v>
       </c>
-      <c r="D107" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E107" s="16" t="s">
-        <v>296</v>
-      </c>
       <c r="F107" s="4" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="G107" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H107" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I107" s="3">
         <f>VLOOKUP(H107,cardsort_group_IDs!A:B,2,0)</f>
@@ -10082,13 +10100,13 @@
         <v>6</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R107" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S107" s="14" t="s">
         <v>9</v>
@@ -10099,10 +10117,10 @@
         <v>138</v>
       </c>
       <c r="B108" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="C108" s="4" t="s">
-        <v>298</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>9</v>
@@ -10111,10 +10129,10 @@
         <v>236</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G108" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -10147,13 +10165,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R108" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S108" s="14" t="s">
         <v>9</v>
@@ -10164,7 +10182,7 @@
         <v>139</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10176,10 +10194,10 @@
         <v>9</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -10189,7 +10207,7 @@
         <v>202</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K109" s="3">
         <f>VLOOKUP(J109,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10212,13 +10230,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R109" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S109" s="14" t="s">
         <v>9</v>
@@ -10229,22 +10247,22 @@
         <v>140</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>15</v>
@@ -10277,13 +10295,13 @@
         <v>18</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="Q110" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R110" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S110" s="14">
         <v>2</v>
@@ -10294,22 +10312,22 @@
         <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>55</v>
@@ -10342,13 +10360,13 @@
         <v>3</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R111" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S111" s="14">
         <v>129</v>
@@ -10359,22 +10377,22 @@
         <v>142</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>55</v>
@@ -10407,13 +10425,13 @@
         <v>2</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R112" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S112" s="14">
         <v>19</v>
@@ -10424,22 +10442,22 @@
         <v>143</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
@@ -10472,13 +10490,13 @@
         <v>5</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R113" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S113" s="14" t="s">
         <v>9</v>
@@ -10489,22 +10507,22 @@
         <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>15</v>
@@ -10537,16 +10555,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R114" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S114" s="14" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10554,22 +10572,22 @@
         <v>145</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -10602,16 +10620,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R115" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="S115" s="14" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10619,22 +10637,22 @@
         <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="D116" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -10667,16 +10685,16 @@
         <v>6</v>
       </c>
       <c r="P116" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="Q116" s="14" t="s">
+        <v>707</v>
+      </c>
+      <c r="R116" t="s">
+        <v>712</v>
+      </c>
+      <c r="S116" s="14" t="s">
         <v>618</v>
-      </c>
-      <c r="Q116" s="14" t="s">
-        <v>718</v>
-      </c>
-      <c r="R116" t="s">
-        <v>723</v>
-      </c>
-      <c r="S116" s="14" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -10684,22 +10702,22 @@
         <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10732,16 +10750,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="Q117" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R117" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S117" s="14" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10749,22 +10767,22 @@
         <v>148</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>681</v>
+        <v>670</v>
       </c>
       <c r="D118" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>10</v>
@@ -10800,13 +10818,13 @@
         <v>128</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R118" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S118" s="14" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -10814,22 +10832,22 @@
         <v>149</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -10839,7 +10857,7 @@
         <v>202</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K119" s="3">
         <f>VLOOKUP(J119,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10865,13 +10883,13 @@
         <v>128</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R119" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S119" s="14" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
@@ -10879,25 +10897,25 @@
         <v>150</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
@@ -10930,13 +10948,13 @@
         <v>128</v>
       </c>
       <c r="Q120" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R120" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S120" s="14" t="s">
-        <v>662</v>
+        <v>654</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10944,22 +10962,22 @@
         <v>151</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>682</v>
+        <v>671</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>673</v>
+        <v>665</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -10995,10 +11013,10 @@
         <v>128</v>
       </c>
       <c r="Q121" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="R121" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S121" s="14" t="s">
         <v>9</v>
@@ -11009,7 +11027,7 @@
         <v>152</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
@@ -11018,16 +11036,16 @@
         <v>9</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>689</v>
+        <v>678</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11060,10 +11078,10 @@
         <v>128</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="R122" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S122" s="14" t="s">
         <v>9</v>
@@ -11074,7 +11092,7 @@
         <v>153</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11083,16 +11101,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="F123" t="s">
-        <v>692</v>
+        <v>681</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11125,13 +11143,13 @@
         <v>128</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="R123" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="S123" s="14" t="s">
-        <v>691</v>
+        <v>680</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -11139,7 +11157,7 @@
         <v>154</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>9</v>
@@ -11148,16 +11166,16 @@
         <v>9</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>697</v>
+        <v>686</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="I124" s="3">
         <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
@@ -11171,7 +11189,7 @@
         <v>313</v>
       </c>
       <c r="L124" s="3">
-        <f t="shared" ref="L124" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <f t="shared" ref="L124:L125" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M124" s="3">
@@ -11183,20 +11201,85 @@
         <v>1</v>
       </c>
       <c r="O124" s="3">
-        <f t="shared" ref="O124" si="31">SUM(M124:N124)</f>
+        <f t="shared" ref="O124:O125" si="31">SUM(M124:N124)</f>
         <v>1</v>
       </c>
       <c r="P124" s="14" t="s">
         <v>128</v>
       </c>
       <c r="Q124" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="R124" t="s">
+        <v>712</v>
+      </c>
+      <c r="S124" s="14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A125" s="3">
+        <v>155</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" s="15" t="s">
+        <v>741</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="G125" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="R124" t="s">
-        <v>723</v>
-      </c>
-      <c r="S124" s="14" t="s">
-        <v>695</v>
+      <c r="H125" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="I125" s="3">
+        <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J125" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K125" s="3">
+        <f>VLOOKUP(J125,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>322</v>
+      </c>
+      <c r="L125" s="3">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="M125" s="3">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="N125" s="3">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="O125" s="3">
+        <f t="shared" si="31"/>
+        <v>2</v>
+      </c>
+      <c r="P125" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q125" s="14" t="s">
+        <v>706</v>
+      </c>
+      <c r="R125" t="s">
+        <v>711</v>
+      </c>
+      <c r="S125" s="14" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -11307,7 +11390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
@@ -11318,16 +11401,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="B1" t="s">
         <v>410</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>689</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>411</v>
-      </c>
-      <c r="C1" t="s">
-        <v>700</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11335,13 +11418,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D2" t="s">
         <v>304</v>
-      </c>
-      <c r="C2" t="s">
-        <v>710</v>
-      </c>
-      <c r="D2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11349,27 +11432,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C3" t="s">
+        <v>699</v>
+      </c>
+      <c r="D3" t="s">
         <v>306</v>
-      </c>
-      <c r="C3" t="s">
-        <v>710</v>
-      </c>
-      <c r="D3" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C4" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11377,13 +11460,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" t="s">
+        <v>699</v>
+      </c>
+      <c r="D5" t="s">
         <v>308</v>
-      </c>
-      <c r="C5" t="s">
-        <v>710</v>
-      </c>
-      <c r="D5" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11391,13 +11474,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" t="s">
+        <v>699</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>310</v>
-      </c>
-      <c r="C6" t="s">
-        <v>710</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11405,13 +11488,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" t="s">
+        <v>699</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>312</v>
-      </c>
-      <c r="C7" t="s">
-        <v>710</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11419,13 +11502,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C8" t="s">
+        <v>699</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>314</v>
-      </c>
-      <c r="C8" t="s">
-        <v>710</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11433,13 +11516,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C9" t="s">
+        <v>699</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>316</v>
-      </c>
-      <c r="C9" t="s">
-        <v>710</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11447,13 +11530,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>317</v>
+      </c>
+      <c r="C10" t="s">
+        <v>699</v>
+      </c>
+      <c r="D10" s="10" t="s">
         <v>318</v>
-      </c>
-      <c r="C10" t="s">
-        <v>710</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11461,13 +11544,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C11" t="s">
+        <v>699</v>
+      </c>
+      <c r="D11" s="10" t="s">
         <v>320</v>
-      </c>
-      <c r="C11" t="s">
-        <v>710</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11475,13 +11558,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C12" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D12" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11489,13 +11572,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
+        <v>321</v>
+      </c>
+      <c r="C13" t="s">
+        <v>699</v>
+      </c>
+      <c r="D13" s="10" t="s">
         <v>322</v>
-      </c>
-      <c r="C13" t="s">
-        <v>710</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11503,13 +11586,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" t="s">
+        <v>699</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>324</v>
-      </c>
-      <c r="C14" t="s">
-        <v>710</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11517,13 +11600,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
+        <v>325</v>
+      </c>
+      <c r="C15" t="s">
+        <v>699</v>
+      </c>
+      <c r="D15" s="10" t="s">
         <v>326</v>
-      </c>
-      <c r="C15" t="s">
-        <v>710</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11531,13 +11614,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" t="s">
+        <v>699</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>328</v>
-      </c>
-      <c r="C16" t="s">
-        <v>710</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11545,13 +11628,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
+        <v>329</v>
+      </c>
+      <c r="C17" t="s">
+        <v>699</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>330</v>
-      </c>
-      <c r="C17" t="s">
-        <v>710</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11559,13 +11642,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="C18" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D18" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11573,13 +11656,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
+        <v>331</v>
+      </c>
+      <c r="C19" t="s">
+        <v>699</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>332</v>
-      </c>
-      <c r="C19" t="s">
-        <v>710</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11587,13 +11670,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="C20" t="s">
-        <v>710</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11601,13 +11684,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C21" t="s">
+        <v>699</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>336</v>
-      </c>
-      <c r="C21" t="s">
-        <v>710</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11615,13 +11698,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>337</v>
+      </c>
+      <c r="C22" t="s">
+        <v>699</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>338</v>
-      </c>
-      <c r="C22" t="s">
-        <v>710</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11629,13 +11712,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" t="s">
+        <v>699</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>340</v>
-      </c>
-      <c r="C23" t="s">
-        <v>710</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11643,13 +11726,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" t="s">
+        <v>699</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>342</v>
-      </c>
-      <c r="C24" t="s">
-        <v>710</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11657,13 +11740,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" t="s">
+        <v>699</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>344</v>
-      </c>
-      <c r="C25" t="s">
-        <v>710</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11671,13 +11754,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
+        <v>345</v>
+      </c>
+      <c r="C26" t="s">
+        <v>699</v>
+      </c>
+      <c r="D26" s="10" t="s">
         <v>346</v>
-      </c>
-      <c r="C26" t="s">
-        <v>710</v>
-      </c>
-      <c r="D26" s="10" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11685,13 +11768,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
+        <v>347</v>
+      </c>
+      <c r="C27" t="s">
+        <v>699</v>
+      </c>
+      <c r="D27" s="10" t="s">
         <v>348</v>
-      </c>
-      <c r="C27" t="s">
-        <v>710</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11699,13 +11782,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" t="s">
+        <v>699</v>
+      </c>
+      <c r="D28" s="10" t="s">
         <v>350</v>
-      </c>
-      <c r="C28" t="s">
-        <v>710</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11713,13 +11796,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
+        <v>351</v>
+      </c>
+      <c r="C29" t="s">
+        <v>699</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>352</v>
-      </c>
-      <c r="C29" t="s">
-        <v>710</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11727,13 +11810,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
+        <v>353</v>
+      </c>
+      <c r="C30" t="s">
+        <v>699</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>354</v>
-      </c>
-      <c r="C30" t="s">
-        <v>710</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11741,13 +11824,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="C31" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11755,13 +11838,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
+        <v>356</v>
+      </c>
+      <c r="C32" t="s">
+        <v>699</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>357</v>
-      </c>
-      <c r="C32" t="s">
-        <v>710</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11769,13 +11852,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" t="s">
+        <v>699</v>
+      </c>
+      <c r="D33" s="10" t="s">
         <v>359</v>
-      </c>
-      <c r="C33" t="s">
-        <v>710</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11783,13 +11866,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" t="s">
+        <v>699</v>
+      </c>
+      <c r="D34" s="10" t="s">
         <v>361</v>
-      </c>
-      <c r="C34" t="s">
-        <v>710</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11797,13 +11880,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
+        <v>362</v>
+      </c>
+      <c r="C35" t="s">
+        <v>699</v>
+      </c>
+      <c r="D35" s="10" t="s">
         <v>363</v>
-      </c>
-      <c r="C35" t="s">
-        <v>710</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11811,13 +11894,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
+        <v>364</v>
+      </c>
+      <c r="C36" t="s">
+        <v>699</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>365</v>
-      </c>
-      <c r="C36" t="s">
-        <v>710</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11825,13 +11908,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
+        <v>366</v>
+      </c>
+      <c r="C37" t="s">
+        <v>699</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>367</v>
-      </c>
-      <c r="C37" t="s">
-        <v>710</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11839,13 +11922,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
+        <v>369</v>
+      </c>
+      <c r="C38" t="s">
+        <v>699</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>370</v>
-      </c>
-      <c r="C38" t="s">
-        <v>710</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -11853,13 +11936,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
+        <v>371</v>
+      </c>
+      <c r="C39" t="s">
+        <v>699</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>372</v>
-      </c>
-      <c r="C39" t="s">
-        <v>710</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11867,13 +11950,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
+        <v>373</v>
+      </c>
+      <c r="C40" t="s">
+        <v>699</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>374</v>
-      </c>
-      <c r="C40" t="s">
-        <v>710</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11884,10 +11967,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11895,13 +11978,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
+        <v>376</v>
+      </c>
+      <c r="C42" t="s">
+        <v>699</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>377</v>
-      </c>
-      <c r="C42" t="s">
-        <v>710</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11909,13 +11992,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
+        <v>378</v>
+      </c>
+      <c r="C43" t="s">
+        <v>699</v>
+      </c>
+      <c r="D43" s="10" t="s">
         <v>379</v>
-      </c>
-      <c r="C43" t="s">
-        <v>710</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -11923,13 +12006,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="C44" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11937,13 +12020,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C45" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11954,10 +12037,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -11965,13 +12048,13 @@
         <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -11979,13 +12062,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C48" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D48" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -11993,13 +12076,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C49" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12007,13 +12090,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C50" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12021,10 +12104,10 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
+        <v>387</v>
+      </c>
+      <c r="D51" s="10" t="s">
         <v>388</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12032,13 +12115,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C52" t="s">
+        <v>699</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>390</v>
-      </c>
-      <c r="C52" t="s">
-        <v>710</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12046,13 +12129,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
+        <v>391</v>
+      </c>
+      <c r="C53" t="s">
+        <v>699</v>
+      </c>
+      <c r="D53" s="10" t="s">
         <v>392</v>
-      </c>
-      <c r="C53" t="s">
-        <v>710</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12060,13 +12143,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
+        <v>393</v>
+      </c>
+      <c r="C54" t="s">
+        <v>699</v>
+      </c>
+      <c r="D54" s="10" t="s">
         <v>394</v>
-      </c>
-      <c r="C54" t="s">
-        <v>710</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12074,13 +12157,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
+        <v>395</v>
+      </c>
+      <c r="C55" t="s">
+        <v>699</v>
+      </c>
+      <c r="D55" s="10" t="s">
         <v>396</v>
-      </c>
-      <c r="C55" t="s">
-        <v>710</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12088,13 +12171,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
+        <v>397</v>
+      </c>
+      <c r="C56" t="s">
+        <v>699</v>
+      </c>
+      <c r="D56" s="10" t="s">
         <v>398</v>
-      </c>
-      <c r="C56" t="s">
-        <v>710</v>
-      </c>
-      <c r="D56" s="10" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12102,13 +12185,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
+        <v>399</v>
+      </c>
+      <c r="C57" t="s">
+        <v>699</v>
+      </c>
+      <c r="D57" s="10" t="s">
         <v>400</v>
-      </c>
-      <c r="C57" t="s">
-        <v>710</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12116,13 +12199,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
+        <v>401</v>
+      </c>
+      <c r="C58" t="s">
+        <v>699</v>
+      </c>
+      <c r="D58" s="10" t="s">
         <v>402</v>
-      </c>
-      <c r="C58" t="s">
-        <v>710</v>
-      </c>
-      <c r="D58" s="10" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12130,13 +12213,13 @@
         <v>241</v>
       </c>
       <c r="B59" t="s">
+        <v>403</v>
+      </c>
+      <c r="C59" t="s">
+        <v>699</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>404</v>
-      </c>
-      <c r="C59" t="s">
-        <v>710</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12144,13 +12227,13 @@
         <v>243</v>
       </c>
       <c r="B60" t="s">
+        <v>405</v>
+      </c>
+      <c r="C60" t="s">
+        <v>699</v>
+      </c>
+      <c r="D60" s="10" t="s">
         <v>406</v>
-      </c>
-      <c r="C60" t="s">
-        <v>710</v>
-      </c>
-      <c r="D60" s="10" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12158,13 +12241,13 @@
         <v>244</v>
       </c>
       <c r="B61" t="s">
+        <v>407</v>
+      </c>
+      <c r="C61" t="s">
+        <v>699</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>408</v>
-      </c>
-      <c r="C61" t="s">
-        <v>710</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12172,13 +12255,13 @@
         <v>501</v>
       </c>
       <c r="B62" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C62" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12186,13 +12269,13 @@
         <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C63" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12200,13 +12283,13 @@
         <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C64" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12214,13 +12297,13 @@
         <v>504</v>
       </c>
       <c r="B65" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="C65" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12228,13 +12311,13 @@
         <v>505</v>
       </c>
       <c r="B66" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C66" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12245,10 +12328,10 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12256,13 +12339,13 @@
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C68" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12273,10 +12356,10 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12284,13 +12367,13 @@
         <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>738</v>
       </c>
       <c r="C70" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12298,923 +12381,937 @@
         <v>510</v>
       </c>
       <c r="B71" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="C71" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D71" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B72" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C72" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C73" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="C74" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C75" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B76" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C76" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C77" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C78" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B80" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="C80" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B81" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C81" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B82" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C82" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B83" t="s">
-        <v>699</v>
+        <v>688</v>
       </c>
       <c r="C83" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B84" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C84" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="C85" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C86" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C87" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C88" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C89" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B90" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C90" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B91" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C91" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C92" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B93" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C93" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B94" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C94" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B95" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C95" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B96" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C96" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B97" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C97" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B98" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C98" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B99" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C99" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B100" t="s">
         <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B101" t="s">
         <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B102" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C102" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B103" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C103" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B104" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C104" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B106" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C106" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B108" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="C108" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B109" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C109" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B110" t="s">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="C110" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B111" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C111" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B112" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C112" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B114" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C114" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B115" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C115" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B116" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="C116" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D116" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="B117" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="C117" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D117" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="B118" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C118" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D118" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="B119" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="C119" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D119" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="B120" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C120" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D120" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="B121" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C121" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D121" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="B122" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="C122" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D122" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B123" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C123" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D123" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="B124" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C124" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D124" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="B125" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C125" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D125" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="B126" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C126" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D126" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="B127" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C127" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D127" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="B128" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C128" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D128" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="B129" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C129" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D129" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B130" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="C130" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="D130" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="B131" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="C131" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D131" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="B132" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C132" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="D132" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="B133" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="C133" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D133" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="B134" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="C134" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="D134" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="B135" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C135" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D135" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>683</v>
+        <v>672</v>
       </c>
       <c r="B136" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="C136" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="D136" t="s">
-        <v>684</v>
+        <v>673</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="B137" t="s">
+        <v>726</v>
+      </c>
+      <c r="C137" t="s">
+        <v>699</v>
+      </c>
+      <c r="D137" t="s">
+        <v>727</v>
       </c>
     </row>
   </sheetData>
@@ -13265,7 +13362,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13350,7 +13447,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13534,7 +13631,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -13542,7 +13639,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13550,7 +13647,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13558,7 +13655,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13566,7 +13663,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13592,50 +13689,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>700</v>
+        <v>689</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>703</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>702</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>707</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>705</v>
+        <v>694</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>706</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>708</v>
+        <v>697</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>710</v>
+        <v>699</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8CB8A3-5C8B-4EE7-BE73-5BB2CFCB5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36499D2F-D5DD-4779-929B-6BA97A3720EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="company_sizes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">urls!$A$1:$D$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="767">
   <si>
     <t>id</t>
   </si>
@@ -469,9 +469,6 @@
     <t>Collaboration</t>
   </si>
   <si>
-    <t>Flow State</t>
-  </si>
-  <si>
     <t>Flow Through the System</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
   </si>
   <si>
     <t>Inner / Outer Loop Time Spent</t>
-  </si>
-  <si>
-    <t>To identify specific areas for improvement, it’s helpful to think of the activities involved in software development as being arranged in two loops. An inner loop comprises activities directly related to creating the product: coding, building, and unit testing. An outer loop comprises other tasks developers must do to push their code to production: integration, integration testing, releasing, and deployment. From both a productivity and personal-experience standpoint, maximizing the amount of time developers spend in the inner loop is desirable: building products directly generates value and is what most developers are excited to do. Outer-loop activities are seen by most developers as necessary but generally unsatisfying chores. Putting time into better tooling and automation for the outer loop allows developers to spend more time on inner-loop activities.</t>
   </si>
   <si>
     <t>Interruptions</t>
@@ -912,9 +906,6 @@
     <t>Developer Build Time (P50 and P90); Build Time; NextJS Page Compilation Duration; Application/Package Build Duration; Build Time Efficiency</t>
   </si>
   <si>
-    <t>Diff Authoring Time (DAT); Diffs per Engineer (PRs or MRs); Commits Performed by Time; Time Spent per Task; Commit Count, Implementation Time per User Story; Task Completion Time; Coding Time; Time to Commit per LOC Changed</t>
-  </si>
-  <si>
     <t>Number of Blocked Tickets</t>
   </si>
   <si>
@@ -1353,9 +1344,6 @@
     <t>DORA Framework</t>
   </si>
   <si>
-    <t>https://www.mckinsey.com/industries/technology-media-and-telecommunications/our-insights/yes-you-can-measure-software-developer-productivity#/</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/assessments/e50f7040-f235-4360-9d1d-cf753e12fed1/</t>
   </si>
   <si>
@@ -2256,9 +2244,6 @@
     <t>quantitative</t>
   </si>
   <si>
-    <t>Deep Work; Focused Work; Focus Time; Uninterrupted Time</t>
-  </si>
-  <si>
     <t>The ability to work in focus or flow, i.e. uninterrupted, in meeting-free blocks that allow the developer to concentrate deeply on their work. Often reported as percentage of total time or average time.</t>
   </si>
   <si>
@@ -2271,9 +2256,6 @@
     <t>both</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
@@ -2326,13 +2308,107 @@
   </si>
   <si>
     <t>514; 509</t>
+  </si>
+  <si>
+    <t>Diff Authoring Time (DAT); PR Authoring Time; Diffs per Engineer (PRs or MRs); Commits Performed by Time; Time Spent per Task; Commit Count, Implementation Time per User Story; Task Completion Time; Coding Time; Time to Commit per LOC Changed</t>
+  </si>
+  <si>
+    <t>Diff Risk Score</t>
+  </si>
+  <si>
+    <t>PR Risk Score</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/pdf/10.1145/3722216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicts the likelihood of a code change (diff) causing a production incident. </t>
+  </si>
+  <si>
+    <t>515b</t>
+  </si>
+  <si>
+    <t>515a</t>
+  </si>
+  <si>
+    <t>https://engineering.fb.com/2025/08/06/developer-tools/diff-risk-score-drs-ai-risk-aware-software-development-meta/</t>
+  </si>
+  <si>
+    <t>Mockus (2025)</t>
+  </si>
+  <si>
+    <t>https://www.mckinsey.com/industries/technology-media-and-telecommunications/our-insights/yes-you-can-measure-software-developer-productivity</t>
+  </si>
+  <si>
+    <t>Time spent Coding</t>
+  </si>
+  <si>
+    <t>Active Coding Time; Coding Time; Focus Coding Time</t>
+  </si>
+  <si>
+    <t>The amount or proportion of a developer's working time actively spent writing or editing code, as measured by IDE telemetry. Excludes building, testing, meetings, and other non-coding activities. Helps to identify whether developers have sufficient uninterrupted time for core development work.</t>
+  </si>
+  <si>
+    <t>516a</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/8666786</t>
+  </si>
+  <si>
+    <t>Meyer (2021)</t>
+  </si>
+  <si>
+    <t>516b</t>
+  </si>
+  <si>
+    <t>https://linearb.io/blog/how-meta-measures-coding-time</t>
+  </si>
+  <si>
+    <t>Lloyds</t>
+  </si>
+  <si>
+    <t>516c</t>
+  </si>
+  <si>
+    <t>516d</t>
+  </si>
+  <si>
+    <t>516e</t>
+  </si>
+  <si>
+    <t>https://dpe.org/sessions/hilary-lanham-tom-kelk/measuring-engineering-productivity-from-a-standing-start-a-330-year-old-banks-journey/</t>
+  </si>
+  <si>
+    <t>https://devops.com/how-to-get-developer-productivity-engineering-right/</t>
+  </si>
+  <si>
+    <t>516b; 516c; 516d; 516e</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Focus Time</t>
+  </si>
+  <si>
+    <t>Flow State; Deep Work; Focused Work; Uninterrupted Time</t>
+  </si>
+  <si>
+    <t>59; 157</t>
+  </si>
+  <si>
+    <t>The proportion of a developer's working time spent on inner-loop activities (coding, building, unit testing) vs. outer-loop activities (integration testing, releasing, deployment). Typically collected via self-report survey or time-tracking tools.
+Software development activities can be arranged in two loops. The inner loop covers activities directly related to creating the product: coding, building, and unit testing. The outer loop covers tasks needed to push code to production: integration testing, releasing, and deployment. Maximizing inner-loop time is desirable — it directly generates value and is what most developers find most engaging. Better tooling and automation for outer-loop activities frees up more time for inner-loop work.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2375,6 +2451,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2393,10 +2477,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2446,8 +2531,13 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
@@ -3143,7 +3233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3174,16 +3264,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3201,25 +3291,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3233,16 +3323,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3275,16 +3365,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3307,7 +3397,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3340,13 +3430,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R3" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>9</v>
@@ -3363,16 +3453,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3405,13 +3495,13 @@
         <v>3</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R4" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>9</v>
@@ -3425,22 +3515,22 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3470,13 +3560,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R5" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>9</v>
@@ -3502,7 +3592,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3535,13 +3625,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R6" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>9</v>
@@ -3558,16 +3648,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -3600,13 +3690,13 @@
         <v>26</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q7" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R7" t="s">
         <v>708</v>
-      </c>
-      <c r="R7" t="s">
-        <v>712</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>9</v>
@@ -3632,7 +3722,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -3665,13 +3755,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R8" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>9</v>
@@ -3688,7 +3778,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E9" s="15">
         <v>501</v>
@@ -3697,7 +3787,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -3730,13 +3820,13 @@
         <v>2</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q9" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R9" t="s">
         <v>708</v>
-      </c>
-      <c r="R9" t="s">
-        <v>712</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>9</v>
@@ -3753,7 +3843,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="E10" s="15">
         <v>501</v>
@@ -3762,7 +3852,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3795,13 +3885,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R10" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>9</v>
@@ -3818,16 +3908,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -3860,13 +3950,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q11" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R11" t="s">
         <v>708</v>
-      </c>
-      <c r="R11" t="s">
-        <v>712</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>9</v>
@@ -3883,16 +3973,16 @@
         <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>50</v>
@@ -3925,13 +4015,13 @@
         <v>8</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R12" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>9</v>
@@ -3945,10 +4035,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="E13" s="15">
         <v>131</v>
@@ -3957,7 +4047,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -3990,13 +4080,13 @@
         <v>4</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q13" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R13" t="s">
         <v>708</v>
-      </c>
-      <c r="R13" t="s">
-        <v>712</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>9</v>
@@ -4010,19 +4100,19 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -4055,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R14" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>9</v>
@@ -4075,22 +4165,22 @@
         <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4120,13 +4210,13 @@
         <v>5</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R15" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>9</v>
@@ -4143,16 +4233,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4185,13 +4275,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q16" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R16" t="s">
         <v>707</v>
-      </c>
-      <c r="R16" t="s">
-        <v>711</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>9</v>
@@ -4205,19 +4295,19 @@
         <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>50</v>
@@ -4250,13 +4340,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q17" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R17" t="s">
         <v>707</v>
-      </c>
-      <c r="R17" t="s">
-        <v>711</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>9</v>
@@ -4282,7 +4372,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4315,13 +4405,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R18" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>9</v>
@@ -4341,13 +4431,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>73</v>
@@ -4380,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R19" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>9</v>
@@ -4403,7 +4493,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E20" s="15">
         <v>131</v>
@@ -4412,7 +4502,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>73</v>
@@ -4445,13 +4535,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q20" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R20" t="s">
         <v>708</v>
-      </c>
-      <c r="R20" t="s">
-        <v>712</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>9</v>
@@ -4465,19 +4555,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4510,13 +4600,13 @@
         <v>16</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R21" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>9</v>
@@ -4530,7 +4620,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>9</v>
@@ -4542,7 +4632,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>34</v>
@@ -4575,13 +4665,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q22" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R22" t="s">
         <v>708</v>
-      </c>
-      <c r="R22" t="s">
-        <v>712</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>9</v>
@@ -4598,16 +4688,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>73</v>
@@ -4640,13 +4730,13 @@
         <v>21</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R23" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>9</v>
@@ -4660,19 +4750,19 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D24" s="14">
         <v>170</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>34</v>
@@ -4705,13 +4795,13 @@
         <v>4</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R24" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>9</v>
@@ -4728,7 +4818,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E25" s="15">
         <v>501</v>
@@ -4737,7 +4827,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>73</v>
@@ -4770,13 +4860,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R25" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>9</v>
@@ -4793,16 +4883,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4835,13 +4925,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R26" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>9</v>
@@ -4855,19 +4945,19 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -4900,13 +4990,13 @@
         <v>8</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R27" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>9</v>
@@ -4923,19 +5013,19 @@
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -4965,13 +5055,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R28" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>9</v>
@@ -4985,22 +5075,22 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
@@ -5030,13 +5120,13 @@
         <v>43</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R29" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>9</v>
@@ -5062,7 +5152,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5095,13 +5185,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R30" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>9</v>
@@ -5115,19 +5205,19 @@
         <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>270</v>
+        <v>736</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5160,13 +5250,13 @@
         <v>17</v>
       </c>
       <c r="P31" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R31" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>9</v>
@@ -5183,16 +5273,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5225,13 +5315,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R32" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>9</v>
@@ -5248,19 +5338,19 @@
         <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5290,13 +5380,13 @@
         <v>14</v>
       </c>
       <c r="P33" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R33" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>9</v>
@@ -5310,22 +5400,22 @@
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
@@ -5355,13 +5445,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R34" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>9</v>
@@ -5375,19 +5465,19 @@
         <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
@@ -5420,13 +5510,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q35" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R35" t="s">
         <v>708</v>
-      </c>
-      <c r="R35" t="s">
-        <v>712</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>9</v>
@@ -5443,19 +5533,19 @@
         <v>9</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5485,13 +5575,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R36" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>9</v>
@@ -5505,19 +5595,19 @@
         <v>113</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5550,13 +5640,13 @@
         <v>3</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q37" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R37" t="s">
         <v>707</v>
-      </c>
-      <c r="R37" t="s">
-        <v>711</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>9</v>
@@ -5576,13 +5666,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5615,13 +5705,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R38" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>9</v>
@@ -5641,13 +5731,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -5680,13 +5770,13 @@
         <v>2</v>
       </c>
       <c r="P39" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R39" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>9</v>
@@ -5697,25 +5787,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>123</v>
+        <v>763</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>718</v>
+        <v>764</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5745,16 +5835,16 @@
         <v>13</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R40" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>723</v>
+        <v>765</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5762,7 +5852,7 @@
         <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>9</v>
@@ -5774,10 +5864,10 @@
         <v>506</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5810,13 +5900,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q41" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R41" t="s">
         <v>707</v>
-      </c>
-      <c r="R41" t="s">
-        <v>711</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>9</v>
@@ -5827,7 +5917,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>9</v>
@@ -5839,10 +5929,10 @@
         <v>506</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>15</v>
@@ -5875,13 +5965,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q42" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R42" t="s">
         <v>707</v>
-      </c>
-      <c r="R42" t="s">
-        <v>711</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>9</v>
@@ -5892,25 +5982,25 @@
         <v>56</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>429</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>532</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="G43" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -5940,13 +6030,13 @@
         <v>4</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R43" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>9</v>
@@ -5957,7 +6047,7 @@
         <v>57</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>9</v>
@@ -5969,10 +6059,10 @@
         <v>514</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -6005,42 +6095,42 @@
         <v>1</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R44" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="360" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="345" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>58</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>133</v>
+        <v>766</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6070,16 +6160,16 @@
         <v>4</v>
       </c>
       <c r="P45" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R45" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S45" s="14" t="s">
-        <v>9</v>
+        <v>761</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -6087,25 +6177,25 @@
         <v>59</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I46" s="3">
         <f>VLOOKUP(H46,cardsort_group_IDs!A:B,2,0)</f>
@@ -6135,16 +6225,16 @@
         <v>4</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R46" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S46" s="14" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6152,22 +6242,22 @@
         <v>62</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>734</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="G47" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -6200,13 +6290,13 @@
         <v>11</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R47" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>9</v>
@@ -6217,22 +6307,22 @@
         <v>63</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>658</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="G48" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>34</v>
@@ -6265,13 +6355,13 @@
         <v>4</v>
       </c>
       <c r="P48" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q48" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R48" t="s">
         <v>708</v>
-      </c>
-      <c r="R48" t="s">
-        <v>712</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>9</v>
@@ -6282,7 +6372,7 @@
         <v>64</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>9</v>
@@ -6294,10 +6384,10 @@
         <v>9</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6330,13 +6420,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R49" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>9</v>
@@ -6347,22 +6437,22 @@
         <v>65</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -6395,13 +6485,13 @@
         <v>16</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R50" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>9</v>
@@ -6412,10 +6502,10 @@
         <v>66</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>9</v>
@@ -6424,10 +6514,10 @@
         <v>235</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>50</v>
@@ -6460,13 +6550,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q51" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R51" t="s">
         <v>707</v>
-      </c>
-      <c r="R51" t="s">
-        <v>711</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>9</v>
@@ -6477,22 +6567,22 @@
         <v>67</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>50</v>
@@ -6525,13 +6615,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q52" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R52" t="s">
         <v>707</v>
-      </c>
-      <c r="R52" t="s">
-        <v>711</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>9</v>
@@ -6542,22 +6632,22 @@
         <v>69</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>73</v>
@@ -6590,13 +6680,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R53" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>9</v>
@@ -6607,22 +6697,22 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>34</v>
@@ -6655,13 +6745,13 @@
         <v>2</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q54" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R54" t="s">
         <v>708</v>
-      </c>
-      <c r="R54" t="s">
-        <v>712</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>9</v>
@@ -6672,22 +6762,22 @@
         <v>71</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -6720,13 +6810,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q55" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R55" t="s">
         <v>707</v>
-      </c>
-      <c r="R55" t="s">
-        <v>711</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>9</v>
@@ -6737,22 +6827,22 @@
         <v>72</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>10</v>
@@ -6762,7 +6852,7 @@
         <v>201</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K56" s="3">
         <f>VLOOKUP(J56,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6785,13 +6875,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R56" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>9</v>
@@ -6802,22 +6892,22 @@
         <v>73</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
@@ -6827,7 +6917,7 @@
         <v>202</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K57" s="3">
         <f>VLOOKUP(J57,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6850,13 +6940,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q57" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R57" t="s">
         <v>707</v>
-      </c>
-      <c r="R57" t="s">
-        <v>711</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>9</v>
@@ -6867,7 +6957,7 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>9</v>
@@ -6879,10 +6969,10 @@
         <v>183</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -6915,13 +7005,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R58" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>9</v>
@@ -6932,22 +7022,22 @@
         <v>75</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="E59" s="15">
         <v>183</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
@@ -6980,13 +7070,13 @@
         <v>2</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R59" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>9</v>
@@ -6997,22 +7087,22 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7045,13 +7135,13 @@
         <v>2</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q60" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R60" t="s">
         <v>707</v>
-      </c>
-      <c r="R60" t="s">
-        <v>711</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>9</v>
@@ -7062,25 +7152,25 @@
         <v>78</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>542</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>650</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>546</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I61" s="3">
         <f>VLOOKUP(H61,cardsort_group_IDs!A:B,2,0)</f>
@@ -7110,13 +7200,13 @@
         <v>11</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R61" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>9</v>
@@ -7127,22 +7217,22 @@
         <v>79</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>73</v>
@@ -7175,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R62" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>9</v>
@@ -7192,7 +7282,7 @@
         <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>9</v>
@@ -7204,10 +7294,10 @@
         <v>514</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>73</v>
@@ -7240,13 +7330,13 @@
         <v>1</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q63" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R63" t="s">
         <v>708</v>
-      </c>
-      <c r="R63" t="s">
-        <v>712</v>
       </c>
       <c r="S63" s="14" t="s">
         <v>9</v>
@@ -7257,22 +7347,22 @@
         <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E64" s="15">
         <v>202</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>34</v>
@@ -7305,13 +7395,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R64" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S64" s="14" t="s">
         <v>9</v>
@@ -7322,7 +7412,7 @@
         <v>82</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>9</v>
@@ -7334,10 +7424,10 @@
         <v>514</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>10</v>
@@ -7347,7 +7437,7 @@
         <v>201</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K65" s="3">
         <f>VLOOKUP(J65,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7370,13 +7460,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q65" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R65" t="s">
         <v>707</v>
-      </c>
-      <c r="R65" t="s">
-        <v>711</v>
       </c>
       <c r="S65" s="14" t="s">
         <v>9</v>
@@ -7387,32 +7477,32 @@
         <v>83</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I66" s="3">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K66" s="3">
         <f>VLOOKUP(J66,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7435,13 +7525,13 @@
         <v>5</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q66" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R66" t="s">
         <v>707</v>
-      </c>
-      <c r="R66" t="s">
-        <v>711</v>
       </c>
       <c r="S66" s="14" t="s">
         <v>9</v>
@@ -7458,16 +7548,16 @@
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E67" s="15">
         <v>501</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>21</v>
@@ -7500,13 +7590,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q67" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R67" t="s">
         <v>707</v>
-      </c>
-      <c r="R67" t="s">
-        <v>711</v>
       </c>
       <c r="S67" s="14" t="s">
         <v>9</v>
@@ -7517,22 +7607,22 @@
         <v>85</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>15</v>
@@ -7565,13 +7655,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R68" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S68" s="14" t="s">
         <v>9</v>
@@ -7582,22 +7672,22 @@
         <v>87</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7630,13 +7720,13 @@
         <v>3</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R69" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S69" s="14" t="s">
         <v>9</v>
@@ -7647,22 +7737,22 @@
         <v>88</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>34</v>
@@ -7695,13 +7785,13 @@
         <v>3</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q70" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R70" t="s">
         <v>708</v>
-      </c>
-      <c r="R70" t="s">
-        <v>712</v>
       </c>
       <c r="S70" s="14" t="s">
         <v>9</v>
@@ -7712,22 +7802,22 @@
         <v>89</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>34</v>
@@ -7760,13 +7850,13 @@
         <v>4</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R71" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S71" s="14" t="s">
         <v>9</v>
@@ -7777,22 +7867,22 @@
         <v>90</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>34</v>
@@ -7825,13 +7915,13 @@
         <v>14</v>
       </c>
       <c r="P72" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R72" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S72" s="14" t="s">
         <v>9</v>
@@ -7842,22 +7932,22 @@
         <v>91</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -7890,13 +7980,13 @@
         <v>4</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R73" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S73" s="14" t="s">
         <v>9</v>
@@ -7907,22 +7997,22 @@
         <v>92</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>50</v>
@@ -7955,13 +8045,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q74" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R74" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S74" s="14" t="s">
         <v>9</v>
@@ -7972,7 +8062,7 @@
         <v>93</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>9</v>
@@ -7984,10 +8074,10 @@
         <v>514</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8020,13 +8110,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R75" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>9</v>
@@ -8037,22 +8127,22 @@
         <v>94</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>73</v>
@@ -8085,13 +8175,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R76" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S76" s="14" t="s">
         <v>9</v>
@@ -8102,22 +8192,22 @@
         <v>95</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>561</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="G77" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>21</v>
@@ -8127,7 +8217,7 @@
         <v>202</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K77" s="3">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8150,13 +8240,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R77" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S77" s="14" t="s">
         <v>9</v>
@@ -8167,7 +8257,7 @@
         <v>97</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>9</v>
@@ -8179,10 +8269,10 @@
         <v>508</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8215,13 +8305,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q78" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R78" t="s">
         <v>708</v>
-      </c>
-      <c r="R78" t="s">
-        <v>712</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>9</v>
@@ -8232,10 +8322,10 @@
         <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D79" s="12">
         <v>209</v>
@@ -8244,10 +8334,10 @@
         <v>506</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>10</v>
@@ -8257,7 +8347,7 @@
         <v>201</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K79" s="3">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8280,13 +8370,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R79" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S79" s="14" t="s">
         <v>9</v>
@@ -8297,7 +8387,7 @@
         <v>99</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>9</v>
@@ -8309,10 +8399,10 @@
         <v>508</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>10</v>
@@ -8345,13 +8435,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R80" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S80" s="14" t="s">
         <v>9</v>
@@ -8362,7 +8452,7 @@
         <v>100</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>9</v>
@@ -8374,10 +8464,10 @@
         <v>514</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>10</v>
@@ -8410,13 +8500,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R81" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S81" s="14" t="s">
         <v>9</v>
@@ -8427,22 +8517,22 @@
         <v>102</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E82" s="15">
         <v>501</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8475,13 +8565,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R82" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S82" s="14" t="s">
         <v>9</v>
@@ -8492,25 +8582,25 @@
         <v>104</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I83" s="3">
         <f>VLOOKUP(H83,cardsort_group_IDs!A:B,2,0)</f>
@@ -8540,13 +8630,13 @@
         <v>2</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R83" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S83" s="14" t="s">
         <v>9</v>
@@ -8557,22 +8647,22 @@
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>21</v>
@@ -8605,13 +8695,13 @@
         <v>4</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q84" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R84" t="s">
         <v>708</v>
-      </c>
-      <c r="R84" t="s">
-        <v>712</v>
       </c>
       <c r="S84" s="14" t="s">
         <v>9</v>
@@ -8622,22 +8712,22 @@
         <v>107</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8670,13 +8760,13 @@
         <v>7</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q85" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R85" t="s">
         <v>707</v>
-      </c>
-      <c r="R85" t="s">
-        <v>711</v>
       </c>
       <c r="S85" s="14" t="s">
         <v>9</v>
@@ -8687,22 +8777,22 @@
         <v>108</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8735,13 +8825,13 @@
         <v>8</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q86" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R86" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S86" s="14" t="s">
         <v>9</v>
@@ -8752,22 +8842,22 @@
         <v>109</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8777,7 +8867,7 @@
         <v>202</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K87" s="3">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8800,13 +8890,13 @@
         <v>8</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q87" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R87" t="s">
         <v>708</v>
-      </c>
-      <c r="R87" t="s">
-        <v>712</v>
       </c>
       <c r="S87" s="14" t="s">
         <v>9</v>
@@ -8817,32 +8907,32 @@
         <v>112</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I88" s="3">
         <f>VLOOKUP(H88,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K88" s="3">
         <f>VLOOKUP(J88,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8865,13 +8955,13 @@
         <v>2</v>
       </c>
       <c r="P88" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q88" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R88" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S88" s="14" t="s">
         <v>9</v>
@@ -8882,22 +8972,22 @@
         <v>114</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>55</v>
@@ -8930,13 +9020,13 @@
         <v>14</v>
       </c>
       <c r="P89" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R89" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S89" s="14" t="s">
         <v>9</v>
@@ -8947,7 +9037,7 @@
         <v>115</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>9</v>
@@ -8959,10 +9049,10 @@
         <v>183</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>50</v>
@@ -8995,13 +9085,13 @@
         <v>1</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q90" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R90" t="s">
         <v>707</v>
-      </c>
-      <c r="R90" t="s">
-        <v>711</v>
       </c>
       <c r="S90" s="14" t="s">
         <v>9</v>
@@ -9012,22 +9102,22 @@
         <v>116</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>34</v>
@@ -9037,7 +9127,7 @@
         <v>205</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9060,13 +9150,13 @@
         <v>4</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R91" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S91" s="14" t="s">
         <v>9</v>
@@ -9080,19 +9170,19 @@
         <v>39</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>34</v>
@@ -9125,13 +9215,13 @@
         <v>5</v>
       </c>
       <c r="P92" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q92" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R92" t="s">
         <v>708</v>
-      </c>
-      <c r="R92" t="s">
-        <v>712</v>
       </c>
       <c r="S92" s="14" t="s">
         <v>9</v>
@@ -9142,7 +9232,7 @@
         <v>118</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>9</v>
@@ -9154,10 +9244,10 @@
         <v>9</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>21</v>
@@ -9167,7 +9257,7 @@
         <v>202</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9190,13 +9280,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R93" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S93" s="14" t="s">
         <v>9</v>
@@ -9207,22 +9297,22 @@
         <v>119</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E94" s="15">
         <v>501</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>15</v>
@@ -9255,13 +9345,13 @@
         <v>2</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q94" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R94" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S94" s="14" t="s">
         <v>9</v>
@@ -9272,22 +9362,22 @@
         <v>120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
@@ -9308,11 +9398,11 @@
         <v>3</v>
       </c>
       <c r="M95" s="3">
-        <f t="shared" ref="M95:M125" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
+        <f t="shared" ref="M95:M126" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="N95" s="3">
-        <f t="shared" ref="N95:N125" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
+        <f t="shared" ref="N95:N126" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O95" s="3">
@@ -9320,13 +9410,13 @@
         <v>3</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q95" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R95" t="s">
         <v>707</v>
-      </c>
-      <c r="R95" t="s">
-        <v>711</v>
       </c>
       <c r="S95" s="14" t="s">
         <v>9</v>
@@ -9337,22 +9427,22 @@
         <v>121</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>15</v>
@@ -9385,13 +9475,13 @@
         <v>8</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q96" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R96" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S96" s="14" t="s">
         <v>9</v>
@@ -9402,22 +9492,22 @@
         <v>122</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9450,13 +9540,13 @@
         <v>5</v>
       </c>
       <c r="P97" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q97" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R97" t="s">
         <v>707</v>
-      </c>
-      <c r="R97" t="s">
-        <v>711</v>
       </c>
       <c r="S97" s="14" t="s">
         <v>9</v>
@@ -9467,25 +9557,25 @@
         <v>124</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>517</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>731</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C98" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="D98" s="14" t="s">
-        <v>521</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>737</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>249</v>
-      </c>
       <c r="G98" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9515,13 +9605,13 @@
         <v>7</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q98" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R98" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S98" s="14" t="s">
         <v>9</v>
@@ -9532,22 +9622,22 @@
         <v>126</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E99" s="15">
         <v>501</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>55</v>
@@ -9580,13 +9670,13 @@
         <v>2</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R99" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S99" s="14" t="s">
         <v>9</v>
@@ -9597,22 +9687,22 @@
         <v>127</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>430</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>434</v>
-      </c>
-      <c r="E100" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>255</v>
-      </c>
       <c r="G100" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>55</v>
@@ -9645,13 +9735,13 @@
         <v>3</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R100" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S100" s="14" t="s">
         <v>9</v>
@@ -9662,22 +9752,22 @@
         <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E101" s="15">
         <v>501</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>55</v>
@@ -9710,13 +9800,13 @@
         <v>2</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q101" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R101" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S101" s="14" t="s">
         <v>9</v>
@@ -9727,22 +9817,22 @@
         <v>129</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>55</v>
@@ -9775,13 +9865,13 @@
         <v>27</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R102" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S102" s="14" t="s">
         <v>9</v>
@@ -9792,25 +9882,25 @@
         <v>130</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I103" s="3">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
@@ -9840,13 +9930,13 @@
         <v>5</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R103" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S103" s="14" t="s">
         <v>9</v>
@@ -9857,22 +9947,22 @@
         <v>134</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="G104" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -9905,13 +9995,13 @@
         <v>11</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q104" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R104" t="s">
         <v>708</v>
-      </c>
-      <c r="R104" t="s">
-        <v>712</v>
       </c>
       <c r="S104" s="14" t="s">
         <v>9</v>
@@ -9922,7 +10012,7 @@
         <v>135</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -9934,20 +10024,20 @@
         <v>183</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="G105" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H105" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I105" s="3">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J105" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K105" s="3">
         <f>VLOOKUP(J105,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9970,13 +10060,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q105" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R105" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S105" s="14" t="s">
         <v>9</v>
@@ -9987,7 +10077,7 @@
         <v>136</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
@@ -9999,10 +10089,10 @@
         <v>240</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="G106" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H106" t="s">
         <v>55</v>
@@ -10035,13 +10125,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q106" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R106" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="S106" s="14" t="s">
         <v>9</v>
@@ -10052,25 +10142,25 @@
         <v>137</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G107" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H107" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I107" s="3">
         <f>VLOOKUP(H107,cardsort_group_IDs!A:B,2,0)</f>
@@ -10100,13 +10190,13 @@
         <v>6</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R107" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S107" s="14" t="s">
         <v>9</v>
@@ -10117,10 +10207,10 @@
         <v>138</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>9</v>
@@ -10129,10 +10219,10 @@
         <v>236</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="G108" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -10165,13 +10255,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R108" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S108" s="14" t="s">
         <v>9</v>
@@ -10182,7 +10272,7 @@
         <v>139</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10194,10 +10284,10 @@
         <v>9</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -10207,7 +10297,7 @@
         <v>202</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K109" s="3">
         <f>VLOOKUP(J109,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10230,13 +10320,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q109" s="14" t="s">
+        <v>704</v>
+      </c>
+      <c r="R109" t="s">
         <v>708</v>
-      </c>
-      <c r="R109" t="s">
-        <v>712</v>
       </c>
       <c r="S109" s="14" t="s">
         <v>9</v>
@@ -10247,22 +10337,22 @@
         <v>140</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>15</v>
@@ -10295,13 +10385,13 @@
         <v>18</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Q110" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R110" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S110" s="14">
         <v>2</v>
@@ -10312,22 +10402,22 @@
         <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>55</v>
@@ -10360,13 +10450,13 @@
         <v>3</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R111" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S111" s="14">
         <v>129</v>
@@ -10377,22 +10467,22 @@
         <v>142</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>55</v>
@@ -10425,13 +10515,13 @@
         <v>2</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R112" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S112" s="14">
         <v>19</v>
@@ -10442,22 +10532,22 @@
         <v>143</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
@@ -10490,13 +10580,13 @@
         <v>5</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R113" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S113" s="14" t="s">
         <v>9</v>
@@ -10507,22 +10597,22 @@
         <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>15</v>
@@ -10555,16 +10645,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R114" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S114" s="14" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10572,22 +10662,22 @@
         <v>145</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -10620,16 +10710,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R115" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S115" s="14" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10637,22 +10727,22 @@
         <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D116" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -10685,16 +10775,16 @@
         <v>6</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="Q116" s="14" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="R116" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S116" s="14" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -10702,22 +10792,22 @@
         <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10750,16 +10840,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="Q117" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R117" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S117" s="14" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10767,22 +10857,22 @@
         <v>148</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D118" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>10</v>
@@ -10815,16 +10905,16 @@
         <v>11</v>
       </c>
       <c r="P118" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q118" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R118" t="s">
         <v>707</v>
       </c>
-      <c r="R118" t="s">
-        <v>711</v>
-      </c>
       <c r="S118" s="14" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -10832,22 +10922,22 @@
         <v>149</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -10857,7 +10947,7 @@
         <v>202</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K119" s="3">
         <f>VLOOKUP(J119,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10880,16 +10970,16 @@
         <v>3</v>
       </c>
       <c r="P119" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R119" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S119" s="14" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
@@ -10897,25 +10987,25 @@
         <v>150</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
@@ -10945,16 +11035,16 @@
         <v>2</v>
       </c>
       <c r="P120" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q120" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R120" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S120" s="14" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10962,22 +11052,22 @@
         <v>151</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11010,13 +11100,13 @@
         <v>1</v>
       </c>
       <c r="P121" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q121" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R121" t="s">
         <v>707</v>
-      </c>
-      <c r="R121" t="s">
-        <v>711</v>
       </c>
       <c r="S121" s="14" t="s">
         <v>9</v>
@@ -11027,7 +11117,7 @@
         <v>152</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
@@ -11036,16 +11126,16 @@
         <v>9</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11075,13 +11165,13 @@
         <v>1</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R122" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S122" s="14" t="s">
         <v>9</v>
@@ -11092,7 +11182,7 @@
         <v>153</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11101,16 +11191,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F123" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11140,16 +11230,16 @@
         <v>1</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="R123" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S123" s="14" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -11157,7 +11247,7 @@
         <v>154</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>9</v>
@@ -11166,16 +11256,16 @@
         <v>9</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I124" s="3">
         <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
@@ -11189,7 +11279,7 @@
         <v>313</v>
       </c>
       <c r="L124" s="3">
-        <f t="shared" ref="L124:L125" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <f t="shared" ref="L124:L126" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M124" s="3">
@@ -11201,20 +11291,20 @@
         <v>1</v>
       </c>
       <c r="O124" s="3">
-        <f t="shared" ref="O124:O125" si="31">SUM(M124:N124)</f>
+        <f t="shared" ref="O124:O126" si="31">SUM(M124:N124)</f>
         <v>1</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q124" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R124" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="S124" s="14" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
@@ -11222,7 +11312,7 @@
         <v>155</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>9</v>
@@ -11231,16 +11321,16 @@
         <v>9</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="I125" s="3">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11270,20 +11360,150 @@
         <v>2</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="Q125" s="14" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="R125" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="S125" s="14" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>156</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>741</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>742</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I126" s="3">
+        <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
+        <v>205</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K126" s="3">
+        <f>VLOOKUP(J126,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>319</v>
+      </c>
+      <c r="L126" s="3">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="M126" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="N126" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O126" s="3">
+        <f t="shared" si="31"/>
+        <v>2</v>
+      </c>
+      <c r="P126" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q126" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="R126" t="s">
+        <v>709</v>
+      </c>
+      <c r="S126" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>157</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C127" t="s">
+        <v>747</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>760</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>749</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="I127" s="3">
+        <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" s="3">
+        <f>VLOOKUP(J127,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>305</v>
+      </c>
+      <c r="L127" s="3">
+        <f t="shared" ref="L127" si="32">IF(E127="-",0,1)+IF(D127="-",0,2)</f>
+        <v>3</v>
+      </c>
+      <c r="M127" s="3">
+        <f t="shared" ref="M127" si="33">IF(D127="-",0,LEN(D127)-LEN(SUBSTITUTE(D127,";",""))+1)</f>
+        <v>4</v>
+      </c>
+      <c r="N127" s="3">
+        <f t="shared" ref="N127" si="34">IF(E127="-",0,LEN(E127)-LEN(SUBSTITUTE(E127,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O127" s="3">
+        <f t="shared" ref="O127" si="35">SUM(M127:N127)</f>
+        <v>5</v>
+      </c>
+      <c r="P127" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="Q127" s="14" t="s">
+        <v>702</v>
+      </c>
+      <c r="R127" t="s">
+        <v>707</v>
+      </c>
+      <c r="S127" s="14" t="s">
+        <v>762</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B1:B108">
     <cfRule type="duplicateValues" dxfId="38" priority="45"/>
@@ -11390,7 +11610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D144"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
@@ -11401,16 +11621,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C1" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11418,13 +11638,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11432,27 +11652,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C3" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C4" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11460,13 +11680,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C5" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11474,13 +11694,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11488,13 +11708,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11502,13 +11722,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C8" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11516,13 +11736,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C9" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11530,13 +11750,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11544,13 +11764,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11558,13 +11778,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C12" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D12" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11572,13 +11792,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C13" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11586,13 +11806,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C14" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11600,13 +11820,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C15" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11614,13 +11834,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C16" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11628,13 +11848,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C17" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11642,13 +11862,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C18" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D18" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11656,13 +11876,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C19" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11670,13 +11890,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C20" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11684,13 +11904,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C21" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11698,13 +11918,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C22" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11712,13 +11932,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C23" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11726,13 +11946,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C24" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11740,13 +11960,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C25" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11754,13 +11974,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C26" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11768,13 +11988,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C27" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11782,13 +12002,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C28" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11796,13 +12016,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C29" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11810,13 +12030,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C30" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11824,13 +12044,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C31" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11838,13 +12058,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C32" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11852,13 +12072,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C33" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11866,13 +12086,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C34" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11880,13 +12100,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C35" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11894,13 +12114,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11908,13 +12128,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C37" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11922,13 +12142,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C38" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -11936,13 +12156,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C39" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11950,13 +12170,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C40" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11967,10 +12187,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11978,13 +12198,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C42" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11992,13 +12212,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12006,13 +12226,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C44" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12020,13 +12240,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C45" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12037,10 +12257,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12048,13 +12268,13 @@
         <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12062,13 +12282,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C48" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D48" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12076,13 +12296,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C49" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12090,13 +12310,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C50" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12104,10 +12324,10 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12115,13 +12335,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12129,13 +12349,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C53" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12143,13 +12363,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C54" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12157,13 +12377,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C55" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12171,13 +12391,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C56" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12185,13 +12405,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C57" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12199,13 +12419,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C58" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12213,13 +12433,13 @@
         <v>241</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C59" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12227,13 +12447,13 @@
         <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="C60" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12241,13 +12461,13 @@
         <v>244</v>
       </c>
       <c r="B61" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C61" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12255,13 +12475,13 @@
         <v>501</v>
       </c>
       <c r="B62" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C62" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12269,13 +12489,13 @@
         <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C63" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12283,13 +12503,13 @@
         <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C64" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12297,13 +12517,13 @@
         <v>504</v>
       </c>
       <c r="B65" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="C65" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12311,13 +12531,13 @@
         <v>505</v>
       </c>
       <c r="B66" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C66" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12328,10 +12548,10 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>699</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>417</v>
+        <v>695</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>745</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12339,13 +12559,13 @@
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C68" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12356,10 +12576,10 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12367,13 +12587,13 @@
         <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="C70" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12381,937 +12601,1035 @@
         <v>510</v>
       </c>
       <c r="B71" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C71" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D71" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B72" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C72" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C73" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B74" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C74" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B75" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C75" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B76" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B77" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C77" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B78" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C78" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B80" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C80" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B81" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C81" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B82" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C82" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="B83" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C83" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C84" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B85" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C85" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C86" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B87" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C87" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C88" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B89" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C89" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B90" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C90" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B91" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C91" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C92" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B93" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C93" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B94" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C94" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B95" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B96" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C96" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C97" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B98" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C98" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B99" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C99" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B100" t="s">
         <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B101" t="s">
         <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B102" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C102" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B103" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C103" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B104" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C104" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C106" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B108" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C108" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C109" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B110" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="C110" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B111" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C111" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B112" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C112" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B114" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C114" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B115" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C115" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B116" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C116" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D116" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B117" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C117" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D117" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B118" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C118" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D118" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B119" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C119" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D119" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B120" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C120" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D120" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C121" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D121" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B122" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C122" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D122" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B123" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="C123" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D123" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B124" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C124" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D124" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B125" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="C125" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D125" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B126" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="C126" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D126" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B127" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="C127" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D127" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B128" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="C128" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D128" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B129" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="C129" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D129" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B130" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C130" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D130" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B131" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C131" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D131" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B132" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C132" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D132" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B133" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="C133" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D133" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B134" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="C134" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D134" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B135" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C135" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D135" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B136" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C136" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D136" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="B137" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="C137" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D137" t="s">
-        <v>727</v>
+        <v>721</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="B138" t="s">
+        <v>744</v>
+      </c>
+      <c r="C138" t="s">
+        <v>695</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="B139" t="s">
+        <v>684</v>
+      </c>
+      <c r="C139" t="s">
+        <v>686</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B140" t="s">
+        <v>751</v>
+      </c>
+      <c r="C140" t="s">
+        <v>695</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="B141" t="s">
+        <v>684</v>
+      </c>
+      <c r="C141" t="s">
+        <v>686</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="B142" t="s">
+        <v>754</v>
+      </c>
+      <c r="C142" t="s">
+        <v>686</v>
+      </c>
+      <c r="D142" s="19" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="12" t="s">
+        <v>756</v>
+      </c>
+      <c r="B143" t="s">
+        <v>365</v>
+      </c>
+      <c r="C143" t="s">
+        <v>686</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="12" t="s">
+        <v>757</v>
+      </c>
+      <c r="B144" t="s">
+        <v>591</v>
+      </c>
+      <c r="C144" t="s">
+        <v>686</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>759</v>
       </c>
     </row>
   </sheetData>
@@ -13320,7 +13638,11 @@
       <sortCondition ref="A1:A115"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="D67" r:id="rId1" xr:uid="{59EFEB55-B7A4-4807-A75B-EA48D4BA0ABA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -13362,7 +13684,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13447,7 +13769,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13631,7 +13953,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -13639,7 +13961,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13647,7 +13969,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13655,7 +13977,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13663,7 +13985,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13689,50 +14011,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36499D2F-D5DD-4779-929B-6BA97A3720EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDA6B45-D2A6-4EDA-9DC5-A47702197CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2046" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="778">
   <si>
     <t>id</t>
   </si>
@@ -840,9 +840,6 @@
     <t>Time to Xth Pull Request</t>
   </si>
   <si>
-    <t>Time to 10th PR; Time to 1st and 10th PR; Time to First Commit</t>
-  </si>
-  <si>
     <t xml:space="preserve">Is a metric that measures the time it takes for a new engineer to create their 1st and 10th pull request (PR) after joining a development team or platform (e.g., GitHub). </t>
   </si>
   <si>
@@ -951,12 +948,6 @@
     <t>Velocity; Developer Velocity</t>
   </si>
   <si>
-    <t>Technical Debt</t>
-  </si>
-  <si>
-    <t>Number of Comments Left; PR Review Comments and Requests for Changes</t>
-  </si>
-  <si>
     <t>9; 31</t>
   </si>
   <si>
@@ -1425,9 +1416,6 @@
     <t>501; 131</t>
   </si>
   <si>
-    <t>501m; 131l</t>
-  </si>
-  <si>
     <t>31; 131</t>
   </si>
   <si>
@@ -1440,9 +1428,6 @@
     <t>70; 131</t>
   </si>
   <si>
-    <t>131f; 131g</t>
-  </si>
-  <si>
     <t>105; 234; 235; 131</t>
   </si>
   <si>
@@ -1653,18 +1638,12 @@
     <t xml:space="preserve">5; 501; 115; 183; </t>
   </si>
   <si>
-    <t>202a; 131i; 131g</t>
-  </si>
-  <si>
     <t>501b; 501d</t>
   </si>
   <si>
     <t>160; 501; 146</t>
   </si>
   <si>
-    <t>170; 146b; 131l</t>
-  </si>
-  <si>
     <t>506; 131; 146; 183; 146</t>
   </si>
   <si>
@@ -1995,9 +1974,6 @@
     <t>Time From Creating a Patch to Patch Release; Time to Value; Time to Merge (TTM); PR Cycle Time</t>
   </si>
   <si>
-    <t>501m; 131i; 501d; 209; 510; 511b; 511r; 511m; 511h; 511q; 511p</t>
-  </si>
-  <si>
     <t>Unit Test Quality; Code Quality; Process Quality; System Quality; Code Maintainability</t>
   </si>
   <si>
@@ -2046,9 +2022,6 @@
     <t>Friction</t>
   </si>
   <si>
-    <t>511b; 511l</t>
-  </si>
-  <si>
     <t>Monitors friction introduced or removed across the developer workflow.</t>
   </si>
   <si>
@@ -2115,9 +2088,6 @@
     <t>Chen (2026)</t>
   </si>
   <si>
-    <t>504; 11; 96; 214; 513</t>
-  </si>
-  <si>
     <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 232; 513</t>
   </si>
   <si>
@@ -2250,9 +2220,6 @@
     <t>504; 214; 6; 501; 240; 183; 503</t>
   </si>
   <si>
-    <t>501n; 501j; 501b; 203; 6a; 501m</t>
-  </si>
-  <si>
     <t>both</t>
   </si>
   <si>
@@ -2362,9 +2329,6 @@
   </si>
   <si>
     <t>https://linearb.io/blog/how-meta-measures-coding-time</t>
-  </si>
-  <si>
-    <t>Lloyds</t>
   </si>
   <si>
     <t>516c</t>
@@ -2402,6 +2366,75 @@
   <si>
     <t>The proportion of a developer's working time spent on inner-loop activities (coding, building, unit testing) vs. outer-loop activities (integration testing, releasing, deployment). Typically collected via self-report survey or time-tracking tools.
 Software development activities can be arranged in two loops. The inner loop covers activities directly related to creating the product: coding, building, and unit testing. The outer loop covers tasks needed to push code to production: integration testing, releasing, and deployment. Maximizing inner-loop time is desirable — it directly generates value and is what most developers find most engaging. Better tooling and automation for outer-loop activities frees up more time for inner-loop work.</t>
+  </si>
+  <si>
+    <t>517a</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?reload=9&amp;app=desktop&amp;v=GG8JLosF_AI</t>
+  </si>
+  <si>
+    <t>501n; 501j; 501b; 203; 6a; 501m; 517a</t>
+  </si>
+  <si>
+    <t>517b</t>
+  </si>
+  <si>
+    <t>Kanat-Alexander (2025)</t>
+  </si>
+  <si>
+    <t>https://www.codesimplicity.com/post/what-makes-a-great-developer-experience/</t>
+  </si>
+  <si>
+    <t>202a; 131i; 131g; 516c</t>
+  </si>
+  <si>
+    <t>Time to First Commit; Time to technical ability to commit</t>
+  </si>
+  <si>
+    <t>501m; 131i; 501d; 209; 510; 511b; 511r; 511m; 511h; 511q; 511p; 517a; 516c</t>
+  </si>
+  <si>
+    <t>131f; 131g; 516c</t>
+  </si>
+  <si>
+    <t>Technical Debt; time spent remediating tech debt</t>
+  </si>
+  <si>
+    <t>501j; 516c</t>
+  </si>
+  <si>
+    <t>170; 146b; 131l; 517a; 516c</t>
+  </si>
+  <si>
+    <t>501h; 516c</t>
+  </si>
+  <si>
+    <t>501n; 516c</t>
+  </si>
+  <si>
+    <t>Number of Comments Left; PR Review Comments and Requests for Changes; PRs merged per active developer per week</t>
+  </si>
+  <si>
+    <t>32a; 516c</t>
+  </si>
+  <si>
+    <t>501m; 131l; 516c</t>
+  </si>
+  <si>
+    <t>Lloyds Banking Group</t>
+  </si>
+  <si>
+    <t>511b; 511l; 516c</t>
+  </si>
+  <si>
+    <t>ease to access tools, ease to access applications</t>
+  </si>
+  <si>
+    <t>504; 11; 96; 214; 513; 517b</t>
   </si>
 </sst>
 </file>
@@ -2481,7 +2514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2532,9 +2565,11 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3264,16 +3299,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>258</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>259</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3291,25 +3326,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3323,16 +3358,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3365,16 +3400,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R2" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3397,7 +3432,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3430,13 +3465,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R3" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>9</v>
@@ -3453,16 +3488,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>465</v>
+        <v>767</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3484,7 +3519,7 @@
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="1"/>
@@ -3492,16 +3527,16 @@
       </c>
       <c r="O4" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R4" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>9</v>
@@ -3515,22 +3550,22 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3560,13 +3595,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R5" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>9</v>
@@ -3592,7 +3627,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3625,13 +3660,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R6" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>9</v>
@@ -3648,16 +3683,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -3693,10 +3728,10 @@
         <v>127</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R7" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>9</v>
@@ -3722,7 +3757,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -3755,13 +3790,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R8" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>9</v>
@@ -3778,7 +3813,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E9" s="15">
         <v>501</v>
@@ -3787,7 +3822,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -3820,13 +3855,13 @@
         <v>2</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R9" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>9</v>
@@ -3843,7 +3878,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E10" s="15">
         <v>501</v>
@@ -3852,7 +3887,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3885,13 +3920,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R10" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>9</v>
@@ -3908,16 +3943,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -3950,13 +3985,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R11" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>9</v>
@@ -3973,16 +4008,16 @@
         <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>520</v>
+        <v>768</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>50</v>
@@ -4004,7 +4039,7 @@
       </c>
       <c r="M12" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="1"/>
@@ -4012,16 +4047,16 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R12" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>9</v>
@@ -4035,10 +4070,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="E13" s="15">
         <v>131</v>
@@ -4047,7 +4082,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -4083,10 +4118,10 @@
         <v>127</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R13" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>9</v>
@@ -4100,19 +4135,19 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -4145,13 +4180,13 @@
         <v>26</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R14" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>9</v>
@@ -4165,22 +4200,22 @@
         <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>671</v>
+        <v>777</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4203,20 +4238,20 @@
       </c>
       <c r="N15" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="14" t="s">
         <v>127</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R15" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>9</v>
@@ -4233,16 +4268,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4275,13 +4310,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R16" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>9</v>
@@ -4295,19 +4330,19 @@
         <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>50</v>
@@ -4340,13 +4375,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R17" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>9</v>
@@ -4372,7 +4407,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4405,13 +4440,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R18" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>9</v>
@@ -4431,13 +4466,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>73</v>
@@ -4470,13 +4505,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R19" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>9</v>
@@ -4493,7 +4528,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E20" s="15">
         <v>131</v>
@@ -4502,7 +4537,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>73</v>
@@ -4535,13 +4570,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R20" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>9</v>
@@ -4555,19 +4590,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>631</v>
+        <v>764</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4589,7 +4624,7 @@
       </c>
       <c r="M21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N21" s="3">
         <f t="shared" si="1"/>
@@ -4597,16 +4632,16 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P21" s="14" t="s">
         <v>127</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R21" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>9</v>
@@ -4620,7 +4655,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>9</v>
@@ -4632,7 +4667,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>34</v>
@@ -4665,13 +4700,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R22" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>9</v>
@@ -4688,16 +4723,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>73</v>
@@ -4733,10 +4768,10 @@
         <v>127</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R23" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>9</v>
@@ -4750,19 +4785,19 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D24" s="14">
         <v>170</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>34</v>
@@ -4795,13 +4830,13 @@
         <v>4</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R24" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>9</v>
@@ -4818,7 +4853,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E25" s="15">
         <v>501</v>
@@ -4827,7 +4862,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>73</v>
@@ -4860,13 +4895,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R25" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>9</v>
@@ -4883,16 +4918,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4925,13 +4960,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R26" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>9</v>
@@ -4945,19 +4980,19 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -4990,13 +5025,13 @@
         <v>8</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R27" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>9</v>
@@ -5013,19 +5048,19 @@
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -5055,13 +5090,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R28" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>9</v>
@@ -5075,22 +5110,22 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>641</v>
+        <v>633</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
@@ -5123,10 +5158,10 @@
         <v>127</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R29" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>9</v>
@@ -5152,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5185,13 +5220,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R30" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>9</v>
@@ -5205,19 +5240,19 @@
         <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5253,10 +5288,10 @@
         <v>127</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R31" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>9</v>
@@ -5273,16 +5308,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5315,13 +5350,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R32" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>9</v>
@@ -5338,19 +5373,19 @@
         <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5383,10 +5418,10 @@
         <v>127</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R33" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>9</v>
@@ -5400,22 +5435,22 @@
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
@@ -5445,13 +5480,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R34" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>9</v>
@@ -5465,19 +5500,19 @@
         <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
@@ -5510,13 +5545,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R35" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>9</v>
@@ -5533,19 +5568,19 @@
         <v>9</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5575,13 +5610,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R36" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>9</v>
@@ -5595,19 +5630,19 @@
         <v>113</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5643,10 +5678,10 @@
         <v>127</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R37" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>9</v>
@@ -5666,13 +5701,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5705,13 +5740,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R38" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>9</v>
@@ -5731,13 +5766,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -5773,10 +5808,10 @@
         <v>127</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R39" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>9</v>
@@ -5787,25 +5822,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>716</v>
+        <v>758</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5824,7 +5859,7 @@
       </c>
       <c r="M40" s="3">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N40" s="3">
         <f t="shared" si="5"/>
@@ -5832,19 +5867,19 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R40" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5867,7 +5902,7 @@
         <v>124</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5900,13 +5935,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R41" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>9</v>
@@ -5932,7 +5967,7 @@
         <v>126</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>15</v>
@@ -5965,13 +6000,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R42" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>9</v>
@@ -5985,22 +6020,22 @@
         <v>127</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>128</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -6030,13 +6065,13 @@
         <v>4</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R43" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>9</v>
@@ -6062,7 +6097,7 @@
         <v>130</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -6095,13 +6130,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R44" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>9</v>
@@ -6115,22 +6150,22 @@
         <v>131</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6163,13 +6198,13 @@
         <v>127</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R45" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S45" s="14" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -6180,22 +6215,22 @@
         <v>132</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>133</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I46" s="3">
         <f>VLOOKUP(H46,cardsort_group_IDs!A:B,2,0)</f>
@@ -6228,13 +6263,13 @@
         <v>127</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R46" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S46" s="14" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6248,16 +6283,16 @@
         <v>136</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>728</v>
+        <v>717</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>137</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -6290,13 +6325,13 @@
         <v>11</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R47" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>9</v>
@@ -6310,19 +6345,19 @@
         <v>138</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>140</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>34</v>
@@ -6358,10 +6393,10 @@
         <v>127</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R48" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>9</v>
@@ -6387,7 +6422,7 @@
         <v>142</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6420,13 +6455,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R49" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>9</v>
@@ -6440,19 +6475,19 @@
         <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -6485,13 +6520,13 @@
         <v>16</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R50" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>9</v>
@@ -6505,7 +6540,7 @@
         <v>145</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>9</v>
@@ -6517,7 +6552,7 @@
         <v>146</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>50</v>
@@ -6550,13 +6585,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R51" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>9</v>
@@ -6567,22 +6602,22 @@
         <v>67</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>147</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>50</v>
@@ -6615,13 +6650,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R52" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>9</v>
@@ -6635,19 +6670,19 @@
         <v>148</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>149</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>73</v>
@@ -6680,13 +6715,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R53" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>9</v>
@@ -6700,19 +6735,19 @@
         <v>150</v>
       </c>
       <c r="C54" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>275</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E54" s="15" t="s">
-        <v>276</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>34</v>
@@ -6745,13 +6780,13 @@
         <v>2</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R54" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>9</v>
@@ -6768,16 +6803,16 @@
         <v>9</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>153</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -6810,13 +6845,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R55" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>9</v>
@@ -6833,16 +6868,16 @@
         <v>9</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>10</v>
@@ -6875,13 +6910,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R56" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>9</v>
@@ -6898,16 +6933,16 @@
         <v>9</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>158</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
@@ -6940,13 +6975,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R57" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>9</v>
@@ -6972,7 +7007,7 @@
         <v>161</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -7005,13 +7040,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R58" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>9</v>
@@ -7028,7 +7063,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="E59" s="15">
         <v>183</v>
@@ -7037,7 +7072,7 @@
         <v>163</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
@@ -7070,13 +7105,13 @@
         <v>2</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R59" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>9</v>
@@ -7090,19 +7125,19 @@
         <v>164</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>165</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7135,13 +7170,13 @@
         <v>2</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R60" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>9</v>
@@ -7158,19 +7193,19 @@
         <v>167</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>168</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I61" s="3">
         <f>VLOOKUP(H61,cardsort_group_IDs!A:B,2,0)</f>
@@ -7203,10 +7238,10 @@
         <v>127</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R61" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>9</v>
@@ -7223,16 +7258,16 @@
         <v>9</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>170</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>73</v>
@@ -7268,10 +7303,10 @@
         <v>127</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R62" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>9</v>
@@ -7297,7 +7332,7 @@
         <v>172</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>73</v>
@@ -7330,13 +7365,13 @@
         <v>1</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R63" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S63" s="14" t="s">
         <v>9</v>
@@ -7353,7 +7388,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E64" s="15">
         <v>202</v>
@@ -7362,7 +7397,7 @@
         <v>174</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>34</v>
@@ -7395,13 +7430,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R64" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S64" s="14" t="s">
         <v>9</v>
@@ -7427,7 +7462,7 @@
         <v>176</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>10</v>
@@ -7460,13 +7495,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R65" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S65" s="14" t="s">
         <v>9</v>
@@ -7480,22 +7515,22 @@
         <v>177</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>639</v>
+        <v>631</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>640</v>
+        <v>632</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>178</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I66" s="3">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
@@ -7528,10 +7563,10 @@
         <v>127</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R66" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S66" s="14" t="s">
         <v>9</v>
@@ -7548,7 +7583,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E67" s="15">
         <v>501</v>
@@ -7557,7 +7592,7 @@
         <v>179</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>21</v>
@@ -7590,13 +7625,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R67" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S67" s="14" t="s">
         <v>9</v>
@@ -7613,7 +7648,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>9</v>
@@ -7622,7 +7657,7 @@
         <v>181</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>15</v>
@@ -7655,13 +7690,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R68" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S68" s="14" t="s">
         <v>9</v>
@@ -7678,16 +7713,16 @@
         <v>9</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>424</v>
+        <v>769</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>183</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7709,7 +7744,7 @@
       </c>
       <c r="M69" s="3">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="3">
         <f t="shared" si="9"/>
@@ -7717,16 +7752,16 @@
       </c>
       <c r="O69" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R69" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S69" s="14" t="s">
         <v>9</v>
@@ -7740,19 +7775,19 @@
         <v>184</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>512</v>
+        <v>772</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>185</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>34</v>
@@ -7774,7 +7809,7 @@
       </c>
       <c r="M70" s="3">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="3">
         <f t="shared" si="9"/>
@@ -7782,16 +7817,16 @@
       </c>
       <c r="O70" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q70" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R70" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S70" s="14" t="s">
         <v>9</v>
@@ -7808,16 +7843,16 @@
         <v>9</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>441</v>
+        <v>773</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>187</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>34</v>
@@ -7839,7 +7874,7 @@
       </c>
       <c r="M71" s="3">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N71" s="3">
         <f t="shared" si="9"/>
@@ -7847,16 +7882,16 @@
       </c>
       <c r="O71" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R71" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S71" s="14" t="s">
         <v>9</v>
@@ -7870,19 +7905,19 @@
         <v>188</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>189</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>34</v>
@@ -7918,10 +7953,10 @@
         <v>127</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R72" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S72" s="14" t="s">
         <v>9</v>
@@ -7935,19 +7970,19 @@
         <v>190</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>191</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -7980,13 +8015,13 @@
         <v>4</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R73" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S73" s="14" t="s">
         <v>9</v>
@@ -8003,16 +8038,16 @@
         <v>9</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>193</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>50</v>
@@ -8045,13 +8080,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q74" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R74" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S74" s="14" t="s">
         <v>9</v>
@@ -8077,7 +8112,7 @@
         <v>195</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8110,13 +8145,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R75" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>9</v>
@@ -8130,19 +8165,19 @@
         <v>196</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>197</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>73</v>
@@ -8175,13 +8210,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R76" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S76" s="14" t="s">
         <v>9</v>
@@ -8198,16 +8233,16 @@
         <v>199</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>200</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>21</v>
@@ -8240,13 +8275,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R77" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S77" s="14" t="s">
         <v>9</v>
@@ -8272,7 +8307,7 @@
         <v>202</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8305,13 +8340,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q78" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R78" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>9</v>
@@ -8325,7 +8360,7 @@
         <v>203</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D79" s="12">
         <v>209</v>
@@ -8337,7 +8372,7 @@
         <v>204</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>10</v>
@@ -8370,13 +8405,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R79" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S79" s="14" t="s">
         <v>9</v>
@@ -8402,7 +8437,7 @@
         <v>206</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>10</v>
@@ -8435,13 +8470,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R80" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S80" s="14" t="s">
         <v>9</v>
@@ -8467,7 +8502,7 @@
         <v>208</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>10</v>
@@ -8500,13 +8535,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R81" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S81" s="14" t="s">
         <v>9</v>
@@ -8523,7 +8558,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E82" s="15">
         <v>501</v>
@@ -8532,7 +8567,7 @@
         <v>211</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8565,13 +8600,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R82" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S82" s="14" t="s">
         <v>9</v>
@@ -8588,7 +8623,7 @@
         <v>213</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>9</v>
@@ -8597,10 +8632,10 @@
         <v>214</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I83" s="3">
         <f>VLOOKUP(H83,cardsort_group_IDs!A:B,2,0)</f>
@@ -8630,13 +8665,13 @@
         <v>2</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R83" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S83" s="14" t="s">
         <v>9</v>
@@ -8650,19 +8685,19 @@
         <v>215</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>216</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>21</v>
@@ -8695,13 +8730,13 @@
         <v>4</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q84" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R84" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S84" s="14" t="s">
         <v>9</v>
@@ -8718,16 +8753,16 @@
         <v>9</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>218</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8760,13 +8795,13 @@
         <v>7</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q85" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R85" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S85" s="14" t="s">
         <v>9</v>
@@ -8780,19 +8815,19 @@
         <v>219</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8825,13 +8860,13 @@
         <v>8</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q86" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R86" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S86" s="14" t="s">
         <v>9</v>
@@ -8845,19 +8880,19 @@
         <v>221</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>222</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8890,13 +8925,13 @@
         <v>8</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q87" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R87" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S87" s="14" t="s">
         <v>9</v>
@@ -8910,22 +8945,22 @@
         <v>223</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>224</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I88" s="3">
         <f>VLOOKUP(H88,cardsort_group_IDs!A:B,2,0)</f>
@@ -8958,10 +8993,10 @@
         <v>127</v>
       </c>
       <c r="Q88" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R88" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S88" s="14" t="s">
         <v>9</v>
@@ -8975,19 +9010,19 @@
         <v>226</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>227</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>55</v>
@@ -9023,10 +9058,10 @@
         <v>127</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R89" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S89" s="14" t="s">
         <v>9</v>
@@ -9052,7 +9087,7 @@
         <v>229</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>50</v>
@@ -9085,13 +9120,13 @@
         <v>1</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q90" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R90" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S90" s="14" t="s">
         <v>9</v>
@@ -9105,19 +9140,19 @@
         <v>230</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>283</v>
+        <v>766</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>446</v>
+        <v>765</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>231</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>34</v>
@@ -9139,7 +9174,7 @@
       </c>
       <c r="M91" s="3">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <f t="shared" si="9"/>
@@ -9147,16 +9182,16 @@
       </c>
       <c r="O91" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R91" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S91" s="14" t="s">
         <v>9</v>
@@ -9170,19 +9205,19 @@
         <v>39</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>233</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>34</v>
@@ -9218,10 +9253,10 @@
         <v>127</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R92" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S92" s="14" t="s">
         <v>9</v>
@@ -9247,7 +9282,7 @@
         <v>235</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>21</v>
@@ -9280,13 +9315,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R93" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S93" s="14" t="s">
         <v>9</v>
@@ -9303,7 +9338,7 @@
         <v>9</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E94" s="15">
         <v>501</v>
@@ -9312,7 +9347,7 @@
         <v>238</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>15</v>
@@ -9345,13 +9380,13 @@
         <v>2</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q94" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R94" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S94" s="14" t="s">
         <v>9</v>
@@ -9368,16 +9403,16 @@
         <v>9</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>240</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
@@ -9410,13 +9445,13 @@
         <v>3</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R95" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S95" s="14" t="s">
         <v>9</v>
@@ -9430,19 +9465,19 @@
         <v>241</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>644</v>
+        <v>636</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F96" s="4" t="s">
         <v>242</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>15</v>
@@ -9478,10 +9513,10 @@
         <v>127</v>
       </c>
       <c r="Q96" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R96" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S96" s="14" t="s">
         <v>9</v>
@@ -9495,19 +9530,19 @@
         <v>243</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>642</v>
+        <v>634</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>643</v>
+        <v>635</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>244</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9543,10 +9578,10 @@
         <v>127</v>
       </c>
       <c r="Q97" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R97" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S97" s="14" t="s">
         <v>9</v>
@@ -9560,22 +9595,22 @@
         <v>245</v>
       </c>
       <c r="C98" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="D98" s="14" t="s">
+        <v>762</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>720</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="D98" s="14" t="s">
-        <v>517</v>
-      </c>
-      <c r="E98" s="15" t="s">
-        <v>731</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="G98" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9594,7 +9629,7 @@
       </c>
       <c r="M98" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N98" s="3">
         <f t="shared" si="11"/>
@@ -9602,16 +9637,16 @@
       </c>
       <c r="O98" s="3">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q98" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R98" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S98" s="14" t="s">
         <v>9</v>
@@ -9622,22 +9657,22 @@
         <v>126</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E99" s="15">
         <v>501</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>55</v>
@@ -9670,39 +9705,39 @@
         <v>2</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R99" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S99" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>127</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>284</v>
+        <v>771</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>430</v>
+        <v>770</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>55</v>
@@ -9724,7 +9759,7 @@
       </c>
       <c r="M100" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N100" s="3">
         <f t="shared" si="11"/>
@@ -9732,16 +9767,16 @@
       </c>
       <c r="O100" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R100" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S100" s="14" t="s">
         <v>9</v>
@@ -9752,22 +9787,22 @@
         <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E101" s="15">
         <v>501</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>55</v>
@@ -9800,13 +9835,13 @@
         <v>2</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q101" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R101" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S101" s="14" t="s">
         <v>9</v>
@@ -9817,22 +9852,22 @@
         <v>129</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>55</v>
@@ -9868,10 +9903,10 @@
         <v>127</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R102" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S102" s="14" t="s">
         <v>9</v>
@@ -9882,25 +9917,25 @@
         <v>130</v>
       </c>
       <c r="B103" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="14" t="s">
+        <v>512</v>
+      </c>
+      <c r="E103" s="15" t="s">
+        <v>513</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="C103" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D103" s="14" t="s">
-        <v>518</v>
-      </c>
-      <c r="E103" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="F103" s="4" t="s">
-        <v>257</v>
-      </c>
       <c r="G103" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I103" s="3">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
@@ -9930,13 +9965,13 @@
         <v>5</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R103" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S103" s="14" t="s">
         <v>9</v>
@@ -9947,22 +9982,22 @@
         <v>134</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="G104" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -9998,10 +10033,10 @@
         <v>127</v>
       </c>
       <c r="Q104" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R104" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S104" s="14" t="s">
         <v>9</v>
@@ -10012,7 +10047,7 @@
         <v>135</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -10024,13 +10059,13 @@
         <v>183</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G105" t="s">
+        <v>702</v>
+      </c>
+      <c r="H105" t="s">
         <v>504</v>
-      </c>
-      <c r="G105" t="s">
-        <v>712</v>
-      </c>
-      <c r="H105" t="s">
-        <v>509</v>
       </c>
       <c r="I105" s="3">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
@@ -10060,13 +10095,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q105" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R105" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S105" s="14" t="s">
         <v>9</v>
@@ -10077,7 +10112,7 @@
         <v>136</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
@@ -10089,10 +10124,10 @@
         <v>240</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G106" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H106" t="s">
         <v>55</v>
@@ -10125,13 +10160,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q106" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R106" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S106" s="14" t="s">
         <v>9</v>
@@ -10142,25 +10177,25 @@
         <v>137</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="G107" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H107" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I107" s="3">
         <f>VLOOKUP(H107,cardsort_group_IDs!A:B,2,0)</f>
@@ -10190,13 +10225,13 @@
         <v>6</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R107" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S107" s="14" t="s">
         <v>9</v>
@@ -10207,10 +10242,10 @@
         <v>138</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>9</v>
@@ -10219,10 +10254,10 @@
         <v>236</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="G108" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -10255,13 +10290,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R108" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S108" s="14" t="s">
         <v>9</v>
@@ -10272,7 +10307,7 @@
         <v>139</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10284,10 +10319,10 @@
         <v>9</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -10320,13 +10355,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R109" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S109" s="14" t="s">
         <v>9</v>
@@ -10337,22 +10372,22 @@
         <v>140</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>15</v>
@@ -10385,13 +10420,13 @@
         <v>18</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q110" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R110" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S110" s="14">
         <v>2</v>
@@ -10402,22 +10437,22 @@
         <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>55</v>
@@ -10450,13 +10485,13 @@
         <v>3</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R111" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S111" s="14">
         <v>129</v>
@@ -10467,22 +10502,22 @@
         <v>142</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>55</v>
@@ -10515,13 +10550,13 @@
         <v>2</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R112" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S112" s="14">
         <v>19</v>
@@ -10532,22 +10567,22 @@
         <v>143</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
@@ -10580,13 +10615,13 @@
         <v>5</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R113" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S113" s="14" t="s">
         <v>9</v>
@@ -10597,22 +10632,22 @@
         <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>15</v>
@@ -10645,16 +10680,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R114" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S114" s="14" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10662,22 +10697,22 @@
         <v>145</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -10710,16 +10745,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R115" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S115" s="14" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10727,22 +10762,22 @@
         <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D116" t="s">
+        <v>606</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="D116" t="s">
-        <v>613</v>
-      </c>
-      <c r="E116" s="15" t="s">
-        <v>658</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>615</v>
-      </c>
       <c r="G116" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -10775,16 +10810,16 @@
         <v>6</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="Q116" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R116" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S116" s="14" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -10792,22 +10827,22 @@
         <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10840,16 +10875,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="Q117" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R117" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S117" s="14" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10857,22 +10892,22 @@
         <v>148</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D118" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>10</v>
@@ -10908,13 +10943,13 @@
         <v>127</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R118" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S118" s="14" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -10922,22 +10957,22 @@
         <v>149</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -10973,39 +11008,39 @@
         <v>127</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R119" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S119" s="14" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>150</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>9</v>
+        <v>776</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>648</v>
+        <v>775</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
@@ -11024,7 +11059,7 @@
       </c>
       <c r="M120" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N120" s="3">
         <f t="shared" si="11"/>
@@ -11032,19 +11067,19 @@
       </c>
       <c r="O120" s="3">
         <f t="shared" ref="O120" si="23">SUM(M120:N120)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P120" s="14" t="s">
         <v>127</v>
       </c>
       <c r="Q120" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R120" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S120" s="14" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11052,22 +11087,22 @@
         <v>151</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11103,10 +11138,10 @@
         <v>127</v>
       </c>
       <c r="Q121" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R121" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S121" s="14" t="s">
         <v>9</v>
@@ -11117,7 +11152,7 @@
         <v>152</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
@@ -11126,16 +11161,16 @@
         <v>9</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11168,10 +11203,10 @@
         <v>127</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R122" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S122" s="14" t="s">
         <v>9</v>
@@ -11182,7 +11217,7 @@
         <v>153</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11191,16 +11226,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F123" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11233,13 +11268,13 @@
         <v>127</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="R123" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S123" s="14" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -11247,7 +11282,7 @@
         <v>154</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>9</v>
@@ -11256,16 +11291,16 @@
         <v>9</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I124" s="3">
         <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
@@ -11298,13 +11333,13 @@
         <v>127</v>
       </c>
       <c r="Q124" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R124" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="S124" s="14" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
@@ -11312,7 +11347,7 @@
         <v>155</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>9</v>
@@ -11321,16 +11356,16 @@
         <v>9</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I125" s="3">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11360,13 +11395,13 @@
         <v>2</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q125" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R125" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S125" s="14" t="s">
         <v>9</v>
@@ -11377,22 +11412,22 @@
         <v>156</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="D126" s="14" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="E126" s="15" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>34</v>
@@ -11425,13 +11460,13 @@
         <v>2</v>
       </c>
       <c r="P126" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q126" s="14" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="R126" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="S126" s="14" t="s">
         <v>9</v>
@@ -11442,25 +11477,25 @@
         <v>157</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="C127" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="D127" s="14" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="E127" s="15" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="I127" s="3">
         <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
@@ -11490,16 +11525,16 @@
         <v>5</v>
       </c>
       <c r="P127" s="14" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="Q127" s="14" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="R127" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="S127" s="14" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
     </row>
   </sheetData>
@@ -11610,7 +11645,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D144"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
@@ -11621,16 +11656,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C1" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11638,13 +11673,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11652,27 +11687,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C4" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D4" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11680,13 +11715,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D5" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11694,13 +11729,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11708,13 +11743,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11722,13 +11757,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11736,13 +11771,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11750,13 +11785,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11764,13 +11799,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11778,13 +11813,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="C12" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D12" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11792,13 +11827,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C13" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11806,13 +11841,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C14" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11820,13 +11855,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="C15" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11834,13 +11869,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C16" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11848,13 +11883,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11862,13 +11897,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>536</v>
+      </c>
+      <c r="C18" t="s">
+        <v>685</v>
+      </c>
+      <c r="D18" t="s">
         <v>543</v>
-      </c>
-      <c r="C18" t="s">
-        <v>695</v>
-      </c>
-      <c r="D18" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11876,13 +11911,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11890,13 +11925,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C20" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11904,13 +11939,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C21" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11918,13 +11953,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C22" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11932,13 +11967,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C23" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11946,13 +11981,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11960,13 +11995,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C25" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11974,13 +12009,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C26" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11988,13 +12023,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C27" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12002,13 +12037,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C28" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12016,13 +12051,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C29" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12030,13 +12065,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12044,13 +12079,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="C31" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12058,13 +12093,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12072,13 +12107,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C33" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12086,13 +12121,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12100,13 +12135,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C35" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12114,13 +12149,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C36" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12128,13 +12163,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12142,13 +12177,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C38" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -12156,13 +12191,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C39" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12170,13 +12205,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C40" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12187,10 +12222,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12198,13 +12233,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C42" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12212,13 +12247,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C43" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12226,13 +12261,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="C44" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12240,13 +12275,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C45" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12257,10 +12292,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12271,10 +12306,10 @@
         <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12282,13 +12317,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C48" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D48" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12296,13 +12331,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C49" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12310,13 +12345,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C50" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12324,10 +12359,10 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12335,13 +12370,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C52" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12349,13 +12384,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C53" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12363,13 +12398,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C54" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12377,13 +12412,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C55" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12391,13 +12426,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C56" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12405,13 +12440,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C57" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12419,13 +12454,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C58" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12433,13 +12468,13 @@
         <v>241</v>
       </c>
       <c r="B59" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C59" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12447,13 +12482,13 @@
         <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C60" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12461,13 +12496,13 @@
         <v>244</v>
       </c>
       <c r="B61" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C61" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12475,13 +12510,13 @@
         <v>501</v>
       </c>
       <c r="B62" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C62" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12489,13 +12524,13 @@
         <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C63" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12503,13 +12538,13 @@
         <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C64" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12517,13 +12552,13 @@
         <v>504</v>
       </c>
       <c r="B65" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C65" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12531,13 +12566,13 @@
         <v>505</v>
       </c>
       <c r="B66" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C66" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12548,10 +12583,10 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>695</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>745</v>
+        <v>685</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12559,13 +12594,13 @@
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C68" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12576,10 +12611,10 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12587,13 +12622,13 @@
         <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="C70" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12601,1035 +12636,1063 @@
         <v>510</v>
       </c>
       <c r="B71" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C71" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D71" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C72" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C73" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="B74" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="C74" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C75" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s">
         <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C77" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B78" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C78" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C80" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C81" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C82" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C83" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C84" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B85" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C85" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C86" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C87" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B88" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C88" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C89" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B90" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C90" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C91" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C92" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C93" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C94" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B95" t="s">
         <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="B96" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C96" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C97" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C98" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C99" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B100" t="s">
         <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B101" t="s">
         <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B102" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C102" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C103" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B104" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="C104" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B106" t="s">
         <v>210</v>
       </c>
       <c r="C106" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B108" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="C108" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C109" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B110" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C110" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B111" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C111" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B112" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C112" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B114" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C115" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="C116" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D116" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="B117" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C117" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D117" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="B118" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C118" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D118" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B119" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C119" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D119" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B120" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="C120" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D120" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="B121" t="s">
         <v>210</v>
       </c>
       <c r="C121" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D121" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="B122" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C122" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D122" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="B123" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="C123" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D123" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="B124" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="C124" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D124" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="B125" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="C125" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D125" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="B126" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="C126" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D126" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="B127" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="C127" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D127" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="B128" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="C128" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D128" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="B129" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="C129" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D129" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="B130" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="C130" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D130" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="B131" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C131" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D131" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="B132" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C132" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="D132" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="B133" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="C133" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D133" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="B134" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="C134" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D134" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C135" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D135" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="B136" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="C136" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D136" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="B137" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="C137" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D137" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B138" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="C138" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D138" s="19" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="B139" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C139" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D139" s="19" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="B140" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="C140" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="D140" s="19" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="B141" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C141" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D141" s="19" t="s">
-        <v>753</v>
+        <v>742</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="B142" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="C142" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D142" s="19" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B143" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C143" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D143" s="19" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B144" t="s">
+        <v>584</v>
+      </c>
+      <c r="C144" t="s">
+        <v>676</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="B145" t="s">
+        <v>756</v>
+      </c>
+      <c r="C145" t="s">
+        <v>676</v>
+      </c>
+      <c r="D145" s="20" t="s">
         <v>757</v>
       </c>
-      <c r="B144" t="s">
-        <v>591</v>
-      </c>
-      <c r="C144" t="s">
-        <v>686</v>
-      </c>
-      <c r="D144" s="19" t="s">
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="12" t="s">
         <v>759</v>
+      </c>
+      <c r="B146" t="s">
+        <v>760</v>
+      </c>
+      <c r="C146" t="s">
+        <v>685</v>
+      </c>
+      <c r="D146" s="22" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -13640,9 +13703,11 @@
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="D67" r:id="rId1" xr:uid="{59EFEB55-B7A4-4807-A75B-EA48D4BA0ABA}"/>
+    <hyperlink ref="D145" r:id="rId2" xr:uid="{D917F0D9-8FA3-42FC-8D59-6D5DA7D992BF}"/>
+    <hyperlink ref="D146" r:id="rId3" xr:uid="{4212A9B2-9B1D-41C8-8E67-D931B1DC9F17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -13684,7 +13749,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -14011,50 +14076,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDDA6B45-D2A6-4EDA-9DC5-A47702197CFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB7680-23B3-4D06-92B1-D5AE3E75C3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -2514,7 +2514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2565,11 +2565,9 @@
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -12585,7 +12583,7 @@
       <c r="C67" t="s">
         <v>685</v>
       </c>
-      <c r="D67" s="21" t="s">
+      <c r="D67" s="20" t="s">
         <v>734</v>
       </c>
     </row>
@@ -13677,7 +13675,7 @@
       <c r="C145" t="s">
         <v>676</v>
       </c>
-      <c r="D145" s="20" t="s">
+      <c r="D145" s="19" t="s">
         <v>757</v>
       </c>
     </row>
@@ -13691,7 +13689,7 @@
       <c r="C146" t="s">
         <v>685</v>
       </c>
-      <c r="D146" s="22" t="s">
+      <c r="D146" s="19" t="s">
         <v>761</v>
       </c>
     </row>
@@ -13703,11 +13701,9 @@
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="D67" r:id="rId1" xr:uid="{59EFEB55-B7A4-4807-A75B-EA48D4BA0ABA}"/>
-    <hyperlink ref="D145" r:id="rId2" xr:uid="{D917F0D9-8FA3-42FC-8D59-6D5DA7D992BF}"/>
-    <hyperlink ref="D146" r:id="rId3" xr:uid="{4212A9B2-9B1D-41C8-8E67-D931B1DC9F17}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8CB8A3-5C8B-4EE7-BE73-5BB2CFCB5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB7680-23B3-4D06-92B1-D5AE3E75C3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="company_sizes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$126</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">urls!$A$1:$D$115</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2054" uniqueCount="778">
   <si>
     <t>id</t>
   </si>
@@ -469,9 +469,6 @@
     <t>Collaboration</t>
   </si>
   <si>
-    <t>Flow State</t>
-  </si>
-  <si>
     <t>Flow Through the System</t>
   </si>
   <si>
@@ -497,9 +494,6 @@
   </si>
   <si>
     <t>Inner / Outer Loop Time Spent</t>
-  </si>
-  <si>
-    <t>To identify specific areas for improvement, it’s helpful to think of the activities involved in software development as being arranged in two loops. An inner loop comprises activities directly related to creating the product: coding, building, and unit testing. An outer loop comprises other tasks developers must do to push their code to production: integration, integration testing, releasing, and deployment. From both a productivity and personal-experience standpoint, maximizing the amount of time developers spend in the inner loop is desirable: building products directly generates value and is what most developers are excited to do. Outer-loop activities are seen by most developers as necessary but generally unsatisfying chores. Putting time into better tooling and automation for the outer loop allows developers to spend more time on inner-loop activities.</t>
   </si>
   <si>
     <t>Interruptions</t>
@@ -846,9 +840,6 @@
     <t>Time to Xth Pull Request</t>
   </si>
   <si>
-    <t>Time to 10th PR; Time to 1st and 10th PR; Time to First Commit</t>
-  </si>
-  <si>
     <t xml:space="preserve">Is a metric that measures the time it takes for a new engineer to create their 1st and 10th pull request (PR) after joining a development team or platform (e.g., GitHub). </t>
   </si>
   <si>
@@ -912,9 +903,6 @@
     <t>Developer Build Time (P50 and P90); Build Time; NextJS Page Compilation Duration; Application/Package Build Duration; Build Time Efficiency</t>
   </si>
   <si>
-    <t>Diff Authoring Time (DAT); Diffs per Engineer (PRs or MRs); Commits Performed by Time; Time Spent per Task; Commit Count, Implementation Time per User Story; Task Completion Time; Coding Time; Time to Commit per LOC Changed</t>
-  </si>
-  <si>
     <t>Number of Blocked Tickets</t>
   </si>
   <si>
@@ -960,12 +948,6 @@
     <t>Velocity; Developer Velocity</t>
   </si>
   <si>
-    <t>Technical Debt</t>
-  </si>
-  <si>
-    <t>Number of Comments Left; PR Review Comments and Requests for Changes</t>
-  </si>
-  <si>
     <t>9; 31</t>
   </si>
   <si>
@@ -1353,9 +1335,6 @@
     <t>DORA Framework</t>
   </si>
   <si>
-    <t>https://www.mckinsey.com/industries/technology-media-and-telecommunications/our-insights/yes-you-can-measure-software-developer-productivity#/</t>
-  </si>
-  <si>
     <t>https://learn.microsoft.com/en-us/assessments/e50f7040-f235-4360-9d1d-cf753e12fed1/</t>
   </si>
   <si>
@@ -1437,9 +1416,6 @@
     <t>501; 131</t>
   </si>
   <si>
-    <t>501m; 131l</t>
-  </si>
-  <si>
     <t>31; 131</t>
   </si>
   <si>
@@ -1452,9 +1428,6 @@
     <t>70; 131</t>
   </si>
   <si>
-    <t>131f; 131g</t>
-  </si>
-  <si>
     <t>105; 234; 235; 131</t>
   </si>
   <si>
@@ -1665,18 +1638,12 @@
     <t xml:space="preserve">5; 501; 115; 183; </t>
   </si>
   <si>
-    <t>202a; 131i; 131g</t>
-  </si>
-  <si>
     <t>501b; 501d</t>
   </si>
   <si>
     <t>160; 501; 146</t>
   </si>
   <si>
-    <t>170; 146b; 131l</t>
-  </si>
-  <si>
     <t>506; 131; 146; 183; 146</t>
   </si>
   <si>
@@ -2007,9 +1974,6 @@
     <t>Time From Creating a Patch to Patch Release; Time to Value; Time to Merge (TTM); PR Cycle Time</t>
   </si>
   <si>
-    <t>501m; 131i; 501d; 209; 510; 511b; 511r; 511m; 511h; 511q; 511p</t>
-  </si>
-  <si>
     <t>Unit Test Quality; Code Quality; Process Quality; System Quality; Code Maintainability</t>
   </si>
   <si>
@@ -2058,9 +2022,6 @@
     <t>Friction</t>
   </si>
   <si>
-    <t>511b; 511l</t>
-  </si>
-  <si>
     <t>Monitors friction introduced or removed across the developer workflow.</t>
   </si>
   <si>
@@ -2127,9 +2088,6 @@
     <t>Chen (2026)</t>
   </si>
   <si>
-    <t>504; 11; 96; 214; 513</t>
-  </si>
-  <si>
     <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 232; 513</t>
   </si>
   <si>
@@ -2256,24 +2214,15 @@
     <t>quantitative</t>
   </si>
   <si>
-    <t>Deep Work; Focused Work; Focus Time; Uninterrupted Time</t>
-  </si>
-  <si>
     <t>The ability to work in focus or flow, i.e. uninterrupted, in meeting-free blocks that allow the developer to concentrate deeply on their work. Often reported as percentage of total time or average time.</t>
   </si>
   <si>
     <t>504; 214; 6; 501; 240; 183; 503</t>
   </si>
   <si>
-    <t>501n; 501j; 501b; 203; 6a; 501m</t>
-  </si>
-  <si>
     <t>both</t>
   </si>
   <si>
-    <t>59</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
@@ -2326,13 +2275,173 @@
   </si>
   <si>
     <t>514; 509</t>
+  </si>
+  <si>
+    <t>Diff Authoring Time (DAT); PR Authoring Time; Diffs per Engineer (PRs or MRs); Commits Performed by Time; Time Spent per Task; Commit Count, Implementation Time per User Story; Task Completion Time; Coding Time; Time to Commit per LOC Changed</t>
+  </si>
+  <si>
+    <t>Diff Risk Score</t>
+  </si>
+  <si>
+    <t>PR Risk Score</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/pdf/10.1145/3722216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Predicts the likelihood of a code change (diff) causing a production incident. </t>
+  </si>
+  <si>
+    <t>515b</t>
+  </si>
+  <si>
+    <t>515a</t>
+  </si>
+  <si>
+    <t>https://engineering.fb.com/2025/08/06/developer-tools/diff-risk-score-drs-ai-risk-aware-software-development-meta/</t>
+  </si>
+  <si>
+    <t>Mockus (2025)</t>
+  </si>
+  <si>
+    <t>https://www.mckinsey.com/industries/technology-media-and-telecommunications/our-insights/yes-you-can-measure-software-developer-productivity</t>
+  </si>
+  <si>
+    <t>Time spent Coding</t>
+  </si>
+  <si>
+    <t>Active Coding Time; Coding Time; Focus Coding Time</t>
+  </si>
+  <si>
+    <t>The amount or proportion of a developer's working time actively spent writing or editing code, as measured by IDE telemetry. Excludes building, testing, meetings, and other non-coding activities. Helps to identify whether developers have sufficient uninterrupted time for core development work.</t>
+  </si>
+  <si>
+    <t>516a</t>
+  </si>
+  <si>
+    <t>https://ieeexplore.ieee.org/document/8666786</t>
+  </si>
+  <si>
+    <t>Meyer (2021)</t>
+  </si>
+  <si>
+    <t>516b</t>
+  </si>
+  <si>
+    <t>https://linearb.io/blog/how-meta-measures-coding-time</t>
+  </si>
+  <si>
+    <t>516c</t>
+  </si>
+  <si>
+    <t>516d</t>
+  </si>
+  <si>
+    <t>516e</t>
+  </si>
+  <si>
+    <t>https://dpe.org/sessions/hilary-lanham-tom-kelk/measuring-engineering-productivity-from-a-standing-start-a-330-year-old-banks-journey/</t>
+  </si>
+  <si>
+    <t>https://devops.com/how-to-get-developer-productivity-engineering-right/</t>
+  </si>
+  <si>
+    <t>516b; 516c; 516d; 516e</t>
+  </si>
+  <si>
+    <t>157</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>Focus Time</t>
+  </si>
+  <si>
+    <t>Flow State; Deep Work; Focused Work; Uninterrupted Time</t>
+  </si>
+  <si>
+    <t>59; 157</t>
+  </si>
+  <si>
+    <t>The proportion of a developer's working time spent on inner-loop activities (coding, building, unit testing) vs. outer-loop activities (integration testing, releasing, deployment). Typically collected via self-report survey or time-tracking tools.
+Software development activities can be arranged in two loops. The inner loop covers activities directly related to creating the product: coding, building, and unit testing. The outer loop covers tasks needed to push code to production: integration testing, releasing, and deployment. Maximizing inner-loop time is desirable — it directly generates value and is what most developers find most engaging. Better tooling and automation for outer-loop activities frees up more time for inner-loop work.</t>
+  </si>
+  <si>
+    <t>517a</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?reload=9&amp;app=desktop&amp;v=GG8JLosF_AI</t>
+  </si>
+  <si>
+    <t>501n; 501j; 501b; 203; 6a; 501m; 517a</t>
+  </si>
+  <si>
+    <t>517b</t>
+  </si>
+  <si>
+    <t>Kanat-Alexander (2025)</t>
+  </si>
+  <si>
+    <t>https://www.codesimplicity.com/post/what-makes-a-great-developer-experience/</t>
+  </si>
+  <si>
+    <t>202a; 131i; 131g; 516c</t>
+  </si>
+  <si>
+    <t>Time to First Commit; Time to technical ability to commit</t>
+  </si>
+  <si>
+    <t>501m; 131i; 501d; 209; 510; 511b; 511r; 511m; 511h; 511q; 511p; 517a; 516c</t>
+  </si>
+  <si>
+    <t>131f; 131g; 516c</t>
+  </si>
+  <si>
+    <t>Technical Debt; time spent remediating tech debt</t>
+  </si>
+  <si>
+    <t>501j; 516c</t>
+  </si>
+  <si>
+    <t>170; 146b; 131l; 517a; 516c</t>
+  </si>
+  <si>
+    <t>501h; 516c</t>
+  </si>
+  <si>
+    <t>501n; 516c</t>
+  </si>
+  <si>
+    <t>Number of Comments Left; PR Review Comments and Requests for Changes; PRs merged per active developer per week</t>
+  </si>
+  <si>
+    <t>32a; 516c</t>
+  </si>
+  <si>
+    <t>501m; 131l; 516c</t>
+  </si>
+  <si>
+    <t>Lloyds Banking Group</t>
+  </si>
+  <si>
+    <t>511b; 511l; 516c</t>
+  </si>
+  <si>
+    <t>ease to access tools, ease to access applications</t>
+  </si>
+  <si>
+    <t>504; 11; 96; 214; 513; 517b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2375,6 +2484,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2393,10 +2510,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2446,8 +2564,13 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="39">
@@ -3143,7 +3266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:S127"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3174,16 +3297,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3201,25 +3324,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="P1" s="17" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>705</v>
+        <v>691</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>710</v>
+        <v>696</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3233,16 +3356,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>703</v>
+        <v>689</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3275,16 +3398,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R2" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>704</v>
+        <v>690</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3307,7 +3430,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3340,13 +3463,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R3" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>9</v>
@@ -3363,16 +3486,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>469</v>
+        <v>767</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3394,7 +3517,7 @@
       </c>
       <c r="M4" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" s="3">
         <f t="shared" si="1"/>
@@ -3402,16 +3525,16 @@
       </c>
       <c r="O4" s="3">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R4" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>9</v>
@@ -3425,22 +3548,22 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3470,13 +3593,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R5" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>9</v>
@@ -3502,7 +3625,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3535,13 +3658,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R6" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>9</v>
@@ -3558,16 +3681,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -3600,13 +3723,13 @@
         <v>26</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R7" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>9</v>
@@ -3632,7 +3755,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -3665,13 +3788,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q8" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R8" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>9</v>
@@ -3688,7 +3811,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E9" s="15">
         <v>501</v>
@@ -3697,7 +3820,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -3730,13 +3853,13 @@
         <v>2</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R9" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>9</v>
@@ -3753,7 +3876,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="E10" s="15">
         <v>501</v>
@@ -3762,7 +3885,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3795,13 +3918,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R10" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>9</v>
@@ -3818,16 +3941,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -3860,13 +3983,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R11" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>9</v>
@@ -3883,16 +4006,16 @@
         <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>524</v>
+        <v>768</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>50</v>
@@ -3914,7 +4037,7 @@
       </c>
       <c r="M12" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12" s="3">
         <f t="shared" si="1"/>
@@ -3922,16 +4045,16 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R12" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>9</v>
@@ -3945,10 +4068,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="E13" s="15">
         <v>131</v>
@@ -3957,7 +4080,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -3990,13 +4113,13 @@
         <v>4</v>
       </c>
       <c r="P13" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R13" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>9</v>
@@ -4010,19 +4133,19 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -4055,13 +4178,13 @@
         <v>26</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R14" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>9</v>
@@ -4075,22 +4198,22 @@
         <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>675</v>
+        <v>777</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4113,20 +4236,20 @@
       </c>
       <c r="N15" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O15" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R15" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>9</v>
@@ -4143,16 +4266,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4185,13 +4308,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R16" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>9</v>
@@ -4205,19 +4328,19 @@
         <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>50</v>
@@ -4250,13 +4373,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R17" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>9</v>
@@ -4282,7 +4405,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4315,13 +4438,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R18" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>9</v>
@@ -4341,13 +4464,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>73</v>
@@ -4380,13 +4503,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R19" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>9</v>
@@ -4403,7 +4526,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="E20" s="15">
         <v>131</v>
@@ -4412,7 +4535,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>73</v>
@@ -4445,13 +4568,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R20" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>9</v>
@@ -4465,19 +4588,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>635</v>
+        <v>764</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4499,7 +4622,7 @@
       </c>
       <c r="M21" s="3">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N21" s="3">
         <f t="shared" si="1"/>
@@ -4507,16 +4630,16 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P21" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R21" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>9</v>
@@ -4530,7 +4653,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>9</v>
@@ -4542,7 +4665,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>34</v>
@@ -4575,13 +4698,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R22" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>9</v>
@@ -4598,16 +4721,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>640</v>
+        <v>628</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>729</v>
+        <v>712</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>73</v>
@@ -4640,13 +4763,13 @@
         <v>21</v>
       </c>
       <c r="P23" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R23" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>9</v>
@@ -4660,19 +4783,19 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D24" s="14">
         <v>170</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>34</v>
@@ -4705,13 +4828,13 @@
         <v>4</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R24" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>9</v>
@@ -4728,7 +4851,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="E25" s="15">
         <v>501</v>
@@ -4737,7 +4860,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>73</v>
@@ -4770,13 +4893,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R25" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>9</v>
@@ -4793,16 +4916,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4835,13 +4958,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R26" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>9</v>
@@ -4855,19 +4978,19 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -4900,13 +5023,13 @@
         <v>8</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R27" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>9</v>
@@ -4923,19 +5046,19 @@
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -4965,13 +5088,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R28" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>9</v>
@@ -4985,22 +5108,22 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>687</v>
+        <v>673</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>730</v>
+        <v>713</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
@@ -5030,13 +5153,13 @@
         <v>43</v>
       </c>
       <c r="P29" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R29" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>9</v>
@@ -5062,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5095,13 +5218,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R30" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>9</v>
@@ -5115,19 +5238,19 @@
         <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>270</v>
+        <v>725</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5160,13 +5283,13 @@
         <v>17</v>
       </c>
       <c r="P31" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R31" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>9</v>
@@ -5183,16 +5306,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5225,13 +5348,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R32" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>9</v>
@@ -5248,19 +5371,19 @@
         <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>732</v>
+        <v>715</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5290,13 +5413,13 @@
         <v>14</v>
       </c>
       <c r="P33" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R33" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>9</v>
@@ -5310,22 +5433,22 @@
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
@@ -5355,13 +5478,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R34" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>9</v>
@@ -5375,19 +5498,19 @@
         <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
@@ -5420,13 +5543,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R35" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>9</v>
@@ -5443,19 +5566,19 @@
         <v>9</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5485,13 +5608,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R36" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>9</v>
@@ -5505,19 +5628,19 @@
         <v>113</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5550,13 +5673,13 @@
         <v>3</v>
       </c>
       <c r="P37" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R37" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>9</v>
@@ -5576,13 +5699,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5615,13 +5738,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R38" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>9</v>
@@ -5641,13 +5764,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -5680,13 +5803,13 @@
         <v>2</v>
       </c>
       <c r="P39" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R39" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>9</v>
@@ -5697,25 +5820,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>123</v>
+        <v>751</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>718</v>
+        <v>752</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>721</v>
+        <v>758</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>720</v>
+        <v>705</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>719</v>
+        <v>704</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>722</v>
+        <v>706</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5734,7 +5857,7 @@
       </c>
       <c r="M40" s="3">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N40" s="3">
         <f t="shared" si="5"/>
@@ -5742,19 +5865,19 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="2"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R40" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>723</v>
+        <v>753</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5762,7 +5885,7 @@
         <v>51</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>9</v>
@@ -5774,10 +5897,10 @@
         <v>506</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5810,13 +5933,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R41" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>9</v>
@@ -5827,7 +5950,7 @@
         <v>54</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>9</v>
@@ -5839,10 +5962,10 @@
         <v>506</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>15</v>
@@ -5875,13 +5998,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R42" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>9</v>
@@ -5892,25 +6015,25 @@
         <v>56</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D43" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>433</v>
-      </c>
-      <c r="E43" s="15" t="s">
-        <v>536</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="G43" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -5940,13 +6063,13 @@
         <v>4</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R43" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>9</v>
@@ -5957,7 +6080,7 @@
         <v>57</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>9</v>
@@ -5969,10 +6092,10 @@
         <v>514</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -6005,42 +6128,42 @@
         <v>1</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R44" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="360" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="345" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>58</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>133</v>
+        <v>754</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>717</v>
+        <v>702</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6070,16 +6193,16 @@
         <v>4</v>
       </c>
       <c r="P45" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R45" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S45" s="14" t="s">
-        <v>9</v>
+        <v>749</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -6087,25 +6210,25 @@
         <v>59</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I46" s="3">
         <f>VLOOKUP(H46,cardsort_group_IDs!A:B,2,0)</f>
@@ -6135,16 +6258,16 @@
         <v>4</v>
       </c>
       <c r="P46" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R46" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S46" s="14" t="s">
-        <v>724</v>
+        <v>707</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6152,22 +6275,22 @@
         <v>62</v>
       </c>
       <c r="B47" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>629</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>717</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>641</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>734</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="G47" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -6200,13 +6323,13 @@
         <v>11</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R47" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>9</v>
@@ -6217,22 +6340,22 @@
         <v>63</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>658</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="G48" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>34</v>
@@ -6265,13 +6388,13 @@
         <v>4</v>
       </c>
       <c r="P48" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R48" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>9</v>
@@ -6282,7 +6405,7 @@
         <v>64</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>9</v>
@@ -6294,10 +6417,10 @@
         <v>9</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6330,13 +6453,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R49" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>9</v>
@@ -6347,22 +6470,22 @@
         <v>65</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>642</v>
+        <v>630</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -6395,13 +6518,13 @@
         <v>16</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R50" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>9</v>
@@ -6412,10 +6535,10 @@
         <v>66</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>9</v>
@@ -6424,10 +6547,10 @@
         <v>235</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>50</v>
@@ -6460,13 +6583,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R51" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>9</v>
@@ -6477,22 +6600,22 @@
         <v>67</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>50</v>
@@ -6525,13 +6648,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R52" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>9</v>
@@ -6542,22 +6665,22 @@
         <v>69</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>73</v>
@@ -6590,13 +6713,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R53" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>9</v>
@@ -6607,22 +6730,22 @@
         <v>70</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>34</v>
@@ -6655,13 +6778,13 @@
         <v>2</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R54" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>9</v>
@@ -6672,22 +6795,22 @@
         <v>71</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -6720,13 +6843,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R55" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>9</v>
@@ -6737,22 +6860,22 @@
         <v>72</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>10</v>
@@ -6762,7 +6885,7 @@
         <v>201</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K56" s="3">
         <f>VLOOKUP(J56,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6785,13 +6908,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R56" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>9</v>
@@ -6802,22 +6925,22 @@
         <v>73</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
@@ -6827,7 +6950,7 @@
         <v>202</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K57" s="3">
         <f>VLOOKUP(J57,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6850,13 +6973,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R57" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>9</v>
@@ -6867,7 +6990,7 @@
         <v>74</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>9</v>
@@ -6879,10 +7002,10 @@
         <v>183</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -6915,13 +7038,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R58" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>9</v>
@@ -6932,22 +7055,22 @@
         <v>75</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="E59" s="15">
         <v>183</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
@@ -6980,13 +7103,13 @@
         <v>2</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R59" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>9</v>
@@ -6997,22 +7120,22 @@
         <v>76</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7045,13 +7168,13 @@
         <v>2</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R60" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>9</v>
@@ -7062,25 +7185,25 @@
         <v>78</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>650</v>
-      </c>
-      <c r="E61" s="15" t="s">
-        <v>546</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="G61" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I61" s="3">
         <f>VLOOKUP(H61,cardsort_group_IDs!A:B,2,0)</f>
@@ -7110,13 +7233,13 @@
         <v>11</v>
       </c>
       <c r="P61" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R61" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>9</v>
@@ -7127,22 +7250,22 @@
         <v>79</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>736</v>
+        <v>719</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>73</v>
@@ -7175,13 +7298,13 @@
         <v>4</v>
       </c>
       <c r="P62" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R62" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>9</v>
@@ -7192,7 +7315,7 @@
         <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>9</v>
@@ -7204,10 +7327,10 @@
         <v>514</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>73</v>
@@ -7240,13 +7363,13 @@
         <v>1</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R63" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S63" s="14" t="s">
         <v>9</v>
@@ -7257,22 +7380,22 @@
         <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="E64" s="15">
         <v>202</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>34</v>
@@ -7305,13 +7428,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R64" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S64" s="14" t="s">
         <v>9</v>
@@ -7322,7 +7445,7 @@
         <v>82</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>9</v>
@@ -7334,10 +7457,10 @@
         <v>514</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>10</v>
@@ -7347,7 +7470,7 @@
         <v>201</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K65" s="3">
         <f>VLOOKUP(J65,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7370,13 +7493,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R65" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S65" s="14" t="s">
         <v>9</v>
@@ -7387,32 +7510,32 @@
         <v>83</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>735</v>
+        <v>718</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I66" s="3">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K66" s="3">
         <f>VLOOKUP(J66,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7435,13 +7558,13 @@
         <v>5</v>
       </c>
       <c r="P66" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R66" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S66" s="14" t="s">
         <v>9</v>
@@ -7458,16 +7581,16 @@
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="E67" s="15">
         <v>501</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>21</v>
@@ -7500,13 +7623,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R67" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S67" s="14" t="s">
         <v>9</v>
@@ -7517,22 +7640,22 @@
         <v>85</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>15</v>
@@ -7565,13 +7688,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R68" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S68" s="14" t="s">
         <v>9</v>
@@ -7582,22 +7705,22 @@
         <v>87</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>428</v>
+        <v>769</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7619,7 +7742,7 @@
       </c>
       <c r="M69" s="3">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="3">
         <f t="shared" si="9"/>
@@ -7627,16 +7750,16 @@
       </c>
       <c r="O69" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R69" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S69" s="14" t="s">
         <v>9</v>
@@ -7647,22 +7770,22 @@
         <v>88</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>516</v>
+        <v>772</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>34</v>
@@ -7684,7 +7807,7 @@
       </c>
       <c r="M70" s="3">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="3">
         <f t="shared" si="9"/>
@@ -7692,16 +7815,16 @@
       </c>
       <c r="O70" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q70" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R70" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S70" s="14" t="s">
         <v>9</v>
@@ -7712,22 +7835,22 @@
         <v>89</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>445</v>
+        <v>773</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>34</v>
@@ -7749,7 +7872,7 @@
       </c>
       <c r="M71" s="3">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N71" s="3">
         <f t="shared" si="9"/>
@@ -7757,16 +7880,16 @@
       </c>
       <c r="O71" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R71" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S71" s="14" t="s">
         <v>9</v>
@@ -7777,22 +7900,22 @@
         <v>90</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>34</v>
@@ -7825,13 +7948,13 @@
         <v>14</v>
       </c>
       <c r="P72" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R72" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S72" s="14" t="s">
         <v>9</v>
@@ -7842,22 +7965,22 @@
         <v>91</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -7890,13 +8013,13 @@
         <v>4</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q73" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R73" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S73" s="14" t="s">
         <v>9</v>
@@ -7907,22 +8030,22 @@
         <v>92</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>50</v>
@@ -7955,13 +8078,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q74" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R74" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S74" s="14" t="s">
         <v>9</v>
@@ -7972,7 +8095,7 @@
         <v>93</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>9</v>
@@ -7984,10 +8107,10 @@
         <v>514</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8020,13 +8143,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R75" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>9</v>
@@ -8037,22 +8160,22 @@
         <v>94</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>73</v>
@@ -8085,13 +8208,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R76" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S76" s="14" t="s">
         <v>9</v>
@@ -8102,22 +8225,22 @@
         <v>95</v>
       </c>
       <c r="B77" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="F77" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E77" s="15" t="s">
-        <v>561</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>202</v>
-      </c>
       <c r="G77" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>21</v>
@@ -8127,7 +8250,7 @@
         <v>202</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K77" s="3">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8150,13 +8273,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q77" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R77" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S77" s="14" t="s">
         <v>9</v>
@@ -8167,7 +8290,7 @@
         <v>97</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>9</v>
@@ -8179,10 +8302,10 @@
         <v>508</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8215,13 +8338,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q78" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R78" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>9</v>
@@ -8232,10 +8355,10 @@
         <v>98</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D79" s="12">
         <v>209</v>
@@ -8244,10 +8367,10 @@
         <v>506</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>10</v>
@@ -8257,7 +8380,7 @@
         <v>201</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K79" s="3">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8280,13 +8403,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R79" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S79" s="14" t="s">
         <v>9</v>
@@ -8297,7 +8420,7 @@
         <v>99</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>9</v>
@@ -8309,10 +8432,10 @@
         <v>508</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>10</v>
@@ -8345,13 +8468,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R80" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S80" s="14" t="s">
         <v>9</v>
@@ -8362,7 +8485,7 @@
         <v>100</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>9</v>
@@ -8374,10 +8497,10 @@
         <v>514</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>10</v>
@@ -8410,13 +8533,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R81" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S81" s="14" t="s">
         <v>9</v>
@@ -8427,22 +8550,22 @@
         <v>102</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E82" s="15">
         <v>501</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8475,13 +8598,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R82" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S82" s="14" t="s">
         <v>9</v>
@@ -8492,25 +8615,25 @@
         <v>104</v>
       </c>
       <c r="B83" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D83" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>431</v>
-      </c>
-      <c r="E83" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I83" s="3">
         <f>VLOOKUP(H83,cardsort_group_IDs!A:B,2,0)</f>
@@ -8540,13 +8663,13 @@
         <v>2</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R83" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S83" s="14" t="s">
         <v>9</v>
@@ -8557,22 +8680,22 @@
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D84" s="15" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="E84" s="15" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>21</v>
@@ -8605,13 +8728,13 @@
         <v>4</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q84" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R84" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S84" s="14" t="s">
         <v>9</v>
@@ -8622,22 +8745,22 @@
         <v>107</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D85" s="14" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E85" s="15" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8670,13 +8793,13 @@
         <v>7</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q85" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R85" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S85" s="14" t="s">
         <v>9</v>
@@ -8687,22 +8810,22 @@
         <v>108</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8735,13 +8858,13 @@
         <v>8</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q86" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R86" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S86" s="14" t="s">
         <v>9</v>
@@ -8752,22 +8875,22 @@
         <v>109</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8777,7 +8900,7 @@
         <v>202</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K87" s="3">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8800,13 +8923,13 @@
         <v>8</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q87" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R87" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S87" s="14" t="s">
         <v>9</v>
@@ -8817,32 +8940,32 @@
         <v>112</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I88" s="3">
         <f>VLOOKUP(H88,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K88" s="3">
         <f>VLOOKUP(J88,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8865,13 +8988,13 @@
         <v>2</v>
       </c>
       <c r="P88" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q88" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R88" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S88" s="14" t="s">
         <v>9</v>
@@ -8882,22 +9005,22 @@
         <v>114</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>676</v>
+        <v>662</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>55</v>
@@ -8930,13 +9053,13 @@
         <v>14</v>
       </c>
       <c r="P89" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R89" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S89" s="14" t="s">
         <v>9</v>
@@ -8947,7 +9070,7 @@
         <v>115</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>9</v>
@@ -8959,10 +9082,10 @@
         <v>183</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>50</v>
@@ -8995,13 +9118,13 @@
         <v>1</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q90" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R90" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S90" s="14" t="s">
         <v>9</v>
@@ -9012,22 +9135,22 @@
         <v>116</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>286</v>
+        <v>766</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>450</v>
+        <v>765</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>34</v>
@@ -9037,7 +9160,7 @@
         <v>205</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9049,7 +9172,7 @@
       </c>
       <c r="M91" s="3">
         <f t="shared" si="8"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <f t="shared" si="9"/>
@@ -9057,16 +9180,16 @@
       </c>
       <c r="O91" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q91" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R91" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S91" s="14" t="s">
         <v>9</v>
@@ -9080,19 +9203,19 @@
         <v>39</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>34</v>
@@ -9125,13 +9248,13 @@
         <v>5</v>
       </c>
       <c r="P92" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R92" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S92" s="14" t="s">
         <v>9</v>
@@ -9142,7 +9265,7 @@
         <v>118</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>9</v>
@@ -9154,10 +9277,10 @@
         <v>9</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>21</v>
@@ -9167,7 +9290,7 @@
         <v>202</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9190,13 +9313,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R93" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S93" s="14" t="s">
         <v>9</v>
@@ -9207,22 +9330,22 @@
         <v>119</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="E94" s="15">
         <v>501</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>15</v>
@@ -9255,13 +9378,13 @@
         <v>2</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q94" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R94" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S94" s="14" t="s">
         <v>9</v>
@@ -9272,22 +9395,22 @@
         <v>120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
@@ -9308,11 +9431,11 @@
         <v>3</v>
       </c>
       <c r="M95" s="3">
-        <f t="shared" ref="M95:M125" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
+        <f t="shared" ref="M95:M126" si="10">IF(D95="-",0,LEN(D95)-LEN(SUBSTITUTE(D95,";",""))+1)</f>
         <v>1</v>
       </c>
       <c r="N95" s="3">
-        <f t="shared" ref="N95:N125" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
+        <f t="shared" ref="N95:N126" si="11">IF(E95="-",0,LEN(E95)-LEN(SUBSTITUTE(E95,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O95" s="3">
@@ -9320,13 +9443,13 @@
         <v>3</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R95" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S95" s="14" t="s">
         <v>9</v>
@@ -9337,22 +9460,22 @@
         <v>121</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>15</v>
@@ -9385,13 +9508,13 @@
         <v>8</v>
       </c>
       <c r="P96" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q96" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R96" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S96" s="14" t="s">
         <v>9</v>
@@ -9402,22 +9525,22 @@
         <v>122</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9450,13 +9573,13 @@
         <v>5</v>
       </c>
       <c r="P97" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q97" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R97" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S97" s="14" t="s">
         <v>9</v>
@@ -9467,25 +9590,25 @@
         <v>124</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>248</v>
+        <v>763</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>521</v>
+        <v>762</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>737</v>
+        <v>720</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9504,7 +9627,7 @@
       </c>
       <c r="M98" s="3">
         <f t="shared" si="10"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N98" s="3">
         <f t="shared" si="11"/>
@@ -9512,16 +9635,16 @@
       </c>
       <c r="O98" s="3">
         <f t="shared" si="7"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q98" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R98" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S98" s="14" t="s">
         <v>9</v>
@@ -9532,22 +9655,22 @@
         <v>126</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="E99" s="15">
         <v>501</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>55</v>
@@ -9580,39 +9703,39 @@
         <v>2</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R99" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S99" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>127</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>287</v>
+        <v>771</v>
       </c>
       <c r="D100" s="14" t="s">
-        <v>434</v>
+        <v>770</v>
       </c>
       <c r="E100" s="15" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>55</v>
@@ -9634,7 +9757,7 @@
       </c>
       <c r="M100" s="3">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N100" s="3">
         <f t="shared" si="11"/>
@@ -9642,16 +9765,16 @@
       </c>
       <c r="O100" s="3">
         <f t="shared" si="7"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R100" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S100" s="14" t="s">
         <v>9</v>
@@ -9662,22 +9785,22 @@
         <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="E101" s="15">
         <v>501</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>55</v>
@@ -9710,13 +9833,13 @@
         <v>2</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q101" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R101" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S101" s="14" t="s">
         <v>9</v>
@@ -9727,22 +9850,22 @@
         <v>129</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>55</v>
@@ -9775,13 +9898,13 @@
         <v>27</v>
       </c>
       <c r="P102" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R102" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S102" s="14" t="s">
         <v>9</v>
@@ -9792,25 +9915,25 @@
         <v>130</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I103" s="3">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
@@ -9840,13 +9963,13 @@
         <v>5</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R103" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S103" s="14" t="s">
         <v>9</v>
@@ -9857,22 +9980,22 @@
         <v>134</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G104" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -9905,13 +10028,13 @@
         <v>11</v>
       </c>
       <c r="P104" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q104" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R104" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S104" s="14" t="s">
         <v>9</v>
@@ -9922,7 +10045,7 @@
         <v>135</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -9934,20 +10057,20 @@
         <v>183</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="G105" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H105" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I105" s="3">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J105" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K105" s="3">
         <f>VLOOKUP(J105,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9970,13 +10093,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q105" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R105" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S105" s="14" t="s">
         <v>9</v>
@@ -9987,7 +10110,7 @@
         <v>136</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
@@ -9999,10 +10122,10 @@
         <v>240</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="G106" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H106" t="s">
         <v>55</v>
@@ -10035,13 +10158,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q106" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R106" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="S106" s="14" t="s">
         <v>9</v>
@@ -10052,25 +10175,25 @@
         <v>137</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="G107" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H107" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I107" s="3">
         <f>VLOOKUP(H107,cardsort_group_IDs!A:B,2,0)</f>
@@ -10100,13 +10223,13 @@
         <v>6</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q107" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R107" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S107" s="14" t="s">
         <v>9</v>
@@ -10117,10 +10240,10 @@
         <v>138</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>9</v>
@@ -10129,10 +10252,10 @@
         <v>236</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="G108" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -10165,13 +10288,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R108" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S108" s="14" t="s">
         <v>9</v>
@@ -10182,7 +10305,7 @@
         <v>139</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10194,10 +10317,10 @@
         <v>9</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -10207,7 +10330,7 @@
         <v>202</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K109" s="3">
         <f>VLOOKUP(J109,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10230,13 +10353,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R109" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S109" s="14" t="s">
         <v>9</v>
@@ -10247,22 +10370,22 @@
         <v>140</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>15</v>
@@ -10295,13 +10418,13 @@
         <v>18</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="Q110" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R110" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S110" s="14">
         <v>2</v>
@@ -10312,22 +10435,22 @@
         <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>55</v>
@@ -10360,13 +10483,13 @@
         <v>3</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R111" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S111" s="14">
         <v>129</v>
@@ -10377,22 +10500,22 @@
         <v>142</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>55</v>
@@ -10425,13 +10548,13 @@
         <v>2</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R112" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S112" s="14">
         <v>19</v>
@@ -10442,22 +10565,22 @@
         <v>143</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
@@ -10490,13 +10613,13 @@
         <v>5</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R113" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S113" s="14" t="s">
         <v>9</v>
@@ -10507,22 +10630,22 @@
         <v>144</v>
       </c>
       <c r="B114" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="E114" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>15</v>
@@ -10555,16 +10678,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R114" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S114" s="14" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10572,22 +10695,22 @@
         <v>145</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -10620,16 +10743,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R115" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S115" s="14" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10637,22 +10760,22 @@
         <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="D116" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -10685,16 +10808,16 @@
         <v>6</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="Q116" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R116" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S116" s="14" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -10702,22 +10825,22 @@
         <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10750,16 +10873,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="Q117" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R117" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S117" s="14" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10767,22 +10890,22 @@
         <v>148</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="D118" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>10</v>
@@ -10815,16 +10938,16 @@
         <v>11</v>
       </c>
       <c r="P118" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R118" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S118" s="14" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -10832,22 +10955,22 @@
         <v>149</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="E119" s="15" t="s">
         <v>649</v>
       </c>
-      <c r="E119" s="15" t="s">
-        <v>662</v>
-      </c>
       <c r="F119" s="3" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -10857,7 +10980,7 @@
         <v>202</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K119" s="3">
         <f>VLOOKUP(J119,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10880,42 +11003,42 @@
         <v>3</v>
       </c>
       <c r="P119" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R119" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S119" s="14" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>150</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>9</v>
+        <v>776</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>652</v>
+        <v>775</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
@@ -10934,7 +11057,7 @@
       </c>
       <c r="M120" s="3">
         <f t="shared" si="10"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N120" s="3">
         <f t="shared" si="11"/>
@@ -10942,19 +11065,19 @@
       </c>
       <c r="O120" s="3">
         <f t="shared" ref="O120" si="23">SUM(M120:N120)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P120" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q120" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R120" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S120" s="14" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10962,22 +11085,22 @@
         <v>151</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="15" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11010,13 +11133,13 @@
         <v>1</v>
       </c>
       <c r="P121" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q121" s="14" t="s">
-        <v>707</v>
+        <v>693</v>
       </c>
       <c r="R121" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S121" s="14" t="s">
         <v>9</v>
@@ -11027,7 +11150,7 @@
         <v>152</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>677</v>
+        <v>663</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
@@ -11036,16 +11159,16 @@
         <v>9</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>678</v>
+        <v>664</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11075,13 +11198,13 @@
         <v>1</v>
       </c>
       <c r="P122" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R122" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S122" s="14" t="s">
         <v>9</v>
@@ -11092,7 +11215,7 @@
         <v>153</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11101,16 +11224,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="F123" t="s">
-        <v>681</v>
+        <v>667</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11140,16 +11263,16 @@
         <v>1</v>
       </c>
       <c r="P123" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q123" s="14" t="s">
-        <v>708</v>
+        <v>694</v>
       </c>
       <c r="R123" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S123" s="14" t="s">
-        <v>680</v>
+        <v>666</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -11157,7 +11280,7 @@
         <v>154</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>685</v>
+        <v>671</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>9</v>
@@ -11166,16 +11289,16 @@
         <v>9</v>
       </c>
       <c r="E124" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="F124" s="3" t="s">
-        <v>686</v>
-      </c>
       <c r="G124" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I124" s="3">
         <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
@@ -11189,7 +11312,7 @@
         <v>313</v>
       </c>
       <c r="L124" s="3">
-        <f t="shared" ref="L124:L125" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
+        <f t="shared" ref="L124:L126" si="30">IF(E124="-",0,1)+IF(D124="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M124" s="3">
@@ -11201,20 +11324,20 @@
         <v>1</v>
       </c>
       <c r="O124" s="3">
-        <f t="shared" ref="O124:O125" si="31">SUM(M124:N124)</f>
+        <f t="shared" ref="O124:O126" si="31">SUM(M124:N124)</f>
         <v>1</v>
       </c>
       <c r="P124" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q124" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R124" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="S124" s="14" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
@@ -11222,7 +11345,7 @@
         <v>155</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>739</v>
+        <v>722</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>9</v>
@@ -11231,16 +11354,16 @@
         <v>9</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>741</v>
+        <v>724</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>740</v>
+        <v>723</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="I125" s="3">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11270,20 +11393,150 @@
         <v>2</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="Q125" s="14" t="s">
-        <v>706</v>
+        <v>692</v>
       </c>
       <c r="R125" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="S125" s="14" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A126" s="3">
+        <v>156</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>730</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>731</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I126" s="3">
+        <f>VLOOKUP(H126,cardsort_group_IDs!A:B,2,0)</f>
+        <v>205</v>
+      </c>
+      <c r="J126" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K126" s="3">
+        <f>VLOOKUP(J126,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>319</v>
+      </c>
+      <c r="L126" s="3">
+        <f t="shared" si="30"/>
+        <v>3</v>
+      </c>
+      <c r="M126" s="3">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="N126" s="3">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="O126" s="3">
+        <f t="shared" si="31"/>
+        <v>2</v>
+      </c>
+      <c r="P126" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q126" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="R126" t="s">
+        <v>699</v>
+      </c>
+      <c r="S126" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A127" s="3">
+        <v>157</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="C127" t="s">
+        <v>736</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>748</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>738</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="I127" s="3">
+        <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J127" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K127" s="3">
+        <f>VLOOKUP(J127,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>305</v>
+      </c>
+      <c r="L127" s="3">
+        <f t="shared" ref="L127" si="32">IF(E127="-",0,1)+IF(D127="-",0,2)</f>
+        <v>3</v>
+      </c>
+      <c r="M127" s="3">
+        <f t="shared" ref="M127" si="33">IF(D127="-",0,LEN(D127)-LEN(SUBSTITUTE(D127,";",""))+1)</f>
+        <v>4</v>
+      </c>
+      <c r="N127" s="3">
+        <f t="shared" ref="N127" si="34">IF(E127="-",0,LEN(E127)-LEN(SUBSTITUTE(E127,";",""))+1)</f>
+        <v>1</v>
+      </c>
+      <c r="O127" s="3">
+        <f t="shared" ref="O127" si="35">SUM(M127:N127)</f>
+        <v>5</v>
+      </c>
+      <c r="P127" s="14" t="s">
+        <v>593</v>
+      </c>
+      <c r="Q127" s="14" t="s">
+        <v>692</v>
+      </c>
+      <c r="R127" t="s">
+        <v>697</v>
+      </c>
+      <c r="S127" s="14" t="s">
+        <v>750</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M126" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B1:B108">
     <cfRule type="duplicateValues" dxfId="38" priority="45"/>
@@ -11390,7 +11643,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D146"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="12"/>
@@ -11401,16 +11654,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C1" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11418,13 +11671,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11432,27 +11685,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C3" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D3" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B4" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C4" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11460,13 +11713,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C5" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D5" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11474,13 +11727,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="C6" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11488,13 +11741,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11502,13 +11755,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="C8" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11516,13 +11769,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="C9" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11530,13 +11783,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11544,13 +11797,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="C11" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11558,13 +11811,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="C12" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D12" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11572,13 +11825,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="C13" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11586,13 +11839,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="C14" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11600,13 +11853,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C15" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11614,13 +11867,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C16" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11628,13 +11881,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11642,13 +11895,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="C18" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D18" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11656,13 +11909,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C19" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11670,13 +11923,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="C20" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11684,13 +11937,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="C21" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11698,13 +11951,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="C22" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11712,13 +11965,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C23" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11726,13 +11979,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="C24" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11740,13 +11993,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="C25" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11754,13 +12007,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="C26" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11768,13 +12021,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="C27" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11782,13 +12035,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="C28" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11796,13 +12049,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="C29" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11810,13 +12063,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C30" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11824,13 +12077,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="C31" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11838,13 +12091,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="C32" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11852,13 +12105,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="C33" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11866,13 +12119,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C34" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11880,13 +12133,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C35" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11894,13 +12147,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="C36" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11908,13 +12161,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -11922,13 +12175,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C38" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -11936,13 +12189,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="C39" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -11950,13 +12203,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C40" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11967,10 +12220,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11978,13 +12231,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C42" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -11992,13 +12245,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="C43" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12006,13 +12259,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C44" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12020,13 +12273,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C45" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12037,10 +12290,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12048,13 +12301,13 @@
         <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12062,13 +12315,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C48" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D48" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12076,13 +12329,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C49" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12090,13 +12343,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C50" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12104,10 +12357,10 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12115,13 +12368,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C52" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12129,13 +12382,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C53" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12143,13 +12396,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C54" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12157,13 +12410,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="C55" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12171,13 +12424,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="C56" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12185,13 +12438,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="C57" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12199,13 +12452,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C58" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12213,13 +12466,13 @@
         <v>241</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C59" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12227,13 +12480,13 @@
         <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="C60" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12241,13 +12494,13 @@
         <v>244</v>
       </c>
       <c r="B61" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C61" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12255,13 +12508,13 @@
         <v>501</v>
       </c>
       <c r="B62" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C62" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12269,13 +12522,13 @@
         <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C63" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12283,13 +12536,13 @@
         <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C64" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12297,13 +12550,13 @@
         <v>504</v>
       </c>
       <c r="B65" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="C65" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12311,13 +12564,13 @@
         <v>505</v>
       </c>
       <c r="B66" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C66" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12328,10 +12581,10 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>699</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>417</v>
+        <v>685</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>734</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12339,13 +12592,13 @@
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C68" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12356,10 +12609,10 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12367,13 +12620,13 @@
         <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="C70" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12381,937 +12634,1063 @@
         <v>510</v>
       </c>
       <c r="B71" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="C71" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D71" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C72" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B73" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C73" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B74" t="s">
-        <v>701</v>
+        <v>687</v>
       </c>
       <c r="C74" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C75" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B76" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="B77" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="C77" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="B78" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="C78" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="C80" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C81" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B82" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C82" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="C83" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B84" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="C84" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="B85" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="C85" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C86" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B87" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C87" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="B88" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="C88" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="B89" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="C89" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B90" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="C90" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C91" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="C92" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C93" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B94" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="C94" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="B95" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="B96" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C96" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C97" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B98" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C98" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B99" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C99" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="B100" t="s">
         <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="B101" t="s">
         <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B102" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C102" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="B103" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="C103" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="B104" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C104" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C106" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B108" t="s">
-        <v>702</v>
+        <v>688</v>
       </c>
       <c r="C108" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="B109" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C109" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B110" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="C110" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B111" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C111" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B112" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C112" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="B114" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C114" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B115" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C115" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="B116" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="C116" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D116" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="B117" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C117" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D117" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="B118" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C118" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D118" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="B119" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C119" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D119" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="B120" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="C120" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D120" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C121" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D121" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="B122" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C122" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D122" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="B123" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="C123" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D123" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B124" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C124" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D124" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="B125" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C125" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D125" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="B126" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="C126" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D126" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="B127" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C127" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D127" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="B128" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="C128" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D128" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="B129" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="C129" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D129" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="B130" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C130" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="D130" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="B131" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="C131" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D131" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="B132" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="C132" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="D132" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="B133" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="C133" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D133" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="B134" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="C134" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="D134" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="B135" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C135" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D135" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="B136" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C136" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D136" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>725</v>
+        <v>708</v>
       </c>
       <c r="B137" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="C137" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="D137" t="s">
-        <v>727</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="B138" t="s">
+        <v>733</v>
+      </c>
+      <c r="C138" t="s">
+        <v>685</v>
+      </c>
+      <c r="D138" s="19" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="B139" t="s">
+        <v>674</v>
+      </c>
+      <c r="C139" t="s">
+        <v>676</v>
+      </c>
+      <c r="D139" s="19" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="B140" t="s">
+        <v>740</v>
+      </c>
+      <c r="C140" t="s">
+        <v>685</v>
+      </c>
+      <c r="D140" s="19" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="12" t="s">
+        <v>741</v>
+      </c>
+      <c r="B141" t="s">
+        <v>674</v>
+      </c>
+      <c r="C141" t="s">
+        <v>676</v>
+      </c>
+      <c r="D141" s="19" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="B142" t="s">
+        <v>774</v>
+      </c>
+      <c r="C142" t="s">
+        <v>676</v>
+      </c>
+      <c r="D142" s="19" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="12" t="s">
+        <v>744</v>
+      </c>
+      <c r="B143" t="s">
+        <v>362</v>
+      </c>
+      <c r="C143" t="s">
+        <v>676</v>
+      </c>
+      <c r="D143" s="19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="12" t="s">
+        <v>745</v>
+      </c>
+      <c r="B144" t="s">
+        <v>584</v>
+      </c>
+      <c r="C144" t="s">
+        <v>676</v>
+      </c>
+      <c r="D144" s="19" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="B145" t="s">
+        <v>756</v>
+      </c>
+      <c r="C145" t="s">
+        <v>676</v>
+      </c>
+      <c r="D145" s="19" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="B146" t="s">
+        <v>760</v>
+      </c>
+      <c r="C146" t="s">
+        <v>685</v>
+      </c>
+      <c r="D146" s="19" t="s">
+        <v>761</v>
       </c>
     </row>
   </sheetData>
@@ -13320,7 +13699,11 @@
       <sortCondition ref="A1:A115"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="D67" r:id="rId1" xr:uid="{59EFEB55-B7A4-4807-A75B-EA48D4BA0ABA}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -13362,7 +13745,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13447,7 +13830,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13631,7 +14014,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -13639,7 +14022,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13647,7 +14030,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13655,7 +14038,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13663,7 +14046,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13689,50 +14072,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
-        <v>689</v>
+        <v>675</v>
       </c>
       <c r="B1" s="18" t="s">
-        <v>692</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>691</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>693</v>
+        <v>679</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>696</v>
+        <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>694</v>
+        <v>680</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>695</v>
+        <v>681</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>697</v>
+        <v>683</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>698</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>699</v>
+        <v>685</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABB7680-23B3-4D06-92B1-D5AE3E75C3CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED70EA7A-A7F0-4941-8252-1B3DAC604260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="39750" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="17145" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -747,9 +747,6 @@
     <t>Developers’ emotional responses and perceptions of their interactions with tools, documentation, and workflows. It focuses on how developers feel about using the platform and whether they find it empowering, frustrating, or aligned with their goals.</t>
   </si>
   <si>
-    <t>Service Uptime and Deployment Speed Metrics</t>
-  </si>
-  <si>
     <t>Measures service uptime and deployment speed.</t>
   </si>
   <si>
@@ -759,9 +756,6 @@
     <t>Relates to how quickly software engineers can accomplish their tasks, focusing on the efficiency of workflows and processes that enable rapid delivery without compromising quality. This includes quantiative metrics (logs for task durations, deployment statistics, and CI/CD pipeline metrics) and qualitative metrics (developer surveys, diary studies, and interviews to understand perceptions and identify pain points).</t>
   </si>
   <si>
-    <t>Sprint Velocity</t>
-  </si>
-  <si>
     <t>The amount of work completed per sprint/time period. Helps with planning and tracking.</t>
   </si>
   <si>
@@ -943,9 +937,6 @@
   </si>
   <si>
     <t>Production Downtime; Deployment Time</t>
-  </si>
-  <si>
-    <t>Velocity; Developer Velocity</t>
   </si>
   <si>
     <t>9; 31</t>
@@ -2371,9 +2362,6 @@
     <t>517a</t>
   </si>
   <si>
-    <t>Capital One</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?reload=9&amp;app=desktop&amp;v=GG8JLosF_AI</t>
   </si>
   <si>
@@ -2435,6 +2423,18 @@
   </si>
   <si>
     <t>504; 11; 96; 214; 513; 517b</t>
+  </si>
+  <si>
+    <t>CapitalOne</t>
+  </si>
+  <si>
+    <t>Velocity</t>
+  </si>
+  <si>
+    <t>Sprint Velocity; Developer Velocity</t>
+  </si>
+  <si>
+    <t>Service Uptime and Deployment Speed</t>
   </si>
 </sst>
 </file>
@@ -2514,7 +2514,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2564,7 +2564,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3297,16 +3296,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3324,25 +3323,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="P1" s="17" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="Q1" s="17" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="S1" s="17" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3356,16 +3355,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3398,16 +3397,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q2" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S2" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3430,7 +3429,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3463,13 +3462,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q3" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S3" s="14" t="s">
         <v>9</v>
@@ -3486,16 +3485,16 @@
         <v>9</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3528,13 +3527,13 @@
         <v>4</v>
       </c>
       <c r="P4" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q4" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R4" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S4" s="14" t="s">
         <v>9</v>
@@ -3548,22 +3547,22 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3593,13 +3592,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q5" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R5" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S5" s="14" t="s">
         <v>9</v>
@@ -3625,7 +3624,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3658,13 +3657,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q6" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R6" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S6" s="14" t="s">
         <v>9</v>
@@ -3681,16 +3680,16 @@
         <v>9</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>34</v>
@@ -3726,10 +3725,10 @@
         <v>127</v>
       </c>
       <c r="Q7" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R7" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S7" s="14" t="s">
         <v>9</v>
@@ -3755,7 +3754,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>34</v>
@@ -3788,13 +3787,13 @@
         <v>1</v>
       </c>
       <c r="P8" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q8" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R8" t="s">
         <v>694</v>
-      </c>
-      <c r="R8" t="s">
-        <v>697</v>
       </c>
       <c r="S8" s="14" t="s">
         <v>9</v>
@@ -3811,7 +3810,7 @@
         <v>9</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E9" s="15">
         <v>501</v>
@@ -3820,7 +3819,7 @@
         <v>41</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>34</v>
@@ -3853,13 +3852,13 @@
         <v>2</v>
       </c>
       <c r="P9" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R9" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S9" s="14" t="s">
         <v>9</v>
@@ -3876,7 +3875,7 @@
         <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E10" s="15">
         <v>501</v>
@@ -3885,7 +3884,7 @@
         <v>43</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3918,13 +3917,13 @@
         <v>3</v>
       </c>
       <c r="P10" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q10" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R10" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S10" s="14" t="s">
         <v>9</v>
@@ -3941,16 +3940,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>34</v>
@@ -3983,13 +3982,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q11" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R11" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S11" s="14" t="s">
         <v>9</v>
@@ -4006,16 +4005,16 @@
         <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>50</v>
@@ -4048,13 +4047,13 @@
         <v>10</v>
       </c>
       <c r="P12" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q12" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R12" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S12" s="14" t="s">
         <v>9</v>
@@ -4068,10 +4067,10 @@
         <v>51</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E13" s="15">
         <v>131</v>
@@ -4080,7 +4079,7 @@
         <v>52</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>34</v>
@@ -4116,10 +4115,10 @@
         <v>127</v>
       </c>
       <c r="Q13" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R13" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S13" s="14" t="s">
         <v>9</v>
@@ -4133,19 +4132,19 @@
         <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>54</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>55</v>
@@ -4178,13 +4177,13 @@
         <v>26</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R14" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S14" s="14" t="s">
         <v>9</v>
@@ -4198,22 +4197,22 @@
         <v>57</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4246,10 +4245,10 @@
         <v>127</v>
       </c>
       <c r="Q15" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R15" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S15" s="14" t="s">
         <v>9</v>
@@ -4266,16 +4265,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>62</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4308,13 +4307,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R16" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S16" s="14" t="s">
         <v>9</v>
@@ -4328,19 +4327,19 @@
         <v>63</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>65</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>50</v>
@@ -4373,13 +4372,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S17" s="14" t="s">
         <v>9</v>
@@ -4405,7 +4404,7 @@
         <v>69</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4438,13 +4437,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R18" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S18" s="14" t="s">
         <v>9</v>
@@ -4464,13 +4463,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>72</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>73</v>
@@ -4503,13 +4502,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q19" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R19" t="s">
         <v>694</v>
-      </c>
-      <c r="R19" t="s">
-        <v>697</v>
       </c>
       <c r="S19" s="14" t="s">
         <v>9</v>
@@ -4526,7 +4525,7 @@
         <v>9</v>
       </c>
       <c r="D20" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E20" s="15">
         <v>131</v>
@@ -4535,7 +4534,7 @@
         <v>75</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>73</v>
@@ -4568,13 +4567,13 @@
         <v>3</v>
       </c>
       <c r="P20" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R20" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S20" s="14" t="s">
         <v>9</v>
@@ -4588,19 +4587,19 @@
         <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4636,10 +4635,10 @@
         <v>127</v>
       </c>
       <c r="Q21" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R21" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S21" s="14" t="s">
         <v>9</v>
@@ -4653,7 +4652,7 @@
         <v>78</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>9</v>
@@ -4665,7 +4664,7 @@
         <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>34</v>
@@ -4698,13 +4697,13 @@
         <v>1</v>
       </c>
       <c r="P22" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q22" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R22" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S22" s="14" t="s">
         <v>9</v>
@@ -4721,16 +4720,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>73</v>
@@ -4766,10 +4765,10 @@
         <v>127</v>
       </c>
       <c r="Q23" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R23" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S23" s="14" t="s">
         <v>9</v>
@@ -4783,19 +4782,19 @@
         <v>82</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D24" s="14">
         <v>170</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>83</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>34</v>
@@ -4828,13 +4827,13 @@
         <v>4</v>
       </c>
       <c r="P24" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q24" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R24" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S24" s="14" t="s">
         <v>9</v>
@@ -4851,7 +4850,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E25" s="15">
         <v>501</v>
@@ -4860,7 +4859,7 @@
         <v>87</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>73</v>
@@ -4893,13 +4892,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R25" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S25" s="14" t="s">
         <v>9</v>
@@ -4916,16 +4915,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>89</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -4958,13 +4957,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R26" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S26" s="14" t="s">
         <v>9</v>
@@ -4978,19 +4977,19 @@
         <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E27" s="15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>92</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5023,13 +5022,13 @@
         <v>8</v>
       </c>
       <c r="P27" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R27" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S27" s="14" t="s">
         <v>9</v>
@@ -5046,19 +5045,19 @@
         <v>9</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -5088,13 +5087,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R28" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S28" s="14" t="s">
         <v>9</v>
@@ -5108,22 +5107,22 @@
         <v>96</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>97</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
@@ -5156,10 +5155,10 @@
         <v>127</v>
       </c>
       <c r="Q29" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R29" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S29" s="14" t="s">
         <v>9</v>
@@ -5185,7 +5184,7 @@
         <v>100</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5218,13 +5217,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q30" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R30" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S30" s="14" t="s">
         <v>9</v>
@@ -5238,19 +5237,19 @@
         <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5286,10 +5285,10 @@
         <v>127</v>
       </c>
       <c r="Q31" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R31" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S31" s="14" t="s">
         <v>9</v>
@@ -5306,16 +5305,16 @@
         <v>9</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>103</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5348,13 +5347,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q32" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R32" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S32" s="14" t="s">
         <v>9</v>
@@ -5371,19 +5370,19 @@
         <v>104</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5416,10 +5415,10 @@
         <v>127</v>
       </c>
       <c r="Q33" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R33" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S33" s="14" t="s">
         <v>9</v>
@@ -5433,22 +5432,22 @@
         <v>106</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>107</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
@@ -5478,13 +5477,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q34" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R34" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S34" s="14" t="s">
         <v>9</v>
@@ -5498,19 +5497,19 @@
         <v>108</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
@@ -5543,13 +5542,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q35" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R35" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S35" s="14" t="s">
         <v>9</v>
@@ -5566,19 +5565,19 @@
         <v>9</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>111</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
@@ -5608,13 +5607,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q36" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R36" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S36" s="14" t="s">
         <v>9</v>
@@ -5628,19 +5627,19 @@
         <v>113</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5676,10 +5675,10 @@
         <v>127</v>
       </c>
       <c r="Q37" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R37" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S37" s="14" t="s">
         <v>9</v>
@@ -5699,13 +5698,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>118</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5738,13 +5737,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q38" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R38" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S38" s="14" t="s">
         <v>9</v>
@@ -5764,13 +5763,13 @@
         <v>9</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>121</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>50</v>
@@ -5806,10 +5805,10 @@
         <v>127</v>
       </c>
       <c r="Q39" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R39" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S39" s="14" t="s">
         <v>9</v>
@@ -5820,25 +5819,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="E40" s="15" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5868,16 +5867,16 @@
         <v>14</v>
       </c>
       <c r="P40" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q40" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R40" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S40" s="14" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5900,7 +5899,7 @@
         <v>124</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5933,13 +5932,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q41" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R41" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S41" s="14" t="s">
         <v>9</v>
@@ -5965,7 +5964,7 @@
         <v>126</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>15</v>
@@ -5998,13 +5997,13 @@
         <v>1</v>
       </c>
       <c r="P42" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q42" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R42" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S42" s="14" t="s">
         <v>9</v>
@@ -6018,22 +6017,22 @@
         <v>127</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>128</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -6063,13 +6062,13 @@
         <v>4</v>
       </c>
       <c r="P43" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q43" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R43" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S43" s="14" t="s">
         <v>9</v>
@@ -6095,7 +6094,7 @@
         <v>130</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>10</v>
@@ -6128,13 +6127,13 @@
         <v>1</v>
       </c>
       <c r="P44" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q44" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R44" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S44" s="14" t="s">
         <v>9</v>
@@ -6148,22 +6147,22 @@
         <v>131</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E45" s="15" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6196,13 +6195,13 @@
         <v>127</v>
       </c>
       <c r="Q45" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R45" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S45" s="14" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.25">
@@ -6213,22 +6212,22 @@
         <v>132</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E46" s="15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>133</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I46" s="3">
         <f>VLOOKUP(H46,cardsort_group_IDs!A:B,2,0)</f>
@@ -6261,13 +6260,13 @@
         <v>127</v>
       </c>
       <c r="Q46" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R46" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S46" s="14" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6281,16 +6280,16 @@
         <v>136</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>137</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>15</v>
@@ -6323,13 +6322,13 @@
         <v>11</v>
       </c>
       <c r="P47" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q47" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R47" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S47" s="14" t="s">
         <v>9</v>
@@ -6343,19 +6342,19 @@
         <v>138</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E48" s="15" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>140</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>34</v>
@@ -6391,10 +6390,10 @@
         <v>127</v>
       </c>
       <c r="Q48" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R48" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S48" s="14" t="s">
         <v>9</v>
@@ -6420,7 +6419,7 @@
         <v>142</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6453,13 +6452,13 @@
         <v>1</v>
       </c>
       <c r="P49" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q49" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R49" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S49" s="14" t="s">
         <v>9</v>
@@ -6473,19 +6472,19 @@
         <v>143</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D50" s="15" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="E50" s="15" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>21</v>
@@ -6518,13 +6517,13 @@
         <v>16</v>
       </c>
       <c r="P50" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q50" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R50" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S50" s="14" t="s">
         <v>9</v>
@@ -6538,7 +6537,7 @@
         <v>145</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D51" s="14" t="s">
         <v>9</v>
@@ -6550,7 +6549,7 @@
         <v>146</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>50</v>
@@ -6583,13 +6582,13 @@
         <v>1</v>
       </c>
       <c r="P51" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q51" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R51" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S51" s="14" t="s">
         <v>9</v>
@@ -6600,22 +6599,22 @@
         <v>67</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E52" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>147</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>50</v>
@@ -6648,13 +6647,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q52" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R52" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S52" s="14" t="s">
         <v>9</v>
@@ -6668,19 +6667,19 @@
         <v>148</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E53" s="15" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>149</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>73</v>
@@ -6713,13 +6712,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q53" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R53" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S53" s="14" t="s">
         <v>9</v>
@@ -6733,19 +6732,19 @@
         <v>150</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D54" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E54" s="15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>151</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>34</v>
@@ -6778,13 +6777,13 @@
         <v>2</v>
       </c>
       <c r="P54" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q54" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R54" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S54" s="14" t="s">
         <v>9</v>
@@ -6801,16 +6800,16 @@
         <v>9</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>153</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>15</v>
@@ -6843,13 +6842,13 @@
         <v>3</v>
       </c>
       <c r="P55" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q55" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R55" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S55" s="14" t="s">
         <v>9</v>
@@ -6866,16 +6865,16 @@
         <v>9</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E56" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>10</v>
@@ -6908,13 +6907,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q56" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R56" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S56" s="14" t="s">
         <v>9</v>
@@ -6931,16 +6930,16 @@
         <v>9</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E57" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>158</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>21</v>
@@ -6973,13 +6972,13 @@
         <v>3</v>
       </c>
       <c r="P57" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q57" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R57" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S57" s="14" t="s">
         <v>9</v>
@@ -7005,7 +7004,7 @@
         <v>161</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -7038,13 +7037,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q58" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R58" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S58" s="14" t="s">
         <v>9</v>
@@ -7061,7 +7060,7 @@
         <v>9</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E59" s="15">
         <v>183</v>
@@ -7070,7 +7069,7 @@
         <v>163</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>34</v>
@@ -7103,13 +7102,13 @@
         <v>2</v>
       </c>
       <c r="P59" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q59" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R59" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S59" s="14" t="s">
         <v>9</v>
@@ -7123,19 +7122,19 @@
         <v>164</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D60" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E60" s="15" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>165</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>10</v>
@@ -7168,13 +7167,13 @@
         <v>2</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q60" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R60" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S60" s="14" t="s">
         <v>9</v>
@@ -7191,19 +7190,19 @@
         <v>167</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E61" s="15" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>168</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I61" s="3">
         <f>VLOOKUP(H61,cardsort_group_IDs!A:B,2,0)</f>
@@ -7236,10 +7235,10 @@
         <v>127</v>
       </c>
       <c r="Q61" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R61" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S61" s="14" t="s">
         <v>9</v>
@@ -7256,16 +7255,16 @@
         <v>9</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E62" s="15" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>170</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>73</v>
@@ -7301,10 +7300,10 @@
         <v>127</v>
       </c>
       <c r="Q62" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R62" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S62" s="14" t="s">
         <v>9</v>
@@ -7330,7 +7329,7 @@
         <v>172</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>73</v>
@@ -7363,13 +7362,13 @@
         <v>1</v>
       </c>
       <c r="P63" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q63" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R63" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S63" s="14" t="s">
         <v>9</v>
@@ -7386,7 +7385,7 @@
         <v>9</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E64" s="15">
         <v>202</v>
@@ -7395,7 +7394,7 @@
         <v>174</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>34</v>
@@ -7428,13 +7427,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q64" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R64" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S64" s="14" t="s">
         <v>9</v>
@@ -7460,7 +7459,7 @@
         <v>176</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>10</v>
@@ -7493,13 +7492,13 @@
         <v>1</v>
       </c>
       <c r="P65" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q65" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R65" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S65" s="14" t="s">
         <v>9</v>
@@ -7513,22 +7512,22 @@
         <v>177</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="E66" s="15" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>178</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I66" s="3">
         <f>VLOOKUP(H66,cardsort_group_IDs!A:B,2,0)</f>
@@ -7561,10 +7560,10 @@
         <v>127</v>
       </c>
       <c r="Q66" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R66" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S66" s="14" t="s">
         <v>9</v>
@@ -7581,7 +7580,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E67" s="15">
         <v>501</v>
@@ -7590,7 +7589,7 @@
         <v>179</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>21</v>
@@ -7623,13 +7622,13 @@
         <v>2</v>
       </c>
       <c r="P67" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q67" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R67" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S67" s="14" t="s">
         <v>9</v>
@@ -7646,7 +7645,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E68" s="15" t="s">
         <v>9</v>
@@ -7655,7 +7654,7 @@
         <v>181</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>15</v>
@@ -7688,13 +7687,13 @@
         <v>1</v>
       </c>
       <c r="P68" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q68" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R68" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S68" s="14" t="s">
         <v>9</v>
@@ -7711,16 +7710,16 @@
         <v>9</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="E69" s="15" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>183</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7753,13 +7752,13 @@
         <v>4</v>
       </c>
       <c r="P69" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q69" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R69" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S69" s="14" t="s">
         <v>9</v>
@@ -7773,19 +7772,19 @@
         <v>184</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E70" s="15" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>185</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>34</v>
@@ -7818,13 +7817,13 @@
         <v>4</v>
       </c>
       <c r="P70" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q70" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R70" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S70" s="14" t="s">
         <v>9</v>
@@ -7841,16 +7840,16 @@
         <v>9</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="E71" s="15" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>187</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>34</v>
@@ -7883,13 +7882,13 @@
         <v>5</v>
       </c>
       <c r="P71" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q71" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R71" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S71" s="14" t="s">
         <v>9</v>
@@ -7903,19 +7902,19 @@
         <v>188</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E72" s="15" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>189</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>34</v>
@@ -7951,10 +7950,10 @@
         <v>127</v>
       </c>
       <c r="Q72" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R72" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S72" s="14" t="s">
         <v>9</v>
@@ -7968,19 +7967,19 @@
         <v>190</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E73" s="15" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>191</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>15</v>
@@ -8013,13 +8012,13 @@
         <v>4</v>
       </c>
       <c r="P73" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q73" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R73" t="s">
         <v>694</v>
-      </c>
-      <c r="R73" t="s">
-        <v>697</v>
       </c>
       <c r="S73" s="14" t="s">
         <v>9</v>
@@ -8036,16 +8035,16 @@
         <v>9</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E74" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>193</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>50</v>
@@ -8078,13 +8077,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q74" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R74" t="s">
         <v>694</v>
-      </c>
-      <c r="R74" t="s">
-        <v>697</v>
       </c>
       <c r="S74" s="14" t="s">
         <v>9</v>
@@ -8110,7 +8109,7 @@
         <v>195</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8143,13 +8142,13 @@
         <v>1</v>
       </c>
       <c r="P75" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q75" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R75" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S75" s="14" t="s">
         <v>9</v>
@@ -8163,19 +8162,19 @@
         <v>196</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D76" s="14" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E76" s="15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>197</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>73</v>
@@ -8208,13 +8207,13 @@
         <v>4</v>
       </c>
       <c r="P76" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q76" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R76" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S76" s="14" t="s">
         <v>9</v>
@@ -8231,16 +8230,16 @@
         <v>199</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>200</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>21</v>
@@ -8273,13 +8272,13 @@
         <v>3</v>
       </c>
       <c r="P77" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q77" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R77" t="s">
         <v>694</v>
-      </c>
-      <c r="R77" t="s">
-        <v>697</v>
       </c>
       <c r="S77" s="14" t="s">
         <v>9</v>
@@ -8305,7 +8304,7 @@
         <v>202</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8338,13 +8337,13 @@
         <v>1</v>
       </c>
       <c r="P78" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q78" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R78" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S78" s="14" t="s">
         <v>9</v>
@@ -8358,7 +8357,7 @@
         <v>203</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D79" s="12">
         <v>209</v>
@@ -8370,7 +8369,7 @@
         <v>204</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>10</v>
@@ -8403,13 +8402,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q79" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R79" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S79" s="14" t="s">
         <v>9</v>
@@ -8435,7 +8434,7 @@
         <v>206</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>10</v>
@@ -8468,13 +8467,13 @@
         <v>1</v>
       </c>
       <c r="P80" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q80" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R80" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S80" s="14" t="s">
         <v>9</v>
@@ -8500,7 +8499,7 @@
         <v>208</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>10</v>
@@ -8533,13 +8532,13 @@
         <v>1</v>
       </c>
       <c r="P81" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q81" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R81" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S81" s="14" t="s">
         <v>9</v>
@@ -8556,7 +8555,7 @@
         <v>9</v>
       </c>
       <c r="D82" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E82" s="15">
         <v>501</v>
@@ -8565,7 +8564,7 @@
         <v>211</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8598,13 +8597,13 @@
         <v>2</v>
       </c>
       <c r="P82" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q82" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R82" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S82" s="14" t="s">
         <v>9</v>
@@ -8621,7 +8620,7 @@
         <v>213</v>
       </c>
       <c r="D83" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E83" s="15" t="s">
         <v>9</v>
@@ -8630,10 +8629,10 @@
         <v>214</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I83" s="3">
         <f>VLOOKUP(H83,cardsort_group_IDs!A:B,2,0)</f>
@@ -8663,13 +8662,13 @@
         <v>2</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q83" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R83" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S83" s="14" t="s">
         <v>9</v>
@@ -8680,22 +8679,22 @@
         <v>105</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D84" s="15" t="s">
+        <v>519</v>
+      </c>
+      <c r="E84" s="15" t="s">
+        <v>520</v>
+      </c>
+      <c r="F84" s="4" t="s">
         <v>215</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="E84" s="15" t="s">
-        <v>523</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="G84" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>21</v>
@@ -8728,13 +8727,13 @@
         <v>4</v>
       </c>
       <c r="P84" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q84" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R84" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S84" s="14" t="s">
         <v>9</v>
@@ -8745,22 +8744,22 @@
         <v>107</v>
       </c>
       <c r="B85" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="E85" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>510</v>
-      </c>
-      <c r="E85" s="15" t="s">
-        <v>511</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="G85" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>15</v>
@@ -8793,13 +8792,13 @@
         <v>7</v>
       </c>
       <c r="P85" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q85" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R85" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S85" s="14" t="s">
         <v>9</v>
@@ -8810,22 +8809,22 @@
         <v>108</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>219</v>
+        <v>775</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>281</v>
+        <v>776</v>
       </c>
       <c r="D86" s="14" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E86" s="15" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8858,13 +8857,13 @@
         <v>8</v>
       </c>
       <c r="P86" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q86" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R86" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S86" s="14" t="s">
         <v>9</v>
@@ -8875,22 +8874,22 @@
         <v>109</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E87" s="15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>21</v>
@@ -8923,13 +8922,13 @@
         <v>8</v>
       </c>
       <c r="P87" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q87" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R87" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S87" s="14" t="s">
         <v>9</v>
@@ -8940,25 +8939,25 @@
         <v>112</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="D88" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E88" s="15" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I88" s="3">
         <f>VLOOKUP(H88,cardsort_group_IDs!A:B,2,0)</f>
@@ -8991,10 +8990,10 @@
         <v>127</v>
       </c>
       <c r="Q88" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R88" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S88" s="14" t="s">
         <v>9</v>
@@ -9005,22 +9004,22 @@
         <v>114</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>55</v>
@@ -9056,10 +9055,10 @@
         <v>127</v>
       </c>
       <c r="Q89" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R89" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S89" s="14" t="s">
         <v>9</v>
@@ -9070,7 +9069,7 @@
         <v>115</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>9</v>
@@ -9082,10 +9081,10 @@
         <v>183</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>50</v>
@@ -9118,13 +9117,13 @@
         <v>1</v>
       </c>
       <c r="P90" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q90" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R90" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S90" s="14" t="s">
         <v>9</v>
@@ -9135,22 +9134,22 @@
         <v>116</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D91" s="14" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E91" s="15" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>34</v>
@@ -9160,7 +9159,7 @@
         <v>205</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9183,13 +9182,13 @@
         <v>5</v>
       </c>
       <c r="P91" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q91" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R91" t="s">
         <v>694</v>
-      </c>
-      <c r="R91" t="s">
-        <v>697</v>
       </c>
       <c r="S91" s="14" t="s">
         <v>9</v>
@@ -9203,19 +9202,19 @@
         <v>39</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D92" s="14" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E92" s="15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>34</v>
@@ -9251,10 +9250,10 @@
         <v>127</v>
       </c>
       <c r="Q92" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R92" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S92" s="14" t="s">
         <v>9</v>
@@ -9265,7 +9264,7 @@
         <v>118</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>9</v>
@@ -9277,10 +9276,10 @@
         <v>9</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>21</v>
@@ -9290,7 +9289,7 @@
         <v>202</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9313,13 +9312,13 @@
         <v>1</v>
       </c>
       <c r="P93" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q93" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R93" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S93" s="14" t="s">
         <v>9</v>
@@ -9330,22 +9329,22 @@
         <v>119</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D94" s="14" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E94" s="15">
         <v>501</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>15</v>
@@ -9378,13 +9377,13 @@
         <v>2</v>
       </c>
       <c r="P94" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q94" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R94" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S94" s="14" t="s">
         <v>9</v>
@@ -9395,22 +9394,22 @@
         <v>120</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E95" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>15</v>
@@ -9443,13 +9442,13 @@
         <v>3</v>
       </c>
       <c r="P95" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q95" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R95" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S95" s="14" t="s">
         <v>9</v>
@@ -9460,22 +9459,22 @@
         <v>121</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D96" s="14" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="E96" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>15</v>
@@ -9511,10 +9510,10 @@
         <v>127</v>
       </c>
       <c r="Q96" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R96" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S96" s="14" t="s">
         <v>9</v>
@@ -9525,22 +9524,22 @@
         <v>122</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="E97" s="15" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>15</v>
@@ -9576,10 +9575,10 @@
         <v>127</v>
       </c>
       <c r="Q97" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R97" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S97" s="14" t="s">
         <v>9</v>
@@ -9590,25 +9589,25 @@
         <v>124</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="D98" s="14" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="E98" s="15" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9638,13 +9637,13 @@
         <v>8</v>
       </c>
       <c r="P98" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q98" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R98" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S98" s="14" t="s">
         <v>9</v>
@@ -9655,22 +9654,22 @@
         <v>126</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E99" s="15">
         <v>501</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H99" s="3" t="s">
         <v>55</v>
@@ -9703,13 +9702,13 @@
         <v>2</v>
       </c>
       <c r="P99" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q99" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R99" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S99" s="14" t="s">
         <v>9</v>
@@ -9720,22 +9719,22 @@
         <v>127</v>
       </c>
       <c r="B100" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D100" s="14" t="s">
+        <v>766</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C100" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>770</v>
-      </c>
-      <c r="E100" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>252</v>
-      </c>
       <c r="G100" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>55</v>
@@ -9768,13 +9767,13 @@
         <v>4</v>
       </c>
       <c r="P100" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q100" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R100" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S100" s="14" t="s">
         <v>9</v>
@@ -9785,22 +9784,22 @@
         <v>128</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E101" s="15">
         <v>501</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>55</v>
@@ -9833,13 +9832,13 @@
         <v>2</v>
       </c>
       <c r="P101" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q101" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R101" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S101" s="14" t="s">
         <v>9</v>
@@ -9850,22 +9849,22 @@
         <v>129</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D102" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E102" s="15" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>55</v>
@@ -9901,10 +9900,10 @@
         <v>127</v>
       </c>
       <c r="Q102" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R102" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S102" s="14" t="s">
         <v>9</v>
@@ -9915,25 +9914,25 @@
         <v>130</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C103" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="14" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E103" s="15" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I103" s="3">
         <f>VLOOKUP(H103,cardsort_group_IDs!A:B,2,0)</f>
@@ -9963,13 +9962,13 @@
         <v>5</v>
       </c>
       <c r="P103" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q103" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R103" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S103" s="14" t="s">
         <v>9</v>
@@ -9980,22 +9979,22 @@
         <v>134</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="E104" s="16" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G104" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H104" t="s">
         <v>34</v>
@@ -10031,10 +10030,10 @@
         <v>127</v>
       </c>
       <c r="Q104" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R104" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S104" s="14" t="s">
         <v>9</v>
@@ -10045,7 +10044,7 @@
         <v>135</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -10057,13 +10056,13 @@
         <v>183</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="G105" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H105" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I105" s="3">
         <f>VLOOKUP(H105,cardsort_group_IDs!A:B,2,0)</f>
@@ -10093,13 +10092,13 @@
         <v>1</v>
       </c>
       <c r="P105" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q105" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R105" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S105" s="14" t="s">
         <v>9</v>
@@ -10110,7 +10109,7 @@
         <v>136</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
@@ -10122,10 +10121,10 @@
         <v>240</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G106" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H106" t="s">
         <v>55</v>
@@ -10158,13 +10157,13 @@
         <v>1</v>
       </c>
       <c r="P106" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q106" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R106" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S106" s="14" t="s">
         <v>9</v>
@@ -10175,25 +10174,25 @@
         <v>137</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="D107" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E107" s="16" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F107" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G107" t="s">
+        <v>699</v>
+      </c>
+      <c r="H107" t="s">
         <v>501</v>
-      </c>
-      <c r="G107" t="s">
-        <v>702</v>
-      </c>
-      <c r="H107" t="s">
-        <v>504</v>
       </c>
       <c r="I107" s="3">
         <f>VLOOKUP(H107,cardsort_group_IDs!A:B,2,0)</f>
@@ -10223,13 +10222,13 @@
         <v>6</v>
       </c>
       <c r="P107" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q107" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R107" t="s">
         <v>694</v>
-      </c>
-      <c r="R107" t="s">
-        <v>697</v>
       </c>
       <c r="S107" s="14" t="s">
         <v>9</v>
@@ -10240,10 +10239,10 @@
         <v>138</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D108" s="14" t="s">
         <v>9</v>
@@ -10252,10 +10251,10 @@
         <v>236</v>
       </c>
       <c r="F108" s="10" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="G108" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H108" t="s">
         <v>10</v>
@@ -10288,13 +10287,13 @@
         <v>1</v>
       </c>
       <c r="P108" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q108" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R108" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S108" s="14" t="s">
         <v>9</v>
@@ -10305,7 +10304,7 @@
         <v>139</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
@@ -10317,10 +10316,10 @@
         <v>9</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>21</v>
@@ -10353,13 +10352,13 @@
         <v>1</v>
       </c>
       <c r="P109" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q109" s="14" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="R109" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S109" s="14" t="s">
         <v>9</v>
@@ -10370,22 +10369,22 @@
         <v>140</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E110" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>15</v>
@@ -10418,13 +10417,13 @@
         <v>18</v>
       </c>
       <c r="P110" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q110" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R110" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S110" s="14">
         <v>2</v>
@@ -10435,22 +10434,22 @@
         <v>141</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D111" s="14" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E111" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>55</v>
@@ -10483,13 +10482,13 @@
         <v>3</v>
       </c>
       <c r="P111" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q111" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R111" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S111" s="14">
         <v>129</v>
@@ -10500,22 +10499,22 @@
         <v>142</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="14" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E112" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>55</v>
@@ -10548,13 +10547,13 @@
         <v>2</v>
       </c>
       <c r="P112" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q112" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R112" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S112" s="14">
         <v>19</v>
@@ -10565,22 +10564,22 @@
         <v>143</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="E113" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>55</v>
@@ -10613,13 +10612,13 @@
         <v>5</v>
       </c>
       <c r="P113" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q113" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R113" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S113" s="14" t="s">
         <v>9</v>
@@ -10630,22 +10629,22 @@
         <v>144</v>
       </c>
       <c r="B114" t="s">
+        <v>597</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C114" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D114" s="12" t="s">
-        <v>574</v>
-      </c>
-      <c r="E114" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>603</v>
-      </c>
       <c r="G114" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>15</v>
@@ -10678,16 +10677,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="14" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="Q114" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R114" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S114" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10695,22 +10694,22 @@
         <v>145</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="C115" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E115" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H115" t="s">
         <v>10</v>
@@ -10743,16 +10742,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="14" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="Q115" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R115" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S115" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10760,22 +10759,22 @@
         <v>146</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D116" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E116" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H116" t="s">
         <v>10</v>
@@ -10808,16 +10807,16 @@
         <v>6</v>
       </c>
       <c r="P116" s="14" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="Q116" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R116" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S116" s="14" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.25">
@@ -10825,22 +10824,22 @@
         <v>147</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E117" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>15</v>
@@ -10873,16 +10872,16 @@
         <v>1</v>
       </c>
       <c r="P117" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="Q117" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R117" t="s">
         <v>694</v>
       </c>
-      <c r="R117" t="s">
-        <v>697</v>
-      </c>
       <c r="S117" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.25">
@@ -10890,22 +10889,22 @@
         <v>148</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D118" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="E118" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>10</v>
@@ -10941,13 +10940,13 @@
         <v>127</v>
       </c>
       <c r="Q118" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R118" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S118" s="14" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -10955,22 +10954,22 @@
         <v>149</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D119" s="14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E119" s="15" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>21</v>
@@ -11006,13 +11005,13 @@
         <v>127</v>
       </c>
       <c r="Q119" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R119" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S119" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="120" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11020,25 +11019,25 @@
         <v>150</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D120" s="14" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E120" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
@@ -11071,13 +11070,13 @@
         <v>127</v>
       </c>
       <c r="Q120" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R120" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S120" s="14" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11085,22 +11084,22 @@
         <v>151</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D121" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="F121" s="3" t="s">
         <v>649</v>
       </c>
-      <c r="F121" s="3" t="s">
-        <v>652</v>
-      </c>
       <c r="G121" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11136,10 +11135,10 @@
         <v>127</v>
       </c>
       <c r="Q121" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R121" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S121" s="14" t="s">
         <v>9</v>
@@ -11150,7 +11149,7 @@
         <v>152</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>9</v>
@@ -11159,16 +11158,16 @@
         <v>9</v>
       </c>
       <c r="E122" s="15" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11201,10 +11200,10 @@
         <v>127</v>
       </c>
       <c r="Q122" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R122" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S122" s="14" t="s">
         <v>9</v>
@@ -11215,7 +11214,7 @@
         <v>153</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11224,16 +11223,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="15" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F123" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11266,13 +11265,13 @@
         <v>127</v>
       </c>
       <c r="Q123" s="14" t="s">
+        <v>691</v>
+      </c>
+      <c r="R123" t="s">
         <v>694</v>
       </c>
-      <c r="R123" t="s">
-        <v>697</v>
-      </c>
       <c r="S123" s="14" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.25">
@@ -11280,7 +11279,7 @@
         <v>154</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>9</v>
@@ -11289,16 +11288,16 @@
         <v>9</v>
       </c>
       <c r="E124" s="15" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I124" s="3">
         <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
@@ -11331,13 +11330,13 @@
         <v>127</v>
       </c>
       <c r="Q124" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R124" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="S124" s="14" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
@@ -11345,7 +11344,7 @@
         <v>155</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>9</v>
@@ -11354,16 +11353,16 @@
         <v>9</v>
       </c>
       <c r="E125" s="15" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I125" s="3">
         <f>VLOOKUP(H125,cardsort_group_IDs!A:B,2,0)</f>
@@ -11393,13 +11392,13 @@
         <v>2</v>
       </c>
       <c r="P125" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q125" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R125" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S125" s="14" t="s">
         <v>9</v>
@@ -11410,22 +11409,22 @@
         <v>156</v>
       </c>
       <c r="B126" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>727</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>728</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>727</v>
-      </c>
-      <c r="D126" s="14" t="s">
-        <v>730</v>
-      </c>
-      <c r="E126" s="15" t="s">
-        <v>731</v>
-      </c>
-      <c r="F126" s="3" t="s">
-        <v>729</v>
-      </c>
       <c r="G126" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>34</v>
@@ -11458,13 +11457,13 @@
         <v>2</v>
       </c>
       <c r="P126" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q126" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="R126" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="S126" s="14" t="s">
         <v>9</v>
@@ -11475,25 +11474,25 @@
         <v>157</v>
       </c>
       <c r="B127" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C127" t="s">
+        <v>733</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>745</v>
+      </c>
+      <c r="E127" s="15" t="s">
         <v>735</v>
       </c>
-      <c r="C127" t="s">
-        <v>736</v>
-      </c>
-      <c r="D127" s="14" t="s">
-        <v>748</v>
-      </c>
-      <c r="E127" s="15" t="s">
-        <v>738</v>
-      </c>
       <c r="F127" s="3" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="I127" s="3">
         <f>VLOOKUP(H127,cardsort_group_IDs!A:B,2,0)</f>
@@ -11523,16 +11522,16 @@
         <v>5</v>
       </c>
       <c r="P127" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="Q127" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="R127" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="S127" s="14" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
   </sheetData>
@@ -11654,16 +11653,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="C1" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11671,13 +11670,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11685,27 +11684,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B4" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C4" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D4" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11713,13 +11712,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11727,13 +11726,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C6" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11741,13 +11740,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C7" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11755,13 +11754,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C8" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11769,13 +11768,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C9" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11783,13 +11782,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C10" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11797,13 +11796,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C11" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11811,13 +11810,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C12" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D12" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11825,13 +11824,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C13" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11839,13 +11838,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C14" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11853,13 +11852,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C15" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11867,13 +11866,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11881,13 +11880,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C17" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11895,13 +11894,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C18" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D18" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11909,13 +11908,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C19" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11923,13 +11922,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C20" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11937,13 +11936,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C21" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11951,13 +11950,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C22" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11965,13 +11964,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C23" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11979,13 +11978,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C24" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11993,13 +11992,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C25" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -12007,13 +12006,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C26" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12021,13 +12020,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C27" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12035,13 +12034,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C28" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12049,13 +12048,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C29" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12063,13 +12062,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C30" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12077,13 +12076,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C31" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12091,13 +12090,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C32" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12105,13 +12104,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C33" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12119,13 +12118,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C34" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12133,13 +12132,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="C35" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12147,13 +12146,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C36" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12161,13 +12160,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C37" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12175,13 +12174,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -12189,13 +12188,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C39" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12203,13 +12202,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C40" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12220,10 +12219,10 @@
         <v>37</v>
       </c>
       <c r="C41" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12231,13 +12230,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C42" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12245,13 +12244,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C43" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12259,13 +12258,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="C44" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12273,13 +12272,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C45" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12290,10 +12289,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12304,10 +12303,10 @@
         <v>139</v>
       </c>
       <c r="C47" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12315,13 +12314,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C48" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D48" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12329,13 +12328,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C49" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12343,13 +12342,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12357,10 +12356,10 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12368,13 +12367,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C52" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12382,13 +12381,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C53" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12396,13 +12395,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C54" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12410,13 +12409,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C55" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12424,13 +12423,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C56" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12438,13 +12437,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C57" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12452,13 +12451,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C58" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12466,13 +12465,13 @@
         <v>241</v>
       </c>
       <c r="B59" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C59" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12480,13 +12479,13 @@
         <v>243</v>
       </c>
       <c r="B60" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C60" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12494,13 +12493,13 @@
         <v>244</v>
       </c>
       <c r="B61" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C61" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12508,13 +12507,13 @@
         <v>501</v>
       </c>
       <c r="B62" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="C62" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12522,13 +12521,13 @@
         <v>502</v>
       </c>
       <c r="B63" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C63" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12536,13 +12535,13 @@
         <v>503</v>
       </c>
       <c r="B64" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C64" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12550,13 +12549,13 @@
         <v>504</v>
       </c>
       <c r="B65" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C65" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12564,13 +12563,13 @@
         <v>505</v>
       </c>
       <c r="B66" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C66" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12581,10 +12580,10 @@
         <v>64</v>
       </c>
       <c r="C67" t="s">
-        <v>685</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>734</v>
+        <v>682</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>731</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12592,13 +12591,13 @@
         <v>507</v>
       </c>
       <c r="B68" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C68" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12609,10 +12608,10 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12620,13 +12619,13 @@
         <v>509</v>
       </c>
       <c r="B70" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C70" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12634,1063 +12633,1063 @@
         <v>510</v>
       </c>
       <c r="B71" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C71" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D71" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B72" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C72" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="12" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C73" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B74" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C74" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="12" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="C75" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B76" t="s">
         <v>210</v>
       </c>
       <c r="C76" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="12" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B77" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="C77" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B78" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C78" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s">
         <v>114</v>
       </c>
       <c r="C79" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C80" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C81" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B82" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C82" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B83" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C83" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B84" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="C84" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="12" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B85" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C85" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B86" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C86" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="12" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B87" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C87" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B88" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C88" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="12" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B89" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="C89" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B90" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C90" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="12" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C91" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C92" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="12" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B93" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C93" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B94" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="C94" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="12" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B95" t="s">
         <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B96" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C96" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="12" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B97" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C97" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B98" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C98" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="12" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B99" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C99" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B100" t="s">
         <v>77</v>
       </c>
       <c r="C100" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="12" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="B101" t="s">
         <v>86</v>
       </c>
       <c r="C101" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B102" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C102" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="12" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B103" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C103" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B104" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C104" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="B105" t="s">
         <v>19</v>
       </c>
       <c r="C105" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B106" t="s">
         <v>210</v>
       </c>
       <c r="C106" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B107" t="s">
         <v>114</v>
       </c>
       <c r="C107" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B108" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="C108" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="12" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B109" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C109" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B110" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C110" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="12" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B111" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C111" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B112" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C112" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="12" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B114" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C114" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="12" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B115" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C115" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B116" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C116" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D116" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="12" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B117" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C117" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D117" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B118" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C118" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D118" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="12" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B119" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C119" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D119" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B120" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C120" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D120" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="12" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B121" t="s">
         <v>210</v>
       </c>
       <c r="C121" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D121" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B122" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C122" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D122" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="12" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="B123" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C123" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D123" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B124" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C124" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D124" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="12" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B125" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C125" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D125" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B126" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C126" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D126" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="12" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="B127" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="C127" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D127" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B128" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C128" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D128" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="12" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B129" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C129" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D129" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B130" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C130" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D130" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="12" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="B131" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C131" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D131" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B132" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C132" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D132" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="12" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B133" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C133" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D133" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="B134" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C134" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D134" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="12" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B135" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C135" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D135" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B136" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C136" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D136" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="12" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B137" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C137" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D137" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B138" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C138" t="s">
-        <v>685</v>
-      </c>
-      <c r="D138" s="19" t="s">
-        <v>728</v>
+        <v>682</v>
+      </c>
+      <c r="D138" t="s">
+        <v>725</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="12" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B139" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C139" t="s">
-        <v>676</v>
-      </c>
-      <c r="D139" s="19" t="s">
-        <v>732</v>
+        <v>673</v>
+      </c>
+      <c r="D139" t="s">
+        <v>729</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="B140" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C140" t="s">
-        <v>685</v>
-      </c>
-      <c r="D140" s="19" t="s">
-        <v>739</v>
+        <v>682</v>
+      </c>
+      <c r="D140" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="12" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B141" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C141" t="s">
-        <v>676</v>
-      </c>
-      <c r="D141" s="19" t="s">
-        <v>742</v>
+        <v>673</v>
+      </c>
+      <c r="D141" t="s">
+        <v>739</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B142" t="s">
+        <v>770</v>
+      </c>
+      <c r="C142" t="s">
+        <v>673</v>
+      </c>
+      <c r="D142" t="s">
         <v>743</v>
-      </c>
-      <c r="B142" t="s">
-        <v>774</v>
-      </c>
-      <c r="C142" t="s">
-        <v>676</v>
-      </c>
-      <c r="D142" s="19" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="12" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B143" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C143" t="s">
-        <v>676</v>
-      </c>
-      <c r="D143" s="19" t="s">
-        <v>361</v>
+        <v>673</v>
+      </c>
+      <c r="D143" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B144" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C144" t="s">
-        <v>676</v>
-      </c>
-      <c r="D144" s="19" t="s">
-        <v>747</v>
+        <v>673</v>
+      </c>
+      <c r="D144" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="12" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B145" t="s">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="C145" t="s">
-        <v>676</v>
-      </c>
-      <c r="D145" s="19" t="s">
-        <v>757</v>
+        <v>673</v>
+      </c>
+      <c r="D145" t="s">
+        <v>753</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B146" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="C146" t="s">
-        <v>685</v>
-      </c>
-      <c r="D146" s="19" t="s">
-        <v>761</v>
+        <v>682</v>
+      </c>
+      <c r="D146" t="s">
+        <v>757</v>
       </c>
     </row>
   </sheetData>
@@ -13745,7 +13744,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -14030,7 +14029,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -14038,7 +14037,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -14046,7 +14045,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -14072,50 +14071,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
+        <v>672</v>
+      </c>
+      <c r="B1" s="18" t="s">
         <v>675</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>676</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>679</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C338500-D8F9-438F-B556-206CB84C09BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B03C30CD-027E-4D57-989F-4AEA7C5D0CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="819">
   <si>
     <t>id</t>
   </si>
@@ -293,9 +293,6 @@
   </si>
   <si>
     <t>Local Build Time</t>
-  </si>
-  <si>
-    <t>Measures the time, in seconds, developers spend waiting for their builds to finish locally during development. Impacts developer flow and productivity.</t>
   </si>
   <si>
     <t>Developer Efficacy</t>
@@ -704,9 +701,6 @@
     <t>Build Success Rate, Task Success</t>
   </si>
   <si>
-    <t>Developer Build Time (P50 and P90); Build Time; NextJS Page Compilation Duration; Application/Package Build Duration; Build Time Efficiency</t>
-  </si>
-  <si>
     <t>Number of Blocked Tickets</t>
   </si>
   <si>
@@ -1406,15 +1400,9 @@
     <t>160; 501; 146</t>
   </si>
   <si>
-    <t>506; 131; 146; 183; 146</t>
-  </si>
-  <si>
     <t>170; 131c; 131o; 201</t>
   </si>
   <si>
-    <t>50; 234; 131; 146</t>
-  </si>
-  <si>
     <t>501; 146</t>
   </si>
   <si>
@@ -1440,9 +1428,6 @@
   </si>
   <si>
     <t>506; 508; 183</t>
-  </si>
-  <si>
-    <t>9; 57; 183</t>
   </si>
   <si>
     <t>232a</t>
@@ -2485,6 +2470,39 @@
   </si>
   <si>
     <t>520c</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>https://linkedin.github.io/dph-framework/</t>
+  </si>
+  <si>
+    <t>LinkedIn DPH Framework</t>
+  </si>
+  <si>
+    <t>Developer Build Time; Build Time; NextJS Page Compilation Duration; Application/Package Build Duration; Build Time Efficiency</t>
+  </si>
+  <si>
+    <t>Measures the time, in seconds, developers spend waiting for their builds to finish locally during development. Impacts developer flow and productivity. Considered e.g. as median (P50) or P90.</t>
+  </si>
+  <si>
+    <t>50; 234; 131; 146; 521</t>
+  </si>
+  <si>
+    <t>501; 521</t>
+  </si>
+  <si>
+    <t>170</t>
+  </si>
+  <si>
+    <t>506; 131; 146; 183; 146; 521</t>
+  </si>
+  <si>
+    <t>9; 57; 183; 521</t>
+  </si>
+  <si>
+    <t>501g; 521</t>
   </si>
 </sst>
 </file>
@@ -3361,16 +3379,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>210</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>211</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3388,25 +3406,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>444</v>
-      </c>
       <c r="P1" s="15" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="Q1" s="15" t="s">
+        <v>610</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>620</v>
-      </c>
       <c r="S1" s="15" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3420,16 +3438,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3462,16 +3480,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q2" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R2" t="s">
         <v>616</v>
       </c>
-      <c r="R2" t="s">
-        <v>621</v>
-      </c>
       <c r="S2" s="12" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3494,7 +3512,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3527,13 +3545,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R3" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
@@ -3544,22 +3562,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3592,16 +3610,16 @@
         <v>4</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q4" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R4" t="s">
         <v>617</v>
       </c>
-      <c r="R4" t="s">
-        <v>622</v>
-      </c>
       <c r="S4" s="12" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -3612,22 +3630,22 @@
         <v>25</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3657,13 +3675,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q5" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R5" t="s">
         <v>616</v>
-      </c>
-      <c r="R5" t="s">
-        <v>621</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
@@ -3689,7 +3707,7 @@
         <v>29</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3722,13 +3740,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R6" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
@@ -3742,19 +3760,19 @@
         <v>30</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -3787,13 +3805,13 @@
         <v>27</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R7" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S7" s="12" t="s">
         <v>9</v>
@@ -3809,17 +3827,17 @@
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="12">
-        <v>170</v>
+      <c r="D8" s="12" t="s">
+        <v>815</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>9</v>
+        <v>808</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -3837,7 +3855,7 @@
       </c>
       <c r="L8" s="3">
         <f t="shared" si="3"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <f t="shared" si="0"/>
@@ -3845,20 +3863,20 @@
       </c>
       <c r="N8" s="3">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" s="3">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R8" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
@@ -3875,16 +3893,16 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="E9" s="13">
-        <v>501</v>
+        <v>818</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>814</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>38</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>31</v>
@@ -3906,24 +3924,24 @@
       </c>
       <c r="M9" s="3">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="3">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R9" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
@@ -3934,22 +3952,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>731</v>
-      </c>
-      <c r="E10" s="13">
-        <v>501</v>
+        <v>726</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>814</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -3975,20 +3993,20 @@
       </c>
       <c r="N10" s="3">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R10" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
@@ -4005,16 +4023,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -4047,13 +4065,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R11" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
@@ -4070,16 +4088,16 @@
         <v>43</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>453</v>
+        <v>816</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>45</v>
@@ -4105,20 +4123,20 @@
       </c>
       <c r="N12" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O12" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q12" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R12" t="s">
         <v>617</v>
-      </c>
-      <c r="R12" t="s">
-        <v>622</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
@@ -4132,19 +4150,19 @@
         <v>46</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>47</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
@@ -4177,13 +4195,13 @@
         <v>5</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R13" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
@@ -4197,19 +4215,19 @@
         <v>48</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>50</v>
@@ -4242,13 +4260,13 @@
         <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q14" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R14" t="s">
         <v>617</v>
-      </c>
-      <c r="R14" t="s">
-        <v>622</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
@@ -4262,22 +4280,22 @@
         <v>51</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>52</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4307,13 +4325,13 @@
         <v>6</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R15" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
@@ -4330,16 +4348,16 @@
         <v>9</v>
       </c>
       <c r="D16" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E16" s="13" t="s">
         <v>373</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>56</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4372,13 +4390,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R16" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
@@ -4392,19 +4410,19 @@
         <v>57</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>59</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>45</v>
@@ -4437,13 +4455,13 @@
         <v>2</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R17" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S17" s="12" t="s">
         <v>9</v>
@@ -4469,7 +4487,7 @@
         <v>63</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4502,13 +4520,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R18" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
@@ -4528,13 +4546,13 @@
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>66</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>67</v>
@@ -4567,13 +4585,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R19" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
@@ -4584,22 +4602,22 @@
         <v>26</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E20" s="13">
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>67</v>
@@ -4632,16 +4650,16 @@
         <v>3</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R20" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -4652,19 +4670,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4697,13 +4715,13 @@
         <v>19</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q21" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R21" t="s">
         <v>617</v>
-      </c>
-      <c r="R21" t="s">
-        <v>622</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
@@ -4717,19 +4735,19 @@
         <v>70</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>71</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
@@ -4762,13 +4780,13 @@
         <v>2</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R22" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
@@ -4785,16 +4803,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>67</v>
@@ -4827,16 +4845,16 @@
         <v>21</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q23" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R23" t="s">
         <v>617</v>
       </c>
-      <c r="R23" t="s">
-        <v>622</v>
-      </c>
       <c r="S23" s="12" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -4847,19 +4865,19 @@
         <v>73</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>465</v>
+        <v>817</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>74</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
@@ -4885,20 +4903,20 @@
       </c>
       <c r="N24" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O24" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q24" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R24" t="s">
         <v>617</v>
-      </c>
-      <c r="R24" t="s">
-        <v>622</v>
       </c>
       <c r="S24" s="12" t="s">
         <v>9</v>
@@ -4915,7 +4933,7 @@
         <v>9</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E25" s="13">
         <v>501</v>
@@ -4924,7 +4942,7 @@
         <v>78</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>67</v>
@@ -4957,13 +4975,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q25" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R25" t="s">
         <v>617</v>
-      </c>
-      <c r="R25" t="s">
-        <v>622</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
@@ -4980,16 +4998,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>373</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>375</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>80</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5022,19 +5040,19 @@
         <v>3</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q26" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="R26" t="s">
         <v>618</v>
       </c>
-      <c r="R26" t="s">
-        <v>623</v>
-      </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>34</v>
       </c>
@@ -5042,19 +5060,19 @@
         <v>82</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>219</v>
+        <v>811</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>455</v>
+        <v>813</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>83</v>
+        <v>812</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5080,20 +5098,20 @@
       </c>
       <c r="N27" s="3">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R27" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
@@ -5104,32 +5122,32 @@
         <v>35</v>
       </c>
       <c r="B28" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K28" s="3">
         <f>VLOOKUP(J28,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5152,13 +5170,13 @@
         <v>3</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R28" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S28" s="12" t="s">
         <v>9</v>
@@ -5169,32 +5187,32 @@
         <v>36</v>
       </c>
       <c r="B29" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>592</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>779</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>597</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>784</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>88</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I29" s="3">
         <f>VLOOKUP(H29,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K29" s="3">
         <f>VLOOKUP(J29,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5217,13 +5235,13 @@
         <v>44</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R29" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
@@ -5234,7 +5252,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>9</v>
@@ -5246,10 +5264,10 @@
         <v>506</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>10</v>
@@ -5282,13 +5300,13 @@
         <v>1</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R30" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
@@ -5299,22 +5317,22 @@
         <v>38</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5347,13 +5365,13 @@
         <v>17</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R31" t="s">
         <v>616</v>
-      </c>
-      <c r="R31" t="s">
-        <v>621</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
@@ -5364,22 +5382,22 @@
         <v>39</v>
       </c>
       <c r="B32" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="G32" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>15</v>
@@ -5412,13 +5430,13 @@
         <v>3</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q32" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R32" t="s">
         <v>616</v>
-      </c>
-      <c r="R32" t="s">
-        <v>621</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
@@ -5432,22 +5450,22 @@
         <v>53</v>
       </c>
       <c r="C33" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>637</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5477,13 +5495,13 @@
         <v>14</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q33" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R33" t="s">
         <v>616</v>
-      </c>
-      <c r="R33" t="s">
-        <v>621</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
@@ -5494,32 +5512,32 @@
         <v>41</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>98</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I34" s="3">
         <f>VLOOKUP(H34,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K34" s="3">
         <f>VLOOKUP(J34,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5542,13 +5560,13 @@
         <v>6</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q34" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R34" t="s">
         <v>616</v>
-      </c>
-      <c r="R34" t="s">
-        <v>621</v>
       </c>
       <c r="S34" s="12" t="s">
         <v>9</v>
@@ -5559,22 +5577,22 @@
         <v>42</v>
       </c>
       <c r="B35" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>31</v>
@@ -5607,13 +5625,13 @@
         <v>2</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R35" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
@@ -5624,32 +5642,32 @@
         <v>43</v>
       </c>
       <c r="B36" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I36" s="3">
         <f>VLOOKUP(H36,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K36" s="3">
         <f>VLOOKUP(J36,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5672,13 +5690,13 @@
         <v>3</v>
       </c>
       <c r="P36" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q36" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R36" t="s">
         <v>616</v>
-      </c>
-      <c r="R36" t="s">
-        <v>621</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
@@ -5689,22 +5707,22 @@
         <v>44</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5714,7 +5732,7 @@
         <v>202</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K37" s="3">
         <f>VLOOKUP(J37,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5737,13 +5755,13 @@
         <v>3</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R37" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
@@ -5754,7 +5772,7 @@
         <v>45</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>9</v>
@@ -5763,13 +5781,13 @@
         <v>9</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>21</v>
@@ -5779,7 +5797,7 @@
         <v>202</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K38" s="3">
         <f>VLOOKUP(J38,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5802,13 +5820,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q38" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R38" t="s">
         <v>617</v>
-      </c>
-      <c r="R38" t="s">
-        <v>622</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
@@ -5819,22 +5837,22 @@
         <v>46</v>
       </c>
       <c r="B39" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="G39" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>45</v>
@@ -5844,7 +5862,7 @@
         <v>206</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K39" s="3">
         <f>VLOOKUP(J39,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5867,13 +5885,13 @@
         <v>2</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q39" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R39" t="s">
         <v>616</v>
-      </c>
-      <c r="R39" t="s">
-        <v>621</v>
       </c>
       <c r="S39" s="12" t="s">
         <v>9</v>
@@ -5884,25 +5902,25 @@
         <v>50</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="C40" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>679</v>
-      </c>
       <c r="E40" s="13" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5932,16 +5950,16 @@
         <v>14</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R40" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S40" s="12" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.25">
@@ -5949,7 +5967,7 @@
         <v>51</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>9</v>
@@ -5961,10 +5979,10 @@
         <v>506</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>15</v>
@@ -5997,13 +6015,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R41" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
@@ -6014,32 +6032,32 @@
         <v>56</v>
       </c>
       <c r="B42" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E42" s="13" t="s">
+        <v>459</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I42" s="3">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K42" s="3">
         <f>VLOOKUP(J42,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6062,13 +6080,13 @@
         <v>4</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R42" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S42" s="12" t="s">
         <v>9</v>
@@ -6079,7 +6097,7 @@
         <v>57</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>9</v>
@@ -6091,10 +6109,10 @@
         <v>514</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>10</v>
@@ -6127,13 +6145,13 @@
         <v>1</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R43" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S43" s="12" t="s">
         <v>9</v>
@@ -6144,25 +6162,25 @@
         <v>58</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I44" s="3">
         <f>VLOOKUP(H44,cardsort_group_IDs!A:B,2,0)</f>
@@ -6192,16 +6210,16 @@
         <v>4</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q44" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R44" t="s">
         <v>616</v>
       </c>
-      <c r="R44" t="s">
-        <v>621</v>
-      </c>
       <c r="S44" s="12" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.25">
@@ -6209,25 +6227,25 @@
         <v>59</v>
       </c>
       <c r="B45" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I45" s="3">
         <f>VLOOKUP(H45,cardsort_group_IDs!A:B,2,0)</f>
@@ -6257,16 +6275,16 @@
         <v>4</v>
       </c>
       <c r="P45" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R45" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S45" s="12" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -6274,22 +6292,22 @@
         <v>62</v>
       </c>
       <c r="B46" s="25" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>15</v>
@@ -6322,13 +6340,13 @@
         <v>11</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q46" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R46" t="s">
         <v>617</v>
-      </c>
-      <c r="R46" t="s">
-        <v>622</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
@@ -6339,22 +6357,22 @@
         <v>63</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>31</v>
@@ -6387,13 +6405,13 @@
         <v>4</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R47" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
@@ -6404,7 +6422,7 @@
         <v>64</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
@@ -6416,10 +6434,10 @@
         <v>9</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>21</v>
@@ -6452,13 +6470,13 @@
         <v>1</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R48" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
@@ -6469,22 +6487,22 @@
         <v>65</v>
       </c>
       <c r="B49" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>453</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>558</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>21</v>
@@ -6494,7 +6512,7 @@
         <v>202</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K49" s="3">
         <f>VLOOKUP(J49,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6517,13 +6535,13 @@
         <v>16</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q49" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R49" t="s">
         <v>617</v>
-      </c>
-      <c r="R49" t="s">
-        <v>622</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
@@ -6534,10 +6552,10 @@
         <v>66</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>9</v>
@@ -6546,10 +6564,10 @@
         <v>235</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>45</v>
@@ -6582,13 +6600,13 @@
         <v>1</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R50" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S50" s="12" t="s">
         <v>9</v>
@@ -6599,22 +6617,22 @@
         <v>67</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D51" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E51" s="13" t="s">
-        <v>375</v>
-      </c>
       <c r="F51" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>45</v>
@@ -6624,7 +6642,7 @@
         <v>206</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K51" s="3">
         <f>VLOOKUP(J51,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6647,13 +6665,13 @@
         <v>3</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R51" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
@@ -6664,22 +6682,22 @@
         <v>69</v>
       </c>
       <c r="B52" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="E52" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="E52" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="G52" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>67</v>
@@ -6712,13 +6730,13 @@
         <v>3</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q52" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R52" t="s">
         <v>617</v>
-      </c>
-      <c r="R52" t="s">
-        <v>622</v>
       </c>
       <c r="S52" s="12" t="s">
         <v>9</v>
@@ -6729,22 +6747,22 @@
         <v>70</v>
       </c>
       <c r="B53" s="24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D53" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>31</v>
@@ -6777,16 +6795,16 @@
         <v>2</v>
       </c>
       <c r="P53" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R53" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S53" s="12" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="54" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -6794,22 +6812,22 @@
         <v>71</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>15</v>
@@ -6842,13 +6860,13 @@
         <v>4</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R54" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S54" s="12" t="s">
         <v>9</v>
@@ -6859,22 +6877,22 @@
         <v>72</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D55" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E55" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E55" s="13" t="s">
-        <v>375</v>
-      </c>
       <c r="F55" s="4" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -6884,7 +6902,7 @@
         <v>201</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K55" s="3">
         <f>VLOOKUP(J55,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6907,16 +6925,16 @@
         <v>3</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q55" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R55" t="s">
         <v>616</v>
       </c>
-      <c r="R55" t="s">
-        <v>621</v>
-      </c>
       <c r="S55" s="12" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="56" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6924,22 +6942,22 @@
         <v>73</v>
       </c>
       <c r="B56" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="G56" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>21</v>
@@ -6949,7 +6967,7 @@
         <v>202</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K56" s="3">
         <f>VLOOKUP(J56,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6972,13 +6990,13 @@
         <v>3</v>
       </c>
       <c r="P56" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R56" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
@@ -6989,22 +7007,22 @@
         <v>75</v>
       </c>
       <c r="B57" s="24" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E57" s="13">
         <v>183</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>31</v>
@@ -7037,13 +7055,13 @@
         <v>2</v>
       </c>
       <c r="P57" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R57" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
@@ -7054,19 +7072,19 @@
         <v>76</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D58" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E58" s="13" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>10</v>
@@ -7076,7 +7094,7 @@
         <v>201</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K58" s="3">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7099,13 +7117,13 @@
         <v>2</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R58" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
@@ -7116,25 +7134,25 @@
         <v>78</v>
       </c>
       <c r="B59" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="D59" s="12" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I59" s="3">
         <f>VLOOKUP(H59,cardsort_group_IDs!A:B,2,0)</f>
@@ -7164,13 +7182,13 @@
         <v>11</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R59" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
@@ -7181,22 +7199,22 @@
         <v>79</v>
       </c>
       <c r="B60" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>636</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>641</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="G60" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>67</v>
@@ -7229,13 +7247,13 @@
         <v>4</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q60" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R60" t="s">
         <v>617</v>
-      </c>
-      <c r="R60" t="s">
-        <v>622</v>
       </c>
       <c r="S60" s="12" t="s">
         <v>9</v>
@@ -7246,7 +7264,7 @@
         <v>80</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>9</v>
@@ -7258,10 +7276,10 @@
         <v>514</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>67</v>
@@ -7294,13 +7312,13 @@
         <v>1</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R61" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S61" s="12" t="s">
         <v>9</v>
@@ -7311,7 +7329,7 @@
         <v>82</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>9</v>
@@ -7323,10 +7341,10 @@
         <v>514</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>10</v>
@@ -7336,7 +7354,7 @@
         <v>201</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K62" s="3">
         <f>VLOOKUP(J62,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7359,13 +7377,13 @@
         <v>1</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R62" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
@@ -7376,32 +7394,32 @@
         <v>83</v>
       </c>
       <c r="B63" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>635</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>559</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>560</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>640</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I63" s="3">
         <f>VLOOKUP(H63,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K63" s="3">
         <f>VLOOKUP(J63,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7424,13 +7442,13 @@
         <v>5</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R63" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
@@ -7441,22 +7459,22 @@
         <v>84</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E64" s="13">
         <v>501</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>21</v>
@@ -7466,7 +7484,7 @@
         <v>202</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K64" s="3">
         <f>VLOOKUP(J64,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7489,13 +7507,13 @@
         <v>2</v>
       </c>
       <c r="P64" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R64" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
@@ -7506,22 +7524,22 @@
         <v>87</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7554,16 +7572,16 @@
         <v>4</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q65" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R65" t="s">
         <v>617</v>
       </c>
-      <c r="R65" t="s">
-        <v>622</v>
-      </c>
       <c r="S65" s="12" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
     </row>
     <row r="66" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -7571,22 +7589,22 @@
         <v>88</v>
       </c>
       <c r="B66" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>685</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="F66" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>690</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="G66" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>31</v>
@@ -7619,13 +7637,13 @@
         <v>4</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R66" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
@@ -7636,22 +7654,22 @@
         <v>89</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>31</v>
@@ -7684,13 +7702,13 @@
         <v>8</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="Q67" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R67" t="s">
         <v>617</v>
-      </c>
-      <c r="R67" t="s">
-        <v>622</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
@@ -7701,22 +7719,22 @@
         <v>90</v>
       </c>
       <c r="B68" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E68" s="13" t="s">
+        <v>575</v>
+      </c>
+      <c r="F68" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>553</v>
-      </c>
-      <c r="E68" s="13" t="s">
-        <v>580</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="G68" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>31</v>
@@ -7749,13 +7767,13 @@
         <v>14</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q68" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="R68" t="s">
         <v>618</v>
-      </c>
-      <c r="R68" t="s">
-        <v>623</v>
       </c>
       <c r="S68" s="12" t="s">
         <v>9</v>
@@ -7766,22 +7784,22 @@
         <v>91</v>
       </c>
       <c r="B69" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="E69" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="E69" s="13" t="s">
-        <v>459</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>160</v>
-      </c>
       <c r="G69" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>15</v>
@@ -7814,13 +7832,13 @@
         <v>4</v>
       </c>
       <c r="P69" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R69" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S69" s="12" t="s">
         <v>9</v>
@@ -7831,22 +7849,22 @@
         <v>92</v>
       </c>
       <c r="B70" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E70" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C70" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E70" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F70" s="5" t="s">
-        <v>162</v>
-      </c>
       <c r="G70" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>45</v>
@@ -7856,7 +7874,7 @@
         <v>206</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K70" s="3">
         <f>VLOOKUP(J70,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7879,13 +7897,13 @@
         <v>3</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R70" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
@@ -7896,7 +7914,7 @@
         <v>93</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>9</v>
@@ -7908,10 +7926,10 @@
         <v>514</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -7944,13 +7962,13 @@
         <v>1</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q71" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R71" t="s">
         <v>617</v>
-      </c>
-      <c r="R71" t="s">
-        <v>622</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
@@ -7961,22 +7979,22 @@
         <v>94</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E72" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>67</v>
@@ -8009,16 +8027,16 @@
         <v>4</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q72" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R72" t="s">
         <v>617</v>
       </c>
-      <c r="R72" t="s">
-        <v>622</v>
-      </c>
       <c r="S72" s="12" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="73" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8026,22 +8044,22 @@
         <v>95</v>
       </c>
       <c r="B73" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="D73" s="13" t="s">
+        <v>367</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F73" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="E73" s="13" t="s">
-        <v>484</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="G73" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>21</v>
@@ -8051,7 +8069,7 @@
         <v>202</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K73" s="3">
         <f>VLOOKUP(J73,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8074,13 +8092,13 @@
         <v>3</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R73" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
@@ -8091,7 +8109,7 @@
         <v>97</v>
       </c>
       <c r="B74" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>9</v>
@@ -8103,10 +8121,10 @@
         <v>508</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>21</v>
@@ -8116,7 +8134,7 @@
         <v>202</v>
       </c>
       <c r="J74" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K74" s="3">
         <f>VLOOKUP(J74,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8139,13 +8157,13 @@
         <v>1</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R74" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
@@ -8156,10 +8174,10 @@
         <v>98</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D75" s="10">
         <v>209</v>
@@ -8168,10 +8186,10 @@
         <v>506</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>10</v>
@@ -8181,7 +8199,7 @@
         <v>201</v>
       </c>
       <c r="J75" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K75" s="3">
         <f>VLOOKUP(J75,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8204,13 +8222,13 @@
         <v>2</v>
       </c>
       <c r="P75" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q75" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R75" t="s">
         <v>617</v>
-      </c>
-      <c r="R75" t="s">
-        <v>622</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
@@ -8221,7 +8239,7 @@
         <v>99</v>
       </c>
       <c r="B76" s="18" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>9</v>
@@ -8233,10 +8251,10 @@
         <v>508</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>10</v>
@@ -8246,7 +8264,7 @@
         <v>201</v>
       </c>
       <c r="J76" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K76" s="3">
         <f>VLOOKUP(J76,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8269,13 +8287,13 @@
         <v>1</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q76" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R76" t="s">
         <v>617</v>
-      </c>
-      <c r="R76" t="s">
-        <v>622</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
@@ -8286,7 +8304,7 @@
         <v>100</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>9</v>
@@ -8298,10 +8316,10 @@
         <v>514</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>10</v>
@@ -8311,7 +8329,7 @@
         <v>201</v>
       </c>
       <c r="J77" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K77" s="3">
         <f>VLOOKUP(J77,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8334,13 +8352,13 @@
         <v>1</v>
       </c>
       <c r="P77" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q77" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R77" t="s">
         <v>617</v>
-      </c>
-      <c r="R77" t="s">
-        <v>622</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
@@ -8351,22 +8369,22 @@
         <v>102</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>749</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>754</v>
-      </c>
-      <c r="C78" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D78" s="12" t="s">
-        <v>759</v>
       </c>
       <c r="E78" s="13">
         <v>501</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>15</v>
@@ -8399,13 +8417,13 @@
         <v>3</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q78" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R78" t="s">
         <v>616</v>
-      </c>
-      <c r="R78" t="s">
-        <v>621</v>
       </c>
       <c r="S78" s="12" t="s">
         <v>9</v>
@@ -8416,32 +8434,32 @@
         <v>104</v>
       </c>
       <c r="B79" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="D79" s="12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E79" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I79" s="3">
         <f>VLOOKUP(H79,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K79" s="3">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8464,13 +8482,13 @@
         <v>2</v>
       </c>
       <c r="P79" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q79" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R79" t="s">
         <v>616</v>
-      </c>
-      <c r="R79" t="s">
-        <v>621</v>
       </c>
       <c r="S79" s="12" t="s">
         <v>9</v>
@@ -8481,22 +8499,22 @@
         <v>105</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D80" s="13" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>21</v>
@@ -8506,7 +8524,7 @@
         <v>202</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K80" s="3">
         <f>VLOOKUP(J80,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8529,13 +8547,13 @@
         <v>4</v>
       </c>
       <c r="P80" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R80" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S80" s="12" t="s">
         <v>9</v>
@@ -8546,22 +8564,22 @@
         <v>107</v>
       </c>
       <c r="B81" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>447</v>
+      </c>
+      <c r="E81" s="13" t="s">
+        <v>448</v>
+      </c>
+      <c r="F81" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D81" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="E81" s="13" t="s">
-        <v>450</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="G81" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>15</v>
@@ -8594,13 +8612,13 @@
         <v>7</v>
       </c>
       <c r="P81" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R81" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
@@ -8611,22 +8629,22 @@
         <v>108</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>15</v>
@@ -8659,13 +8677,13 @@
         <v>8</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q82" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R82" t="s">
         <v>617</v>
-      </c>
-      <c r="R82" t="s">
-        <v>622</v>
       </c>
       <c r="S82" s="12" t="s">
         <v>9</v>
@@ -8676,22 +8694,22 @@
         <v>109</v>
       </c>
       <c r="B83" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>469</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D83" s="13" t="s">
-        <v>474</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>21</v>
@@ -8701,7 +8719,7 @@
         <v>202</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K83" s="3">
         <f>VLOOKUP(J83,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8724,13 +8742,13 @@
         <v>8</v>
       </c>
       <c r="P83" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q83" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R83" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S83" s="12" t="s">
         <v>9</v>
@@ -8741,32 +8759,32 @@
         <v>112</v>
       </c>
       <c r="B84" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="D84" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>188</v>
-      </c>
       <c r="G84" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I84" s="3">
         <f>VLOOKUP(H84,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K84" s="3">
         <f>VLOOKUP(J84,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8789,13 +8807,13 @@
         <v>2</v>
       </c>
       <c r="P84" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R84" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
@@ -8806,22 +8824,22 @@
         <v>114</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="E85" s="13" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>50</v>
@@ -8854,13 +8872,13 @@
         <v>14</v>
       </c>
       <c r="P85" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q85" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R85" t="s">
         <v>617</v>
-      </c>
-      <c r="R85" t="s">
-        <v>622</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
@@ -8871,7 +8889,7 @@
         <v>115</v>
       </c>
       <c r="B86" s="29" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>9</v>
@@ -8883,10 +8901,10 @@
         <v>183</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>45</v>
@@ -8896,7 +8914,7 @@
         <v>206</v>
       </c>
       <c r="J86" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K86" s="3">
         <f>VLOOKUP(J86,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8919,13 +8937,13 @@
         <v>1</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R86" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S86" s="12" t="s">
         <v>9</v>
@@ -8936,22 +8954,22 @@
         <v>116</v>
       </c>
       <c r="B87" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>684</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>194</v>
-      </c>
       <c r="G87" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>31</v>
@@ -8961,7 +8979,7 @@
         <v>205</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K87" s="3">
         <f>VLOOKUP(J87,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8984,13 +9002,13 @@
         <v>5</v>
       </c>
       <c r="P87" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R87" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
@@ -9004,19 +9022,19 @@
         <v>36</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>31</v>
@@ -9049,13 +9067,13 @@
         <v>5</v>
       </c>
       <c r="P88" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R88" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S88" s="12" t="s">
         <v>9</v>
@@ -9066,7 +9084,7 @@
         <v>118</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>9</v>
@@ -9078,10 +9096,10 @@
         <v>9</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>21</v>
@@ -9091,7 +9109,7 @@
         <v>202</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K89" s="3">
         <f>VLOOKUP(J89,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9114,13 +9132,13 @@
         <v>1</v>
       </c>
       <c r="P89" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R89" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S89" s="12" t="s">
         <v>9</v>
@@ -9131,22 +9149,22 @@
         <v>119</v>
       </c>
       <c r="B90" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E90" s="13">
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>15</v>
@@ -9179,13 +9197,13 @@
         <v>2</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q90" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R90" t="s">
         <v>617</v>
-      </c>
-      <c r="R90" t="s">
-        <v>622</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
@@ -9196,22 +9214,22 @@
         <v>120</v>
       </c>
       <c r="B91" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="E91" s="13" t="s">
+        <v>373</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C91" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="E91" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="G91" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>15</v>
@@ -9244,13 +9262,13 @@
         <v>3</v>
       </c>
       <c r="P91" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R91" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S91" s="12" t="s">
         <v>9</v>
@@ -9261,22 +9279,22 @@
         <v>121</v>
       </c>
       <c r="B92" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D92" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="E92" s="13" t="s">
+        <v>785</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="D92" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="E92" s="13" t="s">
-        <v>790</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>205</v>
-      </c>
       <c r="G92" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>15</v>
@@ -9309,13 +9327,13 @@
         <v>9</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q92" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R92" t="s">
         <v>617</v>
-      </c>
-      <c r="R92" t="s">
-        <v>622</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
@@ -9326,22 +9344,22 @@
         <v>122</v>
       </c>
       <c r="B93" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="E93" s="13" t="s">
+        <v>770</v>
+      </c>
+      <c r="F93" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>774</v>
-      </c>
-      <c r="E93" s="13" t="s">
-        <v>775</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>207</v>
-      </c>
       <c r="G93" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>15</v>
@@ -9374,13 +9392,13 @@
         <v>5</v>
       </c>
       <c r="P93" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R93" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
@@ -9391,32 +9409,32 @@
         <v>124</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I94" s="3">
         <f>VLOOKUP(H94,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K94" s="3">
         <f>VLOOKUP(J94,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9439,16 +9457,16 @@
         <v>9</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q94" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R94" t="s">
         <v>616</v>
       </c>
-      <c r="R94" t="s">
-        <v>621</v>
-      </c>
       <c r="S94" s="12" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9456,22 +9474,22 @@
         <v>126</v>
       </c>
       <c r="B95" s="20" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E95" s="13">
         <v>501</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>50</v>
@@ -9504,13 +9522,13 @@
         <v>2</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q95" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R95" t="s">
         <v>617</v>
-      </c>
-      <c r="R95" t="s">
-        <v>622</v>
       </c>
       <c r="S95" s="12" t="s">
         <v>9</v>
@@ -9521,22 +9539,22 @@
         <v>127</v>
       </c>
       <c r="B96" s="20" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>50</v>
@@ -9569,13 +9587,13 @@
         <v>4</v>
       </c>
       <c r="P96" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q96" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R96" t="s">
         <v>617</v>
-      </c>
-      <c r="R96" t="s">
-        <v>622</v>
       </c>
       <c r="S96" s="12" t="s">
         <v>9</v>
@@ -9586,22 +9604,22 @@
         <v>128</v>
       </c>
       <c r="B97" s="20" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E97" s="13">
         <v>501</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H97" s="3" t="s">
         <v>50</v>
@@ -9634,13 +9652,13 @@
         <v>2</v>
       </c>
       <c r="P97" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q97" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R97" t="s">
         <v>617</v>
-      </c>
-      <c r="R97" t="s">
-        <v>622</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
@@ -9651,22 +9669,22 @@
         <v>129</v>
       </c>
       <c r="B98" s="20" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="E98" s="13" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H98" s="3" t="s">
         <v>50</v>
@@ -9699,13 +9717,13 @@
         <v>27</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q98" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R98" t="s">
         <v>617</v>
-      </c>
-      <c r="R98" t="s">
-        <v>622</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
@@ -9716,25 +9734,25 @@
         <v>130</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E99" s="13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="G99" s="18" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I99" s="3">
         <f>VLOOKUP(H99,cardsort_group_IDs!A:B,2,0)</f>
@@ -9764,13 +9782,13 @@
         <v>5</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q99" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R99" t="s">
         <v>616</v>
-      </c>
-      <c r="R99" t="s">
-        <v>621</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
@@ -9781,22 +9799,22 @@
         <v>134</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="E100" s="14" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G100" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H100" t="s">
         <v>31</v>
@@ -9829,13 +9847,13 @@
         <v>11</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R100" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
@@ -9846,7 +9864,7 @@
         <v>135</v>
       </c>
       <c r="B101" s="20" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>9</v>
@@ -9858,20 +9876,20 @@
         <v>183</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G101" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H101" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I101" s="3">
         <f>VLOOKUP(H101,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J101" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K101" s="3">
         <f>VLOOKUP(J101,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9894,13 +9912,13 @@
         <v>1</v>
       </c>
       <c r="P101" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q101" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R101" t="s">
         <v>616</v>
-      </c>
-      <c r="R101" t="s">
-        <v>621</v>
       </c>
       <c r="S101" s="12" t="s">
         <v>9</v>
@@ -9911,25 +9929,25 @@
         <v>137</v>
       </c>
       <c r="B102" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C102" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E102" s="14" t="s">
-        <v>240</v>
-      </c>
       <c r="F102" s="4" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G102" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H102" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I102" s="3">
         <f>VLOOKUP(H102,cardsort_group_IDs!A:B,2,0)</f>
@@ -9959,13 +9977,13 @@
         <v>6</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R102" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S102" s="12" t="s">
         <v>9</v>
@@ -9976,10 +9994,10 @@
         <v>138</v>
       </c>
       <c r="B103" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>9</v>
@@ -9988,10 +10006,10 @@
         <v>236</v>
       </c>
       <c r="F103" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G103" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H103" t="s">
         <v>10</v>
@@ -10024,13 +10042,13 @@
         <v>1</v>
       </c>
       <c r="P103" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q103" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R103" t="s">
         <v>617</v>
-      </c>
-      <c r="R103" t="s">
-        <v>622</v>
       </c>
       <c r="S103" s="12" t="s">
         <v>9</v>
@@ -10041,7 +10059,7 @@
         <v>139</v>
       </c>
       <c r="B104" s="18" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>9</v>
@@ -10053,10 +10071,10 @@
         <v>9</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>21</v>
@@ -10066,7 +10084,7 @@
         <v>202</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10089,13 +10107,13 @@
         <v>1</v>
       </c>
       <c r="P104" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R104" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
@@ -10106,22 +10124,22 @@
         <v>140</v>
       </c>
       <c r="B105" s="24" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="E105" s="13" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10154,13 +10172,13 @@
         <v>18</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R105" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S105" s="12">
         <v>2</v>
@@ -10171,22 +10189,22 @@
         <v>141</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E106" s="13" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H106" s="3" t="s">
         <v>50</v>
@@ -10196,7 +10214,7 @@
         <v>207</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K106" s="3">
         <f>VLOOKUP(J106,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10219,13 +10237,13 @@
         <v>4</v>
       </c>
       <c r="P106" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q106" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R106" t="s">
         <v>617</v>
-      </c>
-      <c r="R106" t="s">
-        <v>622</v>
       </c>
       <c r="S106" s="12">
         <v>129</v>
@@ -10236,22 +10254,22 @@
         <v>142</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H107" s="3" t="s">
         <v>50</v>
@@ -10261,7 +10279,7 @@
         <v>207</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K107" s="3">
         <f>VLOOKUP(J107,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10284,13 +10302,13 @@
         <v>3</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q107" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R107" t="s">
         <v>617</v>
-      </c>
-      <c r="R107" t="s">
-        <v>622</v>
       </c>
       <c r="S107" s="12">
         <v>19</v>
@@ -10301,22 +10319,22 @@
         <v>143</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>50</v>
@@ -10326,7 +10344,7 @@
         <v>207</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K108" s="3">
         <f>VLOOKUP(J108,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10349,13 +10367,13 @@
         <v>5</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q108" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R108" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S108" s="12" t="s">
         <v>9</v>
@@ -10366,22 +10384,22 @@
         <v>144</v>
       </c>
       <c r="B109" s="27" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E109" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>15</v>
@@ -10414,16 +10432,16 @@
         <v>1</v>
       </c>
       <c r="P109" s="12" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R109" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
@@ -10431,22 +10449,22 @@
         <v>145</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E110" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H110" t="s">
         <v>10</v>
@@ -10479,16 +10497,16 @@
         <v>1</v>
       </c>
       <c r="P110" s="12" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Q110" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R110" t="s">
         <v>617</v>
       </c>
-      <c r="R110" t="s">
-        <v>622</v>
-      </c>
       <c r="S110" s="12" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10496,22 +10514,22 @@
         <v>146</v>
       </c>
       <c r="B111" s="24" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D111" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H111" t="s">
         <v>10</v>
@@ -10544,16 +10562,16 @@
         <v>6</v>
       </c>
       <c r="P111" s="12" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="Q111" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R111" t="s">
         <v>617</v>
       </c>
-      <c r="R111" t="s">
-        <v>622</v>
-      </c>
       <c r="S111" s="12" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
@@ -10561,22 +10579,22 @@
         <v>147</v>
       </c>
       <c r="B112" s="24" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="E112" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10609,16 +10627,16 @@
         <v>1</v>
       </c>
       <c r="P112" s="12" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R112" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.25">
@@ -10626,22 +10644,22 @@
         <v>148</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="D113" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>10</v>
@@ -10674,16 +10692,16 @@
         <v>11</v>
       </c>
       <c r="P113" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R113" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.25">
@@ -10691,22 +10709,22 @@
         <v>149</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>21</v>
@@ -10716,7 +10734,7 @@
         <v>202</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K114" s="3">
         <f>VLOOKUP(J114,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10739,16 +10757,16 @@
         <v>3</v>
       </c>
       <c r="P114" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q114" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R114" t="s">
         <v>616</v>
       </c>
-      <c r="R114" t="s">
-        <v>621</v>
-      </c>
       <c r="S114" s="12" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
     </row>
     <row r="115" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10756,25 +10774,25 @@
         <v>150</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="E115" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I115" s="3">
         <f>VLOOKUP(H115,cardsort_group_IDs!A:B,2,0)</f>
@@ -10804,16 +10822,16 @@
         <v>3</v>
       </c>
       <c r="P115" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q115" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R115" t="s">
         <v>616</v>
       </c>
-      <c r="R115" t="s">
-        <v>621</v>
-      </c>
       <c r="S115" s="12" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10821,22 +10839,22 @@
         <v>151</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>15</v>
@@ -10869,13 +10887,13 @@
         <v>1</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R116" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S116" s="12" t="s">
         <v>9</v>
@@ -10886,7 +10904,7 @@
         <v>152</v>
       </c>
       <c r="B117" s="24" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>9</v>
@@ -10895,23 +10913,23 @@
         <v>9</v>
       </c>
       <c r="E117" s="13" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I117" s="3">
         <f>VLOOKUP(H117,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K117" s="3">
         <f>VLOOKUP(J117,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10934,13 +10952,13 @@
         <v>1</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q117" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R117" t="s">
         <v>616</v>
-      </c>
-      <c r="R117" t="s">
-        <v>621</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
@@ -10951,7 +10969,7 @@
         <v>153</v>
       </c>
       <c r="B118" s="24" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>9</v>
@@ -10960,23 +10978,23 @@
         <v>9</v>
       </c>
       <c r="E118" s="13" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F118" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I118" s="3">
         <f>VLOOKUP(H118,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K118" s="3">
         <f>VLOOKUP(J118,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10999,16 +11017,16 @@
         <v>1</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="R118" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.25">
@@ -11016,7 +11034,7 @@
         <v>154</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>9</v>
@@ -11025,16 +11043,16 @@
         <v>9</v>
       </c>
       <c r="E119" s="13" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I119" s="3">
         <f>VLOOKUP(H119,cardsort_group_IDs!A:B,2,0)</f>
@@ -11064,16 +11082,16 @@
         <v>1</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="R119" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="S119" s="12" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.25">
@@ -11081,7 +11099,7 @@
         <v>155</v>
       </c>
       <c r="B120" s="24" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>9</v>
@@ -11090,23 +11108,23 @@
         <v>9</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I120" s="3">
         <f>VLOOKUP(H120,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K120" s="3">
         <f>VLOOKUP(J120,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -11129,13 +11147,13 @@
         <v>2</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q120" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R120" t="s">
         <v>616</v>
-      </c>
-      <c r="R120" t="s">
-        <v>621</v>
       </c>
       <c r="S120" s="12" t="s">
         <v>9</v>
@@ -11146,22 +11164,22 @@
         <v>156</v>
       </c>
       <c r="B121" s="24" t="s">
+        <v>643</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>648</v>
       </c>
-      <c r="C121" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="D121" s="12" t="s">
-        <v>652</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>653</v>
-      </c>
       <c r="F121" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>31</v>
@@ -11194,13 +11212,13 @@
         <v>2</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R121" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="S121" s="12" t="s">
         <v>9</v>
@@ -11211,25 +11229,25 @@
         <v>157</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C122" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="I122" s="3">
         <f>VLOOKUP(H122,cardsort_group_IDs!A:B,2,0)</f>
@@ -11259,16 +11277,16 @@
         <v>5</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q122" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="R122" t="s">
         <v>616</v>
       </c>
-      <c r="R122" t="s">
-        <v>621</v>
-      </c>
       <c r="S122" s="12" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.25">
@@ -11276,10 +11294,10 @@
         <v>158</v>
       </c>
       <c r="B123" s="24" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="D123" s="12" t="s">
         <v>9</v>
@@ -11288,10 +11306,10 @@
         <v>505</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>31</v>
@@ -11324,13 +11342,13 @@
         <v>1</v>
       </c>
       <c r="P123" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q123" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R123" t="s">
         <v>617</v>
-      </c>
-      <c r="R123" t="s">
-        <v>622</v>
       </c>
       <c r="S123" s="12" t="s">
         <v>9</v>
@@ -11341,22 +11359,22 @@
         <v>159</v>
       </c>
       <c r="B124" s="24" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="C124" t="s">
+        <v>789</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="13" t="s">
         <v>794</v>
       </c>
-      <c r="D124" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" s="13" t="s">
-        <v>799</v>
-      </c>
       <c r="F124" s="3" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H124" s="3" t="s">
         <v>15</v>
@@ -11389,16 +11407,16 @@
         <v>2</v>
       </c>
       <c r="P124" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q124" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="R124" t="s">
         <v>617</v>
       </c>
-      <c r="R124" t="s">
-        <v>622</v>
-      </c>
       <c r="S124" s="12" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.25">
@@ -11406,22 +11424,22 @@
         <v>160</v>
       </c>
       <c r="B125" s="24" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C125" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="D125" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E125" s="13" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H125" s="3" t="s">
         <v>15</v>
@@ -11454,16 +11472,16 @@
         <v>2</v>
       </c>
       <c r="P125" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q125" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R125" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
     </row>
     <row r="126" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11471,22 +11489,22 @@
         <v>161</v>
       </c>
       <c r="B126" s="24" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="D126" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E126" s="13" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
       <c r="H126" s="3" t="s">
         <v>15</v>
@@ -11519,16 +11537,16 @@
         <v>2</v>
       </c>
       <c r="P126" s="12" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q126" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="R126" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="S126" s="12" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -11635,7 +11653,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -11646,16 +11664,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1" t="s">
+        <v>594</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>351</v>
-      </c>
-      <c r="B1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C1" t="s">
-        <v>599</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11663,13 +11681,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11677,27 +11695,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C3" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C4" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11705,13 +11723,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C5" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11719,13 +11737,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C6" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11733,13 +11751,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11747,13 +11765,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11761,13 +11779,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11775,13 +11793,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C10" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11789,13 +11807,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C11" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11803,13 +11821,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C12" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D12" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11817,13 +11835,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11831,13 +11849,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C14" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11845,13 +11863,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11859,13 +11877,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C16" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11873,13 +11891,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C17" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11887,13 +11905,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C18" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D18" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11901,13 +11919,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C19" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11915,13 +11933,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C20" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11929,13 +11947,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C21" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11943,13 +11961,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C22" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11957,13 +11975,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C23" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11971,13 +11989,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C24" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11985,13 +12003,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C25" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11999,13 +12017,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C26" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -12013,13 +12031,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C27" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12027,13 +12045,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C28" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12041,13 +12059,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C29" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12055,13 +12073,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C30" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12069,13 +12087,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C31" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12083,13 +12101,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C32" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12097,13 +12115,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C33" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12111,13 +12129,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12125,13 +12143,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C35" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12139,13 +12157,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C36" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12153,13 +12171,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C37" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12167,13 +12185,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C38" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -12181,13 +12199,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C39" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12195,13 +12213,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C40" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12212,10 +12230,10 @@
         <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12223,13 +12241,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C42" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12237,13 +12255,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C43" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12251,13 +12269,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C44" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12265,13 +12283,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C45" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12282,10 +12300,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12293,13 +12311,13 @@
         <v>202</v>
       </c>
       <c r="B47" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C47" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12307,13 +12325,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C48" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D48" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12321,13 +12339,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C49" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12335,13 +12353,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C50" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12349,13 +12367,13 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12363,13 +12381,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C52" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12377,13 +12395,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C53" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12391,13 +12409,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C54" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12405,13 +12423,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C55" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12419,13 +12437,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C56" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12433,13 +12451,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C57" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12447,13 +12465,13 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C58" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12461,13 +12479,13 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C59" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12475,13 +12493,13 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C60" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12489,13 +12507,13 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C61" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12503,13 +12521,13 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C62" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12517,13 +12535,13 @@
         <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C63" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12531,13 +12549,13 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C64" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12545,13 +12563,13 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C65" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12562,10 +12580,10 @@
         <v>58</v>
       </c>
       <c r="C66" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12573,13 +12591,13 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C67" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12590,10 +12608,10 @@
         <v>62</v>
       </c>
       <c r="C68" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12601,13 +12619,13 @@
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C69" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12615,1133 +12633,1147 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C70" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D70" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B71" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C71" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B72" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C72" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C73" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B74" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C74" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C75" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B76" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C76" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B77" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C77" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C78" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B79" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C79" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B80" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C80" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B81" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C81" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B82" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C82" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B83" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C83" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B84" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C84" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B85" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C85" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B86" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C86" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B87" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C87" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B88" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C88" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B89" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C89" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B90" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C90" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B91" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C91" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B92" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C92" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B93" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C93" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B94" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C94" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="B95" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C95" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B96" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C96" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B97" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C97" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B98" t="s">
         <v>69</v>
       </c>
       <c r="C98" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B99" t="s">
         <v>77</v>
       </c>
       <c r="C99" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B100" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C100" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B101" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C101" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B102" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C102" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
       </c>
       <c r="C103" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B104" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C104" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C105" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B106" t="s">
-        <v>612</v>
+        <v>607</v>
       </c>
       <c r="C106" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B107" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C107" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B108" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="C108" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B109" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C109" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B110" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C110" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B111" t="s">
         <v>34</v>
       </c>
       <c r="C111" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B112" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C112" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B113" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C113" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B114" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C114" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D114" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B115" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C115" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D115" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B116" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C116" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D116" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B117" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C117" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D117" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B118" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C118" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D118" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B119" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D119" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B120" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C120" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D120" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B121" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C121" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D121" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B122" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C122" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D122" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B123" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C123" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D123" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B124" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="C124" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D124" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B125" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C125" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D125" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B126" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C126" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D126" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B127" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C127" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D127" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B128" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C128" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="D128" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B129" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C129" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D129" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B130" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C130" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="D130" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="B131" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="C131" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D131" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="B132" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C132" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D132" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="B133" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C133" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D133" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B134" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="C134" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D134" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="B135" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="C135" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D135" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="B136" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C136" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D136" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B137" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C137" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D137" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="B138" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="C138" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D138" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B139" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="C139" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D139" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="B140" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="C140" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D140" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="B141" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C141" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D141" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B142" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="C142" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D142" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="B143" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="C143" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D143" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="B144" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C144" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D144" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B145" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C145" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D145" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="B146" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C146" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D146" s="28" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B147" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C147" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D147" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="B148" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C148" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D148" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="B149" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C149" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D149" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="B150" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C150" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="D150" t="s">
-        <v>811</v>
+        <v>806</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B151" t="s">
+        <v>810</v>
+      </c>
+      <c r="C151" t="s">
+        <v>604</v>
+      </c>
+      <c r="D151" t="s">
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -13796,7 +13828,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13881,7 +13913,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -14009,7 +14041,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20">
         <v>321</v>
@@ -14017,7 +14049,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B21">
         <v>322</v>
@@ -14025,7 +14057,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B22">
         <v>323</v>
@@ -14033,7 +14065,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B23">
         <v>324</v>
@@ -14041,7 +14073,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B24">
         <v>325</v>
@@ -14049,7 +14081,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B25">
         <v>326</v>
@@ -14065,7 +14097,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -14073,7 +14105,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -14081,7 +14113,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -14089,7 +14121,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -14097,7 +14129,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -14105,7 +14137,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -14131,50 +14163,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EA3D5A-17A5-4657-955B-AA7062A4046D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0A027B-6CD5-414A-A9FC-D4EF0AA7ACB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="840">
   <si>
     <t>id</t>
   </si>
@@ -260,9 +260,6 @@
   </si>
   <si>
     <t>Satisfaction</t>
-  </si>
-  <si>
-    <t>Developer Velocity Index Benchmark</t>
   </si>
   <si>
     <t>The Developer Velocity Index (DVI) is a survey that measures an enterprise’s technology, working practices, and organizational enablement and benchmarks them against peers. This comparison helps unearth specific areas of opportunity, whether in backlog management, testing, or security and compliance. For example, one company, well known for its technological progress and all-star developers, sought to define standard working practices more thoughtfully for cross-team collaboration after discovering a high amount of dissatisfaction, rework, and inefficiency reported by developers.</t>
@@ -1382,16 +1379,10 @@
     <t>AI Specific Category</t>
   </si>
   <si>
-    <t>Acceptance rate of AI suggestions</t>
-  </si>
-  <si>
     <t>511b; 511e; 511h; 511o; 511p</t>
   </si>
   <si>
     <t>Cost</t>
-  </si>
-  <si>
-    <t>AI Power users</t>
   </si>
   <si>
     <t>AI Spend</t>
@@ -1833,9 +1824,6 @@
     <t>Sprint Velocity; Developer Velocity</t>
   </si>
   <si>
-    <t>Number of Code Reviews per Developer</t>
-  </si>
-  <si>
     <t>Number of Deployments per Developer</t>
   </si>
   <si>
@@ -1896,9 +1884,6 @@
     <t>Time for Onboarding New Hires</t>
   </si>
   <si>
-    <t>Number of Design DOCs Generated per Developer</t>
-  </si>
-  <si>
     <t>501m; 131l; 516c; 202a</t>
   </si>
   <si>
@@ -2064,9 +2049,6 @@
     <t>Percentage of Code written by AI</t>
   </si>
   <si>
-    <t>Number of Unused AI licenses</t>
-  </si>
-  <si>
     <t>Degree of Self-sufficiency</t>
   </si>
   <si>
@@ -2187,18 +2169,9 @@
     <t>CI/CD Health Score</t>
   </si>
   <si>
-    <t>Customer Experience; Customer Satisfaction; Customer Satisfaction Scores; User/customer satisfaction; NPS</t>
-  </si>
-  <si>
-    <t>Contribution Volume per Developer</t>
-  </si>
-  <si>
     <t>The number of contribution units, such as modifications, modules touched, work items closed, or requirements implemented, by an individual developer or team within a period. Used to spot trends in team capacity, not as a standalone productivity score.</t>
   </si>
   <si>
-    <t>Customer Satisfaction Score (CSAT)</t>
-  </si>
-  <si>
     <t>Number of Defects</t>
   </si>
   <si>
@@ -2322,12 +2295,6 @@
     <t>Monitors AI being built into products, not just used by developer throughout the SLDC.</t>
   </si>
   <si>
-    <t>Percentage of Product Features Incoroporating AI</t>
-  </si>
-  <si>
-    <t>Percentage of AI Adoption in Products</t>
-  </si>
-  <si>
     <t>501g; 521; 510</t>
   </si>
   <si>
@@ -2545,6 +2512,60 @@
   </si>
   <si>
     <t>The ratio of deployments that are unplanned but happen as a result of an incident in production.</t>
+  </si>
+  <si>
+    <t>Design Docs per Developer</t>
+  </si>
+  <si>
+    <t>Number of Design Docs Generated per Developer</t>
+  </si>
+  <si>
+    <t>Percentage of Product Features Incorporating AI; Percentage of AI Adoption in Products</t>
+  </si>
+  <si>
+    <t>AI Product Adoption Rate</t>
+  </si>
+  <si>
+    <t>Acceptance rate of AI Suggestions</t>
+  </si>
+  <si>
+    <t>Number of Unused AI Licenses</t>
+  </si>
+  <si>
+    <t>AI Power Users</t>
+  </si>
+  <si>
+    <t>Code Reviews per Developer</t>
+  </si>
+  <si>
+    <t>Service Readiness Score</t>
+  </si>
+  <si>
+    <t>Regrettable Attrition Rate</t>
+  </si>
+  <si>
+    <t>Deployments per Developer</t>
+  </si>
+  <si>
+    <t>CSAT; Customer Experience; Customer Satisfaction; Customer Satisfaction Scores; User/customer satisfaction; NPS</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction Score</t>
+  </si>
+  <si>
+    <t>Velocity Index Benchmark</t>
+  </si>
+  <si>
+    <t>Contribution Volume</t>
+  </si>
+  <si>
+    <t>AI Suggestion Acceptance Rate</t>
+  </si>
+  <si>
+    <t>AI-Assisted PR Rate</t>
+  </si>
+  <si>
+    <t>AI-Written Code Share</t>
   </si>
 </sst>
 </file>
@@ -2734,7 +2755,57 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="42">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -3416,16 +3487,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>160</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>161</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3443,25 +3514,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="O1" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -3475,16 +3546,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3517,16 +3588,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -3549,7 +3620,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3582,13 +3653,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R3" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
@@ -3599,22 +3670,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3647,16 +3718,16 @@
         <v>4</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R4" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -3664,25 +3735,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3712,13 +3783,13 @@
         <v>4</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
@@ -3744,7 +3815,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3777,13 +3848,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
@@ -3797,19 +3868,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -3842,16 +3913,16 @@
         <v>27</v>
       </c>
       <c r="P7" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R7" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="165" x14ac:dyDescent="0.25">
@@ -3865,16 +3936,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -3907,13 +3978,13 @@
         <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q8" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R8" t="s">
         <v>519</v>
-      </c>
-      <c r="R8" t="s">
-        <v>522</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
@@ -3930,16 +4001,16 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>760</v>
+        <v>749</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -3972,13 +4043,13 @@
         <v>5</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
@@ -3989,22 +4060,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -4037,13 +4108,13 @@
         <v>5</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R10" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
@@ -4060,16 +4131,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>307</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>308</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -4102,13 +4173,13 @@
         <v>6</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R11" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
@@ -4119,22 +4190,22 @@
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>42</v>
@@ -4167,13 +4238,13 @@
         <v>11</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R12" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
@@ -4187,19 +4258,19 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -4232,13 +4303,13 @@
         <v>5</v>
       </c>
       <c r="P13" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R13" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
@@ -4252,19 +4323,19 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>46</v>
@@ -4297,13 +4368,13 @@
         <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R14" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
@@ -4314,25 +4385,25 @@
         <v>20</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4362,13 +4433,13 @@
         <v>6</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R15" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
@@ -4379,22 +4450,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4427,13 +4498,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R16" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
@@ -4444,22 +4515,22 @@
         <v>23</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>714</v>
+        <v>836</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>715</v>
+        <v>707</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>42</v>
@@ -4492,16 +4563,16 @@
         <v>2</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R17" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>803</v>
+        <v>792</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -4524,7 +4595,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4557,39 +4628,39 @@
         <v>1</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R18" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>25</v>
       </c>
-      <c r="B19" s="18" t="s">
-        <v>716</v>
+      <c r="B19" s="24" t="s">
+        <v>834</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>713</v>
+        <v>833</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>56</v>
@@ -4622,13 +4693,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q19" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R19" t="s">
         <v>519</v>
-      </c>
-      <c r="R19" t="s">
-        <v>522</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
@@ -4639,19 +4710,19 @@
         <v>26</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E20" s="13">
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>56</v>
@@ -4684,16 +4755,16 @@
         <v>3</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R20" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>814</v>
+        <v>803</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -4704,19 +4775,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4749,13 +4820,13 @@
         <v>19</v>
       </c>
       <c r="P21" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R21" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
@@ -4766,22 +4837,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>812</v>
+        <v>801</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>813</v>
+        <v>802</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -4814,13 +4885,13 @@
         <v>3</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R22" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
@@ -4837,16 +4908,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -4879,16 +4950,16 @@
         <v>21</v>
       </c>
       <c r="P23" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R23" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -4899,19 +4970,19 @@
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="F24" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
@@ -4944,16 +5015,16 @@
         <v>5</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R24" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="120" x14ac:dyDescent="0.25">
@@ -4961,13 +5032,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E25" s="13">
         <v>501</v>
@@ -4976,7 +5047,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>56</v>
@@ -5009,13 +5080,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R25" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
@@ -5032,16 +5103,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5074,13 +5145,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R26" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
@@ -5094,19 +5165,19 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5139,13 +5210,13 @@
         <v>9</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R27" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
@@ -5159,22 +5230,22 @@
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -5204,16 +5275,16 @@
         <v>44</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R28" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="255" x14ac:dyDescent="0.25">
@@ -5221,7 +5292,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>72</v>
+        <v>835</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5233,10 +5304,10 @@
         <v>506</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>10</v>
@@ -5269,13 +5340,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R29" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
@@ -5286,22 +5357,22 @@
         <v>38</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -5334,13 +5405,13 @@
         <v>17</v>
       </c>
       <c r="P30" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R30" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
@@ -5351,22 +5422,22 @@
         <v>39</v>
       </c>
       <c r="B31" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5399,13 +5470,13 @@
         <v>3</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R31" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
@@ -5419,22 +5490,22 @@
         <v>47</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>538</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="G32" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I32" s="3">
         <f>VLOOKUP(H32,cardsort_group_IDs!A:B,2,0)</f>
@@ -5464,13 +5535,13 @@
         <v>14</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R32" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
@@ -5481,25 +5552,25 @@
         <v>41</v>
       </c>
       <c r="B33" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>303</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>293</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5529,13 +5600,13 @@
         <v>6</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R33" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
@@ -5546,22 +5617,22 @@
         <v>42</v>
       </c>
       <c r="B34" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>798</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>809</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -5594,16 +5665,16 @@
         <v>3</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R34" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>810</v>
+        <v>799</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -5611,32 +5682,32 @@
         <v>43</v>
       </c>
       <c r="B35" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>84</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I35" s="3">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K35" s="3">
         <f>VLOOKUP(J35,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5659,13 +5730,13 @@
         <v>3</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R35" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
@@ -5676,22 +5747,22 @@
         <v>44</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
@@ -5701,7 +5772,7 @@
         <v>202</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K36" s="3">
         <f>VLOOKUP(J36,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5724,13 +5795,13 @@
         <v>4</v>
       </c>
       <c r="P36" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R36" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
@@ -5741,7 +5812,7 @@
         <v>45</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>9</v>
@@ -5750,13 +5821,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5766,7 +5837,7 @@
         <v>202</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K37" s="3">
         <f>VLOOKUP(J37,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5789,13 +5860,13 @@
         <v>2</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R37" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
@@ -5806,22 +5877,22 @@
         <v>46</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>42</v>
@@ -5831,7 +5902,7 @@
         <v>206</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K38" s="3">
         <f>VLOOKUP(J38,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -5854,13 +5925,13 @@
         <v>2</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R38" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
@@ -5871,25 +5942,25 @@
         <v>50</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I39" s="3">
         <f>VLOOKUP(H39,cardsort_group_IDs!A:B,2,0)</f>
@@ -5919,16 +5990,16 @@
         <v>14</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R39" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="135" x14ac:dyDescent="0.25">
@@ -5936,25 +6007,25 @@
         <v>56</v>
       </c>
       <c r="B40" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="G40" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -5984,13 +6055,13 @@
         <v>4</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R40" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S40" s="12" t="s">
         <v>9</v>
@@ -6001,7 +6072,7 @@
         <v>57</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>9</v>
@@ -6013,10 +6084,10 @@
         <v>514</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>10</v>
@@ -6049,13 +6120,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R41" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
@@ -6066,25 +6137,25 @@
         <v>58</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I42" s="3">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -6114,16 +6185,16 @@
         <v>4</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R42" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -6131,25 +6202,25 @@
         <v>59</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -6179,16 +6250,16 @@
         <v>4</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R43" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -6196,22 +6267,22 @@
         <v>62</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6244,13 +6315,13 @@
         <v>14</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R44" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>9</v>
@@ -6261,22 +6332,22 @@
         <v>63</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -6309,13 +6380,13 @@
         <v>4</v>
       </c>
       <c r="P45" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R45" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>9</v>
@@ -6326,7 +6397,7 @@
         <v>64</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>9</v>
@@ -6338,10 +6409,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -6374,13 +6445,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R46" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
@@ -6391,22 +6462,22 @@
         <v>65</v>
       </c>
       <c r="B47" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>467</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="E47" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>106</v>
-      </c>
       <c r="G47" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -6416,7 +6487,7 @@
         <v>202</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K47" s="3">
         <f>VLOOKUP(J47,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6439,13 +6510,13 @@
         <v>16</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R47" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
@@ -6456,22 +6527,22 @@
         <v>67</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>42</v>
@@ -6481,7 +6552,7 @@
         <v>206</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K48" s="3">
         <f>VLOOKUP(J48,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6504,13 +6575,13 @@
         <v>3</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R48" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
@@ -6521,22 +6592,22 @@
         <v>69</v>
       </c>
       <c r="B49" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" t="s">
+        <v>729</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C49" t="s">
-        <v>738</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="E49" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="G49" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>56</v>
@@ -6569,13 +6640,13 @@
         <v>3</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R49" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
@@ -6586,22 +6657,22 @@
         <v>70</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>804</v>
+        <v>793</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>805</v>
+        <v>794</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>806</v>
+        <v>795</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -6634,16 +6705,16 @@
         <v>5</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R50" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>807</v>
+        <v>796</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -6651,22 +6722,22 @@
         <v>71</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -6699,13 +6770,13 @@
         <v>4</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R51" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
@@ -6716,22 +6787,22 @@
         <v>72</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>10</v>
@@ -6741,7 +6812,7 @@
         <v>201</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K52" s="3">
         <f>VLOOKUP(J52,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6764,16 +6835,16 @@
         <v>3</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R52" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -6781,22 +6852,22 @@
         <v>73</v>
       </c>
       <c r="B53" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E53" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E53" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="G53" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -6806,7 +6877,7 @@
         <v>202</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K53" s="3">
         <f>VLOOKUP(J53,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6829,39 +6900,39 @@
         <v>3</v>
       </c>
       <c r="P53" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R53" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S53" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>75</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>640</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>9</v>
+        <v>830</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>635</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E54" s="13">
         <v>183</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -6894,16 +6965,16 @@
         <v>2</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R54" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -6911,19 +6982,19 @@
         <v>76</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -6933,7 +7004,7 @@
         <v>201</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K55" s="3">
         <f>VLOOKUP(J55,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -6956,13 +7027,13 @@
         <v>2</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q55" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R55" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>9</v>
@@ -6973,25 +7044,25 @@
         <v>78</v>
       </c>
       <c r="B56" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C56" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="D56" s="12" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I56" s="3">
         <f>VLOOKUP(H56,cardsort_group_IDs!A:B,2,0)</f>
@@ -7021,13 +7092,13 @@
         <v>11</v>
       </c>
       <c r="P56" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R56" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
@@ -7038,22 +7109,22 @@
         <v>79</v>
       </c>
       <c r="B57" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>538</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>300</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>118</v>
-      </c>
       <c r="G57" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
@@ -7086,24 +7157,24 @@
         <v>4</v>
       </c>
       <c r="P57" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R57" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>80</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>9</v>
@@ -7115,10 +7186,10 @@
         <v>514</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>56</v>
@@ -7151,13 +7222,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R58" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
@@ -7168,10 +7239,10 @@
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>121</v>
+        <v>831</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
       <c r="D59" s="12" t="s">
         <v>9</v>
@@ -7180,10 +7251,10 @@
         <v>514</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -7193,7 +7264,7 @@
         <v>201</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K59" s="3">
         <f>VLOOKUP(J59,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7216,49 +7287,49 @@
         <v>1</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R59" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>83</v>
       </c>
       <c r="B60" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>537</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>471</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>472</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="G60" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I60" s="3">
         <f>VLOOKUP(H60,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K60" s="3">
         <f>VLOOKUP(J60,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7281,16 +7352,16 @@
         <v>5</v>
       </c>
       <c r="P60" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R60" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -7298,22 +7369,22 @@
         <v>87</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>15</v>
@@ -7346,16 +7417,16 @@
         <v>4</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R61" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -7363,22 +7434,22 @@
         <v>88</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -7411,13 +7482,13 @@
         <v>4</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R62" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
@@ -7428,22 +7499,22 @@
         <v>89</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -7476,13 +7547,13 @@
         <v>8</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>618</v>
+        <v>613</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R63" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
@@ -7493,22 +7564,22 @@
         <v>90</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -7541,13 +7612,13 @@
         <v>14</v>
       </c>
       <c r="P64" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R64" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
@@ -7558,22 +7629,22 @@
         <v>91</v>
       </c>
       <c r="B65" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="E65" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="E65" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="G65" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7606,13 +7677,13 @@
         <v>4</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q65" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R65" t="s">
         <v>519</v>
-      </c>
-      <c r="R65" t="s">
-        <v>522</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>9</v>
@@ -7623,22 +7694,22 @@
         <v>92</v>
       </c>
       <c r="B66" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E66" s="13" t="s">
+        <v>302</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="E66" s="13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="G66" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>42</v>
@@ -7648,7 +7719,7 @@
         <v>206</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K66" s="3">
         <f>VLOOKUP(J66,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7671,13 +7742,13 @@
         <v>3</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q66" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R66" t="s">
         <v>519</v>
-      </c>
-      <c r="R66" t="s">
-        <v>522</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
@@ -7688,7 +7759,7 @@
         <v>93</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C67" s="5" t="s">
         <v>9</v>
@@ -7700,10 +7771,10 @@
         <v>514</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>10</v>
@@ -7736,13 +7807,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R67" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
@@ -7753,22 +7824,22 @@
         <v>94</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>56</v>
@@ -7801,16 +7872,16 @@
         <v>4</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R68" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -7818,22 +7889,22 @@
         <v>95</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>766</v>
+        <v>755</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>21</v>
@@ -7843,7 +7914,7 @@
         <v>202</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K69" s="3">
         <f>VLOOKUP(J69,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7866,16 +7937,16 @@
         <v>2</v>
       </c>
       <c r="P69" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q69" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R69" t="s">
         <v>519</v>
       </c>
-      <c r="R69" t="s">
-        <v>522</v>
-      </c>
       <c r="S69" s="12" t="s">
-        <v>762</v>
+        <v>751</v>
       </c>
     </row>
     <row r="70" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -7883,7 +7954,7 @@
         <v>97</v>
       </c>
       <c r="B70" s="18" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>9</v>
@@ -7895,10 +7966,10 @@
         <v>508</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -7908,7 +7979,7 @@
         <v>202</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K70" s="3">
         <f>VLOOKUP(J70,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7931,13 +8002,13 @@
         <v>1</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R70" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
@@ -7948,10 +8019,10 @@
         <v>98</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D71" s="10">
         <v>209</v>
@@ -7960,10 +8031,10 @@
         <v>506</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -7973,7 +8044,7 @@
         <v>201</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K71" s="3">
         <f>VLOOKUP(J71,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7996,13 +8067,13 @@
         <v>2</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R71" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
@@ -8013,7 +8084,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8025,10 +8096,10 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -8038,7 +8109,7 @@
         <v>201</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K72" s="3">
         <f>VLOOKUP(J72,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8061,13 +8132,13 @@
         <v>1</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R72" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S72" s="12" t="s">
         <v>9</v>
@@ -8078,7 +8149,7 @@
         <v>100</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>9</v>
@@ -8090,10 +8161,10 @@
         <v>514</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>10</v>
@@ -8103,7 +8174,7 @@
         <v>201</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K73" s="3">
         <f>VLOOKUP(J73,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8126,13 +8197,13 @@
         <v>1</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R73" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
@@ -8143,22 +8214,22 @@
         <v>102</v>
       </c>
       <c r="B74" s="24" t="s">
+        <v>637</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>642</v>
-      </c>
-      <c r="C74" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>647</v>
       </c>
       <c r="E74" s="13">
         <v>501</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>15</v>
@@ -8191,13 +8262,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R74" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
@@ -8208,25 +8279,25 @@
         <v>104</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I75" s="3">
         <f>VLOOKUP(H75,cardsort_group_IDs!A:B,2,0)</f>
@@ -8256,13 +8327,13 @@
         <v>2</v>
       </c>
       <c r="P75" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R75" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
@@ -8273,22 +8344,22 @@
         <v>107</v>
       </c>
       <c r="B76" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="F76" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>376</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="G76" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8321,13 +8392,13 @@
         <v>7</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R76" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
@@ -8338,22 +8409,22 @@
         <v>108</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -8386,13 +8457,13 @@
         <v>8</v>
       </c>
       <c r="P77" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R77" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
@@ -8403,22 +8474,22 @@
         <v>109</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>745</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>754</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>765</v>
-      </c>
       <c r="D78" s="13" t="s">
-        <v>761</v>
+        <v>750</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>763</v>
+        <v>752</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8428,7 +8499,7 @@
         <v>202</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K78" s="3">
         <f>VLOOKUP(J78,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8451,16 +8522,16 @@
         <v>7</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R78" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>764</v>
+        <v>753</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -8468,7 +8539,7 @@
         <v>112</v>
       </c>
       <c r="B79" s="24" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>9</v>
@@ -8477,23 +8548,23 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I79" s="3">
         <f>VLOOKUP(H79,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K79" s="3">
         <f>VLOOKUP(J79,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8516,16 +8587,16 @@
         <v>1</v>
       </c>
       <c r="P79" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R79" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -8533,32 +8604,32 @@
         <v>113</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I80" s="3">
         <f>VLOOKUP(H80,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K80" s="3">
         <f>VLOOKUP(J80,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8581,16 +8652,16 @@
         <v>1</v>
       </c>
       <c r="P80" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R80" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -8598,22 +8669,22 @@
         <v>114</v>
       </c>
       <c r="B81" s="24" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>46</v>
@@ -8646,13 +8717,13 @@
         <v>14</v>
       </c>
       <c r="P81" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R81" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
@@ -8663,10 +8734,10 @@
         <v>115</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>776</v>
+        <v>765</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8675,10 +8746,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>775</v>
+        <v>764</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>42</v>
@@ -8688,7 +8759,7 @@
         <v>206</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K82" s="3">
         <f>VLOOKUP(J82,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8711,16 +8782,16 @@
         <v>1</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R82" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>777</v>
+        <v>766</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -8728,22 +8799,22 @@
         <v>116</v>
       </c>
       <c r="B83" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>580</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F83" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>778</v>
-      </c>
-      <c r="D83" s="12" t="s">
-        <v>583</v>
-      </c>
-      <c r="E83" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="G83" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>30</v>
@@ -8753,7 +8824,7 @@
         <v>205</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K83" s="3">
         <f>VLOOKUP(J83,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8776,13 +8847,13 @@
         <v>5</v>
       </c>
       <c r="P83" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q83" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R83" t="s">
         <v>519</v>
-      </c>
-      <c r="R83" t="s">
-        <v>522</v>
       </c>
       <c r="S83" s="12" t="s">
         <v>9</v>
@@ -8796,19 +8867,19 @@
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>30</v>
@@ -8841,13 +8912,13 @@
         <v>6</v>
       </c>
       <c r="P84" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R84" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
@@ -8858,7 +8929,7 @@
         <v>118</v>
       </c>
       <c r="B85" s="24" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>9</v>
@@ -8870,10 +8941,10 @@
         <v>9</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>21</v>
@@ -8883,7 +8954,7 @@
         <v>202</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K85" s="3">
         <f>VLOOKUP(J85,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8906,13 +8977,13 @@
         <v>1</v>
       </c>
       <c r="P85" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R85" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
@@ -8923,22 +8994,22 @@
         <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>782</v>
+        <v>771</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>785</v>
+        <v>774</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F86" t="s">
-        <v>783</v>
+        <v>772</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -8971,16 +9042,16 @@
         <v>3</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R86" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>784</v>
+        <v>773</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -8988,22 +9059,22 @@
         <v>121</v>
       </c>
       <c r="B87" s="29" t="s">
+        <v>154</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>470</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>668</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>473</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>674</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="G87" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>15</v>
@@ -9036,13 +9107,13 @@
         <v>9</v>
       </c>
       <c r="P87" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R87" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
@@ -9053,22 +9124,22 @@
         <v>122</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>787</v>
+        <v>776</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -9101,16 +9172,16 @@
         <v>5</v>
       </c>
       <c r="P88" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R88" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>786</v>
+        <v>775</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -9118,32 +9189,32 @@
         <v>124</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I89" s="3">
         <f>VLOOKUP(H89,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K89" s="3">
         <f>VLOOKUP(J89,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9166,16 +9237,16 @@
         <v>9</v>
       </c>
       <c r="P89" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R89" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>627</v>
+        <v>622</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9183,22 +9254,22 @@
         <v>126</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>596</v>
+        <v>832</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>9</v>
+        <v>592</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E90" s="13">
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>46</v>
@@ -9231,13 +9302,13 @@
         <v>2</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R90" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
@@ -9248,22 +9319,22 @@
         <v>127</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>595</v>
+        <v>829</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>789</v>
+        <v>778</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>46</v>
@@ -9296,39 +9367,39 @@
         <v>4</v>
       </c>
       <c r="P91" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R91" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>790</v>
+        <v>779</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>128</v>
       </c>
-      <c r="B92" s="20" t="s">
-        <v>616</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>9</v>
+      <c r="B92" s="26" t="s">
+        <v>822</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>823</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E92" s="13">
         <v>501</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>46</v>
@@ -9361,13 +9432,13 @@
         <v>2</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R92" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
@@ -9378,22 +9449,22 @@
         <v>129</v>
       </c>
       <c r="B93" s="26" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>791</v>
+        <v>780</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>46</v>
@@ -9426,13 +9497,13 @@
         <v>27</v>
       </c>
       <c r="P93" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R93" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
@@ -9443,25 +9514,25 @@
         <v>130</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>792</v>
+        <v>781</v>
       </c>
       <c r="D94" s="12" t="s">
+        <v>377</v>
+      </c>
+      <c r="E94" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="E94" s="13" t="s">
-        <v>379</v>
-      </c>
       <c r="F94" s="4" t="s">
-        <v>793</v>
+        <v>782</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I94" s="3">
         <f>VLOOKUP(H94,cardsort_group_IDs!A:B,2,0)</f>
@@ -9491,13 +9562,13 @@
         <v>5</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q94" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R94" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S94" s="12" t="s">
         <v>9</v>
@@ -9508,22 +9579,22 @@
         <v>133</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>794</v>
+        <v>783</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>795</v>
+        <v>784</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>797</v>
+        <v>786</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>30</v>
@@ -9556,16 +9627,16 @@
         <v>1</v>
       </c>
       <c r="P95" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q95" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R95" t="s">
         <v>519</v>
       </c>
-      <c r="R95" t="s">
-        <v>522</v>
-      </c>
       <c r="S95" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -9573,7 +9644,7 @@
         <v>134</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
@@ -9582,13 +9653,13 @@
         <v>9</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>30</v>
@@ -9621,16 +9692,16 @@
         <v>1</v>
       </c>
       <c r="P96" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R96" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S96" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9638,7 +9709,7 @@
         <v>135</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>9</v>
@@ -9650,20 +9721,20 @@
         <v>183</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H97" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I97" s="3">
         <f>VLOOKUP(H97,cardsort_group_IDs!A:B,2,0)</f>
         <v>203</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K97" s="3">
         <f>VLOOKUP(J97,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9686,13 +9757,13 @@
         <v>1</v>
       </c>
       <c r="P97" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q97" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R97" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
@@ -9703,25 +9774,25 @@
         <v>137</v>
       </c>
       <c r="B98" s="30" t="s">
+        <v>171</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="D98" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="31" t="s">
-        <v>174</v>
-      </c>
       <c r="F98" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H98" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9751,13 +9822,13 @@
         <v>6</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q98" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R98" t="s">
         <v>519</v>
-      </c>
-      <c r="R98" t="s">
-        <v>522</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
@@ -9768,10 +9839,10 @@
         <v>138</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>816</v>
+        <v>805</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>817</v>
+        <v>806</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9780,10 +9851,10 @@
         <v>236</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G99" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -9816,13 +9887,13 @@
         <v>1</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q99" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R99" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
@@ -9833,7 +9904,7 @@
         <v>139</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>9</v>
@@ -9845,10 +9916,10 @@
         <v>9</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>21</v>
@@ -9858,7 +9929,7 @@
         <v>202</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K100" s="3">
         <f>VLOOKUP(J100,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9881,13 +9952,13 @@
         <v>1</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="R100" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
@@ -9898,22 +9969,22 @@
         <v>140</v>
       </c>
       <c r="B101" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>455</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>815</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>458</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>483</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>435</v>
-      </c>
       <c r="G101" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>15</v>
@@ -9946,39 +10017,39 @@
         <v>18</v>
       </c>
       <c r="P101" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R101" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S101" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>141</v>
       </c>
       <c r="B102" s="24" t="s">
-        <v>670</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>9</v>
+        <v>838</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>665</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>46</v>
@@ -9988,7 +10059,7 @@
         <v>207</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="K102" s="3">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10011,39 +10082,39 @@
         <v>4</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R102" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S102" s="12">
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>142</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>671</v>
-      </c>
-      <c r="C103" s="4" t="s">
-        <v>9</v>
+        <v>839</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>666</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>46</v>
@@ -10053,7 +10124,7 @@
         <v>207</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="K103" s="3">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10076,39 +10147,39 @@
         <v>3</v>
       </c>
       <c r="P103" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R103" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S103" s="12">
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>143</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>445</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>9</v>
+        <v>837</v>
+      </c>
+      <c r="C104" s="24" t="s">
+        <v>826</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>46</v>
@@ -10118,7 +10189,7 @@
         <v>207</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10141,13 +10212,13 @@
         <v>5</v>
       </c>
       <c r="P104" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R104" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
@@ -10158,22 +10229,22 @@
         <v>144</v>
       </c>
       <c r="B105" s="24" t="s">
-        <v>448</v>
+        <v>828</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10206,16 +10277,16 @@
         <v>1</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R105" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10223,22 +10294,22 @@
         <v>145</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>672</v>
+        <v>827</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -10271,16 +10342,16 @@
         <v>1</v>
       </c>
       <c r="P106" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q106" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R106" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10288,22 +10359,22 @@
         <v>146</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="D107" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -10336,16 +10407,16 @@
         <v>6</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q107" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R107" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="108" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -10353,22 +10424,22 @@
         <v>147</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>759</v>
+        <v>825</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>758</v>
+        <v>824</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>15</v>
@@ -10401,16 +10472,16 @@
         <v>1</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q108" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R108" t="s">
         <v>519</v>
       </c>
-      <c r="R108" t="s">
-        <v>522</v>
-      </c>
       <c r="S108" s="12" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
@@ -10418,22 +10489,22 @@
         <v>148</v>
       </c>
       <c r="B109" s="24" t="s">
-        <v>821</v>
+        <v>810</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D109" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>10</v>
@@ -10466,16 +10537,16 @@
         <v>11</v>
       </c>
       <c r="P109" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R109" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -10483,22 +10554,22 @@
         <v>149</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>822</v>
+        <v>811</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>820</v>
+        <v>809</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>21</v>
@@ -10508,7 +10579,7 @@
         <v>202</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K110" s="3">
         <f>VLOOKUP(J110,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10531,16 +10602,16 @@
         <v>3</v>
       </c>
       <c r="P110" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q110" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R110" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -10548,25 +10619,25 @@
         <v>150</v>
       </c>
       <c r="B111" s="24" t="s">
-        <v>824</v>
+        <v>813</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>825</v>
+        <v>814</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E111" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I111" s="3">
         <f>VLOOKUP(H111,cardsort_group_IDs!A:B,2,0)</f>
@@ -10596,16 +10667,16 @@
         <v>3</v>
       </c>
       <c r="P111" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q111" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R111" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
@@ -10613,7 +10684,7 @@
         <v>151</v>
       </c>
       <c r="B112" s="24" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
@@ -10622,13 +10693,13 @@
         <v>9</v>
       </c>
       <c r="E112" s="13" t="s">
+        <v>480</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="F112" s="4" t="s">
-        <v>486</v>
-      </c>
       <c r="G112" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10661,13 +10732,13 @@
         <v>1</v>
       </c>
       <c r="P112" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R112" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S112" s="12" t="s">
         <v>9</v>
@@ -10678,7 +10749,7 @@
         <v>152</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
@@ -10687,16 +10758,16 @@
         <v>9</v>
       </c>
       <c r="E113" s="13" t="s">
+        <v>487</v>
+      </c>
+      <c r="F113" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>493</v>
-      </c>
       <c r="G113" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I113" s="3">
         <f>VLOOKUP(H113,cardsort_group_IDs!A:B,2,0)</f>
@@ -10726,13 +10797,13 @@
         <v>1</v>
       </c>
       <c r="P113" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R113" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S113" s="12" t="s">
         <v>9</v>
@@ -10743,7 +10814,7 @@
         <v>153</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10752,16 +10823,16 @@
         <v>9</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I114" s="3">
         <f>VLOOKUP(H114,cardsort_group_IDs!A:B,2,0)</f>
@@ -10791,16 +10862,16 @@
         <v>1</v>
       </c>
       <c r="P114" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q114" s="12" t="s">
+        <v>516</v>
+      </c>
+      <c r="R114" t="s">
         <v>519</v>
       </c>
-      <c r="R114" t="s">
-        <v>522</v>
-      </c>
       <c r="S114" s="12" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10808,25 +10879,25 @@
         <v>154</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>828</v>
+        <v>817</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I115" s="3">
         <f>VLOOKUP(H115,cardsort_group_IDs!A:B,2,0)</f>
@@ -10856,16 +10927,16 @@
         <v>1</v>
       </c>
       <c r="P115" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Q115" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R115" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -10873,7 +10944,7 @@
         <v>155</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>9</v>
@@ -10882,16 +10953,16 @@
         <v>9</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I116" s="3">
         <f>VLOOKUP(H116,cardsort_group_IDs!A:B,2,0)</f>
@@ -10921,16 +10992,16 @@
         <v>2</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R116" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10938,22 +11009,22 @@
         <v>156</v>
       </c>
       <c r="B117" s="24" t="s">
+        <v>544</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>548</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>549</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>551</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>552</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>550</v>
-      </c>
       <c r="G117" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>30</v>
@@ -10986,13 +11057,13 @@
         <v>2</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q117" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R117" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
@@ -11003,25 +11074,25 @@
         <v>157</v>
       </c>
       <c r="B118" s="24" t="s">
+        <v>553</v>
+      </c>
+      <c r="C118" t="s">
+        <v>554</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>566</v>
+      </c>
+      <c r="E118" s="13" t="s">
         <v>556</v>
       </c>
-      <c r="C118" t="s">
-        <v>557</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>569</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>559</v>
-      </c>
       <c r="F118" s="4" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I118" s="3">
         <f>VLOOKUP(H118,cardsort_group_IDs!A:B,2,0)</f>
@@ -11051,16 +11122,16 @@
         <v>5</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="R118" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11068,10 +11139,10 @@
         <v>158</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11080,10 +11151,10 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>30</v>
@@ -11116,13 +11187,13 @@
         <v>1</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R119" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S119" s="12" t="s">
         <v>9</v>
@@ -11133,22 +11204,22 @@
         <v>159</v>
       </c>
       <c r="B120" s="24" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="C120" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11181,16 +11252,16 @@
         <v>2</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q120" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R120" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -11198,22 +11269,22 @@
         <v>160</v>
       </c>
       <c r="B121" s="24" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="C121" t="s">
+        <v>678</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="13" t="s">
         <v>684</v>
       </c>
-      <c r="D121" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>690</v>
-      </c>
       <c r="F121" s="4" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11246,16 +11317,16 @@
         <v>2</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R121" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S121" s="12" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -11263,22 +11334,22 @@
         <v>161</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>15</v>
@@ -11311,111 +11382,126 @@
         <v>2</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Q122" s="12" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R122" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="S122" s="12" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B4">
-    <cfRule type="duplicateValues" dxfId="36" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15">
-    <cfRule type="duplicateValues" dxfId="35" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16">
-    <cfRule type="duplicateValues" dxfId="34" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="38" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B30">
+    <cfRule type="duplicateValues" dxfId="37" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="duplicateValues" dxfId="36" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B32">
+    <cfRule type="duplicateValues" dxfId="35" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:B38">
+    <cfRule type="duplicateValues" dxfId="34" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
     <cfRule type="duplicateValues" dxfId="33" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
+  <conditionalFormatting sqref="B42">
     <cfRule type="duplicateValues" dxfId="32" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31">
+  <conditionalFormatting sqref="B43">
     <cfRule type="duplicateValues" dxfId="31" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B32">
-    <cfRule type="duplicateValues" dxfId="30" priority="33"/>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="30" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B35:B38">
-    <cfRule type="duplicateValues" dxfId="29" priority="42"/>
+  <conditionalFormatting sqref="B85">
+    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
-    <cfRule type="duplicateValues" dxfId="28" priority="31"/>
+  <conditionalFormatting sqref="B100:B1048576">
+    <cfRule type="duplicateValues" dxfId="28" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
-    <cfRule type="duplicateValues" dxfId="27" priority="30"/>
+  <conditionalFormatting sqref="F5">
+    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43">
+  <conditionalFormatting sqref="F33">
     <cfRule type="duplicateValues" dxfId="26" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
-    <cfRule type="duplicateValues" dxfId="25" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="24" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B100:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="43"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="22" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F33">
-    <cfRule type="duplicateValues" dxfId="21" priority="24"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="18" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="17" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J42">
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J56">
-    <cfRule type="duplicateValues" dxfId="9" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J60">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J94">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C108">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B85 C74 B1:B73 B87:B99">
-    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C104">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11435,16 +11521,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" t="s">
         <v>279</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>497</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>280</v>
-      </c>
-      <c r="C1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11452,13 +11538,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D2" t="s">
         <v>178</v>
-      </c>
-      <c r="C2" t="s">
-        <v>510</v>
-      </c>
-      <c r="D2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11466,27 +11552,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" t="s">
+        <v>507</v>
+      </c>
+      <c r="D3" t="s">
         <v>180</v>
-      </c>
-      <c r="C3" t="s">
-        <v>510</v>
-      </c>
-      <c r="D3" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11494,13 +11580,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D5" t="s">
         <v>182</v>
-      </c>
-      <c r="C5" t="s">
-        <v>510</v>
-      </c>
-      <c r="D5" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11508,13 +11594,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>184</v>
-      </c>
-      <c r="C6" t="s">
-        <v>510</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11522,13 +11608,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>186</v>
-      </c>
-      <c r="C7" t="s">
-        <v>510</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11536,13 +11622,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C8" t="s">
+        <v>507</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>188</v>
-      </c>
-      <c r="C8" t="s">
-        <v>510</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11550,13 +11636,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C9" t="s">
+        <v>507</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>190</v>
-      </c>
-      <c r="C9" t="s">
-        <v>510</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11564,13 +11650,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" t="s">
+        <v>507</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>192</v>
-      </c>
-      <c r="C10" t="s">
-        <v>510</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11578,13 +11664,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" t="s">
+        <v>507</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>194</v>
-      </c>
-      <c r="C11" t="s">
-        <v>510</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11592,13 +11678,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C12" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D12" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11606,13 +11692,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" t="s">
+        <v>507</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="C13" t="s">
-        <v>510</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11620,13 +11706,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" t="s">
+        <v>507</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>198</v>
-      </c>
-      <c r="C14" t="s">
-        <v>510</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11634,13 +11720,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C15" t="s">
+        <v>507</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>200</v>
-      </c>
-      <c r="C15" t="s">
-        <v>510</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11648,13 +11734,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C16" t="s">
+        <v>507</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>202</v>
-      </c>
-      <c r="C16" t="s">
-        <v>510</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11662,13 +11748,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" t="s">
+        <v>507</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>204</v>
-      </c>
-      <c r="C17" t="s">
-        <v>510</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11676,13 +11762,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C18" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D18" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11690,13 +11776,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
+        <v>205</v>
+      </c>
+      <c r="C19" t="s">
+        <v>507</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>206</v>
-      </c>
-      <c r="C19" t="s">
-        <v>510</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11704,13 +11790,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" t="s">
+        <v>507</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="C20" t="s">
-        <v>510</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11718,13 +11804,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" t="s">
+        <v>507</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>210</v>
-      </c>
-      <c r="C21" t="s">
-        <v>510</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11732,13 +11818,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C22" t="s">
+        <v>507</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="C22" t="s">
-        <v>510</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11746,13 +11832,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
+        <v>213</v>
+      </c>
+      <c r="C23" t="s">
+        <v>507</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>214</v>
-      </c>
-      <c r="C23" t="s">
-        <v>510</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11760,13 +11846,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
+        <v>215</v>
+      </c>
+      <c r="C24" t="s">
+        <v>507</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>216</v>
-      </c>
-      <c r="C24" t="s">
-        <v>510</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11774,13 +11860,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
+        <v>217</v>
+      </c>
+      <c r="C25" t="s">
+        <v>507</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>218</v>
-      </c>
-      <c r="C25" t="s">
-        <v>510</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11788,13 +11874,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
+        <v>219</v>
+      </c>
+      <c r="C26" t="s">
+        <v>507</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>220</v>
-      </c>
-      <c r="C26" t="s">
-        <v>510</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11802,13 +11888,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C27" t="s">
+        <v>507</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="C27" t="s">
-        <v>510</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -11816,13 +11902,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
+        <v>223</v>
+      </c>
+      <c r="C28" t="s">
+        <v>507</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="C28" t="s">
-        <v>510</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -11830,13 +11916,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" t="s">
+        <v>507</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>226</v>
-      </c>
-      <c r="C29" t="s">
-        <v>510</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -11844,13 +11930,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" t="s">
+        <v>507</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>228</v>
-      </c>
-      <c r="C30" t="s">
-        <v>510</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -11858,13 +11944,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C31" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -11872,13 +11958,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" t="s">
+        <v>507</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>231</v>
-      </c>
-      <c r="C32" t="s">
-        <v>510</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -11886,13 +11972,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" t="s">
+        <v>507</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>233</v>
-      </c>
-      <c r="C33" t="s">
-        <v>510</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -11900,13 +11986,13 @@
         <v>108</v>
       </c>
       <c r="B34" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" t="s">
+        <v>507</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>235</v>
-      </c>
-      <c r="C34" t="s">
-        <v>510</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -11914,13 +12000,13 @@
         <v>111</v>
       </c>
       <c r="B35" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" t="s">
+        <v>507</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>237</v>
-      </c>
-      <c r="C35" t="s">
-        <v>510</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -11928,13 +12014,13 @@
         <v>115</v>
       </c>
       <c r="B36" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" t="s">
+        <v>507</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>239</v>
-      </c>
-      <c r="C36" t="s">
-        <v>510</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -11942,13 +12028,13 @@
         <v>131</v>
       </c>
       <c r="B37" t="s">
+        <v>241</v>
+      </c>
+      <c r="C37" t="s">
+        <v>507</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>242</v>
-      </c>
-      <c r="C37" t="s">
-        <v>510</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="38" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -11956,13 +12042,13 @@
         <v>146</v>
       </c>
       <c r="B38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" t="s">
+        <v>507</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>244</v>
-      </c>
-      <c r="C38" t="s">
-        <v>510</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -11970,13 +12056,13 @@
         <v>160</v>
       </c>
       <c r="B39" t="s">
+        <v>245</v>
+      </c>
+      <c r="C39" t="s">
+        <v>507</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="C39" t="s">
-        <v>510</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11987,10 +12073,10 @@
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -11998,13 +12084,13 @@
         <v>182</v>
       </c>
       <c r="B41" t="s">
+        <v>248</v>
+      </c>
+      <c r="C41" t="s">
+        <v>507</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>249</v>
-      </c>
-      <c r="C41" t="s">
-        <v>510</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -12012,13 +12098,13 @@
         <v>183</v>
       </c>
       <c r="B42" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" t="s">
+        <v>507</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>251</v>
-      </c>
-      <c r="C42" t="s">
-        <v>510</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12026,13 +12112,13 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C43" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12040,13 +12126,13 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C44" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12057,10 +12143,10 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -12068,13 +12154,13 @@
         <v>202</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12082,13 +12168,13 @@
         <v>203</v>
       </c>
       <c r="B47" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D47" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12096,13 +12182,13 @@
         <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12110,13 +12196,13 @@
         <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12124,13 +12210,13 @@
         <v>232</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12138,13 +12224,13 @@
         <v>233</v>
       </c>
       <c r="B51" t="s">
+        <v>260</v>
+      </c>
+      <c r="C51" t="s">
+        <v>507</v>
+      </c>
+      <c r="D51" s="8" t="s">
         <v>261</v>
-      </c>
-      <c r="C51" t="s">
-        <v>510</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12152,13 +12238,13 @@
         <v>234</v>
       </c>
       <c r="B52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C52" t="s">
+        <v>507</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>263</v>
-      </c>
-      <c r="C52" t="s">
-        <v>510</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12166,13 +12252,13 @@
         <v>235</v>
       </c>
       <c r="B53" t="s">
+        <v>264</v>
+      </c>
+      <c r="C53" t="s">
+        <v>507</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>265</v>
-      </c>
-      <c r="C53" t="s">
-        <v>510</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12180,13 +12266,13 @@
         <v>236</v>
       </c>
       <c r="B54" t="s">
+        <v>266</v>
+      </c>
+      <c r="C54" t="s">
+        <v>507</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>267</v>
-      </c>
-      <c r="C54" t="s">
-        <v>510</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12194,13 +12280,13 @@
         <v>237</v>
       </c>
       <c r="B55" t="s">
+        <v>268</v>
+      </c>
+      <c r="C55" t="s">
+        <v>507</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>269</v>
-      </c>
-      <c r="C55" t="s">
-        <v>510</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12208,13 +12294,13 @@
         <v>238</v>
       </c>
       <c r="B56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" t="s">
+        <v>507</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>271</v>
-      </c>
-      <c r="C56" t="s">
-        <v>510</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12222,13 +12308,13 @@
         <v>241</v>
       </c>
       <c r="B57" t="s">
+        <v>272</v>
+      </c>
+      <c r="C57" t="s">
+        <v>507</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>273</v>
-      </c>
-      <c r="C57" t="s">
-        <v>510</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12236,13 +12322,13 @@
         <v>243</v>
       </c>
       <c r="B58" t="s">
+        <v>274</v>
+      </c>
+      <c r="C58" t="s">
+        <v>507</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>275</v>
-      </c>
-      <c r="C58" t="s">
-        <v>510</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12250,13 +12336,13 @@
         <v>244</v>
       </c>
       <c r="B59" t="s">
+        <v>276</v>
+      </c>
+      <c r="C59" t="s">
+        <v>507</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>277</v>
-      </c>
-      <c r="C59" t="s">
-        <v>510</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12264,13 +12350,13 @@
         <v>501</v>
       </c>
       <c r="B60" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12278,13 +12364,13 @@
         <v>502</v>
       </c>
       <c r="B61" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C61" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12292,13 +12378,13 @@
         <v>503</v>
       </c>
       <c r="B62" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12306,13 +12392,13 @@
         <v>504</v>
       </c>
       <c r="B63" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63" t="s">
+        <v>507</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>320</v>
-      </c>
-      <c r="C63" t="s">
-        <v>510</v>
-      </c>
-      <c r="D63" s="8" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12320,13 +12406,13 @@
         <v>505</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12337,10 +12423,10 @@
         <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12348,13 +12434,13 @@
         <v>507</v>
       </c>
       <c r="B66" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C66" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12365,10 +12451,10 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12376,13 +12462,13 @@
         <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C68" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12390,1147 +12476,1147 @@
         <v>510</v>
       </c>
       <c r="B69" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C69" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B70" t="s">
         <v>333</v>
       </c>
-      <c r="B70" t="s">
-        <v>334</v>
-      </c>
       <c r="C70" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B71" t="s">
         <v>335</v>
       </c>
-      <c r="B71" t="s">
-        <v>336</v>
-      </c>
       <c r="C71" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B72" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="B73" t="s">
         <v>338</v>
       </c>
-      <c r="B73" t="s">
-        <v>339</v>
-      </c>
       <c r="C73" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B74" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B75" t="s">
         <v>341</v>
       </c>
-      <c r="B75" t="s">
-        <v>342</v>
-      </c>
       <c r="C75" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B76" t="s">
         <v>343</v>
       </c>
-      <c r="B76" t="s">
-        <v>344</v>
-      </c>
       <c r="C76" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B78" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C78" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B79" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C79" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B80" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C80" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B81" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C81" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B82" t="s">
         <v>349</v>
       </c>
-      <c r="B82" t="s">
-        <v>350</v>
-      </c>
       <c r="C82" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B83" t="s">
         <v>351</v>
       </c>
-      <c r="B83" t="s">
-        <v>352</v>
-      </c>
       <c r="C83" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B84" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C84" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="B85" t="s">
         <v>354</v>
       </c>
-      <c r="B85" t="s">
-        <v>355</v>
-      </c>
       <c r="C85" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="B86" t="s">
         <v>356</v>
       </c>
-      <c r="B86" t="s">
-        <v>357</v>
-      </c>
       <c r="C86" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="B87" t="s">
         <v>358</v>
       </c>
-      <c r="B87" t="s">
-        <v>359</v>
-      </c>
       <c r="C87" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="B88" t="s">
         <v>360</v>
       </c>
-      <c r="B88" t="s">
-        <v>361</v>
-      </c>
       <c r="C88" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B89" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C89" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B90" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="C91" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C92" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B93" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C93" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B94" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B95" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="B96" t="s">
         <v>324</v>
       </c>
-      <c r="B96" t="s">
-        <v>325</v>
-      </c>
       <c r="C96" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s">
         <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B98" t="s">
         <v>62</v>
       </c>
       <c r="C98" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B99" t="s">
         <v>326</v>
       </c>
-      <c r="B99" t="s">
-        <v>327</v>
-      </c>
       <c r="C99" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="B100" t="s">
         <v>328</v>
       </c>
-      <c r="B100" t="s">
-        <v>329</v>
-      </c>
       <c r="C100" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="B101" t="s">
         <v>330</v>
       </c>
-      <c r="B101" t="s">
-        <v>331</v>
-      </c>
       <c r="C101" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B102" t="s">
         <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B104" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C105" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B106" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B107" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C107" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C108" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B109" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C109" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B110" t="s">
         <v>33</v>
       </c>
       <c r="C110" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B111" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B112" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="B113" t="s">
         <v>404</v>
       </c>
-      <c r="B113" t="s">
-        <v>405</v>
-      </c>
       <c r="C113" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D113" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B114" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C114" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D114" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B115" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D115" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B116" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C116" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D116" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B117" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C117" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D117" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B118" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C118" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D118" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B119" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C119" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D119" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B120" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C120" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D120" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B121" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C121" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D121" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B122" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C122" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D122" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B123" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C123" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D123" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B124" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C124" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D124" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B125" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C125" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D125" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B126" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C126" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D126" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B127" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C127" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D127" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B128" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C128" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D128" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B129" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C129" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D129" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B130" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C130" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D130" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B131" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C131" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D131" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B132" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D132" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B133" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C133" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D133" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B134" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C134" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D134" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B135" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="C135" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D135" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B136" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C136" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D136" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B137" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C137" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D137" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B138" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C138" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D138" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="B139" t="s">
+        <v>586</v>
+      </c>
+      <c r="C139" t="s">
+        <v>498</v>
+      </c>
+      <c r="D139" t="s">
         <v>564</v>
-      </c>
-      <c r="B139" t="s">
-        <v>589</v>
-      </c>
-      <c r="C139" t="s">
-        <v>501</v>
-      </c>
-      <c r="D139" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="B140" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D140" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B141" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C141" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D141" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B142" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C142" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D142" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B143" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C143" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D143" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="B144" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D144" t="s">
-        <v>629</v>
+        <v>624</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B145" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="D145" s="27" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="B146" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="C146" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D146" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
+        <v>675</v>
+      </c>
+      <c r="B147" t="s">
         <v>681</v>
       </c>
-      <c r="B147" t="s">
-        <v>687</v>
-      </c>
       <c r="C147" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D147" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="B148" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C148" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D148" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="B149" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C149" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D149" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="B150" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
       <c r="C150" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D150" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
     </row>
   </sheetData>
@@ -13585,7 +13671,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13670,7 +13756,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B4">
         <v>304</v>
@@ -13814,7 +13900,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22">
         <v>323</v>
@@ -13822,7 +13908,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23">
         <v>324</v>
@@ -13830,7 +13916,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24">
         <v>325</v>
@@ -13838,7 +13924,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B25">
         <v>326</v>
@@ -13854,7 +13940,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27">
         <v>328</v>
@@ -13862,7 +13948,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B28">
         <v>329</v>
@@ -13870,7 +13956,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B29">
         <v>330</v>
@@ -13878,7 +13964,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -13886,7 +13972,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -13894,7 +13980,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -13902,8 +13988,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13920,50 +14006,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>497</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>500</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>504</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A0A027B-6CD5-414A-A9FC-D4EF0AA7ACB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A50D6C-33DF-4575-B81D-61EF595F3118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="company_sizes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">metrics!$A$1:$M$123</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">urls!$A$1:$D$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="849">
   <si>
     <t>id</t>
   </si>
@@ -1175,9 +1175,6 @@
     <t>501b; 5a</t>
   </si>
   <si>
-    <t xml:space="preserve">5; 501; 115; 183; </t>
-  </si>
-  <si>
     <t>501b; 501d</t>
   </si>
   <si>
@@ -1502,9 +1499,6 @@
     <t>9; 36; 52; 62; 240; 243; 244; 160; 501; 183; 512</t>
   </si>
   <si>
-    <t>503; 9; 17; 5; 115; 501; 115; 183; 182; 512</t>
-  </si>
-  <si>
     <t>Net time gain per developer</t>
   </si>
   <si>
@@ -1650,9 +1644,6 @@
   </si>
   <si>
     <t>514; 7; 14; 31; 49; 52; 57; 96;108; 192; 234; 32; 131</t>
-  </si>
-  <si>
-    <t>514; 5; 160; 501; 115; 146; 183</t>
   </si>
   <si>
     <t>514; 505</t>
@@ -2040,9 +2031,6 @@
     <t>501; 131; 202; 520</t>
   </si>
   <si>
-    <t>514; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512; 520</t>
-  </si>
-  <si>
     <t>Percentage of PRs assisted by AI</t>
   </si>
   <si>
@@ -2193,12 +2181,6 @@
     <t>Developer Build Time; Build Time;  Application/Package Build Duration; Build Time Efficiency</t>
   </si>
   <si>
-    <t>Developer CSAT; Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System; AI tool CSAT; Bad developer days</t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
     <t>36</t>
   </si>
   <si>
@@ -2566,6 +2548,51 @@
   </si>
   <si>
     <t>AI-Written Code Share</t>
+  </si>
+  <si>
+    <t>Developer CSAT; Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System; AI tool CSAT</t>
+  </si>
+  <si>
+    <t>155; 162</t>
+  </si>
+  <si>
+    <t>Bad Developer Days</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>A composite telemetry metric counting the share of developer-days affected by friction events such as context switching, build failures, incident response, or compliance overhead.</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t>36; 10</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2605.04259</t>
+  </si>
+  <si>
+    <t>514; 5; 160; 501; 115; 146; 183; 522</t>
+  </si>
+  <si>
+    <t>503; 501; 183; 522</t>
+  </si>
+  <si>
+    <t>514; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512; 520; 522</t>
+  </si>
+  <si>
+    <t>501; 183; 522</t>
+  </si>
+  <si>
+    <t>503; 9; 17; 5; 115; 501; 115; 183; 182; 512; 522</t>
+  </si>
+  <si>
+    <t>5; 501; 115; 183; 522</t>
+  </si>
+  <si>
+    <t>Microsoft EngThrive Framework</t>
   </si>
 </sst>
 </file>
@@ -2758,6 +2785,16 @@
   <dxfs count="42">
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -2813,16 +2850,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3456,7 +3483,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S122"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3496,7 +3524,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3523,19 +3551,19 @@
         <v>370</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2</v>
       </c>
@@ -3546,16 +3574,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3588,19 +3616,19 @@
         <v>23</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -3620,7 +3648,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3653,39 +3681,39 @@
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>9</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3718,24 +3746,24 @@
         <v>4</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>10</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -3744,13 +3772,13 @@
         <v>300</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>385</v>
+        <v>843</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>369</v>
@@ -3776,26 +3804,26 @@
       </c>
       <c r="N5" s="3">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O5" s="3">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>11</v>
       </c>
@@ -3815,7 +3843,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3848,19 +3876,19 @@
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R6" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>12</v>
       </c>
@@ -3868,19 +3896,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -3916,16 +3944,16 @@
         <v>93</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>13</v>
       </c>
@@ -3936,16 +3964,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -3978,19 +4006,19 @@
         <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R8" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>14</v>
       </c>
@@ -4001,16 +4029,16 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -4043,39 +4071,39 @@
         <v>5</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R9" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>15</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>613</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>692</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="E10" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>619</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -4108,19 +4136,19 @@
         <v>5</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R10" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>16</v>
       </c>
@@ -4140,7 +4168,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -4173,39 +4201,39 @@
         <v>6</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>42</v>
@@ -4238,19 +4266,19 @@
         <v>11</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>18</v>
       </c>
@@ -4258,19 +4286,19 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>476</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -4306,16 +4334,16 @@
         <v>93</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R13" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>19</v>
       </c>
@@ -4323,19 +4351,19 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>46</v>
@@ -4368,24 +4396,24 @@
         <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R14" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>20</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>162</v>
@@ -4394,13 +4422,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>369</v>
@@ -4436,21 +4464,21 @@
         <v>93</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R15" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>22</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -4465,7 +4493,7 @@
         <v>49</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4498,24 +4526,24 @@
         <v>3</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>23</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>163</v>
@@ -4527,10 +4555,10 @@
         <v>289</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>42</v>
@@ -4563,19 +4591,19 @@
         <v>2</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R17" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>24</v>
       </c>
@@ -4595,7 +4623,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4628,39 +4656,39 @@
         <v>1</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R18" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>25</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>56</v>
@@ -4693,24 +4721,24 @@
         <v>3</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R19" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>26</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>308</v>
@@ -4719,10 +4747,10 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>56</v>
@@ -4755,19 +4783,19 @@
         <v>3</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R20" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>27</v>
       </c>
@@ -4775,19 +4803,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4823,36 +4851,36 @@
         <v>93</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R21" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -4885,19 +4913,19 @@
         <v>3</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R22" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>30</v>
       </c>
@@ -4908,16 +4936,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -4953,16 +4981,16 @@
         <v>93</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R23" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>31</v>
       </c>
@@ -4970,19 +4998,19 @@
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="F24" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
@@ -5015,24 +5043,24 @@
         <v>5</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R24" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -5047,7 +5075,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>56</v>
@@ -5080,19 +5108,19 @@
         <v>2</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R25" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>33</v>
       </c>
@@ -5112,7 +5140,7 @@
         <v>65</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5145,19 +5173,19 @@
         <v>3</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R26" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>34</v>
       </c>
@@ -5165,19 +5193,19 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5210,19 +5238,19 @@
         <v>9</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R27" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>36</v>
       </c>
@@ -5230,19 +5258,19 @@
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>715</v>
+        <v>834</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>664</v>
+        <v>844</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>369</v>
@@ -5268,31 +5296,31 @@
       </c>
       <c r="N28" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O28" s="3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P28" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R28" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="255" x14ac:dyDescent="0.25">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5307,7 +5335,7 @@
         <v>72</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>10</v>
@@ -5340,19 +5368,19 @@
         <v>1</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R29" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>38</v>
       </c>
@@ -5360,19 +5388,19 @@
         <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>523</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -5408,16 +5436,16 @@
         <v>93</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R30" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>39</v>
       </c>
@@ -5437,7 +5465,7 @@
         <v>75</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5470,19 +5498,19 @@
         <v>3</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R31" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>40</v>
       </c>
@@ -5496,13 +5524,13 @@
         <v>374</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>535</v>
+        <v>842</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>369</v>
@@ -5528,26 +5556,26 @@
       </c>
       <c r="N32" s="3">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O32" s="3">
         <f t="shared" si="2"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P32" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R32" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>41</v>
       </c>
@@ -5567,7 +5595,7 @@
         <v>79</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>369</v>
@@ -5600,19 +5628,19 @@
         <v>6</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R33" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>42</v>
       </c>
@@ -5620,19 +5648,19 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -5665,19 +5693,19 @@
         <v>3</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R34" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>43</v>
       </c>
@@ -5697,7 +5725,7 @@
         <v>83</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>369</v>
@@ -5730,19 +5758,19 @@
         <v>3</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R35" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>44</v>
       </c>
@@ -5750,19 +5778,19 @@
         <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
@@ -5798,16 +5826,16 @@
         <v>93</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R36" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45</v>
       </c>
@@ -5821,13 +5849,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5860,27 +5888,27 @@
         <v>2</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R37" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
@@ -5889,10 +5917,10 @@
         <v>317</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>42</v>
@@ -5928,36 +5956,36 @@
         <v>93</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R38" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>50</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>526</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>369</v>
@@ -5990,19 +6018,19 @@
         <v>14</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R39" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>56</v>
       </c>
@@ -6016,13 +6044,13 @@
         <v>300</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>369</v>
@@ -6055,19 +6083,19 @@
         <v>4</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R40" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S40" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>57</v>
       </c>
@@ -6087,7 +6115,7 @@
         <v>96</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>10</v>
@@ -6120,19 +6148,19 @@
         <v>1</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R41" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="345" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>58</v>
       </c>
@@ -6143,16 +6171,16 @@
         <v>164</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>369</v>
@@ -6188,24 +6216,24 @@
         <v>93</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R42" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>59</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
@@ -6217,7 +6245,7 @@
         <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>369</v>
@@ -6253,36 +6281,36 @@
         <v>93</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R43" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>62</v>
       </c>
       <c r="B44" s="25" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6315,19 +6343,19 @@
         <v>14</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R44" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>63</v>
       </c>
@@ -6338,7 +6366,7 @@
         <v>165</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>314</v>
@@ -6347,7 +6375,7 @@
         <v>102</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -6383,16 +6411,16 @@
         <v>93</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R45" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>64</v>
       </c>
@@ -6409,10 +6437,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -6445,19 +6473,19 @@
         <v>1</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R46" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>65</v>
       </c>
@@ -6465,19 +6493,19 @@
         <v>104</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -6510,24 +6538,24 @@
         <v>16</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R47" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>67</v>
       </c>
       <c r="B48" s="26" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
@@ -6542,7 +6570,7 @@
         <v>106</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>42</v>
@@ -6575,19 +6603,19 @@
         <v>3</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R48" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>69</v>
       </c>
@@ -6595,7 +6623,7 @@
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>293</v>
@@ -6607,7 +6635,7 @@
         <v>108</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>56</v>
@@ -6640,19 +6668,19 @@
         <v>3</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R49" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>70</v>
       </c>
@@ -6660,19 +6688,19 @@
         <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -6705,24 +6733,24 @@
         <v>5</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R50" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>71</v>
       </c>
       <c r="B51" s="24" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>92</v>
@@ -6731,13 +6759,13 @@
         <v>300</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -6770,24 +6798,24 @@
         <v>4</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R51" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>72</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
@@ -6799,10 +6827,10 @@
         <v>302</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>10</v>
@@ -6835,19 +6863,19 @@
         <v>3</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R52" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>73</v>
       </c>
@@ -6867,7 +6895,7 @@
         <v>112</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -6900,27 +6928,27 @@
         <v>3</v>
       </c>
       <c r="P53" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R53" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S53" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>75</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>361</v>
@@ -6929,10 +6957,10 @@
         <v>183</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -6965,36 +6993,36 @@
         <v>2</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R54" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>76</v>
       </c>
       <c r="B55" s="24" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -7027,19 +7055,19 @@
         <v>2</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q55" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R55" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>78</v>
       </c>
@@ -7050,16 +7078,16 @@
         <v>115</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>369</v>
@@ -7095,16 +7123,16 @@
         <v>93</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R56" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>79</v>
       </c>
@@ -7118,13 +7146,13 @@
         <v>299</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
@@ -7160,16 +7188,16 @@
         <v>93</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R57" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>80</v>
       </c>
@@ -7189,7 +7217,7 @@
         <v>119</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>56</v>
@@ -7222,24 +7250,24 @@
         <v>1</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R58" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>120</v>
@@ -7254,7 +7282,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -7287,19 +7315,19 @@
         <v>1</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R59" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>83</v>
       </c>
@@ -7307,19 +7335,19 @@
         <v>122</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>469</v>
-      </c>
       <c r="E60" s="13" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>369</v>
@@ -7355,16 +7383,16 @@
         <v>93</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R60" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>87</v>
       </c>
@@ -7375,16 +7403,16 @@
         <v>9</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>384</v>
+        <v>845</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>15</v>
@@ -7410,46 +7438,46 @@
       </c>
       <c r="N61" s="3">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O61" s="3">
         <f t="shared" si="7"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R61" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>88</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>288</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -7482,19 +7510,19 @@
         <v>4</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R62" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>89</v>
       </c>
@@ -7502,19 +7530,19 @@
         <v>125</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D63" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>660</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E63" s="13" t="s">
-        <v>663</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -7547,19 +7575,19 @@
         <v>8</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R63" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>90</v>
       </c>
@@ -7567,19 +7595,19 @@
         <v>126</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="D64" s="12" t="s">
-        <v>464</v>
-      </c>
       <c r="E64" s="13" t="s">
-        <v>485</v>
+        <v>846</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -7605,26 +7633,26 @@
       </c>
       <c r="N64" s="3">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O64" s="3">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P64" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R64" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>91</v>
       </c>
@@ -7638,13 +7666,13 @@
         <v>295</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>128</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7677,19 +7705,19 @@
         <v>4</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R65" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>92</v>
       </c>
@@ -7709,7 +7737,7 @@
         <v>130</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>42</v>
@@ -7742,19 +7770,19 @@
         <v>3</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R66" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>93</v>
       </c>
@@ -7774,7 +7802,7 @@
         <v>132</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>10</v>
@@ -7807,19 +7835,19 @@
         <v>1</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R67" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>94</v>
       </c>
@@ -7836,10 +7864,10 @@
         <v>309</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>56</v>
@@ -7872,39 +7900,39 @@
         <v>4</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R68" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="24">
         <v>95</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>361</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>21</v>
@@ -7937,19 +7965,19 @@
         <v>2</v>
       </c>
       <c r="P69" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R69" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>97</v>
       </c>
@@ -7969,7 +7997,7 @@
         <v>135</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -8002,24 +8030,24 @@
         <v>1</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R70" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>98</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>168</v>
@@ -8034,7 +8062,7 @@
         <v>136</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -8067,24 +8095,24 @@
         <v>2</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R71" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>99</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8096,10 +8124,10 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -8132,19 +8160,19 @@
         <v>1</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R72" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S72" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>100</v>
       </c>
@@ -8164,7 +8192,7 @@
         <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>10</v>
@@ -8197,39 +8225,39 @@
         <v>1</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R73" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="135" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>102</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C74" s="24" t="s">
         <v>139</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E74" s="13">
         <v>501</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>15</v>
@@ -8262,24 +8290,24 @@
         <v>3</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R74" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>104</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
@@ -8291,10 +8319,10 @@
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>369</v>
@@ -8327,19 +8355,19 @@
         <v>2</v>
       </c>
       <c r="P75" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R75" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="180" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="120" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>107</v>
       </c>
@@ -8353,13 +8381,13 @@
         <v>375</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>376</v>
+        <v>847</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>142</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8392,30 +8420,30 @@
         <v>7</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R76" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>108</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>307</v>
@@ -8424,7 +8452,7 @@
         <v>143</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -8457,39 +8485,39 @@
         <v>8</v>
       </c>
       <c r="P77" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R77" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="24">
         <v>109</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>311</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8522,19 +8550,19 @@
         <v>7</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R78" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>112</v>
       </c>
@@ -8548,13 +8576,13 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>369</v>
@@ -8590,36 +8618,36 @@
         <v>93</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R79" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>113</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>369</v>
@@ -8655,36 +8683,36 @@
         <v>93</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R80" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>114</v>
       </c>
       <c r="B81" s="24" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>46</v>
@@ -8720,16 +8748,16 @@
         <v>93</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R81" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>115</v>
       </c>
@@ -8737,7 +8765,7 @@
         <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8746,10 +8774,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>42</v>
@@ -8782,19 +8810,19 @@
         <v>1</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R82" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>116</v>
       </c>
@@ -8802,10 +8830,10 @@
         <v>147</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>312</v>
@@ -8814,7 +8842,7 @@
         <v>148</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>30</v>
@@ -8847,19 +8875,19 @@
         <v>5</v>
       </c>
       <c r="P83" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q83" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R83" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S83" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>117</v>
       </c>
@@ -8867,10 +8895,10 @@
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>313</v>
@@ -8879,7 +8907,7 @@
         <v>150</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>30</v>
@@ -8915,16 +8943,16 @@
         <v>93</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R84" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>118</v>
       </c>
@@ -8944,7 +8972,7 @@
         <v>152</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>21</v>
@@ -8977,27 +9005,27 @@
         <v>1</v>
       </c>
       <c r="P85" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R85" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>300</v>
@@ -9006,10 +9034,10 @@
         <v>302</v>
       </c>
       <c r="F86" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -9042,19 +9070,19 @@
         <v>3</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R86" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>121</v>
       </c>
@@ -9065,16 +9093,16 @@
         <v>176</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>15</v>
@@ -9110,16 +9138,16 @@
         <v>93</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R87" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>122</v>
       </c>
@@ -9127,19 +9155,19 @@
         <v>156</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -9175,36 +9203,36 @@
         <v>93</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R88" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>124</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>369</v>
@@ -9237,27 +9265,27 @@
         <v>9</v>
       </c>
       <c r="P89" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R89" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>126</v>
       </c>
       <c r="B90" s="26" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>297</v>
@@ -9266,10 +9294,10 @@
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>46</v>
@@ -9302,39 +9330,39 @@
         <v>2</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R90" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>127</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>169</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>46</v>
@@ -9367,27 +9395,27 @@
         <v>4</v>
       </c>
       <c r="P91" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R91" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>128</v>
       </c>
       <c r="B92" s="26" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>301</v>
@@ -9396,10 +9424,10 @@
         <v>501</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>46</v>
@@ -9432,39 +9460,39 @@
         <v>2</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R92" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>129</v>
       </c>
       <c r="B93" s="26" t="s">
+        <v>457</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>459</v>
-      </c>
       <c r="E93" s="13" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>46</v>
@@ -9500,36 +9528,36 @@
         <v>93</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R93" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>130</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="D94" s="12" t="s">
+        <v>376</v>
+      </c>
+      <c r="E94" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="E94" s="13" t="s">
-        <v>378</v>
-      </c>
       <c r="F94" s="4" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="G94" s="24" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>369</v>
@@ -9562,39 +9590,39 @@
         <v>5</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q94" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R94" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S94" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="24">
         <v>133</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="D95" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E95" s="13" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="G95" s="24" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>30</v>
@@ -9630,21 +9658,21 @@
         <v>93</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R95" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S95" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="24">
         <v>134</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
@@ -9653,13 +9681,13 @@
         <v>9</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="G96" s="24" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>30</v>
@@ -9695,16 +9723,16 @@
         <v>93</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R96" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S96" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>135</v>
       </c>
@@ -9724,7 +9752,7 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H97" t="s">
         <v>369</v>
@@ -9757,19 +9785,19 @@
         <v>1</v>
       </c>
       <c r="P97" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q97" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R97" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>137</v>
       </c>
@@ -9789,7 +9817,7 @@
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H98" t="s">
         <v>369</v>
@@ -9822,27 +9850,27 @@
         <v>6</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R98" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>138</v>
       </c>
       <c r="B99" s="26" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9854,7 +9882,7 @@
         <v>364</v>
       </c>
       <c r="G99" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -9887,24 +9915,24 @@
         <v>1</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q99" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R99" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>139</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>9</v>
@@ -9916,10 +9944,10 @@
         <v>9</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>21</v>
@@ -9952,39 +9980,39 @@
         <v>1</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R100" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>140</v>
       </c>
       <c r="B101" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>804</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>434</v>
-      </c>
       <c r="G101" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>15</v>
@@ -10017,39 +10045,39 @@
         <v>18</v>
       </c>
       <c r="P101" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R101" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S101" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>141</v>
       </c>
       <c r="B102" s="24" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="C102" s="24" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>46</v>
@@ -10059,7 +10087,7 @@
         <v>207</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K102" s="3">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10082,39 +10110,39 @@
         <v>4</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R102" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S102" s="12">
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>142</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="C103" s="24" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>46</v>
@@ -10124,7 +10152,7 @@
         <v>207</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K103" s="3">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10147,39 +10175,39 @@
         <v>3</v>
       </c>
       <c r="P103" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R103" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S103" s="12">
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>143</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C104" s="24" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E104" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>46</v>
@@ -10189,7 +10217,7 @@
         <v>207</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10212,39 +10240,39 @@
         <v>5</v>
       </c>
       <c r="P104" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R104" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>144</v>
       </c>
       <c r="B105" s="24" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10277,39 +10305,39 @@
         <v>1</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R105" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>145</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -10342,39 +10370,39 @@
         <v>1</v>
       </c>
       <c r="P106" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q106" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R106" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>146</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="D107" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -10407,39 +10435,39 @@
         <v>6</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="Q107" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R107" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="108" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>147</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>15</v>
@@ -10472,39 +10500,39 @@
         <v>1</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q108" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R108" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>148</v>
       </c>
       <c r="B109" s="24" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>10</v>
@@ -10540,36 +10568,36 @@
         <v>93</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R109" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>149</v>
       </c>
       <c r="B110" s="24" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E110" s="13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>21</v>
@@ -10605,13 +10633,13 @@
         <v>93</v>
       </c>
       <c r="Q110" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R110" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -10619,22 +10647,22 @@
         <v>150</v>
       </c>
       <c r="B111" s="24" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>9</v>
+        <v>837</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>369</v>
@@ -10652,7 +10680,7 @@
       </c>
       <c r="L111" s="3">
         <f t="shared" ref="L111" si="26">IF(E111="-",0,1)+IF(D111="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M111" s="3">
         <f t="shared" si="10"/>
@@ -10660,46 +10688,46 @@
       </c>
       <c r="N111" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" s="3">
         <f t="shared" ref="O111" si="27">SUM(M111:N111)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P111" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q111" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R111" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>151</v>
       </c>
       <c r="B112" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>482</v>
       </c>
-      <c r="C112" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>480</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="G112" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10735,21 +10763,21 @@
         <v>93</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R112" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S112" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>152</v>
       </c>
       <c r="B113" s="24" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
@@ -10758,13 +10786,13 @@
         <v>9</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>369</v>
@@ -10800,21 +10828,21 @@
         <v>93</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R113" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S113" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>153</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10823,13 +10851,13 @@
         <v>9</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>369</v>
@@ -10865,36 +10893,36 @@
         <v>93</v>
       </c>
       <c r="Q114" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R114" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>154</v>
       </c>
       <c r="B115" s="24" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>369</v>
@@ -10930,21 +10958,21 @@
         <v>93</v>
       </c>
       <c r="Q115" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R115" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="116" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>155</v>
       </c>
       <c r="B116" s="24" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="C116" s="4" t="s">
         <v>9</v>
@@ -10953,13 +10981,13 @@
         <v>9</v>
       </c>
       <c r="E116" s="13" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>369</v>
@@ -10992,39 +11020,39 @@
         <v>2</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R116" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>156</v>
       </c>
       <c r="B117" s="24" t="s">
+        <v>541</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="D117" s="12" t="s">
-        <v>548</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>547</v>
-      </c>
       <c r="G117" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>30</v>
@@ -11057,39 +11085,39 @@
         <v>2</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q117" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R117" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>157</v>
       </c>
       <c r="B118" s="24" t="s">
+        <v>550</v>
+      </c>
+      <c r="C118" t="s">
+        <v>551</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="E118" s="13" t="s">
         <v>553</v>
       </c>
-      <c r="C118" t="s">
-        <v>554</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>566</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>556</v>
-      </c>
       <c r="F118" s="4" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>369</v>
@@ -11122,27 +11150,27 @@
         <v>5</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="R118" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>158</v>
       </c>
       <c r="B119" s="24" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11151,10 +11179,10 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>30</v>
@@ -11187,39 +11215,39 @@
         <v>1</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R119" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S119" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>159</v>
       </c>
       <c r="B120" s="24" t="s">
+        <v>665</v>
+      </c>
+      <c r="C120" t="s">
+        <v>668</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="F120" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="C120" t="s">
-        <v>672</v>
-      </c>
-      <c r="D120" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>673</v>
-      </c>
       <c r="G120" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11252,39 +11280,39 @@
         <v>2</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q120" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R120" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>160</v>
       </c>
       <c r="B121" s="24" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C121" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11317,39 +11345,39 @@
         <v>2</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R121" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S121" s="12" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>161</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>15</v>
@@ -11366,36 +11394,114 @@
         <v>314</v>
       </c>
       <c r="L122" s="3">
-        <f t="shared" ref="L122" si="51">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
+        <f t="shared" ref="L122:L123" si="51">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M122" s="3">
-        <f t="shared" ref="M122" si="52">IF(D122="-",0,LEN(D122)-LEN(SUBSTITUTE(D122,";",""))+1)</f>
+        <f t="shared" ref="M122:M123" si="52">IF(D122="-",0,LEN(D122)-LEN(SUBSTITUTE(D122,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="N122" s="3">
-        <f t="shared" ref="N122" si="53">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
+        <f t="shared" ref="N122:N123" si="53">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O122" s="3">
-        <f t="shared" ref="O122" si="54">SUM(M122:N122)</f>
+        <f t="shared" ref="O122:O123" si="54">SUM(M122:N122)</f>
         <v>2</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q122" s="12" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="R122" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="S122" s="12" t="s">
-        <v>688</v>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+      <c r="A123" s="3">
+        <v>162</v>
+      </c>
+      <c r="B123" s="24" t="s">
+        <v>836</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="I123" s="3">
+        <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J123" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K123" s="3">
+        <f>VLOOKUP(J123,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>307</v>
+      </c>
+      <c r="L123" s="3">
+        <f t="shared" ref="L123" si="55">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
+        <v>1</v>
+      </c>
+      <c r="M123" s="3">
+        <f t="shared" ref="M123" si="56">IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="N123" s="3">
+        <f>IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
+        <v>0</v>
+      </c>
+      <c r="O123" s="3">
+        <f t="shared" si="54"/>
+        <v>0</v>
+      </c>
+      <c r="P123" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="Q123" s="12" t="s">
+        <v>512</v>
+      </c>
+      <c r="R123" t="s">
+        <v>839</v>
+      </c>
+      <c r="S123" s="12" t="s">
+        <v>840</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M122" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:M123" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="501b; 5a; 522"/>
+        <filter val="501c; 501l; 501b; 501e; 501g; 501d; 5a; 522"/>
+        <filter val="501h; 516c; 522"/>
+        <filter val="501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; 511k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r; 522"/>
+        <filter val="501m; 522"/>
+        <filter val="501m; 5a; 511a; 511f; 522"/>
+        <filter val="511b; 511l; 516c; 522"/>
+        <filter val="522"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B4">
     <cfRule type="duplicateValues" dxfId="41" priority="30"/>
@@ -11486,22 +11592,22 @@
     <cfRule type="duplicateValues" dxfId="8" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B75:B85 C74 B1:B73 B87:B99">
-    <cfRule type="duplicateValues" dxfId="5" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C104">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C103">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11510,7 +11616,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:D151"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -11527,7 +11633,7 @@
         <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>280</v>
@@ -11541,7 +11647,7 @@
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D2" t="s">
         <v>178</v>
@@ -11555,7 +11661,7 @@
         <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D3" t="s">
         <v>180</v>
@@ -11569,7 +11675,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D4" t="s">
         <v>180</v>
@@ -11583,7 +11689,7 @@
         <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -11597,7 +11703,7 @@
         <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>184</v>
@@ -11611,7 +11717,7 @@
         <v>185</v>
       </c>
       <c r="C7" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>186</v>
@@ -11625,7 +11731,7 @@
         <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>188</v>
@@ -11639,7 +11745,7 @@
         <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>190</v>
@@ -11653,7 +11759,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>192</v>
@@ -11667,7 +11773,7 @@
         <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>194</v>
@@ -11678,13 +11784,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D12" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11695,7 +11801,7 @@
         <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>196</v>
@@ -11709,7 +11815,7 @@
         <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>198</v>
@@ -11723,7 +11829,7 @@
         <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>200</v>
@@ -11737,7 +11843,7 @@
         <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>202</v>
@@ -11751,7 +11857,7 @@
         <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>204</v>
@@ -11762,13 +11868,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C18" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D18" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11779,7 +11885,7 @@
         <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>206</v>
@@ -11793,7 +11899,7 @@
         <v>207</v>
       </c>
       <c r="C20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>208</v>
@@ -11807,7 +11913,7 @@
         <v>209</v>
       </c>
       <c r="C21" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>210</v>
@@ -11821,7 +11927,7 @@
         <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>212</v>
@@ -11835,7 +11941,7 @@
         <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>214</v>
@@ -11849,7 +11955,7 @@
         <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>216</v>
@@ -11863,7 +11969,7 @@
         <v>217</v>
       </c>
       <c r="C25" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>218</v>
@@ -11877,7 +11983,7 @@
         <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>220</v>
@@ -11891,7 +11997,7 @@
         <v>221</v>
       </c>
       <c r="C27" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>222</v>
@@ -11905,7 +12011,7 @@
         <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>224</v>
@@ -11919,7 +12025,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>226</v>
@@ -11933,7 +12039,7 @@
         <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>228</v>
@@ -11944,10 +12050,10 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C31" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>229</v>
@@ -11961,7 +12067,7 @@
         <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>231</v>
@@ -11975,7 +12081,7 @@
         <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>233</v>
@@ -11989,7 +12095,7 @@
         <v>234</v>
       </c>
       <c r="C34" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>235</v>
@@ -12003,7 +12109,7 @@
         <v>236</v>
       </c>
       <c r="C35" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>237</v>
@@ -12017,7 +12123,7 @@
         <v>238</v>
       </c>
       <c r="C36" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>239</v>
@@ -12031,7 +12137,7 @@
         <v>241</v>
       </c>
       <c r="C37" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>242</v>
@@ -12045,7 +12151,7 @@
         <v>243</v>
       </c>
       <c r="C38" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>244</v>
@@ -12059,7 +12165,7 @@
         <v>245</v>
       </c>
       <c r="C39" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>246</v>
@@ -12073,7 +12179,7 @@
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>247</v>
@@ -12087,7 +12193,7 @@
         <v>248</v>
       </c>
       <c r="C41" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>249</v>
@@ -12101,7 +12207,7 @@
         <v>250</v>
       </c>
       <c r="C42" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>251</v>
@@ -12112,10 +12218,10 @@
         <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C43" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>252</v>
@@ -12126,10 +12232,10 @@
         <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C44" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>253</v>
@@ -12143,7 +12249,7 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>254</v>
@@ -12157,7 +12263,7 @@
         <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>256</v>
@@ -12171,10 +12277,10 @@
         <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D47" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12185,7 +12291,7 @@
         <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>257</v>
@@ -12199,10 +12305,10 @@
         <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12213,7 +12319,7 @@
         <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>259</v>
@@ -12227,7 +12333,7 @@
         <v>260</v>
       </c>
       <c r="C51" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>261</v>
@@ -12241,7 +12347,7 @@
         <v>262</v>
       </c>
       <c r="C52" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>263</v>
@@ -12255,7 +12361,7 @@
         <v>264</v>
       </c>
       <c r="C53" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>265</v>
@@ -12269,7 +12375,7 @@
         <v>266</v>
       </c>
       <c r="C54" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>267</v>
@@ -12283,7 +12389,7 @@
         <v>268</v>
       </c>
       <c r="C55" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>269</v>
@@ -12297,7 +12403,7 @@
         <v>270</v>
       </c>
       <c r="C56" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>271</v>
@@ -12311,7 +12417,7 @@
         <v>272</v>
       </c>
       <c r="C57" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>273</v>
@@ -12325,7 +12431,7 @@
         <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>275</v>
@@ -12339,7 +12445,7 @@
         <v>276</v>
       </c>
       <c r="C59" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>277</v>
@@ -12353,7 +12459,7 @@
         <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>281</v>
@@ -12367,7 +12473,7 @@
         <v>284</v>
       </c>
       <c r="C61" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>283</v>
@@ -12381,7 +12487,7 @@
         <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>318</v>
@@ -12395,7 +12501,7 @@
         <v>319</v>
       </c>
       <c r="C63" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>320</v>
@@ -12409,7 +12515,7 @@
         <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>321</v>
@@ -12423,10 +12529,10 @@
         <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12434,10 +12540,10 @@
         <v>507</v>
       </c>
       <c r="B66" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C66" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>286</v>
@@ -12451,7 +12557,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>287</v>
@@ -12462,10 +12568,10 @@
         <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C68" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>322</v>
@@ -12476,13 +12582,13 @@
         <v>510</v>
       </c>
       <c r="B69" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C69" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D69" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12493,7 +12599,7 @@
         <v>333</v>
       </c>
       <c r="C70" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>242</v>
@@ -12507,7 +12613,7 @@
         <v>335</v>
       </c>
       <c r="C71" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>242</v>
@@ -12518,10 +12624,10 @@
         <v>336</v>
       </c>
       <c r="B72" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="C72" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>242</v>
@@ -12535,7 +12641,7 @@
         <v>338</v>
       </c>
       <c r="C73" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>242</v>
@@ -12549,7 +12655,7 @@
         <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>242</v>
@@ -12563,7 +12669,7 @@
         <v>341</v>
       </c>
       <c r="C75" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>242</v>
@@ -12577,7 +12683,7 @@
         <v>343</v>
       </c>
       <c r="C76" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>242</v>
@@ -12591,7 +12697,7 @@
         <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>242</v>
@@ -12602,10 +12708,10 @@
         <v>345</v>
       </c>
       <c r="B78" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C78" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>242</v>
@@ -12616,10 +12722,10 @@
         <v>346</v>
       </c>
       <c r="B79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C79" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>242</v>
@@ -12630,10 +12736,10 @@
         <v>315</v>
       </c>
       <c r="B80" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C80" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>242</v>
@@ -12644,10 +12750,10 @@
         <v>347</v>
       </c>
       <c r="B81" t="s">
+        <v>494</v>
+      </c>
+      <c r="C81" t="s">
         <v>496</v>
-      </c>
-      <c r="C81" t="s">
-        <v>498</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>242</v>
@@ -12661,7 +12767,7 @@
         <v>349</v>
       </c>
       <c r="C82" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>242</v>
@@ -12675,7 +12781,7 @@
         <v>351</v>
       </c>
       <c r="C83" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>242</v>
@@ -12689,7 +12795,7 @@
         <v>158</v>
       </c>
       <c r="C84" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>242</v>
@@ -12703,7 +12809,7 @@
         <v>354</v>
       </c>
       <c r="C85" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>242</v>
@@ -12717,7 +12823,7 @@
         <v>356</v>
       </c>
       <c r="C86" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>242</v>
@@ -12731,7 +12837,7 @@
         <v>358</v>
       </c>
       <c r="C87" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>242</v>
@@ -12745,7 +12851,7 @@
         <v>360</v>
       </c>
       <c r="C88" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>242</v>
@@ -12759,7 +12865,7 @@
         <v>358</v>
       </c>
       <c r="C89" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>244</v>
@@ -12773,7 +12879,7 @@
         <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>244</v>
@@ -12784,10 +12890,10 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="C91" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>251</v>
@@ -12801,7 +12907,7 @@
         <v>101</v>
       </c>
       <c r="C92" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>256</v>
@@ -12809,13 +12915,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B93" t="s">
         <v>240</v>
       </c>
       <c r="C93" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>196</v>
@@ -12823,13 +12929,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B94" t="s">
         <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>259</v>
@@ -12843,7 +12949,7 @@
         <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>202</v>
@@ -12857,7 +12963,7 @@
         <v>324</v>
       </c>
       <c r="C96" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>281</v>
@@ -12871,7 +12977,7 @@
         <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>281</v>
@@ -12885,7 +12991,7 @@
         <v>62</v>
       </c>
       <c r="C98" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>281</v>
@@ -12899,7 +13005,7 @@
         <v>326</v>
       </c>
       <c r="C99" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>281</v>
@@ -12913,7 +13019,7 @@
         <v>328</v>
       </c>
       <c r="C100" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>281</v>
@@ -12927,7 +13033,7 @@
         <v>330</v>
       </c>
       <c r="C101" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>281</v>
@@ -12941,7 +13047,7 @@
         <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>281</v>
@@ -12955,7 +13061,7 @@
         <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>281</v>
@@ -12969,7 +13075,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>281</v>
@@ -12980,10 +13086,10 @@
         <v>331</v>
       </c>
       <c r="B105" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C105" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>281</v>
@@ -12997,7 +13103,7 @@
         <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>281</v>
@@ -13008,10 +13114,10 @@
         <v>299</v>
       </c>
       <c r="B107" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C107" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>281</v>
@@ -13022,10 +13128,10 @@
         <v>300</v>
       </c>
       <c r="B108" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C108" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>281</v>
@@ -13039,7 +13145,7 @@
         <v>158</v>
       </c>
       <c r="C109" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>281</v>
@@ -13053,7 +13159,7 @@
         <v>33</v>
       </c>
       <c r="C110" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>281</v>
@@ -13067,7 +13173,7 @@
         <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>178</v>
@@ -13081,7 +13187,7 @@
         <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>180</v>
@@ -13089,391 +13195,391 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B113" t="s">
         <v>403</v>
       </c>
-      <c r="B113" t="s">
-        <v>404</v>
-      </c>
       <c r="C113" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D113" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B114" t="s">
         <v>360</v>
       </c>
       <c r="C114" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D114" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B115" t="s">
         <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D115" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B116" t="s">
         <v>333</v>
       </c>
       <c r="C116" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D116" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B117" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D117" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B118" t="s">
         <v>140</v>
       </c>
       <c r="C118" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D118" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B119" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C119" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D119" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B120" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C120" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D120" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B121" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C121" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D121" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B122" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C122" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D122" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B123" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D123" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B124" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C124" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D124" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B125" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C125" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D125" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B126" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C126" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D126" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B127" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C127" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D127" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B128" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D128" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B129" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C129" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D129" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B130" t="s">
         <v>453</v>
       </c>
-      <c r="B130" t="s">
-        <v>454</v>
-      </c>
       <c r="C130" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D130" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B131" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C131" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D131" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B132" t="s">
         <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D132" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="B133" t="s">
         <v>487</v>
       </c>
-      <c r="B133" t="s">
-        <v>489</v>
-      </c>
       <c r="C133" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D133" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B134" t="s">
+        <v>529</v>
+      </c>
+      <c r="C134" t="s">
+        <v>505</v>
+      </c>
+      <c r="D134" t="s">
         <v>530</v>
-      </c>
-      <c r="B134" t="s">
-        <v>531</v>
-      </c>
-      <c r="C134" t="s">
-        <v>507</v>
-      </c>
-      <c r="D134" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B135" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="C135" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D135" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s">
+        <v>494</v>
+      </c>
+      <c r="C136" t="s">
         <v>496</v>
       </c>
-      <c r="C136" t="s">
-        <v>498</v>
-      </c>
       <c r="D136" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B137" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C137" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D137" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="B138" t="s">
+        <v>494</v>
+      </c>
+      <c r="C138" t="s">
         <v>496</v>
       </c>
-      <c r="C138" t="s">
-        <v>498</v>
-      </c>
       <c r="D138" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="B139" t="s">
+        <v>583</v>
+      </c>
+      <c r="C139" t="s">
+        <v>496</v>
+      </c>
+      <c r="D139" t="s">
         <v>561</v>
-      </c>
-      <c r="B139" t="s">
-        <v>586</v>
-      </c>
-      <c r="C139" t="s">
-        <v>498</v>
-      </c>
-      <c r="D139" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B140" t="s">
         <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D140" t="s">
         <v>239</v>
@@ -13481,142 +13587,156 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B141" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C141" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D141" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B142" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="C142" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D142" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="B143" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C143" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D143" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B144" t="s">
         <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D144" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B145" t="s">
         <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D145" s="27" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B146" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C146" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D146" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B147" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C147" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D147" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B148" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C148" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D148" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B149" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C149" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D149" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B150" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C150" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D150" t="s">
-        <v>692</v>
+        <v>688</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="B151" t="s">
+        <v>848</v>
+      </c>
+      <c r="C151" t="s">
+        <v>505</v>
+      </c>
+      <c r="D151" t="s">
+        <v>841</v>
       </c>
     </row>
   </sheetData>
@@ -13980,7 +14100,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -13988,8 +14108,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -14006,50 +14126,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A50D6C-33DF-4575-B81D-61EF595F3118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6DB41B-B7DB-4BEA-8598-580486DF1DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="34395" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4543" yWindow="13611" windowWidth="24891" windowHeight="14915" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="848">
   <si>
     <t>id</t>
   </si>
@@ -1526,9 +1526,6 @@
     <t>38</t>
   </si>
   <si>
-    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; 511k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r</t>
-  </si>
-  <si>
     <t>Meta</t>
   </si>
   <si>
@@ -2253,9 +2250,6 @@
     <t>Availability; Latency; Performance; Scalability</t>
   </si>
   <si>
-    <t>505</t>
-  </si>
-  <si>
     <t>Tool Sentiment Score</t>
   </si>
   <si>
@@ -2550,9 +2544,6 @@
     <t>AI-Written Code Share</t>
   </si>
   <si>
-    <t>Developer CSAT; Developer Satisfaction Score; Developer Sentiment; Developer Survey with a Focus on Perceptions of Friction; DSAT (Developer Satisfaction); Employee satisfaction; Net User Satisfaction (NSAT); Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; Developer Ratings for the New System; AI tool CSAT</t>
-  </si>
-  <si>
     <t>155; 162</t>
   </si>
   <si>
@@ -2593,6 +2584,12 @@
   </si>
   <si>
     <t>Microsoft EngThrive Framework</t>
+  </si>
+  <si>
+    <t>501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r</t>
+  </si>
+  <si>
+    <t>CSAT; DSAT; NSAT; Satisfaction Score; Developer Sentiment; Developer Satisfaction; Employee satisfaction; Net User Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; AI tool CSAT</t>
   </si>
 </sst>
 </file>
@@ -2690,7 +2687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2755,14 +2752,8 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2790,66 +2781,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2925,16 +2856,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2970,16 +2891,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3030,6 +2941,96 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3193,16 +3194,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3214,10 +3205,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3483,7 +3470,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3524,7 +3510,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3554,16 +3540,16 @@
         <v>442</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S1" s="15" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2</v>
       </c>
@@ -3577,13 +3563,13 @@
         <v>441</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3619,16 +3605,16 @@
         <v>440</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -3648,7 +3634,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3684,36 +3670,36 @@
         <v>440</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>9</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>607</v>
+      <c r="B4" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>383</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3749,21 +3735,21 @@
         <v>440</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>10</v>
       </c>
-      <c r="B5" s="24" t="s">
-        <v>696</v>
+      <c r="B5" s="3" t="s">
+        <v>695</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -3772,13 +3758,13 @@
         <v>300</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>369</v>
@@ -3814,20 +3800,20 @@
         <v>440</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R5" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>11</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="27" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -3843,7 +3829,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3879,36 +3865,36 @@
         <v>440</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>12</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>459</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -3944,16 +3930,16 @@
         <v>93</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>13</v>
       </c>
@@ -3964,16 +3950,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -4009,36 +3995,36 @@
         <v>440</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>14</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -4074,36 +4060,36 @@
         <v>440</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>15</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>612</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>613</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>692</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>616</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -4139,16 +4125,16 @@
         <v>440</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R10" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>16</v>
       </c>
@@ -4168,7 +4154,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -4204,36 +4190,36 @@
         <v>440</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R11" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>696</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>698</v>
-      </c>
       <c r="D12" s="13" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>42</v>
@@ -4269,16 +4255,16 @@
         <v>440</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R12" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>18</v>
       </c>
@@ -4292,13 +4278,13 @@
         <v>475</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -4334,36 +4320,36 @@
         <v>93</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R13" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>19</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>46</v>
@@ -4399,21 +4385,21 @@
         <v>440</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R14" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>20</v>
       </c>
-      <c r="B15" s="24" t="s">
-        <v>701</v>
+      <c r="B15" s="3" t="s">
+        <v>700</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>162</v>
@@ -4422,13 +4408,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>369</v>
@@ -4464,21 +4450,21 @@
         <v>93</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>22</v>
       </c>
-      <c r="B16" s="26" t="s">
-        <v>702</v>
+      <c r="B16" s="4" t="s">
+        <v>701</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -4493,7 +4479,7 @@
         <v>49</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4529,21 +4515,21 @@
         <v>440</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R16" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>23</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>830</v>
+      <c r="B17" s="24" t="s">
+        <v>828</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>163</v>
@@ -4555,10 +4541,10 @@
         <v>289</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>42</v>
@@ -4594,16 +4580,16 @@
         <v>440</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R17" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>24</v>
       </c>
@@ -4623,7 +4609,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4659,24 +4645,24 @@
         <v>440</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R18" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>25</v>
       </c>
-      <c r="B19" s="24" t="s">
-        <v>828</v>
+      <c r="B19" s="3" t="s">
+        <v>826</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
@@ -4688,7 +4674,7 @@
         <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>56</v>
@@ -4724,21 +4710,21 @@
         <v>440</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R19" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>26</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>624</v>
+      <c r="B20" s="3" t="s">
+        <v>623</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>308</v>
@@ -4747,10 +4733,10 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>56</v>
@@ -4786,36 +4772,36 @@
         <v>440</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R20" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>27</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>461</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4851,36 +4837,36 @@
         <v>93</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R21" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>793</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>795</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>796</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -4916,20 +4902,20 @@
         <v>440</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R22" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>30</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="4" t="s">
@@ -4939,13 +4925,13 @@
         <v>465</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -4981,36 +4967,36 @@
         <v>93</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>31</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="3" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="F24" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
@@ -5046,21 +5032,21 @@
         <v>440</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R24" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -5075,7 +5061,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>56</v>
@@ -5111,20 +5097,20 @@
         <v>440</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R25" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>33</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="27" t="s">
         <v>64</v>
       </c>
       <c r="C26" s="4" t="s">
@@ -5140,7 +5126,7 @@
         <v>65</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5176,16 +5162,16 @@
         <v>440</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R26" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>34</v>
       </c>
@@ -5193,19 +5179,19 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>378</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5241,36 +5227,36 @@
         <v>440</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R27" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>36</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>834</v>
+        <v>847</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>493</v>
+        <v>846</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>369</v>
@@ -5292,7 +5278,7 @@
       </c>
       <c r="M28" s="3">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N28" s="3">
         <f t="shared" si="1"/>
@@ -5300,27 +5286,27 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="P28" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R28" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="165" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5335,7 +5321,7 @@
         <v>72</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>10</v>
@@ -5371,16 +5357,16 @@
         <v>440</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R29" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>38</v>
       </c>
@@ -5388,19 +5374,19 @@
         <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>473</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -5436,16 +5422,16 @@
         <v>93</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R30" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>39</v>
       </c>
@@ -5465,7 +5451,7 @@
         <v>75</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5501,10 +5487,10 @@
         <v>440</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
@@ -5524,13 +5510,13 @@
         <v>374</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>369</v>
@@ -5566,16 +5552,16 @@
         <v>93</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R32" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>41</v>
       </c>
@@ -5595,7 +5581,7 @@
         <v>79</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>369</v>
@@ -5631,16 +5617,16 @@
         <v>440</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R33" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>42</v>
       </c>
@@ -5648,19 +5634,19 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -5696,16 +5682,16 @@
         <v>440</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R34" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>43</v>
       </c>
@@ -5725,7 +5711,7 @@
         <v>83</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>369</v>
@@ -5761,16 +5747,16 @@
         <v>440</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R35" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>44</v>
       </c>
@@ -5778,10 +5764,10 @@
         <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>379</v>
@@ -5790,7 +5776,7 @@
         <v>87</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
@@ -5826,20 +5812,20 @@
         <v>93</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R36" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="3" t="s">
         <v>89</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -5849,13 +5835,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5891,24 +5877,24 @@
         <v>440</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R37" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46</v>
       </c>
-      <c r="B38" s="24" t="s">
-        <v>716</v>
+      <c r="B38" s="3" t="s">
+        <v>715</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
@@ -5917,10 +5903,10 @@
         <v>317</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>42</v>
@@ -5956,36 +5942,36 @@
         <v>93</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R38" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>50</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>567</v>
-      </c>
       <c r="D39" s="12" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E39" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>526</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>369</v>
@@ -6021,20 +6007,20 @@
         <v>440</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R39" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>56</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="27" t="s">
         <v>93</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -6050,7 +6036,7 @@
         <v>94</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>369</v>
@@ -6086,16 +6072,16 @@
         <v>440</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R40" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S40" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>57</v>
       </c>
@@ -6115,7 +6101,7 @@
         <v>96</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>10</v>
@@ -6151,16 +6137,16 @@
         <v>440</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R41" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="210" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>58</v>
       </c>
@@ -6177,10 +6163,10 @@
         <v>397</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>369</v>
@@ -6216,24 +6202,24 @@
         <v>93</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R42" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>59</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>719</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>720</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
@@ -6245,7 +6231,7 @@
         <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>369</v>
@@ -6281,36 +6267,36 @@
         <v>93</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R43" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>62</v>
       </c>
-      <c r="B44" s="25" t="s">
+      <c r="B44" s="24" t="s">
+        <v>594</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>760</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>761</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="C44" s="5" t="s">
-        <v>764</v>
-      </c>
-      <c r="D44" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="E44" s="13" t="s">
-        <v>763</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>596</v>
-      </c>
       <c r="G44" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6346,20 +6332,20 @@
         <v>440</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R44" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>63</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -6375,7 +6361,7 @@
         <v>102</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -6411,20 +6397,20 @@
         <v>93</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R45" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>64</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="3" t="s">
         <v>103</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -6437,10 +6423,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -6476,24 +6462,24 @@
         <v>440</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R46" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>65</v>
       </c>
-      <c r="B47" s="24" t="s">
+      <c r="B47" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>466</v>
@@ -6505,7 +6491,7 @@
         <v>105</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -6541,21 +6527,21 @@
         <v>440</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R47" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>67</v>
       </c>
-      <c r="B48" s="26" t="s">
-        <v>515</v>
+      <c r="B48" s="4" t="s">
+        <v>514</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
@@ -6570,7 +6556,7 @@
         <v>106</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>42</v>
@@ -6606,24 +6592,24 @@
         <v>440</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R48" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>69</v>
       </c>
-      <c r="B49" s="25" t="s">
+      <c r="B49" s="24" t="s">
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>293</v>
@@ -6635,7 +6621,7 @@
         <v>108</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>56</v>
@@ -6671,36 +6657,36 @@
         <v>440</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R49" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>70</v>
       </c>
-      <c r="B50" s="24" t="s">
+      <c r="B50" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>786</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>787</v>
       </c>
-      <c r="D50" s="12" t="s">
-        <v>788</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>789</v>
-      </c>
       <c r="F50" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -6736,21 +6722,21 @@
         <v>440</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R50" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>71</v>
       </c>
-      <c r="B51" s="24" t="s">
-        <v>602</v>
+      <c r="B51" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>92</v>
@@ -6759,13 +6745,13 @@
         <v>300</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -6801,21 +6787,21 @@
         <v>440</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R51" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>72</v>
       </c>
-      <c r="B52" s="26" t="s">
-        <v>608</v>
+      <c r="B52" s="4" t="s">
+        <v>607</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
@@ -6827,10 +6813,10 @@
         <v>302</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>10</v>
@@ -6866,20 +6852,20 @@
         <v>440</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R52" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>73</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="26" t="s">
         <v>111</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -6895,7 +6881,7 @@
         <v>112</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -6931,24 +6917,24 @@
         <v>440</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R53" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S53" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>75</v>
       </c>
-      <c r="B54" s="24" t="s">
-        <v>824</v>
-      </c>
-      <c r="C54" s="24" t="s">
-        <v>632</v>
+      <c r="B54" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>631</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>361</v>
@@ -6957,10 +6943,10 @@
         <v>183</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -6996,33 +6982,33 @@
         <v>440</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R54" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>76</v>
       </c>
-      <c r="B55" s="24" t="s">
-        <v>724</v>
+      <c r="B55" s="3" t="s">
+        <v>723</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -7058,16 +7044,16 @@
         <v>440</v>
       </c>
       <c r="Q55" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R55" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>78</v>
       </c>
@@ -7084,10 +7070,10 @@
         <v>389</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>369</v>
@@ -7123,16 +7109,16 @@
         <v>93</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R56" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>79</v>
       </c>
@@ -7146,13 +7132,13 @@
         <v>299</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
@@ -7188,16 +7174,16 @@
         <v>93</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R57" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>80</v>
       </c>
@@ -7217,7 +7203,7 @@
         <v>119</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>56</v>
@@ -7253,21 +7239,21 @@
         <v>440</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R58" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>120</v>
@@ -7282,7 +7268,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -7318,20 +7304,20 @@
         <v>440</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R59" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>83</v>
       </c>
-      <c r="B60" s="26" t="s">
+      <c r="B60" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -7341,13 +7327,13 @@
         <v>468</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>369</v>
@@ -7383,36 +7369,36 @@
         <v>93</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R60" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>87</v>
       </c>
-      <c r="B61" s="24" t="s">
+      <c r="B61" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>15</v>
@@ -7448,36 +7434,36 @@
         <v>440</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R61" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>88</v>
       </c>
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>725</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>726</v>
-      </c>
       <c r="D62" s="10" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>288</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -7513,36 +7499,36 @@
         <v>440</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R62" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>89</v>
       </c>
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="3" t="s">
         <v>125</v>
       </c>
       <c r="C63" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>608</v>
+      </c>
+      <c r="E63" s="13" t="s">
+        <v>659</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="D63" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>660</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>612</v>
-      </c>
       <c r="G63" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -7575,13 +7561,13 @@
         <v>8</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R63" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
@@ -7591,7 +7577,7 @@
       <c r="A64" s="3">
         <v>90</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -7601,13 +7587,13 @@
         <v>463</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -7643,16 +7629,16 @@
         <v>93</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R64" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>91</v>
       </c>
@@ -7672,7 +7658,7 @@
         <v>128</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7708,16 +7694,16 @@
         <v>440</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R65" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>92</v>
       </c>
@@ -7737,7 +7723,7 @@
         <v>130</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>42</v>
@@ -7773,16 +7759,16 @@
         <v>440</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R66" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>93</v>
       </c>
@@ -7802,7 +7788,7 @@
         <v>132</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>10</v>
@@ -7838,20 +7824,20 @@
         <v>440</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R67" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>94</v>
       </c>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C68" s="4" t="s">
@@ -7864,10 +7850,10 @@
         <v>309</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>56</v>
@@ -7903,36 +7889,36 @@
         <v>440</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R68" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="24">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+      <c r="A69" s="3">
         <v>95</v>
       </c>
-      <c r="B69" s="24" t="s">
-        <v>749</v>
+      <c r="B69" s="3" t="s">
+        <v>747</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>361</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>735</v>
+        <v>9</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>21</v>
@@ -7950,7 +7936,7 @@
       </c>
       <c r="L69" s="3">
         <f>IF(E69="-",0,1)+IF(D69="-",0,2)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M69" s="3">
         <f>IF(D69="-",0,LEN(D69)-LEN(SUBSTITUTE(D69,";",""))+1)</f>
@@ -7958,26 +7944,26 @@
       </c>
       <c r="N69" s="3">
         <f>IF(E69="-",0,LEN(E69)-LEN(SUBSTITUTE(E69,";",""))+1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="3">
         <f>SUM(M69:N69)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" s="12" t="s">
         <v>440</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R69" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>97</v>
       </c>
@@ -7997,7 +7983,7 @@
         <v>135</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -8033,21 +8019,21 @@
         <v>440</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R70" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>98</v>
       </c>
-      <c r="B71" s="24" t="s">
-        <v>729</v>
+      <c r="B71" s="3" t="s">
+        <v>728</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>168</v>
@@ -8062,7 +8048,7 @@
         <v>136</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -8098,21 +8084,21 @@
         <v>440</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R71" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>99</v>
       </c>
-      <c r="B72" s="24" t="s">
-        <v>730</v>
+      <c r="B72" s="3" t="s">
+        <v>729</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8124,10 +8110,10 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -8163,16 +8149,16 @@
         <v>440</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R72" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S72" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>100</v>
       </c>
@@ -8192,7 +8178,7 @@
         <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>10</v>
@@ -8228,36 +8214,36 @@
         <v>440</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R73" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>102</v>
       </c>
-      <c r="B74" s="24" t="s">
-        <v>634</v>
-      </c>
-      <c r="C74" s="24" t="s">
+      <c r="B74" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="C74" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E74" s="13">
         <v>501</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>15</v>
@@ -8293,21 +8279,21 @@
         <v>440</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R74" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>104</v>
       </c>
-      <c r="B75" s="24" t="s">
-        <v>736</v>
+      <c r="B75" s="3" t="s">
+        <v>734</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
@@ -8319,10 +8305,10 @@
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>369</v>
@@ -8358,10 +8344,10 @@
         <v>440</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R75" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
@@ -8371,7 +8357,7 @@
       <c r="A76" s="3">
         <v>107</v>
       </c>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="27" t="s">
         <v>141</v>
       </c>
       <c r="C76" s="4" t="s">
@@ -8381,13 +8367,13 @@
         <v>375</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>142</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8423,27 +8409,27 @@
         <v>440</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R76" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>108</v>
       </c>
       <c r="B77" s="18" t="s">
+        <v>586</v>
+      </c>
+      <c r="C77" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>588</v>
-      </c>
       <c r="D77" s="12" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>307</v>
@@ -8452,7 +8438,7 @@
         <v>143</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -8488,36 +8474,36 @@
         <v>440</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R77" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="24">
+    <row r="78" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+      <c r="A78" s="3">
         <v>109</v>
       </c>
-      <c r="B78" s="24" t="s">
-        <v>739</v>
+      <c r="B78" s="3" t="s">
+        <v>737</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>311</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8553,20 +8539,20 @@
         <v>440</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R78" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>112</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="3" t="s">
         <v>144</v>
       </c>
       <c r="C79" s="4" t="s">
@@ -8576,13 +8562,13 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>369</v>
@@ -8618,21 +8604,21 @@
         <v>93</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R79" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>113</v>
       </c>
-      <c r="B80" s="24" t="s">
-        <v>755</v>
+      <c r="B80" s="3" t="s">
+        <v>753</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>491</v>
@@ -8644,10 +8630,10 @@
         <v>479</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>369</v>
@@ -8683,36 +8669,36 @@
         <v>93</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R80" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>114</v>
       </c>
-      <c r="B81" s="24" t="s">
-        <v>631</v>
+      <c r="B81" s="3" t="s">
+        <v>630</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>46</v>
@@ -8748,24 +8734,24 @@
         <v>93</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R81" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>115</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="3" t="s">
         <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8774,10 +8760,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>42</v>
@@ -8813,27 +8799,27 @@
         <v>440</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R82" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>116</v>
       </c>
-      <c r="B83" s="24" t="s">
+      <c r="B83" s="3" t="s">
         <v>147</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>312</v>
@@ -8842,7 +8828,7 @@
         <v>148</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>30</v>
@@ -8878,27 +8864,27 @@
         <v>440</v>
       </c>
       <c r="Q83" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R83" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S83" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>117</v>
       </c>
-      <c r="B84" s="24" t="s">
+      <c r="B84" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>313</v>
@@ -8907,7 +8893,7 @@
         <v>150</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>30</v>
@@ -8943,20 +8929,20 @@
         <v>93</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R84" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>118</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B85" s="3" t="s">
         <v>151</v>
       </c>
       <c r="C85" s="4" t="s">
@@ -8972,7 +8958,7 @@
         <v>152</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>21</v>
@@ -9008,24 +8994,24 @@
         <v>440</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R85" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>300</v>
@@ -9034,10 +9020,10 @@
         <v>302</v>
       </c>
       <c r="F86" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -9073,20 +9059,20 @@
         <v>440</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R86" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>121</v>
       </c>
-      <c r="B87" s="29" t="s">
+      <c r="B87" s="27" t="s">
         <v>154</v>
       </c>
       <c r="C87" s="4" t="s">
@@ -9096,13 +9082,13 @@
         <v>469</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>15</v>
@@ -9138,36 +9124,36 @@
         <v>93</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R87" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>122</v>
       </c>
-      <c r="B88" s="24" t="s">
+      <c r="B88" s="3" t="s">
         <v>156</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D88" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="E88" s="13" t="s">
         <v>654</v>
       </c>
-      <c r="E88" s="13" t="s">
-        <v>655</v>
-      </c>
       <c r="F88" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -9203,36 +9189,36 @@
         <v>93</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R88" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>124</v>
       </c>
-      <c r="B89" s="24" t="s">
+      <c r="B89" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="C89" s="4" t="s">
-        <v>599</v>
-      </c>
       <c r="D89" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="E89" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="E89" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>623</v>
-      </c>
       <c r="G89" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>369</v>
@@ -9268,24 +9254,24 @@
         <v>440</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R89" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>126</v>
       </c>
-      <c r="B90" s="26" t="s">
-        <v>826</v>
+      <c r="B90" s="4" t="s">
+        <v>824</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>297</v>
@@ -9294,10 +9280,10 @@
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>46</v>
@@ -9333,36 +9319,36 @@
         <v>440</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R90" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>127</v>
       </c>
-      <c r="B91" s="26" t="s">
-        <v>823</v>
+      <c r="B91" s="4" t="s">
+        <v>821</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>169</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>46</v>
@@ -9398,24 +9384,24 @@
         <v>440</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R91" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>128</v>
       </c>
-      <c r="B92" s="26" t="s">
-        <v>816</v>
-      </c>
-      <c r="C92" s="26" t="s">
-        <v>817</v>
+      <c r="B92" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>815</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>301</v>
@@ -9424,10 +9410,10 @@
         <v>501</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>46</v>
@@ -9463,24 +9449,24 @@
         <v>440</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R92" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>129</v>
       </c>
-      <c r="B93" s="26" t="s">
+      <c r="B93" s="4" t="s">
         <v>457</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>458</v>
@@ -9489,10 +9475,10 @@
         <v>483</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>46</v>
@@ -9528,24 +9514,24 @@
         <v>93</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R93" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>130</v>
       </c>
-      <c r="B94" s="24" t="s">
-        <v>592</v>
+      <c r="B94" s="3" t="s">
+        <v>591</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>376</v>
@@ -9554,10 +9540,10 @@
         <v>377</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>776</v>
-      </c>
-      <c r="G94" s="24" t="s">
-        <v>522</v>
+        <v>774</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>521</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>369</v>
@@ -9593,36 +9579,36 @@
         <v>440</v>
       </c>
       <c r="Q94" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R94" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S94" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="24">
+    <row r="95" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="3">
         <v>133</v>
       </c>
-      <c r="B95" s="24" t="s">
+      <c r="B95" s="3" t="s">
+        <v>775</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="13" t="s">
         <v>777</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="F95" s="4" t="s">
         <v>778</v>
       </c>
-      <c r="D95" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>779</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="G95" s="24" t="s">
-        <v>523</v>
+      <c r="G95" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>30</v>
@@ -9658,36 +9644,36 @@
         <v>93</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R95" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S95" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="3">
+        <v>134</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="96" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="24">
-        <v>134</v>
-      </c>
-      <c r="B96" s="24" t="s">
+      <c r="C96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>782</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C96" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>784</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>785</v>
-      </c>
-      <c r="G96" s="24" t="s">
-        <v>523</v>
+      <c r="G96" s="3" t="s">
+        <v>522</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>30</v>
@@ -9723,20 +9709,20 @@
         <v>93</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R96" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S96" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>135</v>
       </c>
-      <c r="B97" s="26" t="s">
+      <c r="B97" s="4" t="s">
         <v>170</v>
       </c>
       <c r="C97" s="4" t="s">
@@ -9752,7 +9738,7 @@
         <v>365</v>
       </c>
       <c r="G97" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H97" t="s">
         <v>369</v>
@@ -9788,20 +9774,20 @@
         <v>440</v>
       </c>
       <c r="Q97" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R97" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>137</v>
       </c>
-      <c r="B98" s="30" t="s">
+      <c r="B98" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C98" s="4" t="s">
@@ -9810,14 +9796,14 @@
       <c r="D98" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E98" s="31" t="s">
+      <c r="E98" s="29" t="s">
         <v>173</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>366</v>
       </c>
       <c r="G98" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H98" t="s">
         <v>369</v>
@@ -9853,24 +9839,24 @@
         <v>440</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R98" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>138</v>
       </c>
-      <c r="B99" s="26" t="s">
-        <v>799</v>
+      <c r="B99" s="4" t="s">
+        <v>797</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9882,7 +9868,7 @@
         <v>364</v>
       </c>
       <c r="G99" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -9918,16 +9904,16 @@
         <v>440</v>
       </c>
       <c r="Q99" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R99" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>139</v>
       </c>
@@ -9947,7 +9933,7 @@
         <v>394</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>21</v>
@@ -9983,24 +9969,24 @@
         <v>440</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R100" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>140</v>
       </c>
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="3" t="s">
         <v>432</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D101" s="12" t="s">
         <v>454</v>
@@ -10012,7 +9998,7 @@
         <v>433</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>15</v>
@@ -10048,36 +10034,36 @@
         <v>435</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R101" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S101" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>141</v>
       </c>
-      <c r="B102" s="24" t="s">
-        <v>832</v>
-      </c>
-      <c r="C102" s="24" t="s">
-        <v>661</v>
+      <c r="B102" s="3" t="s">
+        <v>830</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>660</v>
       </c>
       <c r="D102" s="12" t="s">
         <v>438</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>437</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>46</v>
@@ -10087,7 +10073,7 @@
         <v>207</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K102" s="3">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10113,36 +10099,36 @@
         <v>435</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R102" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S102" s="12">
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>142</v>
       </c>
-      <c r="B103" s="24" t="s">
-        <v>833</v>
-      </c>
-      <c r="C103" s="24" t="s">
-        <v>662</v>
+      <c r="B103" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>661</v>
       </c>
       <c r="D103" s="12" t="s">
         <v>415</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>439</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>46</v>
@@ -10152,7 +10138,7 @@
         <v>207</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K103" s="3">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10178,24 +10164,24 @@
         <v>435</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R103" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S103" s="12">
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>143</v>
       </c>
-      <c r="B104" s="24" t="s">
-        <v>831</v>
-      </c>
-      <c r="C104" s="24" t="s">
-        <v>820</v>
+      <c r="B104" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>818</v>
       </c>
       <c r="D104" s="12" t="s">
         <v>443</v>
@@ -10204,10 +10190,10 @@
         <v>9</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>46</v>
@@ -10217,7 +10203,7 @@
         <v>207</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10243,21 +10229,21 @@
         <v>435</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R104" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>144</v>
       </c>
-      <c r="B105" s="24" t="s">
-        <v>822</v>
+      <c r="B105" s="3" t="s">
+        <v>820</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -10272,7 +10258,7 @@
         <v>446</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10308,24 +10294,24 @@
         <v>444</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R105" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S105" s="12" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>145</v>
       </c>
-      <c r="B106" s="24" t="s">
-        <v>821</v>
+      <c r="B106" s="3" t="s">
+        <v>819</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>424</v>
@@ -10337,7 +10323,7 @@
         <v>447</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -10373,24 +10359,24 @@
         <v>444</v>
       </c>
       <c r="Q106" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R106" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S106" s="12" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>146</v>
       </c>
-      <c r="B107" s="24" t="s">
+      <c r="B107" s="3" t="s">
         <v>445</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D107" t="s">
         <v>449</v>
@@ -10402,7 +10388,7 @@
         <v>451</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -10438,24 +10424,24 @@
         <v>444</v>
       </c>
       <c r="Q107" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R107" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S107" s="12" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>147</v>
       </c>
-      <c r="B108" s="24" t="s">
-        <v>819</v>
-      </c>
-      <c r="C108" s="24" t="s">
-        <v>818</v>
+      <c r="B108" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>816</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>452</v>
@@ -10464,10 +10450,10 @@
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>15</v>
@@ -10503,21 +10489,21 @@
         <v>435</v>
       </c>
       <c r="Q108" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R108" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S108" s="12" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>148</v>
       </c>
-      <c r="B109" s="24" t="s">
-        <v>804</v>
+      <c r="B109" s="3" t="s">
+        <v>802</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>484</v>
@@ -10532,7 +10518,7 @@
         <v>455</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>10</v>
@@ -10568,24 +10554,24 @@
         <v>93</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R109" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S109" s="12" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>149</v>
       </c>
-      <c r="B110" s="24" t="s">
-        <v>805</v>
+      <c r="B110" s="3" t="s">
+        <v>803</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>470</v>
@@ -10594,10 +10580,10 @@
         <v>479</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>21</v>
@@ -10633,10 +10619,10 @@
         <v>93</v>
       </c>
       <c r="Q110" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R110" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S110" s="12" t="s">
         <v>464</v>
@@ -10646,23 +10632,23 @@
       <c r="A111" s="3">
         <v>150</v>
       </c>
-      <c r="B111" s="24" t="s">
+      <c r="B111" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>583</v>
+      </c>
+      <c r="E111" s="13" t="s">
+        <v>834</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>807</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>584</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>837</v>
-      </c>
-      <c r="F111" s="4" t="s">
-        <v>809</v>
-      </c>
       <c r="G111" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>369</v>
@@ -10698,20 +10684,20 @@
         <v>93</v>
       </c>
       <c r="Q111" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R111" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S111" s="12" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>151</v>
       </c>
-      <c r="B112" s="24" t="s">
+      <c r="B112" s="3" t="s">
         <v>481</v>
       </c>
       <c r="C112" s="4" t="s">
@@ -10727,7 +10713,7 @@
         <v>482</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10763,21 +10749,21 @@
         <v>93</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R112" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S112" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>152</v>
       </c>
-      <c r="B113" s="24" t="s">
-        <v>663</v>
+      <c r="B113" s="3" t="s">
+        <v>662</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
@@ -10792,7 +10778,7 @@
         <v>488</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>369</v>
@@ -10828,21 +10814,21 @@
         <v>93</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R113" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S113" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>153</v>
       </c>
-      <c r="B114" s="24" t="s">
-        <v>814</v>
+      <c r="B114" s="3" t="s">
+        <v>812</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10857,7 +10843,7 @@
         <v>490</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>369</v>
@@ -10893,24 +10879,24 @@
         <v>93</v>
       </c>
       <c r="Q114" s="12" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="R114" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S114" s="12" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>154</v>
       </c>
-      <c r="B115" s="24" t="s">
-        <v>811</v>
+      <c r="B115" s="3" t="s">
+        <v>809</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
@@ -10919,10 +10905,10 @@
         <v>485</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>369</v>
@@ -10958,36 +10944,36 @@
         <v>93</v>
       </c>
       <c r="Q115" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R115" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S115" s="12" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="105" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>155</v>
       </c>
-      <c r="B116" s="24" t="s">
+      <c r="B116" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F116" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>540</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>539</v>
-      </c>
       <c r="G116" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>369</v>
@@ -11023,36 +11009,36 @@
         <v>440</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R116" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>156</v>
       </c>
-      <c r="B117" s="24" t="s">
+      <c r="B117" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>541</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>542</v>
-      </c>
       <c r="D117" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="E117" s="13" t="s">
         <v>545</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>546</v>
-      </c>
       <c r="F117" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>30</v>
@@ -11088,36 +11074,36 @@
         <v>440</v>
       </c>
       <c r="Q117" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R117" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>157</v>
       </c>
-      <c r="B118" s="24" t="s">
+      <c r="B118" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="C118" t="s">
         <v>550</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="D118" s="12" t="s">
-        <v>563</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>552</v>
-      </c>
       <c r="G118" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>369</v>
@@ -11153,24 +11139,24 @@
         <v>440</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R118" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="119" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>158</v>
       </c>
-      <c r="B119" s="24" t="s">
-        <v>810</v>
+      <c r="B119" s="3" t="s">
+        <v>808</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11179,10 +11165,10 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>30</v>
@@ -11218,36 +11204,36 @@
         <v>440</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R119" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S119" s="12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>159</v>
       </c>
-      <c r="B120" s="24" t="s">
-        <v>665</v>
+      <c r="B120" s="3" t="s">
+        <v>664</v>
       </c>
       <c r="C120" t="s">
+        <v>667</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E120" s="13" t="s">
+        <v>672</v>
+      </c>
+      <c r="F120" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="D120" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E120" s="13" t="s">
-        <v>673</v>
-      </c>
-      <c r="F120" s="4" t="s">
-        <v>669</v>
-      </c>
       <c r="G120" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11283,36 +11269,36 @@
         <v>440</v>
       </c>
       <c r="Q120" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R120" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="121" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>160</v>
       </c>
-      <c r="B121" s="24" t="s">
-        <v>666</v>
+      <c r="B121" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="C121" t="s">
+        <v>673</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E121" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="F121" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="D121" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E121" s="13" t="s">
-        <v>680</v>
-      </c>
-      <c r="F121" s="4" t="s">
-        <v>675</v>
-      </c>
       <c r="G121" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11348,36 +11334,36 @@
         <v>440</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R121" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S121" s="12" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="122" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>161</v>
       </c>
-      <c r="B122" s="24" t="s">
-        <v>667</v>
+      <c r="B122" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="C122" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="13" t="s">
         <v>681</v>
       </c>
-      <c r="D122" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="13" t="s">
+      <c r="F122" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="F122" s="4" t="s">
-        <v>683</v>
-      </c>
       <c r="G122" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>15</v>
@@ -11394,11 +11380,11 @@
         <v>314</v>
       </c>
       <c r="L122" s="3">
-        <f t="shared" ref="L122:L123" si="51">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
+        <f t="shared" ref="L122" si="51">IF(E122="-",0,1)+IF(D122="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M122" s="3">
-        <f t="shared" ref="M122:M123" si="52">IF(D122="-",0,LEN(D122)-LEN(SUBSTITUTE(D122,";",""))+1)</f>
+        <f t="shared" ref="M122" si="52">IF(D122="-",0,LEN(D122)-LEN(SUBSTITUTE(D122,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="N122" s="3">
@@ -11413,21 +11399,21 @@
         <v>440</v>
       </c>
       <c r="Q122" s="12" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="R122" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="S122" s="12" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
         <v>162</v>
       </c>
-      <c r="B123" s="24" t="s">
-        <v>836</v>
+      <c r="B123" s="3" t="s">
+        <v>833</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11436,13 +11422,13 @@
         <v>9</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>369</v>
@@ -11467,41 +11453,28 @@
         <v>0</v>
       </c>
       <c r="N123" s="3">
-        <f>IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
-        <v>0</v>
+        <f t="shared" si="53"/>
+        <v>1</v>
       </c>
       <c r="O123" s="3">
         <f t="shared" si="54"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P123" s="12" t="s">
         <v>440</v>
       </c>
       <c r="Q123" s="12" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R123" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="S123" s="12" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M123" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="501b; 5a; 522"/>
-        <filter val="501c; 501l; 501b; 501e; 501g; 501d; 5a; 522"/>
-        <filter val="501h; 516c; 522"/>
-        <filter val="501l;  501a;  202a; 501m; 501i; 501f; 501h; 170; 501d; 6a; 510; 511a; 511b; 511d; 511f; 511j; 511k; 511k; 511l; 511n; 511q; 511c; 511e; 511g; 511h; 511m; 511n; 511r; 522"/>
-        <filter val="501m; 522"/>
-        <filter val="501m; 5a; 511a; 511f; 522"/>
-        <filter val="511b; 511l; 516c; 522"/>
-        <filter val="522"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B4">
     <cfRule type="duplicateValues" dxfId="41" priority="30"/>
@@ -11539,75 +11512,75 @@
   <conditionalFormatting sqref="B63">
     <cfRule type="duplicateValues" dxfId="30" priority="16"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B75:B85 C74 B1:B73 B87:B99">
+    <cfRule type="duplicateValues" dxfId="29" priority="65"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B85">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B100:B1048576">
-    <cfRule type="duplicateValues" dxfId="28" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C54">
+    <cfRule type="duplicateValues" dxfId="26" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C92">
+    <cfRule type="duplicateValues" dxfId="25" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C102">
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C103">
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C104">
+    <cfRule type="duplicateValues" dxfId="22" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C108">
+    <cfRule type="duplicateValues" dxfId="21" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F5">
-    <cfRule type="duplicateValues" dxfId="27" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F33">
-    <cfRule type="duplicateValues" dxfId="26" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F43">
-    <cfRule type="duplicateValues" dxfId="25" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F62">
-    <cfRule type="duplicateValues" dxfId="23" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F70">
-    <cfRule type="duplicateValues" dxfId="22" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88">
-    <cfRule type="duplicateValues" dxfId="21" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
-    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J42">
-    <cfRule type="duplicateValues" dxfId="16" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J56">
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J60">
-    <cfRule type="duplicateValues" dxfId="12" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J94">
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C108">
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B75:B85 C74 B1:B73 B87:B99">
-    <cfRule type="duplicateValues" dxfId="7" priority="65"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C92">
-    <cfRule type="duplicateValues" dxfId="6" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C54">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C104">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C102">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C103">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11633,7 +11606,7 @@
         <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>280</v>
@@ -11647,7 +11620,7 @@
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D2" t="s">
         <v>178</v>
@@ -11661,7 +11634,7 @@
         <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D3" t="s">
         <v>180</v>
@@ -11675,7 +11648,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D4" t="s">
         <v>180</v>
@@ -11689,7 +11662,7 @@
         <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -11703,7 +11676,7 @@
         <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>184</v>
@@ -11717,7 +11690,7 @@
         <v>185</v>
       </c>
       <c r="C7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>186</v>
@@ -11731,7 +11704,7 @@
         <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>188</v>
@@ -11745,7 +11718,7 @@
         <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>190</v>
@@ -11759,7 +11732,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>192</v>
@@ -11773,7 +11746,7 @@
         <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>194</v>
@@ -11787,7 +11760,7 @@
         <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D12" t="s">
         <v>396</v>
@@ -11801,7 +11774,7 @@
         <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>196</v>
@@ -11815,7 +11788,7 @@
         <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>198</v>
@@ -11829,7 +11802,7 @@
         <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>200</v>
@@ -11843,7 +11816,7 @@
         <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>202</v>
@@ -11857,7 +11830,7 @@
         <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>204</v>
@@ -11871,7 +11844,7 @@
         <v>390</v>
       </c>
       <c r="C18" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D18" t="s">
         <v>395</v>
@@ -11885,7 +11858,7 @@
         <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>206</v>
@@ -11899,7 +11872,7 @@
         <v>207</v>
       </c>
       <c r="C20" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>208</v>
@@ -11913,7 +11886,7 @@
         <v>209</v>
       </c>
       <c r="C21" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>210</v>
@@ -11927,7 +11900,7 @@
         <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>212</v>
@@ -11941,7 +11914,7 @@
         <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>214</v>
@@ -11955,7 +11928,7 @@
         <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>216</v>
@@ -11969,7 +11942,7 @@
         <v>217</v>
       </c>
       <c r="C25" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>218</v>
@@ -11983,7 +11956,7 @@
         <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>220</v>
@@ -11997,7 +11970,7 @@
         <v>221</v>
       </c>
       <c r="C27" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>222</v>
@@ -12011,7 +11984,7 @@
         <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>224</v>
@@ -12025,7 +11998,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>226</v>
@@ -12039,7 +12012,7 @@
         <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>228</v>
@@ -12053,7 +12026,7 @@
         <v>400</v>
       </c>
       <c r="C31" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>229</v>
@@ -12067,7 +12040,7 @@
         <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>231</v>
@@ -12081,7 +12054,7 @@
         <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>233</v>
@@ -12095,7 +12068,7 @@
         <v>234</v>
       </c>
       <c r="C34" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>235</v>
@@ -12109,7 +12082,7 @@
         <v>236</v>
       </c>
       <c r="C35" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>237</v>
@@ -12123,7 +12096,7 @@
         <v>238</v>
       </c>
       <c r="C36" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>239</v>
@@ -12137,9 +12110,9 @@
         <v>241</v>
       </c>
       <c r="C37" t="s">
-        <v>505</v>
-      </c>
-      <c r="D37" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>242</v>
       </c>
     </row>
@@ -12151,7 +12124,7 @@
         <v>243</v>
       </c>
       <c r="C38" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>244</v>
@@ -12165,7 +12138,7 @@
         <v>245</v>
       </c>
       <c r="C39" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>246</v>
@@ -12179,7 +12152,7 @@
         <v>33</v>
       </c>
       <c r="C40" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>247</v>
@@ -12193,7 +12166,7 @@
         <v>248</v>
       </c>
       <c r="C41" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>249</v>
@@ -12207,7 +12180,7 @@
         <v>250</v>
       </c>
       <c r="C42" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>251</v>
@@ -12221,7 +12194,7 @@
         <v>398</v>
       </c>
       <c r="C43" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>252</v>
@@ -12235,7 +12208,7 @@
         <v>434</v>
       </c>
       <c r="C44" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>253</v>
@@ -12249,7 +12222,7 @@
         <v>19</v>
       </c>
       <c r="C45" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>254</v>
@@ -12263,7 +12236,7 @@
         <v>101</v>
       </c>
       <c r="C46" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>256</v>
@@ -12277,7 +12250,7 @@
         <v>360</v>
       </c>
       <c r="C47" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D47" t="s">
         <v>387</v>
@@ -12291,7 +12264,7 @@
         <v>157</v>
       </c>
       <c r="C48" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D48" s="8" t="s">
         <v>257</v>
@@ -12305,7 +12278,7 @@
         <v>258</v>
       </c>
       <c r="C49" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>399</v>
@@ -12319,7 +12292,7 @@
         <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>259</v>
@@ -12333,7 +12306,7 @@
         <v>260</v>
       </c>
       <c r="C51" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>261</v>
@@ -12347,7 +12320,7 @@
         <v>262</v>
       </c>
       <c r="C52" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>263</v>
@@ -12361,7 +12334,7 @@
         <v>264</v>
       </c>
       <c r="C53" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>265</v>
@@ -12375,7 +12348,7 @@
         <v>266</v>
       </c>
       <c r="C54" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>267</v>
@@ -12389,7 +12362,7 @@
         <v>268</v>
       </c>
       <c r="C55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>269</v>
@@ -12403,7 +12376,7 @@
         <v>270</v>
       </c>
       <c r="C56" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>271</v>
@@ -12417,7 +12390,7 @@
         <v>272</v>
       </c>
       <c r="C57" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>273</v>
@@ -12431,7 +12404,7 @@
         <v>274</v>
       </c>
       <c r="C58" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>275</v>
@@ -12445,7 +12418,7 @@
         <v>276</v>
       </c>
       <c r="C59" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>277</v>
@@ -12459,7 +12432,7 @@
         <v>282</v>
       </c>
       <c r="C60" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>281</v>
@@ -12473,7 +12446,7 @@
         <v>284</v>
       </c>
       <c r="C61" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>283</v>
@@ -12487,7 +12460,7 @@
         <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>318</v>
@@ -12501,7 +12474,7 @@
         <v>319</v>
       </c>
       <c r="C63" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>320</v>
@@ -12515,7 +12488,7 @@
         <v>285</v>
       </c>
       <c r="C64" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>321</v>
@@ -12529,10 +12502,10 @@
         <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -12543,7 +12516,7 @@
         <v>434</v>
       </c>
       <c r="C66" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D66" s="8" t="s">
         <v>286</v>
@@ -12557,7 +12530,7 @@
         <v>53</v>
       </c>
       <c r="C67" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>287</v>
@@ -12568,10 +12541,10 @@
         <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C68" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>322</v>
@@ -12585,7 +12558,7 @@
         <v>392</v>
       </c>
       <c r="C69" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D69" t="s">
         <v>391</v>
@@ -12599,7 +12572,7 @@
         <v>333</v>
       </c>
       <c r="C70" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>242</v>
@@ -12613,7 +12586,7 @@
         <v>335</v>
       </c>
       <c r="C71" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>242</v>
@@ -12624,10 +12597,10 @@
         <v>336</v>
       </c>
       <c r="B72" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C72" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>242</v>
@@ -12641,7 +12614,7 @@
         <v>338</v>
       </c>
       <c r="C73" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>242</v>
@@ -12655,7 +12628,7 @@
         <v>140</v>
       </c>
       <c r="C74" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>242</v>
@@ -12669,7 +12642,7 @@
         <v>341</v>
       </c>
       <c r="C75" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>242</v>
@@ -12683,7 +12656,7 @@
         <v>343</v>
       </c>
       <c r="C76" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>242</v>
@@ -12697,7 +12670,7 @@
         <v>86</v>
       </c>
       <c r="C77" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>242</v>
@@ -12708,10 +12681,10 @@
         <v>345</v>
       </c>
       <c r="B78" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C78" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>242</v>
@@ -12725,7 +12698,7 @@
         <v>434</v>
       </c>
       <c r="C79" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>242</v>
@@ -12736,10 +12709,10 @@
         <v>315</v>
       </c>
       <c r="B80" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C80" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>242</v>
@@ -12750,10 +12723,10 @@
         <v>347</v>
       </c>
       <c r="B81" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C81" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>242</v>
@@ -12767,7 +12740,7 @@
         <v>349</v>
       </c>
       <c r="C82" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>242</v>
@@ -12781,7 +12754,7 @@
         <v>351</v>
       </c>
       <c r="C83" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>242</v>
@@ -12795,7 +12768,7 @@
         <v>158</v>
       </c>
       <c r="C84" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>242</v>
@@ -12809,7 +12782,7 @@
         <v>354</v>
       </c>
       <c r="C85" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>242</v>
@@ -12823,7 +12796,7 @@
         <v>356</v>
       </c>
       <c r="C86" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>242</v>
@@ -12837,7 +12810,7 @@
         <v>358</v>
       </c>
       <c r="C87" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>242</v>
@@ -12851,7 +12824,7 @@
         <v>360</v>
       </c>
       <c r="C88" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>242</v>
@@ -12865,7 +12838,7 @@
         <v>358</v>
       </c>
       <c r="C89" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>244</v>
@@ -12879,7 +12852,7 @@
         <v>240</v>
       </c>
       <c r="C90" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>244</v>
@@ -12890,10 +12863,10 @@
         <v>361</v>
       </c>
       <c r="B91" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C91" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>251</v>
@@ -12907,7 +12880,7 @@
         <v>101</v>
       </c>
       <c r="C92" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>256</v>
@@ -12921,7 +12894,7 @@
         <v>240</v>
       </c>
       <c r="C93" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>196</v>
@@ -12935,7 +12908,7 @@
         <v>158</v>
       </c>
       <c r="C94" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>259</v>
@@ -12949,7 +12922,7 @@
         <v>240</v>
       </c>
       <c r="C95" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>202</v>
@@ -12963,7 +12936,7 @@
         <v>324</v>
       </c>
       <c r="C96" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>281</v>
@@ -12977,7 +12950,7 @@
         <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>281</v>
@@ -12991,7 +12964,7 @@
         <v>62</v>
       </c>
       <c r="C98" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>281</v>
@@ -13005,7 +12978,7 @@
         <v>326</v>
       </c>
       <c r="C99" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>281</v>
@@ -13019,7 +12992,7 @@
         <v>328</v>
       </c>
       <c r="C100" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>281</v>
@@ -13033,7 +13006,7 @@
         <v>330</v>
       </c>
       <c r="C101" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>281</v>
@@ -13047,7 +13020,7 @@
         <v>19</v>
       </c>
       <c r="C102" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>281</v>
@@ -13061,7 +13034,7 @@
         <v>140</v>
       </c>
       <c r="C103" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>281</v>
@@ -13075,7 +13048,7 @@
         <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>281</v>
@@ -13086,10 +13059,10 @@
         <v>331</v>
       </c>
       <c r="B105" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C105" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>281</v>
@@ -13103,7 +13076,7 @@
         <v>157</v>
       </c>
       <c r="C106" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>281</v>
@@ -13117,7 +13090,7 @@
         <v>480</v>
       </c>
       <c r="C107" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>281</v>
@@ -13131,7 +13104,7 @@
         <v>434</v>
       </c>
       <c r="C108" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>281</v>
@@ -13145,7 +13118,7 @@
         <v>158</v>
       </c>
       <c r="C109" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>281</v>
@@ -13159,7 +13132,7 @@
         <v>33</v>
       </c>
       <c r="C110" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>281</v>
@@ -13173,7 +13146,7 @@
         <v>240</v>
       </c>
       <c r="C111" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>178</v>
@@ -13187,7 +13160,7 @@
         <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>180</v>
@@ -13201,7 +13174,7 @@
         <v>403</v>
       </c>
       <c r="C113" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D113" t="s">
         <v>401</v>
@@ -13215,7 +13188,7 @@
         <v>360</v>
       </c>
       <c r="C114" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D114" t="s">
         <v>401</v>
@@ -13229,7 +13202,7 @@
         <v>240</v>
       </c>
       <c r="C115" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D115" t="s">
         <v>401</v>
@@ -13243,7 +13216,7 @@
         <v>333</v>
       </c>
       <c r="C116" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D116" t="s">
         <v>401</v>
@@ -13257,7 +13230,7 @@
         <v>405</v>
       </c>
       <c r="C117" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D117" t="s">
         <v>401</v>
@@ -13271,7 +13244,7 @@
         <v>140</v>
       </c>
       <c r="C118" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D118" t="s">
         <v>401</v>
@@ -13285,7 +13258,7 @@
         <v>406</v>
       </c>
       <c r="C119" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D119" t="s">
         <v>401</v>
@@ -13299,7 +13272,7 @@
         <v>407</v>
       </c>
       <c r="C120" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D120" t="s">
         <v>401</v>
@@ -13313,7 +13286,7 @@
         <v>431</v>
       </c>
       <c r="C121" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D121" t="s">
         <v>401</v>
@@ -13327,7 +13300,7 @@
         <v>408</v>
       </c>
       <c r="C122" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D122" t="s">
         <v>401</v>
@@ -13341,7 +13314,7 @@
         <v>409</v>
       </c>
       <c r="C123" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D123" t="s">
         <v>401</v>
@@ -13355,7 +13328,7 @@
         <v>410</v>
       </c>
       <c r="C124" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D124" t="s">
         <v>401</v>
@@ -13369,7 +13342,7 @@
         <v>411</v>
       </c>
       <c r="C125" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D125" t="s">
         <v>401</v>
@@ -13383,7 +13356,7 @@
         <v>412</v>
       </c>
       <c r="C126" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D126" t="s">
         <v>401</v>
@@ -13397,7 +13370,7 @@
         <v>413</v>
       </c>
       <c r="C127" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D127" t="s">
         <v>401</v>
@@ -13411,7 +13384,7 @@
         <v>430</v>
       </c>
       <c r="C128" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D128" t="s">
         <v>401</v>
@@ -13425,7 +13398,7 @@
         <v>414</v>
       </c>
       <c r="C129" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D129" t="s">
         <v>401</v>
@@ -13439,7 +13412,7 @@
         <v>453</v>
       </c>
       <c r="C130" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D130" t="s">
         <v>401</v>
@@ -13453,7 +13426,7 @@
         <v>434</v>
       </c>
       <c r="C131" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D131" t="s">
         <v>401</v>
@@ -13467,7 +13440,7 @@
         <v>255</v>
       </c>
       <c r="C132" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D132" t="s">
         <v>478</v>
@@ -13481,7 +13454,7 @@
         <v>487</v>
       </c>
       <c r="C133" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D133" t="s">
         <v>486</v>
@@ -13489,97 +13462,97 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="B134" t="s">
         <v>528</v>
       </c>
-      <c r="B134" t="s">
+      <c r="C134" t="s">
+        <v>504</v>
+      </c>
+      <c r="D134" t="s">
         <v>529</v>
-      </c>
-      <c r="C134" t="s">
-        <v>505</v>
-      </c>
-      <c r="D134" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B135" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C135" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D135" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B136" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C136" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D136" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="B137" t="s">
+        <v>554</v>
+      </c>
+      <c r="C137" t="s">
+        <v>504</v>
+      </c>
+      <c r="D137" t="s">
         <v>553</v>
-      </c>
-      <c r="B137" t="s">
-        <v>555</v>
-      </c>
-      <c r="C137" t="s">
-        <v>505</v>
-      </c>
-      <c r="D137" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B138" t="s">
+        <v>493</v>
+      </c>
+      <c r="C138" t="s">
+        <v>495</v>
+      </c>
+      <c r="D138" t="s">
         <v>556</v>
-      </c>
-      <c r="B138" t="s">
-        <v>494</v>
-      </c>
-      <c r="C138" t="s">
-        <v>496</v>
-      </c>
-      <c r="D138" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B139" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C139" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D139" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B140" t="s">
         <v>240</v>
       </c>
       <c r="C140" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D140" t="s">
         <v>239</v>
@@ -13587,156 +13560,156 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B141" t="s">
         <v>434</v>
       </c>
       <c r="C141" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D141" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="B142" t="s">
+        <v>585</v>
+      </c>
+      <c r="C142" t="s">
+        <v>495</v>
+      </c>
+      <c r="D142" t="s">
         <v>570</v>
-      </c>
-      <c r="B142" t="s">
-        <v>586</v>
-      </c>
-      <c r="C142" t="s">
-        <v>496</v>
-      </c>
-      <c r="D142" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
+        <v>572</v>
+      </c>
+      <c r="B143" t="s">
         <v>573</v>
       </c>
-      <c r="B143" t="s">
+      <c r="C143" t="s">
+        <v>504</v>
+      </c>
+      <c r="D143" t="s">
         <v>574</v>
-      </c>
-      <c r="C143" t="s">
-        <v>505</v>
-      </c>
-      <c r="D143" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B144" t="s">
         <v>157</v>
       </c>
       <c r="C144" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D144" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B145" t="s">
         <v>140</v>
       </c>
       <c r="C145" t="s">
-        <v>496</v>
-      </c>
-      <c r="D145" s="27" t="s">
-        <v>638</v>
+        <v>495</v>
+      </c>
+      <c r="D145" s="25" t="s">
+        <v>637</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="B146" t="s">
         <v>644</v>
       </c>
-      <c r="B146" t="s">
+      <c r="C146" t="s">
+        <v>504</v>
+      </c>
+      <c r="D146" t="s">
         <v>645</v>
-      </c>
-      <c r="C146" t="s">
-        <v>505</v>
-      </c>
-      <c r="D146" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
+        <v>670</v>
+      </c>
+      <c r="B147" t="s">
+        <v>676</v>
+      </c>
+      <c r="C147" t="s">
+        <v>504</v>
+      </c>
+      <c r="D147" t="s">
         <v>671</v>
-      </c>
-      <c r="B147" t="s">
-        <v>677</v>
-      </c>
-      <c r="C147" t="s">
-        <v>505</v>
-      </c>
-      <c r="D147" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B148" t="s">
+        <v>676</v>
+      </c>
+      <c r="C148" t="s">
+        <v>504</v>
+      </c>
+      <c r="D148" t="s">
         <v>678</v>
-      </c>
-      <c r="B148" t="s">
-        <v>677</v>
-      </c>
-      <c r="C148" t="s">
-        <v>505</v>
-      </c>
-      <c r="D148" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B149" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C149" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D149" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
+        <v>686</v>
+      </c>
+      <c r="B150" t="s">
+        <v>688</v>
+      </c>
+      <c r="C150" t="s">
+        <v>504</v>
+      </c>
+      <c r="D150" t="s">
         <v>687</v>
-      </c>
-      <c r="B150" t="s">
-        <v>689</v>
-      </c>
-      <c r="C150" t="s">
-        <v>505</v>
-      </c>
-      <c r="D150" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="B151" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="C151" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D151" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -13747,9 +13720,10 @@
   </autoFilter>
   <hyperlinks>
     <hyperlink ref="D65" r:id="rId1" xr:uid="{59EFEB55-B7A4-4807-A75B-EA48D4BA0ABA}"/>
+    <hyperlink ref="D37" r:id="rId2" xr:uid="{05A245B2-AD20-486B-88B8-B028211744BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -14100,7 +14074,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -14126,50 +14100,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>496</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>500</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>503</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>505</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>506</v>
       </c>
     </row>
   </sheetData>

--- a/metrics and parser/DevEx_Metrics.xlsx
+++ b/metrics and parser/DevEx_Metrics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6DB41B-B7DB-4BEA-8598-580486DF1DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE2C50DE-D839-4259-8AFB-2BC056542F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4543" yWindow="13611" windowWidth="24891" windowHeight="14915" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" tabRatio="506" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2041" uniqueCount="850">
   <si>
     <t>id</t>
   </si>
@@ -2118,9 +2118,6 @@
     <t>Measures the time, in seconds, developers spend waiting for their builds to finish locally during development. Impacts developer flow and productivity. Considered e.g. as median (P50) or P90.</t>
   </si>
   <si>
-    <t>50; 234; 131; 146; 521</t>
-  </si>
-  <si>
     <t>501; 521</t>
   </si>
   <si>
@@ -2271,9 +2268,6 @@
     <t>Monitors AI being built into products, not just used by developer throughout the SLDC.</t>
   </si>
   <si>
-    <t>501g; 521; 510</t>
-  </si>
-  <si>
     <t>501b; 501a; 131k; 131j</t>
   </si>
   <si>
@@ -2590,6 +2584,18 @@
   </si>
   <si>
     <t>CSAT; DSAT; NSAT; Satisfaction Score; Developer Sentiment; Developer Satisfaction; Employee satisfaction; Net User Satisfaction; Satisfaction with Engineering System; Platform and Tool Satisfaction; AI tool CSAT</t>
+  </si>
+  <si>
+    <t>501g; 510</t>
+  </si>
+  <si>
+    <t>Produced Output</t>
+  </si>
+  <si>
+    <t>Product Quality</t>
+  </si>
+  <si>
+    <t>Review Process</t>
   </si>
 </sst>
 </file>
@@ -3470,6 +3476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:S123"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3549,7 +3556,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>2</v>
       </c>
@@ -3614,7 +3621,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>4</v>
       </c>
@@ -3679,7 +3686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>9</v>
       </c>
@@ -3744,12 +3751,12 @@
         <v>604</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -3758,7 +3765,7 @@
         <v>300</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
@@ -3809,7 +3816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>11</v>
       </c>
@@ -3874,7 +3881,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>12</v>
       </c>
@@ -3936,10 +3943,10 @@
         <v>517</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>13</v>
       </c>
@@ -3950,7 +3957,7 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>686</v>
@@ -4004,7 +4011,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>14</v>
       </c>
@@ -4015,10 +4022,10 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>741</v>
+        <v>846</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
@@ -4046,7 +4053,7 @@
       </c>
       <c r="M9" s="3">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" s="3">
         <f t="shared" si="1"/>
@@ -4054,7 +4061,7 @@
       </c>
       <c r="O9" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P9" s="12" t="s">
         <v>440</v>
@@ -4069,7 +4076,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>15</v>
       </c>
@@ -4083,7 +4090,7 @@
         <v>612</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>615</v>
@@ -4134,7 +4141,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>16</v>
       </c>
@@ -4204,16 +4211,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
+        <v>695</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>696</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>697</v>
       </c>
       <c r="D12" s="13" t="s">
         <v>578</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
@@ -4229,7 +4236,7 @@
         <v>206</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>15</v>
+        <v>849</v>
       </c>
       <c r="K12" s="3">
         <f>VLOOKUP(J12,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4264,7 +4271,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>18</v>
       </c>
@@ -4329,7 +4336,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>19</v>
       </c>
@@ -4337,7 +4344,7 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>649</v>
@@ -4346,7 +4353,7 @@
         <v>648</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>522</v>
@@ -4359,7 +4366,7 @@
         <v>207</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K14" s="3">
         <f>VLOOKUP(J14,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4394,12 +4401,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>20</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>162</v>
@@ -4411,7 +4418,7 @@
         <v>584</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>521</v>
@@ -4459,12 +4466,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -4524,12 +4531,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>23</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>163</v>
@@ -4541,7 +4548,7 @@
         <v>289</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>522</v>
@@ -4586,10 +4593,10 @@
         <v>516</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>24</v>
       </c>
@@ -4654,15 +4661,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>25</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
@@ -4684,7 +4691,7 @@
         <v>208</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>30</v>
+        <v>848</v>
       </c>
       <c r="K19" s="3">
         <f>VLOOKUP(J19,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4719,12 +4726,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>623</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D20" s="12" t="s">
         <v>308</v>
@@ -4746,7 +4756,7 @@
         <v>208</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>30</v>
+        <v>848</v>
       </c>
       <c r="K20" s="3">
         <f>VLOOKUP(J20,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4778,10 +4788,10 @@
         <v>517</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>27</v>
       </c>
@@ -4846,24 +4856,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>791</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>792</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>793</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>794</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>522</v>
@@ -4911,7 +4921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>30</v>
       </c>
@@ -4976,7 +4986,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>31</v>
       </c>
@@ -4984,16 +4994,16 @@
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="F24" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>522</v>
@@ -5038,15 +5048,15 @@
         <v>517</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -5106,7 +5116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>33</v>
       </c>
@@ -5171,7 +5181,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>34</v>
       </c>
@@ -5179,13 +5189,13 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>378</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>690</v>
+        <v>302</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>689</v>
@@ -5217,11 +5227,11 @@
       </c>
       <c r="N27" s="3">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O27" s="3">
         <f t="shared" si="2"/>
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P27" s="12" t="s">
         <v>440</v>
@@ -5236,7 +5246,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>36</v>
       </c>
@@ -5244,13 +5254,13 @@
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
@@ -5298,15 +5308,15 @@
         <v>517</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="29" spans="1:19" ht="165" x14ac:dyDescent="0.25">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5366,7 +5376,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>38</v>
       </c>
@@ -5374,7 +5384,7 @@
         <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D30" s="12" t="s">
         <v>473</v>
@@ -5431,7 +5441,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>39</v>
       </c>
@@ -5496,7 +5506,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>40</v>
       </c>
@@ -5510,7 +5520,7 @@
         <v>374</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>77</v>
@@ -5561,7 +5571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>41</v>
       </c>
@@ -5626,7 +5636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>42</v>
       </c>
@@ -5634,13 +5644,13 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>81</v>
@@ -5688,10 +5698,10 @@
         <v>517</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>791</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>43</v>
       </c>
@@ -5756,7 +5766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>44</v>
       </c>
@@ -5764,10 +5774,10 @@
         <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>379</v>
@@ -5821,7 +5831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>45</v>
       </c>
@@ -5886,15 +5896,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
@@ -5903,7 +5913,7 @@
         <v>317</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>522</v>
@@ -5951,7 +5961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>50</v>
       </c>
@@ -6016,7 +6026,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>56</v>
       </c>
@@ -6081,7 +6091,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>57</v>
       </c>
@@ -6146,7 +6156,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="210" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:19" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>58</v>
       </c>
@@ -6211,15 +6221,15 @@
         <v>563</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>59</v>
       </c>
       <c r="B43" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>718</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>719</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
@@ -6276,7 +6286,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="44" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>62</v>
       </c>
@@ -6284,13 +6294,13 @@
         <v>594</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>595</v>
@@ -6341,7 +6351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>63</v>
       </c>
@@ -6406,7 +6416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>64</v>
       </c>
@@ -6423,7 +6433,7 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>522</v>
@@ -6471,7 +6481,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>65</v>
       </c>
@@ -6479,7 +6489,7 @@
         <v>104</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D47" s="13" t="s">
         <v>466</v>
@@ -6536,7 +6546,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>67</v>
       </c>
@@ -6601,7 +6611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>69</v>
       </c>
@@ -6609,7 +6619,7 @@
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>293</v>
@@ -6666,7 +6676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>70</v>
       </c>
@@ -6674,13 +6684,13 @@
         <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>785</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>786</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>787</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>629</v>
@@ -6728,10 +6738,10 @@
         <v>517</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>71</v>
       </c>
@@ -6796,7 +6806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>72</v>
       </c>
@@ -6861,7 +6871,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>73</v>
       </c>
@@ -6926,12 +6936,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>75</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>631</v>
@@ -6988,15 +6998,15 @@
         <v>518</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
         <v>76</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
@@ -7053,7 +7063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
         <v>78</v>
       </c>
@@ -7118,7 +7128,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
         <v>79</v>
       </c>
@@ -7183,7 +7193,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>80</v>
       </c>
@@ -7213,7 +7223,7 @@
         <v>208</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>30</v>
+        <v>848</v>
       </c>
       <c r="K58" s="3">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7248,12 +7258,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>120</v>
@@ -7313,7 +7323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
         <v>83</v>
       </c>
@@ -7378,7 +7388,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>87</v>
       </c>
@@ -7392,7 +7402,7 @@
         <v>579</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>603</v>
@@ -7443,15 +7453,15 @@
         <v>605</v>
       </c>
     </row>
-    <row r="62" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
         <v>88</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>724</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>725</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>581</v>
@@ -7460,7 +7470,7 @@
         <v>288</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>522</v>
@@ -7508,7 +7518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>89</v>
       </c>
@@ -7573,7 +7583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>90</v>
       </c>
@@ -7587,10 +7597,10 @@
         <v>463</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>521</v>
@@ -7638,7 +7648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>91</v>
       </c>
@@ -7703,7 +7713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
         <v>92</v>
       </c>
@@ -7768,7 +7778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
         <v>93</v>
       </c>
@@ -7833,7 +7843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>94</v>
       </c>
@@ -7898,15 +7908,15 @@
         <v>627</v>
       </c>
     </row>
-    <row r="69" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
         <v>95</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>361</v>
@@ -7915,7 +7925,7 @@
         <v>9</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>525</v>
@@ -7960,10 +7970,10 @@
         <v>516</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>743</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>97</v>
       </c>
@@ -8028,12 +8038,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
         <v>98</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>168</v>
@@ -8093,12 +8103,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
         <v>99</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8110,7 +8120,7 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>522</v>
@@ -8158,7 +8168,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>100</v>
       </c>
@@ -8223,7 +8233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
         <v>102</v>
       </c>
@@ -8288,12 +8298,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
         <v>104</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
@@ -8353,7 +8363,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="120" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
         <v>107</v>
       </c>
@@ -8367,7 +8377,7 @@
         <v>375</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>142</v>
@@ -8418,7 +8428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>108</v>
       </c>
@@ -8483,24 +8493,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="78" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
         <v>109</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>311</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>522</v>
@@ -8545,10 +8555,10 @@
         <v>517</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
         <v>112</v>
       </c>
@@ -8562,10 +8572,10 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>521</v>
@@ -8610,15 +8620,15 @@
         <v>518</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
         <v>113</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>491</v>
@@ -8630,7 +8640,7 @@
         <v>479</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>522</v>
@@ -8675,10 +8685,10 @@
         <v>516</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
         <v>114</v>
       </c>
@@ -8686,7 +8696,7 @@
         <v>630</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D81" s="13" t="s">
         <v>652</v>
@@ -8695,7 +8705,7 @@
         <v>651</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>522</v>
@@ -8708,7 +8718,7 @@
         <v>207</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K81" s="3">
         <f>VLOOKUP(J81,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8743,7 +8753,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>115</v>
       </c>
@@ -8751,7 +8761,7 @@
         <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8760,7 +8770,7 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>525</v>
@@ -8805,10 +8815,10 @@
         <v>518</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>116</v>
       </c>
@@ -8816,7 +8826,7 @@
         <v>147</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D83" s="12" t="s">
         <v>576</v>
@@ -8873,7 +8883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
         <v>117</v>
       </c>
@@ -8881,10 +8891,10 @@
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>313</v>
@@ -8938,7 +8948,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
         <v>118</v>
       </c>
@@ -9003,15 +9013,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
         <v>120</v>
       </c>
       <c r="B86" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>300</v>
@@ -9020,7 +9030,7 @@
         <v>302</v>
       </c>
       <c r="F86" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>522</v>
@@ -9065,10 +9075,10 @@
         <v>516</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
         <v>121</v>
       </c>
@@ -9133,7 +9143,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
         <v>122</v>
       </c>
@@ -9141,7 +9151,7 @@
         <v>156</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D88" s="12" t="s">
         <v>653</v>
@@ -9150,7 +9160,7 @@
         <v>654</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>522</v>
@@ -9195,10 +9205,10 @@
         <v>516</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>124</v>
       </c>
@@ -9263,12 +9273,12 @@
         <v>618</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
         <v>126</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>588</v>
@@ -9293,7 +9303,7 @@
         <v>207</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K90" s="3">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9328,15 +9338,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
         <v>127</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D91" s="12" t="s">
         <v>580</v>
@@ -9358,7 +9368,7 @@
         <v>207</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9390,18 +9400,18 @@
         <v>517</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>128</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>301</v>
@@ -9423,7 +9433,7 @@
         <v>207</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K92" s="3">
         <f>VLOOKUP(J92,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9458,7 +9468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
         <v>129</v>
       </c>
@@ -9466,7 +9476,7 @@
         <v>457</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D93" s="12" t="s">
         <v>458</v>
@@ -9488,7 +9498,7 @@
         <v>207</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>46</v>
+        <v>847</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9523,7 +9533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
         <v>130</v>
       </c>
@@ -9531,7 +9541,7 @@
         <v>591</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>376</v>
@@ -9540,7 +9550,7 @@
         <v>377</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>521</v>
@@ -9588,24 +9598,24 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>133</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="13" t="s">
         <v>775</v>
       </c>
-      <c r="C95" s="4" t="s">
+      <c r="F95" s="4" t="s">
         <v>776</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>777</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>778</v>
       </c>
       <c r="G95" s="3" t="s">
         <v>522</v>
@@ -9650,27 +9660,27 @@
         <v>516</v>
       </c>
       <c r="S95" t="s">
-        <v>779</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>134</v>
       </c>
       <c r="B96" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="13" t="s">
+        <v>780</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E96" s="13" t="s">
-        <v>782</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>783</v>
       </c>
       <c r="G96" s="3" t="s">
         <v>522</v>
@@ -9715,10 +9725,10 @@
         <v>517</v>
       </c>
       <c r="S96" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
         <v>135</v>
       </c>
@@ -9783,7 +9793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
         <v>137</v>
       </c>
@@ -9848,15 +9858,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>138</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9913,7 +9923,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
         <v>139</v>
       </c>
@@ -9978,7 +9988,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
         <v>140</v>
       </c>
@@ -9986,7 +9996,7 @@
         <v>432</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D101" s="12" t="s">
         <v>454</v>
@@ -10043,12 +10053,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
         <v>141</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>660</v>
@@ -10108,12 +10118,12 @@
         <v>129</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>142</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>661</v>
@@ -10173,15 +10183,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="104" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
         <v>143</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D104" s="12" t="s">
         <v>443</v>
@@ -10190,7 +10200,7 @@
         <v>9</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G104" s="3" t="s">
         <v>522</v>
@@ -10238,12 +10248,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>144</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
@@ -10303,15 +10313,15 @@
         <v>448</v>
       </c>
     </row>
-    <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>145</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D106" s="10" t="s">
         <v>424</v>
@@ -10368,7 +10378,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
         <v>146</v>
       </c>
@@ -10376,7 +10386,7 @@
         <v>445</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D107" t="s">
         <v>449</v>
@@ -10433,15 +10443,15 @@
         <v>450</v>
       </c>
     </row>
-    <row r="108" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
         <v>147</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D108" s="10" t="s">
         <v>452</v>
@@ -10450,7 +10460,7 @@
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="G108" s="3" t="s">
         <v>522</v>
@@ -10498,12 +10508,12 @@
         <v>448</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>148</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>484</v>
@@ -10563,15 +10573,15 @@
         <v>456</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>149</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D110" s="12" t="s">
         <v>470</v>
@@ -10580,7 +10590,7 @@
         <v>479</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="G110" s="3" t="s">
         <v>521</v>
@@ -10628,24 +10638,24 @@
         <v>464</v>
       </c>
     </row>
-    <row r="111" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:19" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>150</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D111" s="12" t="s">
         <v>583</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G111" s="3" t="s">
         <v>521</v>
@@ -10693,7 +10703,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>151</v>
       </c>
@@ -10758,7 +10768,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>152</v>
       </c>
@@ -10823,12 +10833,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
         <v>153</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10888,15 +10898,15 @@
         <v>489</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>154</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
@@ -10905,7 +10915,7 @@
         <v>485</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G115" s="3" t="s">
         <v>521</v>
@@ -10953,7 +10963,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="105" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:19" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
         <v>155</v>
       </c>
@@ -11015,10 +11025,10 @@
         <v>516</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
         <v>156</v>
       </c>
@@ -11083,7 +11093,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="90" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:19" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
         <v>157</v>
       </c>
@@ -11148,15 +11158,15 @@
         <v>564</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:19" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
         <v>158</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11165,7 +11175,7 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G119" s="3" t="s">
         <v>522</v>
@@ -11213,7 +11223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
         <v>159</v>
       </c>
@@ -11278,7 +11288,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:19" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
         <v>160</v>
       </c>
@@ -11343,7 +11353,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:19" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
         <v>161</v>
       </c>
@@ -11408,24 +11418,24 @@
         <v>683</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="60" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:1